--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策树" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="决策树" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1.2249</v>
+        <v>0.9185</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.4762</v>
+        <v>1.141</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.664</v>
+        <v>1.3182</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>1.2249</v>
+        <v>0.9185</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.4762</v>
+        <v>1.141</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1.664</v>
+        <v>1.3182</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>521.7145</v>
+        <v>695.7252</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>576.0709000000001</v>
+        <v>745.3097</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>647.5395</v>
+        <v>817.3876</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>-216.2839</v>
+        <v>305.7481</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.2522</v>
+        <v>507.9686</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>207.6193</v>
+        <v>717.1636</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>855.3108999999999</v>
+        <v>333.2788</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>850.1623</v>
+        <v>342.446</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>869.8559</v>
+        <v>360.3116</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>833.0722</v>
+        <v>311.0402</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>827.9236</v>
+        <v>320.2073</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>847.6172</v>
+        <v>338.0729</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>7.2308</v>
+        <v>5.8692</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>6.6662</v>
+        <v>5.6711</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>6.3455</v>
+        <v>5.5573</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>4620.653</v>
+        <v>3750.5995</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>5669.0098</v>
+        <v>4822.8159</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>6837.1358</v>
+        <v>5987.8953</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>693.0979</v>
+        <v>562.5898999999999</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>850.3515</v>
+        <v>723.4224</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>1025.5704</v>
+        <v>898.1843</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2.4894</v>
+        <v>3.0668</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>2.7002</v>
+        <v>3.174</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>2.8366</v>
+        <v>3.239</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>7.2308</v>
+        <v>5.8692</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>6.6662</v>
+        <v>5.6711</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>6.3455</v>
+        <v>5.5573</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>由「换回的价值 / 做透的代价 / 资金从容度 / 体检」四支共同回答，不是一个数</t>
+          <t>由「换回的价值 / 做透的代价 / 体检过不过线 / 估值最终值多少」四支共同回答，不是一个数</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2433.0193</v>
+        <v>305.1412</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5698.2855</v>
+        <v>6103.2921</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9559.369199999999</v>
+        <v>16614.6329</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2433.0193</v>
+        <v>305.1412</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5698.2855</v>
+        <v>6103.2921</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9559.369199999999</v>
+        <v>16614.6329</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3632.8124</v>
+        <v>1570.4536</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5091.6346</v>
+        <v>5496.6412</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6632.8317</v>
+        <v>13461.3107</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9082.0309</v>
+        <v>3926.1339</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12729.0864</v>
+        <v>13741.6031</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16582.0792</v>
+        <v>33653.2767</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>EV − 项目债务（分池计算，单池权益不为负）</t>
+          <t>EV − 稳态debt（分池计算，单池权益不为负）</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11502.4854</v>
+        <v>4731.7539</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>15307.4614</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>19394.5535</v>
+        <v>36261.9883</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>639.027</v>
+        <v>363.9811</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1077.4752</v>
+        <v>1648.2722</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>725.7816</v>
+        <v>414.0896</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>939.5154</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1169.2411</v>
+        <v>1790.217</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>284.2108</v>
+        <v>157.7146</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>435.1126</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>593.4719</v>
+        <v>944.2947</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1421.0538</v>
+        <v>788.573</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>1450.3754</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1483.6797</v>
+        <v>2360.7368</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3098700</v>
+        <v>1962000</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>3285700</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3498100</v>
+        <v>4912700</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>163.7846</v>
+        <v>143.5439</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>157.6502</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>151.4781</v>
+        <v>171.6206</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>换电服务费中枢 0.30 元/kWh（三档 0.2/0.3/0.4）。谱系：焦作商车邦实测 0.2（启源主导市场已打价格战） / → 齐鲁晚报行业 0.3–0.4 → 开源短倒 0.4。中枢 0.30 居中偏稳健；三档全做敏感性</t>
+          <t>换电服务费中枢 0.30 元/kWh。谱系：焦作商车邦实测 0.2（启源主导市场已打价格战） / → 齐鲁晚报行业 0.3–0.4 → 开源短倒 0.4。中枢 0.30 居中偏稳健。</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>407.7128</v>
+        <v>237.3889</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>470.5448</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>541.9112</v>
+        <v>791.9143</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>339.7607</v>
+        <v>197.8241</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>392.1207</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>451.5927</v>
+        <v>659.9286</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>326.5109</v>
+        <v>190.4851</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>378.8709</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>438.3429</v>
+        <v>638.5897</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13.2497</v>
+        <v>7.339</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>13.2497</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13.2497</v>
+        <v>21.339</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>22.0829</v>
+        <v>12.2317</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>22.0829</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>22.0829</v>
+        <v>35.5649</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>28.4428</v>
+        <v>15.7544</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>28.4428</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.4428</v>
+        <v>45.8076</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>22.0829</v>
+        <v>12.2317</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>22.0829</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>22.0829</v>
+        <v>35.5649</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5.4152</v>
+        <v>3.2317</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>5.4152</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>5.4152</v>
+        <v>8.2003</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.3325</v>
+        <v>0.1837</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.3325</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.3325</v>
+        <v>0.5375</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2.2165</v>
+        <v>1.2249</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2.2165</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2.2165</v>
+        <v>3.5836</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>5.0827</v>
+        <v>3.048</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>5.0827</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>5.0827</v>
+        <v>7.6628</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>86.7546</v>
+        <v>50.1085</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>89.1009</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>91.7659</v>
+        <v>141.9448</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46.3387</v>
+        <v>25.7143</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>47.2948</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>48.3809</v>
+        <v>76.98050000000001</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1575.5161</v>
+        <v>874.2874</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>1608.0249</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1644.9492</v>
+        <v>2617.3387</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1421.0538</v>
+        <v>788.573</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>1450.3754</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1483.6797</v>
+        <v>2360.7368</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1421.0538</v>
+        <v>788.573</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>1450.3754</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1483.6797</v>
+        <v>2360.7368</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>16.9275</v>
+        <v>10.3785</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>16.9275</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>16.9275</v>
+        <v>24.9915</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>11285</v>
+        <v>6919</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>11285</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11285</v>
+        <v>16661</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>11.7329</v>
+        <v>6.3426</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>11.7329</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11.7329</v>
+        <v>19.2985</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>3596</v>
+        <v>1853</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>3596</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>3596</v>
+        <v>6126</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>7689</v>
+        <v>5066</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>7689</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>7689</v>
+        <v>10535</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>4.6138</v>
+        <v>2.683</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>5.2316</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>5.9334</v>
+        <v>8.730499999999999</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>4.1134</v>
+        <v>2.3921</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>4.7313</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>5.433</v>
+        <v>7.955</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1.0284</v>
+        <v>0.598</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>1.1828</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1.3583</v>
+        <v>1.9888</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>18</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　项目债务</t>
+          <t xml:space="preserve">　　　　　稳态debt（2030在役资产历史成本×债务比）</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>2420.4544</v>
+        <v>805.6199</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2578.375</v>
+        <v>1565.8584</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2812.4743</v>
+        <v>2608.7115</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>-1199.7931</v>
+        <v>-1265.3124</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>606.6509</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2926.5375</v>
+        <v>3153.3222</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2247,13 +2247,13 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>-59.9897</v>
+        <v>-63.2656</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>30.3325</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>146.3269</v>
+        <v>157.6661</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-59.9897</v>
+        <v>-63.2656</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>-3.8752</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>50.027</v>
+        <v>57.2206</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>47.928</v>
+        <v>28.0858</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>53.7768</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>60.4134</v>
+        <v>87.9637</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-107.9177</v>
+        <v>-91.3514</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>-57.652</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>-10.3864</v>
+        <v>-30.7431</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>34.2078</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>96.29989999999999</v>
+        <v>100.4455</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>2971.864</v>
+        <v>2801.0497</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>3420.7793</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>3851.9969</v>
+        <v>4017.8193</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0.1217</v>
+        <v>0.0153</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.2849</v>
+        <v>0.3052</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.478</v>
+        <v>0.8307</v>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>2433.0193</v>
+        <v>305.1412</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>5698.2855</v>
+        <v>6103.2921</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>9559.369199999999</v>
+        <v>16614.6329</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>645.4545000000001</v>
+        <v>366.0319</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>687.5667</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>749.9931</v>
+        <v>1148.6437</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>645.4545000000001</v>
+        <v>366.0319</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>687.5667</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>749.9931</v>
+        <v>1148.6437</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>4034.0907</v>
+        <v>2287.6995</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>4297.2917</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>4687.4572</v>
+        <v>7179.0234</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>4034.0907</v>
+        <v>2287.6995</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>4297.2917</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>4687.4572</v>
+        <v>7179.0234</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>2332.6204</v>
+        <v>1354.3256</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>2632.0796</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>2971.879</v>
+        <v>4385.7061</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1868.7512</v>
+        <v>1088.1889</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>2168.2104</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>2508.0098</v>
+        <v>3658.873</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>118.1859</v>
+        <v>60.0635</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>118.1859</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>118.1859</v>
+        <v>197.7299</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>297.93</v>
+        <v>158.32</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>297.93</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>297.93</v>
+        <v>481.35</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1701.4703</v>
+        <v>933.3739</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>1665.2121</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1715.5782</v>
+        <v>2793.3173</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>605.1136</v>
+        <v>343.1549</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>644.5937</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>703.1186</v>
+        <v>1076.8535</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>4034.0907</v>
+        <v>2287.6995</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>4297.2917</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>4687.4572</v>
+        <v>7179.0234</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2420.4544</v>
+        <v>1372.6197</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>2578.375</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>2812.4743</v>
+        <v>4307.414</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>4034.0907</v>
+        <v>2287.6995</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>4297.2917</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>4687.4572</v>
+        <v>7179.0234</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>2332.6204</v>
+        <v>1354.3256</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>2632.0796</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>2971.879</v>
+        <v>4385.7061</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>1868.7512</v>
+        <v>1088.1889</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>2168.2104</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>2508.0098</v>
+        <v>3658.873</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>118.1859</v>
+        <v>60.0635</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>118.1859</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>118.1859</v>
+        <v>197.7299</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>297.93</v>
+        <v>158.32</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>297.93</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>297.93</v>
+        <v>481.35</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>1701.4703</v>
+        <v>933.3739</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>1665.2121</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>1715.5782</v>
+        <v>2793.3173</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>0.9185</v>
+        <v>0.9204</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>1.141</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.3182</v>
+        <v>1.3221</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.9185</v>
+        <v>0.9204</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>1.141</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1.3182</v>
+        <v>1.3221</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>639.027</v>
+        <v>363.9811</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1077.4752</v>
+        <v>1648.2722</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>695.7252</v>
+        <v>395.4576</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>745.3097</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>817.3876</v>
+        <v>1246.7121</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>305.7481</v>
+        <v>177.7342</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>507.9686</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>717.1636</v>
+        <v>1080.9944</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>639.027</v>
+        <v>363.9811</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1077.4752</v>
+        <v>1648.2722</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>333.2788</v>
+        <v>186.2469</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>342.446</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>360.3116</v>
+        <v>567.2778</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>311.0402</v>
+        <v>173.3155</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>320.2073</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>338.0729</v>
+        <v>532.8111</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>333.58</v>
+        <v>193.97</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>333.58</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>333.58</v>
+        <v>517</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>297.93</v>
+        <v>158.32</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>297.93</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>297.93</v>
+        <v>481.35</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>5.8692</v>
+        <v>5.8528</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>5.6711</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.5573</v>
+        <v>5.5736</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>3750.5995</v>
+        <v>2130.3168</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>4822.8159</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>5987.8953</v>
+        <v>9186.824000000001</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>562.5898999999999</v>
+        <v>319.5475</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>723.4224</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>898.1843</v>
+        <v>1378.0236</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>639.027</v>
+        <v>363.9811</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1077.4752</v>
+        <v>1648.2722</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>3.0668</v>
+        <v>2.2212</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>3.174</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3.239</v>
+        <v>3.9472</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>18</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>5.8692</v>
+        <v>5.8528</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>5.6711</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>5.5573</v>
+        <v>5.5736</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4010,6 +4010,1625 @@
       </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115" outlineLevel="1">
+      <c r="A115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　估值：这门生意最终值多少钱</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>1570.4536</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>5496.6412</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>13461.3107</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>见下——倍数法与DCF两套独立口径（DCF区分CRF捷径对照版 npv/catl_dcf、有限期账/基础账 npv_true/catl_dcf_true、永续账/开放上限npv_perpetual/catl_dcf_perpetual——两本账都不建模2030后规模增长（capex诊断.md§8.4已论证的既定假设），差异只在'停在2030规模不动'延续多久：15年还是永续，见第四轮§4.7），「押注」是倍数法与DCF基础账的结构性差值；debt_basis_drift、framework_ul_gap 只诊断、不参与本节点校验</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116" outlineLevel="2">
+      <c r="A116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　项目NPV（DCF，CRF捷径EV，仅作对照）</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>-402.1671</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>88.0142</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>1290.2899</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>DCF企业价值(CRF年金捷径) ＋ 期末残值现值(target_year) − 估值资本PV(target_year)</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117" hidden="1" outlineLevel="3">
+      <c r="A117" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)·与门槛同源</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>2130.3168</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>4822.8159</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>9186.824000000001</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118" hidden="1" outlineLevel="3">
+      <c r="A118" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>124.0719</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>239.8246</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>407.1204</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119" hidden="1" outlineLevel="4">
+      <c r="A119" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>92.9051</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>179.5808</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>304.852</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120" hidden="1" outlineLevel="4">
+      <c r="A120" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121" hidden="1" outlineLevel="3">
+      <c r="A121" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>2656.5558</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>4974.6263</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>8303.654500000001</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122" hidden="1" outlineLevel="4">
+      <c r="A122" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>1989.2304</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>3725.0028</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>6217.7809</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123" hidden="1" outlineLevel="4">
+      <c r="A123" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>(1+WACC)^(target_year−base_year)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124" outlineLevel="2">
+      <c r="A124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，CRF捷径EV，仅作对照）</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>579.5075000000001</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1398.7129</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>2794.0931</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>max(0, DCF企业价值(CRF捷径) ＋ 期末残值现值(target_year) − 稳态debt) × 持股比例</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125" hidden="1" outlineLevel="3">
+      <c r="A125" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>2130.3168</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>4822.8159</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>9186.824000000001</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126" hidden="1" outlineLevel="3">
+      <c r="A126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>124.0719</v>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>239.8246</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>407.1204</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127" hidden="1" outlineLevel="4">
+      <c r="A127" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>92.9051</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>179.5808</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>304.852</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128" hidden="1" outlineLevel="4">
+      <c r="A128" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129" hidden="1" outlineLevel="3">
+      <c r="A129" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>805.6199</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>1565.8584</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>2608.7115</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130" hidden="1" outlineLevel="3">
+      <c r="A130" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" outlineLevel="2">
+      <c r="A131" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　项目NPV（DCF，有限期账/基础账）</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>288.2003</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>1650.9343</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>4267.4452</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 估值资本PV(target_year，含真实更新排期)。【2026-09-05d】站体设备不设期末残值——永续账已把它按'每15年到期全额换新、不扣回收'处理，隐含'到期视为耗尽'，有限期账不能再给同一台设备一份残值（两套相反假设），且没有设备二手市场数据支撑折价比例</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132" hidden="1" outlineLevel="3">
+      <c r="A132" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>2820.6842</v>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>6385.736</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>12163.9793</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133" hidden="1" outlineLevel="3">
+      <c r="A133" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>124.0719</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>239.8246</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>407.1204</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134" hidden="1" outlineLevel="4">
+      <c r="A134" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>92.9051</v>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>179.5808</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>304.852</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135" hidden="1" outlineLevel="4">
+      <c r="A135" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136" hidden="1" outlineLevel="3">
+      <c r="A136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>2656.5558</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>4974.6263</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>8303.654500000001</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137" hidden="1" outlineLevel="4">
+      <c r="A137" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>1989.2304</v>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>3725.0028</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>6217.7809</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138" hidden="1" outlineLevel="4">
+      <c r="A138" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>(1+WACC)^(target_year−base_year)</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139" outlineLevel="2">
+      <c r="A139" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>855.6545</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>2023.8809</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>3984.9552</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140" hidden="1" outlineLevel="3">
+      <c r="A140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>2820.6842</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>6385.736</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>12163.9793</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141" hidden="1" outlineLevel="3">
+      <c r="A141" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>124.0719</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>239.8246</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>407.1204</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142" hidden="1" outlineLevel="4">
+      <c r="A142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>92.9051</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>179.5808</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>304.852</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143" hidden="1" outlineLevel="4">
+      <c r="A143" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144" hidden="1" outlineLevel="3">
+      <c r="A144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>805.6199</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>1565.8584</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>2608.7115</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145" hidden="1" outlineLevel="3">
+      <c r="A145" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" outlineLevel="2">
+      <c r="A146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　项目NPV（DCF，永续账/开放上限）</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>1122.7043</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>3740.3257</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>8569.3681</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>DCF企业价值(永续) − 纯初装现值(target_year，剔除更换支出后的一次性投资，永续假设下不含期末残值——不会真的清算)</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147" outlineLevel="2">
+      <c r="A147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，永续账/开放上限）</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>757.4481</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>2088.7319</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>4413.0949</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>max(0, DCF企业价值(永续) − 稳态debt) × 持股比例——与有限期账（基础账）共用同一个debt快照，差异只在EV怎么算（第一轮§1已论证debt该是资产负债表快照，跟期限假设无关）</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148" outlineLevel="2">
+      <c r="A148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　CATL归属价值（倍数法口径）</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>1570.4536</v>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>5496.6412</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>13461.3107</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149" hidden="1" outlineLevel="3">
+      <c r="A149" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　EBITDA</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>363.9811</v>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>850.4145</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>1648.2722</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150" hidden="1" outlineLevel="3">
+      <c r="A150" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　运营EV/EBITDA倍数</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>finance.swap_ev_ebitda</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" hidden="1" outlineLevel="3">
+      <c r="A151" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　稳态debt（同DCF线，2026-09-04起统一）</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>805.6199</v>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1565.8584</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>2608.7115</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152" hidden="1" outlineLevel="3">
+      <c r="A152" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" outlineLevel="2">
+      <c r="A153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　押注部分（结构性差值）</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>714.7991</v>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>3472.7603</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>9476.3554</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>倍数法归属 − DCF归属(真实口径)　【2026-09-04：debt统一后，两条线现在真的在问同一个问题、用同一个debt，此前藏着的第三份「倍数法归属」（_dcf_cross_check内部现算、从未暴露的版本，见 DECISIONS「2026-09-03b」）已删除，三份合并为一份（T3已解决），此处直接用真正的倍数法headline数字相减】</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154" hidden="1" outlineLevel="3">
+      <c r="A154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL归属价值（倍数法口径）</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>1570.4536</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>5496.6412</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>13461.3107</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155" hidden="1" outlineLevel="4">
+      <c r="A155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　EBITDA</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>363.9811</v>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>850.4145</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>1648.2722</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156" hidden="1" outlineLevel="4">
+      <c r="A156" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　运营EV/EBITDA倍数</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>finance.swap_ev_ebitda</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" hidden="1" outlineLevel="4">
+      <c r="A157" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　稳态debt（同DCF线，2026-09-04起统一）</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>805.6199</v>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1565.8584</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>2608.7115</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158" hidden="1" outlineLevel="4">
+      <c r="A158" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" hidden="1" outlineLevel="3">
+      <c r="A159" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>855.6545</v>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>2023.8809</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>3984.9552</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160" hidden="1" outlineLevel="4">
+      <c r="A160" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>2820.6842</v>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>6385.736</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>12163.9793</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161" hidden="1" outlineLevel="4">
+      <c r="A161" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>124.0719</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>239.8246</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>407.1204</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162" hidden="1" outlineLevel="5">
+      <c r="A162" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　期末残值现值（税后，base_year）</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>92.9051</v>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>179.5808</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>304.852</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163" hidden="1" outlineLevel="5">
+      <c r="A163" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164" hidden="1" outlineLevel="4">
+      <c r="A164" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>805.6199</v>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>1565.8584</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>2608.7115</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165" hidden="1" outlineLevel="4">
+      <c r="A165" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" outlineLevel="2">
+      <c r="A166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　稳态debt相对旧口径（门槛底座×债务比）改变了多少</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>-0.4131</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>-0.3927</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>-0.3944</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>(新稳态debt − 旧门槛底座债务) ÷ 旧门槛底座债务——纯诊断：2026-09-04 起两条估值线已统一使用稳态debt，不再是「两条线口径分裂」（那个问题已解决），此节点只记录这次口径修正把debt改变了多少，见 DECISIONS「2026-09-03b」「2026-09-04」</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167" outlineLevel="2">
+      <c r="A167" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　框架L(折现FCFE)相对框架U(EV−debt)的偏离</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>-0.672</v>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>-0.5921</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>-0.5542</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>【T5，2026-09-04，纯诊断】(框架L股权价值 − 框架U股权价值) ÷ 框架U股权价值。框架L：Ke=[WACC−债务比×债务利率×(1−税率)]÷(1−债务比) 折现FCFE（FCFE=真实FCFF−税后利息，debt按steady_state_debt_yi固定不摊销、净新增借款=0，与forward_fcff/sustaining_capex同样的'稳态不变'假设）。两者不精确相等是预期内的：附录'情形C'证明U=L恒等式要求debt按'债务比×剩余项目价值'逐期摊销到0（value降、debt跟着降）；本模型debt是'target_year在役资产历史成本'快照，15年窗口内固定不变——这是两种不同的'稳定杠杆'定义，有限期+终值截断场景下不再代数等价。此gap量化这一口径差异的幅度，不参与上层校验、不代表程序错误</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>305.1412</v>
+        <v>125.3389</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>6103.2921</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16614.6329</v>
+        <v>21970.5222</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>305.1412</v>
+        <v>125.3389</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>6103.2921</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>16614.6329</v>
+        <v>21970.5222</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1570.4536</v>
+        <v>1004.1087</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>5496.6412</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13461.3107</v>
+        <v>18468.6881</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3926.1339</v>
+        <v>3347.0291</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>13741.6031</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33653.2767</v>
+        <v>36937.3762</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4731.7539</v>
+        <v>4018.379</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>15307.4614</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>36261.9883</v>
+        <v>40198.2657</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>363.9811</v>
+        <v>309.1061</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1648.2722</v>
+        <v>1827.1939</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>414.0896</v>
+        <v>367.786</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>939.5154</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1790.217</v>
+        <v>1943.4786</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>237.3889</v>
+        <v>191.0854</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>470.5448</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>791.9143</v>
+        <v>945.1759</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>197.8241</v>
+        <v>199.0473</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>392.1207</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>659.9286</v>
+        <v>656.3721</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7.339</v>
+        <v>8.562200000000001</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>13.2497</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>21.339</v>
+        <v>17.7825</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1157,32 +1157,32 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　单位装机年租金</t>
+          <t xml:space="preserve">　　　　　　　　　单位装机月租金</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>元/kWh·年</t>
+          <t>元/kWh·月</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>swap_business.battery_rent_rmb_kwh_year</t>
+          <t>swap_business.battery_rent_rmb_kwh_month</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>电池租金 120 元/kWh·年 ≈ 10 元/kWh·月（全市场可比综合口径：小车 8.8–9.7/大车 13–17 元加权， / rlut 重卡月租 4500–6000 元佐证"小车便宜大车贵"）</t>
+          <t>电池租金 10 元/kWh·月（全市场可比综合口径：小车 8.8–9.7/大车 13–17 元加权， / rlut 重卡月租 4500–6000 元佐证"小车便宜大车贵"）</t>
         </is>
       </c>
     </row>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>50.1085</v>
+        <v>58.68</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>89.1009</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>141.9448</v>
+        <v>116.2847</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>25.7143</v>
+        <v>34.2858</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>47.2948</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>76.98050000000001</v>
+        <v>51.3204</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>805.6199</v>
+        <v>671.3499</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>1565.8584</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2608.7115</v>
+        <v>3260.8894</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>-1265.3124</v>
+        <v>-878.7698</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>606.6509</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3153.3222</v>
+        <v>3501.8341</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2247,13 +2247,13 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>-63.2656</v>
+        <v>-58.5847</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>30.3325</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>157.6661</v>
+        <v>140.0734</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-63.2656</v>
+        <v>-58.5847</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>-3.8752</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>57.2206</v>
+        <v>42.56</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>28.0858</v>
+        <v>32.7667</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>53.7768</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>87.9637</v>
+        <v>73.3031</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>34.2078</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>100.4455</v>
+        <v>97.5134</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>2801.0497</v>
+        <v>2838.4974</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>3420.7793</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>4017.8193</v>
+        <v>3900.5343</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.0063</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.3052</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.8307</v>
+        <v>1.0985</v>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>305.1412</v>
+        <v>125.3389</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>6103.2921</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>16614.6329</v>
+        <v>21970.5222</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>366.0319</v>
+        <v>343.1549</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>687.5667</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1148.6437</v>
+        <v>897.3779</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>366.0319</v>
+        <v>343.1549</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>687.5667</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1148.6437</v>
+        <v>897.3779</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr"/>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>1372.6197</v>
+        <v>1143.8498</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>2578.375</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>4307.414</v>
+        <v>5384.2675</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr"/>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>0.9204</v>
+        <v>0.7816</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>1.141</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.3221</v>
+        <v>1.4656</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.9204</v>
+        <v>0.7816</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>1.141</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1.3221</v>
+        <v>1.4656</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>363.9811</v>
+        <v>309.1061</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1648.2722</v>
+        <v>1827.1939</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>177.7342</v>
+        <v>122.8592</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>507.9686</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1080.9944</v>
+        <v>1259.9161</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>363.9811</v>
+        <v>309.1061</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1648.2722</v>
+        <v>1827.1939</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>5.8528</v>
+        <v>6.0042</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>5.6711</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.5736</v>
+        <v>5.5174</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2130.3168</v>
+        <v>1855.9418</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>4822.8159</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>9186.824000000001</v>
+        <v>10081.4325</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>319.5475</v>
+        <v>278.3913</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>723.4224</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>1378.0236</v>
+        <v>1512.2149</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>363.9811</v>
+        <v>309.1061</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1648.2722</v>
+        <v>1827.1939</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2.2212</v>
+        <v>2.1651</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>3.174</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3.9472</v>
+        <v>3.9874</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>5.8528</v>
+        <v>6.0042</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>5.6711</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>5.5736</v>
+        <v>5.5174</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>1570.4536</v>
+        <v>1004.1087</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>5496.6412</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>13461.3107</v>
+        <v>18468.6881</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>-402.1671</v>
+        <v>-676.542</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>88.0142</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>1290.2899</v>
+        <v>2184.8984</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2130.3168</v>
+        <v>1855.9418</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>4822.8159</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>9186.824000000001</v>
+        <v>10081.4325</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>579.5075000000001</v>
+        <v>392.5992</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>1398.7129</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>2794.0931</v>
+        <v>3613.8317</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>2130.3168</v>
+        <v>1855.9418</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>4822.8159</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>9186.824000000001</v>
+        <v>10081.4325</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>805.6199</v>
+        <v>671.3499</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>1565.8584</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>2608.7115</v>
+        <v>3260.8894</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>288.2003</v>
+        <v>-75.0908</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>1650.9343</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>4267.4452</v>
+        <v>5451.9676</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>2820.6842</v>
+        <v>2457.3931</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>6385.736</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>12163.9793</v>
+        <v>13348.5017</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>855.6545</v>
+        <v>573.0345</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>2023.8809</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>3984.9552</v>
+        <v>5247.3663</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>2820.6842</v>
+        <v>2457.3931</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>6385.736</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>12163.9793</v>
+        <v>13348.5017</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>805.6199</v>
+        <v>671.3499</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>1565.8584</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>2608.7115</v>
+        <v>3260.8894</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr"/>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1122.7043</v>
+        <v>573.9544</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>3740.3257</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>8569.3681</v>
+        <v>10358.5851</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>757.4481</v>
+        <v>443.7421</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>2088.7319</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>4413.0949</v>
+        <v>6084.8882</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>1570.4536</v>
+        <v>1004.1087</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>5496.6412</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>13461.3107</v>
+        <v>18468.6881</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>363.9811</v>
+        <v>309.1061</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>1648.2722</v>
+        <v>1827.1939</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>805.6199</v>
+        <v>671.3499</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>1565.8584</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>2608.7115</v>
+        <v>3260.8894</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr"/>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>714.7991</v>
+        <v>431.0742</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>3472.7603</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>9476.3554</v>
+        <v>13221.3218</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>1570.4536</v>
+        <v>1004.1087</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>5496.6412</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>13461.3107</v>
+        <v>18468.6881</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>363.9811</v>
+        <v>309.1061</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>850.4145</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>1648.2722</v>
+        <v>1827.1939</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>805.6199</v>
+        <v>671.3499</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>1565.8584</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>2608.7115</v>
+        <v>3260.8894</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5338,13 +5338,13 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr"/>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>855.6545</v>
+        <v>573.0345</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>2023.8809</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3984.9552</v>
+        <v>5247.3663</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>2820.6842</v>
+        <v>2457.3931</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>6385.736</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>12163.9793</v>
+        <v>13348.5017</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -5520,13 +5520,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>805.6199</v>
+        <v>671.3499</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>1565.8584</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>2608.7115</v>
+        <v>3260.8894</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr"/>
@@ -5609,13 +5609,13 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>-0.672</v>
+        <v>-0.714</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>-0.5921</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>-0.5542</v>
+        <v>-0.6542</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>125.3389</v>
+        <v>913.6866</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6103.2921</v>
+        <v>9703.691699999999</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>21970.5222</v>
+        <v>33597.9353</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>125.3389</v>
+        <v>913.6866</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6103.2921</v>
+        <v>9703.691699999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>21970.5222</v>
+        <v>33597.9353</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1004.1087</v>
+        <v>1532.4129</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5496.6412</v>
+        <v>8467.3817</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18468.6881</v>
+        <v>28847.4441</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3347.0291</v>
+        <v>5108.0431</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13741.6031</v>
+        <v>21168.4542</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>36937.3762</v>
+        <v>57694.8882</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4018.379</v>
+        <v>6121.5942</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15307.4614</v>
+        <v>23547.5329</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>40198.2657</v>
+        <v>62705.544</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>309.1061</v>
+        <v>470.8919</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>850.4145</v>
+        <v>1308.1963</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1827.1939</v>
+        <v>2850.252</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>367.786</v>
+        <v>556.5376</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>939.5154</v>
+        <v>1442.0773</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1943.4786</v>
+        <v>3028.7514</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>157.7146</v>
+        <v>238.6605</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>435.1126</v>
+        <v>676.0687</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>944.2947</v>
+        <v>1499.109</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>788.573</v>
+        <v>1193.3026</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1450.3754</v>
+        <v>2253.5624</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2360.7368</v>
+        <v>3747.7726</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1962000</v>
+        <v>2258700</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3285700</v>
+        <v>3874500</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4912700</v>
+        <v>5929200</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>143.5439</v>
+        <v>188.6835</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>157.6502</v>
+        <v>207.7284</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>171.6206</v>
+        <v>225.7455</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>191.0854</v>
+        <v>289.7122</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>470.5448</v>
+        <v>713.9475</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>945.1759</v>
+        <v>1444.1975</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>199.0473</v>
+        <v>301.7835</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>392.1207</v>
+        <v>594.9562</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>656.3721</v>
+        <v>1002.9149</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>190.4851</v>
+        <v>288.78</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>378.8709</v>
+        <v>574.1567</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>638.5897</v>
+        <v>974.2671</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>8.562200000000001</v>
+        <v>13.0035</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>13.2497</v>
+        <v>20.7995</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>17.7825</v>
+        <v>28.6478</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>12.2317</v>
+        <v>18.5764</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>22.0829</v>
+        <v>34.6658</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>35.5649</v>
+        <v>57.2956</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>15.7544</v>
+        <v>23.9265</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.4428</v>
+        <v>44.6495</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45.8076</v>
+        <v>73.7968</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>12.2317</v>
+        <v>18.5764</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>22.0829</v>
+        <v>34.6658</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>35.5649</v>
+        <v>57.2956</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3.2317</v>
+        <v>4.2384</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>5.4152</v>
+        <v>7.4116</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>8.2003</v>
+        <v>11.6482</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.1837</v>
+        <v>0.2895</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.3325</v>
+        <v>0.5422</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.5375</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.2249</v>
+        <v>1.9299</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.2165</v>
+        <v>3.6145</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>3.5836</v>
+        <v>5.9981</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3.048</v>
+        <v>3.9489</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5.0827</v>
+        <v>6.8695</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>7.6628</v>
+        <v>10.7484</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>58.68</v>
+        <v>85.64570000000001</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>89.1009</v>
+        <v>133.881</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>116.2847</v>
+        <v>178.4994</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>34.2858</v>
+        <v>51.8827</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>47.2948</v>
+        <v>73.48569999999999</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>51.3204</v>
+        <v>81.47329999999999</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>874.2874</v>
+        <v>1323.0094</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1608.0249</v>
+        <v>2498.5148</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2617.3387</v>
+        <v>4155.1391</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>788.573</v>
+        <v>1193.3026</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1450.3754</v>
+        <v>2253.5624</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2360.7368</v>
+        <v>3747.7726</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>788.573</v>
+        <v>1193.3026</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1450.3754</v>
+        <v>2253.5624</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2360.7368</v>
+        <v>3747.7726</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>10.3785</v>
+        <v>12.6975</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>16.9275</v>
+        <v>21.5265</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>24.9915</v>
+        <v>32.934</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>6919</v>
+        <v>8465</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>11285</v>
+        <v>14351</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>16661</v>
+        <v>21956</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>6.3426</v>
+        <v>10.4983</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>11.7329</v>
+        <v>19.9743</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>19.2985</v>
+        <v>33.5315</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>1853</v>
+        <v>3399</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>3596</v>
+        <v>6662</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>6126</v>
+        <v>11421</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>2.683</v>
+        <v>4.0337</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5.2316</v>
+        <v>7.9144</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>8.730499999999999</v>
+        <v>13.3451</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>2.3921</v>
+        <v>3.6268</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4.7313</v>
+        <v>7.1841</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>7.955</v>
+        <v>12.1724</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.598</v>
+        <v>0.9067</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1.1828</v>
+        <v>1.796</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1.9888</v>
+        <v>3.0431</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>671.3499</v>
+        <v>1013.5511</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1565.8584</v>
+        <v>2379.0787</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3260.8894</v>
+        <v>5010.6558</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>-878.7698</v>
+        <v>-618.7263</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>606.6509</v>
+        <v>1236.3101</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3501.8341</v>
+        <v>4750.4912</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2247,13 +2247,13 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>-58.5847</v>
+        <v>-41.2484</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>30.3325</v>
+        <v>61.8155</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>140.0734</v>
+        <v>190.0196</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-58.5847</v>
+        <v>-41.2484</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>-3.8752</v>
+        <v>25.2756</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>42.56</v>
+        <v>84.1819</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>32.7667</v>
+        <v>50.103</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>53.7768</v>
+        <v>82.9277</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>73.3031</v>
+        <v>114.925</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>34.2078</v>
+        <v>36.5399</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>97.5134</v>
+        <v>105.8377</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>2838.4974</v>
+        <v>2977.1873</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3420.7793</v>
+        <v>3653.9864</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>3900.5343</v>
+        <v>4233.5095</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0457</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.3052</v>
+        <v>0.4852</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1.0985</v>
+        <v>1.6799</v>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>125.3389</v>
+        <v>913.6866</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>6103.2921</v>
+        <v>9703.691699999999</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>21970.5222</v>
+        <v>33597.9353</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>343.1549</v>
+        <v>509.0041</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>687.5667</v>
+        <v>1038.3084</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>897.3779</v>
+        <v>1369.2061</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>343.1549</v>
+        <v>509.0041</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>687.5667</v>
+        <v>1038.3084</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>897.3779</v>
+        <v>1369.2061</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>2287.6995</v>
+        <v>3393.3607</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>4297.2917</v>
+        <v>6489.4274</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>7179.0234</v>
+        <v>10953.6485</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>2287.6995</v>
+        <v>3393.3607</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>4297.2917</v>
+        <v>6489.4274</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>7179.0234</v>
+        <v>10953.6485</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>1354.3256</v>
+        <v>2035.8419</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2632.0796</v>
+        <v>3980.6461</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>4385.7061</v>
+        <v>6706.2524</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1088.1889</v>
+        <v>1654.9709</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2168.2104</v>
+        <v>3289.238</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>3658.873</v>
+        <v>5586.4582</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>60.0635</v>
+        <v>97.49769999999999</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>118.1859</v>
+        <v>192.4248</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>197.7299</v>
+        <v>325.9409</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>158.32</v>
+        <v>235.62</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>297.93</v>
+        <v>451.23</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>481.35</v>
+        <v>746.1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>933.3739</v>
+        <v>1357.5188</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1665.2121</v>
+        <v>2508.7813</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>2793.3173</v>
+        <v>4247.3961</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>343.1549</v>
+        <v>509.0041</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>644.5937</v>
+        <v>973.4141</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1076.8535</v>
+        <v>1643.0473</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>2287.6995</v>
+        <v>3393.3607</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4297.2917</v>
+        <v>6489.4274</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>7179.0234</v>
+        <v>10953.6485</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>1143.8498</v>
+        <v>1696.6804</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>2578.375</v>
+        <v>3893.6564</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>5384.2675</v>
+        <v>8215.2364</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>2287.6995</v>
+        <v>3393.3607</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>4297.2917</v>
+        <v>6489.4274</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>7179.0234</v>
+        <v>10953.6485</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1354.3256</v>
+        <v>2035.8419</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2632.0796</v>
+        <v>3980.6461</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4385.7061</v>
+        <v>6706.2524</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>1088.1889</v>
+        <v>1654.9709</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2168.2104</v>
+        <v>3289.238</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>3658.873</v>
+        <v>5586.4582</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>60.0635</v>
+        <v>97.49769999999999</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>118.1859</v>
+        <v>192.4248</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>197.7299</v>
+        <v>325.9409</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>158.32</v>
+        <v>235.62</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>297.93</v>
+        <v>451.23</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>481.35</v>
+        <v>746.1</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>933.3739</v>
+        <v>1357.5188</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1665.2121</v>
+        <v>2508.7813</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>2793.3173</v>
+        <v>4247.3961</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>0.7816</v>
+        <v>0.8061</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.141</v>
+        <v>1.1687</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.4656</v>
+        <v>1.5074</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.7816</v>
+        <v>0.8061</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.141</v>
+        <v>1.1687</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1.4656</v>
+        <v>1.5074</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>309.1061</v>
+        <v>470.8919</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>850.4145</v>
+        <v>1308.1963</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1827.1939</v>
+        <v>2850.252</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>395.4576</v>
+        <v>584.1517</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>745.3097</v>
+        <v>1119.3785</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1246.7121</v>
+        <v>1890.8067</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>122.8592</v>
+        <v>187.3306</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>507.9686</v>
+        <v>772.6754</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1259.9161</v>
+        <v>1950.4831</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>309.1061</v>
+        <v>470.8919</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>850.4145</v>
+        <v>1308.1963</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1827.1939</v>
+        <v>2850.252</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>186.2469</v>
+        <v>283.5613</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>342.446</v>
+        <v>535.5209</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>567.2778</v>
+        <v>899.7689</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>173.3155</v>
+        <v>265.4766</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>320.2073</v>
+        <v>503.0622</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>532.8111</v>
+        <v>847.6522</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>193.97</v>
+        <v>271.27</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>333.58</v>
+        <v>486.88</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>517</v>
+        <v>781.75</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>158.32</v>
+        <v>235.62</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>297.93</v>
+        <v>451.23</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>481.35</v>
+        <v>746.1</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>6.0042</v>
+        <v>6.0036</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>5.6711</v>
+        <v>5.6823</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.5174</v>
+        <v>5.5261</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>1855.9418</v>
+        <v>2827.0615</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>4822.8159</v>
+        <v>7433.5162</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>10081.4325</v>
+        <v>15750.8748</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>278.3913</v>
+        <v>424.0592</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>723.4224</v>
+        <v>1115.0274</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>1512.2149</v>
+        <v>2362.6312</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>309.1061</v>
+        <v>470.8919</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>850.4145</v>
+        <v>1308.1963</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1827.1939</v>
+        <v>2850.252</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2.1651</v>
+        <v>2.1654</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3.174</v>
+        <v>3.1678</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3.9874</v>
+        <v>3.9811</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>6.0042</v>
+        <v>6.0036</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>5.6711</v>
+        <v>5.6823</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>5.5174</v>
+        <v>5.5261</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>1004.1087</v>
+        <v>1532.4129</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>5496.6412</v>
+        <v>8467.3817</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18468.6881</v>
+        <v>28847.4441</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>-676.542</v>
+        <v>-924.7573</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>88.0142</v>
+        <v>279.5431</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>2184.8984</v>
+        <v>3687.4901</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>1855.9418</v>
+        <v>2827.0615</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>4822.8159</v>
+        <v>7433.5162</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>10081.4325</v>
+        <v>15750.8748</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>124.0719</v>
+        <v>184.8023</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>239.8246</v>
+        <v>360.085</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>407.1204</v>
+        <v>614.0699</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>92.9051</v>
+        <v>138.3801</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>179.5808</v>
+        <v>269.6318</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>304.852</v>
+        <v>459.8159</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4203,13 +4203,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>2656.5558</v>
+        <v>3936.6211</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>4974.6263</v>
+        <v>7514.0581</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>8303.654500000001</v>
+        <v>12677.4546</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4234,13 +4234,13 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>1989.2304</v>
+        <v>2947.744</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>3725.0028</v>
+        <v>5626.5307</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>6217.7809</v>
+        <v>9492.884700000001</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>392.5992</v>
+        <v>599.4938</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1398.7129</v>
+        <v>2165.809</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>3613.8317</v>
+        <v>5677.1445</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>1855.9418</v>
+        <v>2827.0615</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>4822.8159</v>
+        <v>7433.5162</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>10081.4325</v>
+        <v>15750.8748</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>124.0719</v>
+        <v>184.8023</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>239.8246</v>
+        <v>360.085</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>407.1204</v>
+        <v>614.0699</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>92.9051</v>
+        <v>138.3801</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>179.5808</v>
+        <v>269.6318</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>304.852</v>
+        <v>459.8159</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>671.3499</v>
+        <v>1013.5511</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>1565.8584</v>
+        <v>2379.0787</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>3260.8894</v>
+        <v>5010.6558</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>-75.0908</v>
+        <v>-8.597300000000001</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1650.9343</v>
+        <v>2688.5075</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>5451.9676</v>
+        <v>8791.843999999999</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>2457.3931</v>
+        <v>3743.2215</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>6385.736</v>
+        <v>9842.4807</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>13348.5017</v>
+        <v>20855.2287</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>124.0719</v>
+        <v>184.8023</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>239.8246</v>
+        <v>360.085</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>407.1204</v>
+        <v>614.0699</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>92.9051</v>
+        <v>138.3801</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>179.5808</v>
+        <v>269.6318</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>304.852</v>
+        <v>459.8159</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>2656.5558</v>
+        <v>3936.6211</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>4974.6263</v>
+        <v>7514.0581</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>8303.654500000001</v>
+        <v>12677.4546</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>1989.2304</v>
+        <v>2947.744</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>3725.0028</v>
+        <v>5626.5307</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>6217.7809</v>
+        <v>9492.884700000001</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>573.0345</v>
+        <v>874.3418</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2023.8809</v>
+        <v>3129.3948</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>5247.3663</v>
+        <v>8229.321400000001</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>2457.3931</v>
+        <v>3743.2215</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>6385.736</v>
+        <v>9842.4807</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>13348.5017</v>
+        <v>20855.2287</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>124.0719</v>
+        <v>184.8023</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>239.8246</v>
+        <v>360.085</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>407.1204</v>
+        <v>614.0699</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>92.9051</v>
+        <v>138.3801</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>179.5808</v>
+        <v>269.6318</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>304.852</v>
+        <v>459.8159</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>671.3499</v>
+        <v>1013.5511</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1565.8584</v>
+        <v>2379.0787</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>3260.8894</v>
+        <v>5010.6558</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>573.9544</v>
+        <v>922.0042999999999</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>3740.3257</v>
+        <v>5803.9136</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>10358.5851</v>
+        <v>16262.2756</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>443.7421</v>
+        <v>682.5614</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2088.7319</v>
+        <v>3214.3773</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>6084.8882</v>
+        <v>9507.311100000001</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>1004.1087</v>
+        <v>1532.4129</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>5496.6412</v>
+        <v>8467.3817</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>18468.6881</v>
+        <v>28847.4441</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>309.1061</v>
+        <v>470.8919</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>850.4145</v>
+        <v>1308.1963</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>1827.1939</v>
+        <v>2850.252</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>671.3499</v>
+        <v>1013.5511</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1565.8584</v>
+        <v>2379.0787</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>3260.8894</v>
+        <v>5010.6558</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>431.0742</v>
+        <v>658.0711</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>3472.7603</v>
+        <v>5337.9869</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>13221.3218</v>
+        <v>20618.1227</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>1004.1087</v>
+        <v>1532.4129</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>5496.6412</v>
+        <v>8467.3817</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>18468.6881</v>
+        <v>28847.4441</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>309.1061</v>
+        <v>470.8919</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>850.4145</v>
+        <v>1308.1963</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>1827.1939</v>
+        <v>2850.252</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>671.3499</v>
+        <v>1013.5511</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1565.8584</v>
+        <v>2379.0787</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>3260.8894</v>
+        <v>5010.6558</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>573.0345</v>
+        <v>874.3418</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2023.8809</v>
+        <v>3129.3948</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>5247.3663</v>
+        <v>8229.321400000001</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>2457.3931</v>
+        <v>3743.2215</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>6385.736</v>
+        <v>9842.4807</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>13348.5017</v>
+        <v>20855.2287</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>124.0719</v>
+        <v>184.8023</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>239.8246</v>
+        <v>360.085</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>407.1204</v>
+        <v>614.0699</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>92.9051</v>
+        <v>138.3801</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>179.5808</v>
+        <v>269.6318</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>304.852</v>
+        <v>459.8159</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5520,13 +5520,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>671.3499</v>
+        <v>1013.5511</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1565.8584</v>
+        <v>2379.0787</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>3260.8894</v>
+        <v>5010.6558</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>-0.4131</v>
+        <v>-0.4026</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-0.3927</v>
+        <v>-0.389</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>-0.3944</v>
+        <v>-0.3901</v>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
@@ -5609,13 +5609,13 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>-0.714</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-0.5921</v>
+        <v>-0.5992</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>-0.6542</v>
+        <v>-0.659</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -3009,7 +3009,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>全周期资本底座 − 初装 CAPEX（差额即更新净投入）</t>
+          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>全周期资本底座 − 初装 CAPEX（差额即更新净投入）</t>
+          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="决策树" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策树" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>913.6866</v>
+        <v>2106.0754</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9703.691699999999</v>
+        <v>10118.5588</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33597.9353</v>
+        <v>24067.9771</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>913.6866</v>
+        <v>2106.0754</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9703.691699999999</v>
+        <v>10118.5588</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33597.9353</v>
+        <v>24067.9771</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1532.4129</v>
+        <v>3129.6557</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8467.3817</v>
+        <v>8878.947899999999</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>28847.4441</v>
+        <v>19619.9527</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5108.0431</v>
+        <v>7824.1394</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>21168.4542</v>
+        <v>22197.3697</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>57694.8882</v>
+        <v>49049.8819</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6121.5942</v>
+        <v>9092.6705</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23547.5329</v>
+        <v>24680.0683</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>62705.544</v>
+        <v>53236.443</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>470.8919</v>
+        <v>505.1484</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1308.1963</v>
+        <v>1371.1149</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2850.252</v>
+        <v>2957.5802</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>556.5376</v>
+        <v>581.0802</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1442.0773</v>
+        <v>1511.4766</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3028.7514</v>
+        <v>3187.9553</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>238.6605</v>
+        <v>250.5156</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>676.0687</v>
+        <v>711.634</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1499.109</v>
+        <v>1580.6008</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1193.3026</v>
+        <v>1252.578</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2253.5624</v>
+        <v>2372.1132</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3747.7726</v>
+        <v>3951.502</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2258700</v>
+        <v>2301600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3874500</v>
+        <v>3960300</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5929200</v>
+        <v>6076400</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>188.6835</v>
+        <v>194.3645</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>207.7284</v>
+        <v>213.919</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>225.7455</v>
+        <v>232.2511</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>289.7122</v>
+        <v>301.0758</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>713.9475</v>
+        <v>745.1276</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1444.1975</v>
+        <v>1517.3617</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>301.7835</v>
+        <v>313.6206</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>594.9562</v>
+        <v>620.9397</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1002.9149</v>
+        <v>1053.7234</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>288.78</v>
+        <v>301.9256</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>574.1567</v>
+        <v>599.0395</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>974.2671</v>
+        <v>1017.4599</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13.0035</v>
+        <v>11.695</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>20.7995</v>
+        <v>21.9002</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>28.6478</v>
+        <v>36.2636</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>18.5764</v>
+        <v>19.4916</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>34.6658</v>
+        <v>36.5003</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>57.2956</v>
+        <v>60.4393</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>23.9265</v>
+        <v>25.1052</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>44.6495</v>
+        <v>47.0123</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>73.7968</v>
+        <v>77.8458</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>18.5764</v>
+        <v>19.4916</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>34.6658</v>
+        <v>36.5003</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>57.2956</v>
+        <v>60.4393</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4.2384</v>
+        <v>4.3836</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7.4116</v>
+        <v>7.7027</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11.6482</v>
+        <v>12.1469</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.2895</v>
+        <v>0.3047</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.5422</v>
+        <v>0.5728</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.9299</v>
+        <v>2.0316</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3.6145</v>
+        <v>3.8184</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>5.9981</v>
+        <v>6.3474</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3.9489</v>
+        <v>4.0789</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>6.8695</v>
+        <v>7.1299</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>10.7484</v>
+        <v>11.1948</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>85.64570000000001</v>
+        <v>75.9319</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>133.881</v>
+        <v>140.3617</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>178.4994</v>
+        <v>230.3751</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>51.8827</v>
+        <v>40.8449</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>73.48569999999999</v>
+        <v>77.3515</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>81.47329999999999</v>
+        <v>128.8533</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1323.0094</v>
+        <v>1388.7278</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2498.5148</v>
+        <v>2629.9516</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>4155.1391</v>
+        <v>4381.013</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1193.3026</v>
+        <v>1252.578</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2253.5624</v>
+        <v>2372.1132</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>3747.7726</v>
+        <v>3951.502</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1193.3026</v>
+        <v>1252.578</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2253.5624</v>
+        <v>2372.1132</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3747.7726</v>
+        <v>3951.502</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>12.6975</v>
+        <v>13.032</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>21.5265</v>
+        <v>22.197</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>32.934</v>
+        <v>34.083</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>8465</v>
+        <v>8688</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14351</v>
+        <v>14798</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>21956</v>
+        <v>22722</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>10.4983</v>
+        <v>11.0977</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>19.9743</v>
+        <v>21.1758</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>33.5315</v>
+        <v>35.5905</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>3399</v>
+        <v>3622</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>6662</v>
+        <v>7109</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>11421</v>
+        <v>12187</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>4.0337</v>
+        <v>4.2164</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>7.9144</v>
+        <v>8.263199999999999</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>13.3451</v>
+        <v>13.9493</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>3.6268</v>
+        <v>3.7927</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>7.1841</v>
+        <v>7.4994</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>12.1724</v>
+        <v>12.7192</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.9067</v>
+        <v>0.9482</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1.796</v>
+        <v>1.8748</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>3.0431</v>
+        <v>3.1798</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>18</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>1013.5511</v>
+        <v>1268.5311</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2379.0787</v>
+        <v>2482.6986</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>5010.6558</v>
+        <v>4186.5611</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>-618.7263</v>
+        <v>-1023.5803</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1236.3101</v>
+        <v>1239.6109</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>4750.4912</v>
+        <v>4448.0243</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2247,13 +2247,13 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>-41.2484</v>
+        <v>-51.179</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>61.8155</v>
+        <v>61.9805</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>190.0196</v>
+        <v>222.4012</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-41.2484</v>
+        <v>-51.179</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>25.2756</v>
+        <v>24.4089</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>84.1819</v>
+        <v>108.5285</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>50.103</v>
+        <v>45.6257</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>82.9277</v>
+        <v>88.227</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>114.925</v>
+        <v>147.0211</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-91.3514</v>
+        <v>-96.8047</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>-57.652</v>
+        <v>-63.8181</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>-30.7431</v>
+        <v>-38.4925</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>36.5399</v>
+        <v>37.5716</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>105.8377</v>
+        <v>113.8727</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>2977.1873</v>
+        <v>2991.3345</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3653.9864</v>
+        <v>3757.1609</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>4233.5095</v>
+        <v>4554.907</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0.0457</v>
+        <v>0.1053</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.4852</v>
+        <v>0.5059</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1.6799</v>
+        <v>1.2034</v>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>913.6866</v>
+        <v>2106.0754</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9703.691699999999</v>
+        <v>10118.5588</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>33597.9353</v>
+        <v>24067.9771</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>509.0041</v>
+        <v>567.5324000000001</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1038.3084</v>
+        <v>1087.0169</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1369.2061</v>
+        <v>1836.2982</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>509.0041</v>
+        <v>567.5324000000001</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1038.3084</v>
+        <v>1087.0169</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1369.2061</v>
+        <v>1836.2982</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>3393.3607</v>
+        <v>3547.0776</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>6489.4274</v>
+        <v>6793.8554</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>10953.6485</v>
+        <v>11476.864</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr"/>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>3393.3607</v>
+        <v>3547.0776</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>6489.4274</v>
+        <v>6793.8554</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>10953.6485</v>
+        <v>11476.864</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>2035.8419</v>
+        <v>2122.9569</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>3980.6461</v>
+        <v>4153.3457</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>6706.2524</v>
+        <v>7002.9803</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1654.9709</v>
+        <v>1725.5363</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>3289.238</v>
+        <v>3428.7641</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5586.4582</v>
+        <v>5826.3385</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>97.49769999999999</v>
+        <v>102.8974</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>192.4248</v>
+        <v>203.2483</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>325.9409</v>
+        <v>344.4885</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>235.62</v>
+        <v>246.77</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>451.23</v>
+        <v>473.58</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>746.1</v>
+        <v>784.4</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1357.5188</v>
+        <v>1424.1207</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2508.7813</v>
+        <v>2640.5097</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>4247.3961</v>
+        <v>4473.8838</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>509.0041</v>
+        <v>532.0616</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>973.4141</v>
+        <v>1019.0783</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1643.0473</v>
+        <v>1721.5296</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>3393.3607</v>
+        <v>3547.0776</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>6489.4274</v>
+        <v>6793.8554</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>10953.6485</v>
+        <v>11476.864</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>1696.6804</v>
+        <v>2128.2465</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>3893.6564</v>
+        <v>4076.3132</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>8215.2364</v>
+        <v>6886.1184</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>3393.3607</v>
+        <v>3547.0776</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>6489.4274</v>
+        <v>6793.8554</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>10953.6485</v>
+        <v>11476.864</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>2035.8419</v>
+        <v>2122.9569</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3980.6461</v>
+        <v>4153.3457</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>6706.2524</v>
+        <v>7002.9803</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>1654.9709</v>
+        <v>1725.5363</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>3289.238</v>
+        <v>3428.7641</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5586.4582</v>
+        <v>5826.3385</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>97.49769999999999</v>
+        <v>102.8974</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>192.4248</v>
+        <v>203.2483</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>325.9409</v>
+        <v>344.4885</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>235.62</v>
+        <v>246.77</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>451.23</v>
+        <v>473.58</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>746.1</v>
+        <v>784.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>1357.5188</v>
+        <v>1424.1207</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>2508.7813</v>
+        <v>2640.5097</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>4247.3961</v>
+        <v>4473.8838</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr"/>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>0.8061</v>
+        <v>0.8277</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.1687</v>
+        <v>1.1707</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.5074</v>
+        <v>1.4938</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.8061</v>
+        <v>0.8277</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.1687</v>
+        <v>1.1707</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1.5074</v>
+        <v>1.4938</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>470.8919</v>
+        <v>505.1484</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1308.1963</v>
+        <v>1371.1149</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>2850.252</v>
+        <v>2957.5802</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>584.1517</v>
+        <v>610.3104</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1119.3785</v>
+        <v>1171.1917</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1890.8067</v>
+        <v>1979.8551</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>187.3306</v>
+        <v>207.8332</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>772.6754</v>
+        <v>808.3769</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1950.4831</v>
+        <v>2011.0271</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>470.8919</v>
+        <v>505.1484</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1308.1963</v>
+        <v>1371.1149</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>2850.252</v>
+        <v>2957.5802</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>283.5613</v>
+        <v>297.3152</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>535.5209</v>
+        <v>562.7380000000001</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>899.7689</v>
+        <v>946.553</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>265.4766</v>
+        <v>278.4872</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>503.0622</v>
+        <v>528.7894</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>847.6522</v>
+        <v>891.883</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>271.27</v>
+        <v>282.42</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>486.88</v>
+        <v>509.23</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>781.75</v>
+        <v>820.05</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>235.62</v>
+        <v>246.77</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>451.23</v>
+        <v>473.58</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>746.1</v>
+        <v>784.4</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>6.0036</v>
+        <v>5.981</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>5.6823</v>
+        <v>5.684</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.5261</v>
+        <v>5.5334</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2827.0615</v>
+        <v>3021.2671</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>7433.5162</v>
+        <v>7793.4712</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>15750.8748</v>
+        <v>16365.4892</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>424.0592</v>
+        <v>453.1901</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1115.0274</v>
+        <v>1169.0207</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>2362.6312</v>
+        <v>2454.8234</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>470.8919</v>
+        <v>505.1484</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1308.1963</v>
+        <v>1371.1149</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>2850.252</v>
+        <v>2957.5802</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2.1654</v>
+        <v>3.0096</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3.1678</v>
+        <v>3.1668</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3.9811</v>
+        <v>3.253</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>18</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>6.0036</v>
+        <v>5.981</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>5.6823</v>
+        <v>5.684</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>5.5261</v>
+        <v>5.5334</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>1532.4129</v>
+        <v>3129.6557</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>8467.3817</v>
+        <v>8878.947899999999</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>28847.4441</v>
+        <v>19619.9527</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>-924.7573</v>
+        <v>-883.9767000000001</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>279.5431</v>
+        <v>335.5395</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>3687.4901</v>
+        <v>3779.7215</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2827.0615</v>
+        <v>3021.2671</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>7433.5162</v>
+        <v>7793.4712</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>15750.8748</v>
+        <v>16365.4892</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>184.8023</v>
+        <v>191.8274</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>360.085</v>
+        <v>373.9957</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>614.0699</v>
+        <v>637.98</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>138.3801</v>
+        <v>143.6405</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>269.6318</v>
+        <v>280.0482</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>459.8159</v>
+        <v>477.7198</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4203,13 +4203,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3936.6211</v>
+        <v>4097.0712</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>7514.0581</v>
+        <v>7831.9275</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>12677.4546</v>
+        <v>13223.7477</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4234,13 +4234,13 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>2947.744</v>
+        <v>3067.8891</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>5626.5307</v>
+        <v>5864.5514</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>9492.884700000001</v>
+        <v>9901.9493</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>599.4938</v>
+        <v>777.8253999999999</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2165.809</v>
+        <v>2273.9074</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5677.1445</v>
+        <v>5126.7632</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>2827.0615</v>
+        <v>3021.2671</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>7433.5162</v>
+        <v>7793.4712</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>15750.8748</v>
+        <v>16365.4892</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>184.8023</v>
+        <v>191.8274</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>360.085</v>
+        <v>373.9957</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>614.0699</v>
+        <v>637.98</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>138.3801</v>
+        <v>143.6405</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>269.6318</v>
+        <v>280.0482</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>459.8159</v>
+        <v>477.7198</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>1013.5511</v>
+        <v>1268.5311</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2379.0787</v>
+        <v>2482.6986</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>5010.6558</v>
+        <v>4186.5611</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>-8.597300000000001</v>
+        <v>95.11920000000001</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2688.5075</v>
+        <v>2861.1538</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>8791.843999999999</v>
+        <v>9083.252200000001</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>3743.2215</v>
+        <v>4000.363</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>9842.4807</v>
+        <v>10319.0855</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>20855.2287</v>
+        <v>21669.0199</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>184.8023</v>
+        <v>191.8274</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>360.085</v>
+        <v>373.9957</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>614.0699</v>
+        <v>637.98</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>138.3801</v>
+        <v>143.6405</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>269.6318</v>
+        <v>280.0482</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>459.8159</v>
+        <v>477.7198</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>3936.6211</v>
+        <v>4097.0712</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>7514.0581</v>
+        <v>7831.9275</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>12677.4546</v>
+        <v>13223.7477</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>2947.744</v>
+        <v>3067.8891</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>5626.5307</v>
+        <v>5864.5514</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>9492.884700000001</v>
+        <v>9901.9493</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>874.3418</v>
+        <v>1169.4637</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3129.3948</v>
+        <v>3284.1531</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>8229.321400000001</v>
+        <v>7248.1755</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>3743.2215</v>
+        <v>4000.363</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>9842.4807</v>
+        <v>10319.0855</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>20855.2287</v>
+        <v>21669.0199</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>184.8023</v>
+        <v>191.8274</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>360.085</v>
+        <v>373.9957</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>614.0699</v>
+        <v>637.98</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>138.3801</v>
+        <v>143.6405</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>269.6318</v>
+        <v>280.0482</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>459.8159</v>
+        <v>477.7198</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>1013.5511</v>
+        <v>1268.5311</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2379.0787</v>
+        <v>2482.6986</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>5010.6558</v>
+        <v>4186.5611</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr"/>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>922.0042999999999</v>
+        <v>1100.6386</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>5803.9136</v>
+        <v>6108.3223</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>16262.2756</v>
+        <v>16777.4396</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>682.5614</v>
+        <v>916.2222</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>3214.3773</v>
+        <v>3367.4412</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>9507.311100000001</v>
+        <v>8266.5362</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>1532.4129</v>
+        <v>3129.6557</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>8467.3817</v>
+        <v>8878.947899999999</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>28847.4441</v>
+        <v>19619.9527</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>470.8919</v>
+        <v>505.1484</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1308.1963</v>
+        <v>1371.1149</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>2850.252</v>
+        <v>2957.5802</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>18</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>1013.5511</v>
+        <v>1268.5311</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2379.0787</v>
+        <v>2482.6986</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>5010.6558</v>
+        <v>4186.5611</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr"/>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>658.0711</v>
+        <v>1960.192</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>5337.9869</v>
+        <v>5594.7948</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>20618.1227</v>
+        <v>12371.7772</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>1532.4129</v>
+        <v>3129.6557</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>8467.3817</v>
+        <v>8878.947899999999</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>28847.4441</v>
+        <v>19619.9527</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>470.8919</v>
+        <v>505.1484</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1308.1963</v>
+        <v>1371.1149</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>2850.252</v>
+        <v>2957.5802</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>18</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>1013.5511</v>
+        <v>1268.5311</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2379.0787</v>
+        <v>2482.6986</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>5010.6558</v>
+        <v>4186.5611</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5338,13 +5338,13 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr"/>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>874.3418</v>
+        <v>1169.4637</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>3129.3948</v>
+        <v>3284.1531</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>8229.321400000001</v>
+        <v>7248.1755</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>3743.2215</v>
+        <v>4000.363</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>9842.4807</v>
+        <v>10319.0855</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>20855.2287</v>
+        <v>21669.0199</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>184.8023</v>
+        <v>191.8274</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>360.085</v>
+        <v>373.9957</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>614.0699</v>
+        <v>637.98</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>138.3801</v>
+        <v>143.6405</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>269.6318</v>
+        <v>280.0482</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>459.8159</v>
+        <v>477.7198</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5520,13 +5520,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>1013.5511</v>
+        <v>1268.5311</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2379.0787</v>
+        <v>2482.6986</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>5010.6558</v>
+        <v>4186.5611</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr"/>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>-0.4026</v>
+        <v>-0.404</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-0.389</v>
+        <v>-0.3909</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>-0.3901</v>
+        <v>-0.392</v>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
@@ -5609,13 +5609,13 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7296</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-0.5992</v>
+        <v>-0.6006</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>-0.659</v>
+        <v>-0.5427</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>532.0616</v>
+        <v>401.8839</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1019.0783</v>
+        <v>769.7438</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1721.5296</v>
+        <v>1300.3287</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>0.15</v>
+        <v>0.1133</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.15</v>
+        <v>0.1133</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.15</v>
+        <v>0.1133</v>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>CRF 0.15 ← v3.2 §1.2.2「从全生命 CAPEX 到年 FCFF：期望收益率，非成本线」。 / 关键区分：WACC 7.5% 只是"必须收回成本的下限"，估值要看期望收益率，必然高于成本线。</t>
+          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>0.8277</v>
+        <v>1.1566</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.1707</v>
+        <v>1.6347</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.4938</v>
+        <v>2.0854</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.8277</v>
+        <v>1.1566</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.1707</v>
+        <v>1.6347</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1.4938</v>
+        <v>2.0854</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>610.3104</v>
+        <v>436.7401</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1171.1917</v>
+        <v>838.7457000000001</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1979.8551</v>
+        <v>1418.2539</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>5.981</v>
+        <v>7.9183</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>5.684</v>
+        <v>7.5252</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.5334</v>
+        <v>7.3258</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>3021.2671</v>
+        <v>3999.9123</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>7793.4712</v>
+        <v>10317.9231</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>16365.4892</v>
+        <v>21666.5788</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>0.15</v>
+        <v>0.1133</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.15</v>
+        <v>0.1133</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.15</v>
+        <v>0.1133</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>CRF 0.15 ← v3.2 §1.2.2「从全生命 CAPEX 到年 FCFF：期望收益率，非成本线」。 / 关键区分：WACC 7.5% 只是"必须收回成本的下限"，估值要看期望收益率，必然高于成本线。</t>
+          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
         </is>
       </c>
     </row>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>3.0096</v>
+        <v>2.2732</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3.1668</v>
+        <v>2.392</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3.253</v>
+        <v>2.4571</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>5.981</v>
+        <v>7.9183</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>5.684</v>
+        <v>7.5252</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>5.5334</v>
+        <v>7.3258</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>-883.9767000000001</v>
+        <v>94.66849999999999</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>335.5395</v>
+        <v>2859.9913</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>3779.7215</v>
+        <v>9080.811100000001</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>3021.2671</v>
+        <v>3999.9123</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>7793.4712</v>
+        <v>10317.9231</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>16365.4892</v>
+        <v>21666.5788</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>777.8253999999999</v>
+        <v>1169.2835</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2273.9074</v>
+        <v>3283.6881</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5126.7632</v>
+        <v>7247.1991</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>3021.2671</v>
+        <v>3999.9123</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>7793.4712</v>
+        <v>10317.9231</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>16365.4892</v>
+        <v>21666.5788</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>四个站型的终局站数之和</t>
+          <t>四个站型的兑现年站数之和</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　重卡站数（终局）</t>
+          <t xml:space="preserve">　　　　　　　　　重卡站数（兑现年）</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　巧克力站数（终局）</t>
+          <t xml:space="preserve">　　　　　　　　　巧克力站数（兑现年）</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策树" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="决策树" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>峰谷价差：焦作实证 0.5 元保守取 0.4</t>
+          <t>峰谷套利价差</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>谷电：rlut"低谷 0.3–0.4"取下沿</t>
+          <t>谷电价</t>
         </is>
       </c>
     </row>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="决策树" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策树" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0.1053</v>
+        <v>0.1186</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.5059</v>
+        <v>0.5698</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1.2034</v>
+        <v>1.3554</v>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>20000</v>
+        <v>17757</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>20000</v>
+        <v>17757</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>20000</v>
+        <v>17757</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I167"/>
+  <dimension ref="A1:I169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2106.0754</v>
+        <v>1489.3794</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10118.5588</v>
+        <v>7558.9506</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>24067.9771</v>
+        <v>17706.7884</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2106.0754</v>
+        <v>1489.3794</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10118.5588</v>
+        <v>7558.9506</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>24067.9771</v>
+        <v>17706.7884</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3129.6557</v>
+        <v>2522.5426</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8878.947899999999</v>
+        <v>6815.9699</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>19619.9527</v>
+        <v>14203.372</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7824.1394</v>
+        <v>6306.3565</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>22197.3697</v>
+        <v>17039.9247</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>49049.8819</v>
+        <v>35508.4301</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9092.6705</v>
+        <v>7573.5439</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>24680.0683</v>
+        <v>19531.9321</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>53236.443</v>
+        <v>39710.2183</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>505.1484</v>
+        <v>420.7524</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1371.1149</v>
+        <v>1085.1073</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2957.5802</v>
+        <v>2206.1232</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>581.0802</v>
+        <v>496.6843</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1511.4766</v>
+        <v>1225.4691</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3187.9553</v>
+        <v>2436.4983</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>250.5156</v>
+        <v>108.9743</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>711.634</v>
+        <v>246.6998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1580.6008</v>
+        <v>486.0347</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.2</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.3</v>
+        <v>0.104</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.4</v>
+        <v>0.123</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>换电服务费中枢 0.30 元/kWh。谱系：焦作商车邦实测 0.2（启源主导市场已打价格战） / → 齐鲁晚报行业 0.3–0.4 → 开源短倒 0.4。中枢 0.30 居中偏稳健。</t>
+          <t>【2026-09-21 · 门①】换电服务费跟平充电均衡价（0.104）：服务费天天比价，贵了司机就去隔壁； / 启源、骐骥不跟平（贵 0.1–0.2），份额 2024→2026-06 从 38.4% 掉到 24.6%。利润放在电池月租那条腿上。</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>301.0758</v>
+        <v>358.2212</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>745.1276</v>
+        <v>924.0543</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1517.3617</v>
+        <v>1860.4708</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>计费装机 × 单位装机年租金</t>
+          <t>(计费装机 − 乘用车池计费装机) × 重卡与城配月租 ＋ 乘用车池计费装机 × 乘用车月租</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1157,17 +1157,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　单位装机月租金</t>
+          <t xml:space="preserve">　　　　　　　　　电池月租·重卡与城配</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1188,34 +1188,34 @@
     </row>
     <row r="24" hidden="1" outlineLevel="7">
       <c r="A24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　峰谷套利收入</t>
+        <v>9</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　乘用车池计费装机</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>25.1052</v>
+        <v>63.2705</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>47.0123</v>
+        <v>129.7781</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>77.8458</v>
+        <v>215.1827</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>GWh</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>站内周转装机 × 运营天数 × 峰谷价差 × 站效率</t>
+          <t>乘用车池车端装机 ＋ 站内周转装机中归外部权益的部分</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
     </row>
     <row r="25" hidden="1" outlineLevel="7">
       <c r="A25" s="2" t="n">
@@ -1223,65 +1223,65 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　站内周转装机</t>
+          <t xml:space="preserve">　　　　　　　　　电池月租·乘用车</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>19.4916</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>36.5003</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>60.4393</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>GWh</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
+          <t>元/kWh·月</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.battery_rent_passenger_rmb_kwh_month</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>乘用车月租 9.0（三档 8.8／9.0／9.7）：巧克力 369 元/42 度＝8.8、499 元/56 度＝8.9；蔚来 728 元/75 度＝9.7（台账批次 5 推导链）</t>
+        </is>
+      </c>
     </row>
     <row r="26" hidden="1" outlineLevel="7">
       <c r="A26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　年运营天数</t>
+        <v>8</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　峰谷套利收入</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>350</v>
+        <v>25.1052</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>350</v>
+        <v>47.0123</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>350</v>
+        <v>77.8458</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>天</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.operating_days</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>年运营天数 350 天 ← v3.2 §1.3.1：营运车全年营运，留 15 天检修与极端天气停运</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>站内周转装机 × 运营天数 × 峰谷价差 × 站效率</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
     </row>
     <row r="27" hidden="1" outlineLevel="7">
       <c r="A27" s="2" t="n">
@@ -1289,34 +1289,30 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　峰谷价差</t>
+          <t xml:space="preserve">　　　　　　　　　站内周转装机</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.4</v>
+        <v>19.4916</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.4</v>
+        <v>36.5003</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.4</v>
+        <v>60.4393</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>元/kWh</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.grid_spread_rmb_kwh</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>峰谷套利价差</t>
-        </is>
-      </c>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
     </row>
     <row r="28" hidden="1" outlineLevel="7">
       <c r="A28" s="2" t="n">
@@ -1324,61 +1320,69 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　站内充放效率 RTE</t>
+          <t xml:space="preserve">　　　　　　　　　年运营天数</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.92</v>
+        <v>350</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.92</v>
+        <v>350</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>天</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>swap_business.rte</t>
+          <t>swap_business.operating_days</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>往返效率 RTE 0.92 ← v3.2 §2.3／MANIFEST §5：LFP 系统充放往返效率 88–94% 区间中值（工程常识， / 信源审计台账已核为「保留」）。三处用到它，口径同一：① 充电电量 = 换电电量 ÷ RTE ×(1＋站用电率)；</t>
+          <t>年运营天数 350 天 ← v3.2 §1.3.1：营运车全年营运，留 15 天检修与极端天气停运</t>
         </is>
       </c>
     </row>
     <row r="29" hidden="1" outlineLevel="7">
       <c r="A29" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　电网辅助服务收入</t>
+        <v>9</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　峰谷价差</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4.3836</v>
+        <v>0.4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7.7027</v>
+        <v>0.4</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>12.1469</v>
+        <v>0.4</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>容量补偿 ＋ 孰高( 需求响应, 调频 )　——容量补偿是站建成即可申报的「存在型」收益；后两项须实际提供服务才有收益，且争夺同一份可调容量，同一时段只能干一件事，故孰高取一、不可相加</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>元/kWh</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.grid_spread_rmb_kwh</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>峰谷套利价差</t>
+        </is>
+      </c>
     </row>
     <row r="30" hidden="1" outlineLevel="7">
       <c r="A30" s="2" t="n">
@@ -1386,48 +1390,48 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　容量补偿</t>
+          <t xml:space="preserve">　　　　　　　　　站内充放效率 RTE</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.3047</v>
+        <v>0.92</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.5728</v>
+        <v>0.92</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.9520999999999999</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Σ_池( 站数 × 单站申报容量 × 容量补偿价 )——站在即可申报，无条件计入</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="3" t="inlineStr"/>
+        <v>0.92</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.rte</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>往返效率 RTE 0.92 ← v3.2 §2.3／MANIFEST §5：LFP 系统充放往返效率 88–94% 区间中值（工程常识， / 信源审计台账已核为「保留」）。三处用到它，口径同一：① 充电电量 = 换电电量 ÷ RTE ×(1＋站用电率)；</t>
+        </is>
+      </c>
     </row>
     <row r="31" hidden="1" outlineLevel="7">
       <c r="A31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　需求响应（候选·须实际提供服务）</t>
+        <v>8</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　电网辅助服务收入</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2.0316</v>
+        <v>4.3836</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3.8184</v>
+        <v>7.7027</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>6.3474</v>
+        <v>12.1469</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1436,11 +1440,11 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 站数 × 单站申报容量 × 年响应小时 × 响应价 )</t>
+          <t>容量补偿 ＋ 孰高( 需求响应, 调频 )　——容量补偿是站建成即可申报的「存在型」收益；后两项须实际提供服务才有收益，且争夺同一份可调容量，同一时段只能干一件事，故孰高取一、不可相加</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32" hidden="1" outlineLevel="7">
       <c r="A32" s="2" t="n">
@@ -1448,17 +1452,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　调频（候选·须实际提供服务）</t>
+          <t xml:space="preserve">　　　　　　　　　容量补偿</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4.0789</v>
+        <v>0.3047</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7.1299</v>
+        <v>0.5728</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11.1948</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1467,7 +1471,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 站数 × 单站调频容量 × 年调频小时 × 调频价 )</t>
+          <t>Σ_池( 站数 × 单站申报容量 × 容量补偿价 )——站在即可申报，无条件计入</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -1475,21 +1479,21 @@
     </row>
     <row r="33" hidden="1" outlineLevel="7">
       <c r="A33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　运营 OPEX</t>
+        <v>9</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　需求响应（候选·须实际提供服务）</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>75.9319</v>
+        <v>2.0316</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>140.3617</v>
+        <v>3.8184</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>230.3751</v>
+        <v>6.3474</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1498,29 +1502,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>电费 ＋ 场租 ＋ 人工 ＋ 软件调度 ＋ 保险 ＋ 池化维护 ＋ 仓储物流</t>
+          <t>Σ_池( 站数 × 单站申报容量 × 年响应小时 × 响应价 )</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr"/>
     </row>
     <row r="34" hidden="1" outlineLevel="7">
       <c r="A34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　电费</t>
+        <v>9</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　调频（候选·须实际提供服务）</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>40.8449</v>
+        <v>4.0789</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>77.3515</v>
+        <v>7.1299</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>128.8533</v>
+        <v>11.1948</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1529,38 +1533,38 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>( 充电电量 − 换电电量 ) × 谷电价</t>
+          <t>Σ_池( 站数 × 单站调频容量 × 年调频小时 × 调频价 )</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
     </row>
     <row r="35" hidden="1" outlineLevel="7">
       <c r="A35" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　年充电电量</t>
+          <t xml:space="preserve">　　　　　　　运营 OPEX</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1388.7278</v>
+        <v>75.9319</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2629.9516</v>
+        <v>140.3617</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>4381.013</v>
+        <v>230.3751</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>亿kWh</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>换电电量 ÷ RTE × ( 1 ＋ 站用电率 )</t>
+          <t>电费 ＋ 场租 ＋ 人工 ＋ 软件调度 ＋ 保险 ＋ 池化维护 ＋ 仓储物流</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -1568,65 +1572,65 @@
     </row>
     <row r="36" hidden="1" outlineLevel="7">
       <c r="A36" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　年换电交易电量</t>
+        <v>8</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　电费</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1252.578</v>
+        <v>40.8449</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2372.1132</v>
+        <v>77.3515</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>3951.502</v>
+        <v>128.8533</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>亿kWh</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>( 充电电量 − 换电电量 ) × 谷电价</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
     </row>
     <row r="37" hidden="1" outlineLevel="7">
       <c r="A37" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　站内充放效率 RTE</t>
+        <v>9</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　年充电电量</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.92</v>
+        <v>1388.7278</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.92</v>
+        <v>2629.9516</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.rte</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>往返效率 RTE 0.92 ← v3.2 §2.3／MANIFEST §5：LFP 系统充放往返效率 88–94% 区间中值（工程常识， / 信源审计台账已核为「保留」）。三处用到它，口径同一：① 充电电量 = 换电电量 ÷ RTE ×(1＋站用电率)；</t>
-        </is>
-      </c>
+        <v>4381.013</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>亿kWh</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>换电电量 ÷ RTE × ( 1 ＋ 站用电率 )</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
     </row>
     <row r="38" hidden="1" outlineLevel="7">
       <c r="A38" s="2" t="n">
@@ -1634,127 +1638,123 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　　站用电率</t>
+          <t xml:space="preserve">　　　　　　　　　　年换电交易电量</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.02</v>
+        <v>1252.578</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.02</v>
+        <v>2372.1132</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.auxiliary_power_rate</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>站用电率（厂用电率）2% ← v3.2 §1.3.2 成本端口径：用户换走的电量不计入充电成本， / 只有循环效率损失（1−RTE）与设备自用电两部分按谷电价计成本</t>
-        </is>
-      </c>
+        <v>3951.502</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>亿kWh</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr"/>
     </row>
     <row r="39" hidden="1" outlineLevel="7">
       <c r="A39" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　年换电交易电量</t>
+          <t xml:space="preserve">　　　　　　　　　　站内充放效率 RTE</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1252.578</v>
+        <v>0.92</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2372.1132</v>
+        <v>0.92</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3951.502</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>亿kWh</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
+        <v>0.92</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.rte</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>往返效率 RTE 0.92 ← v3.2 §2.3／MANIFEST §5：LFP 系统充放往返效率 88–94% 区间中值（工程常识， / 信源审计台账已核为「保留」）。三处用到它，口径同一：① 充电电量 = 换电电量 ÷ RTE ×(1＋站用电率)；</t>
+        </is>
+      </c>
     </row>
     <row r="40" hidden="1" outlineLevel="7">
       <c r="A40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　谷段电价</t>
+          <t xml:space="preserve">　　　　　　　　　　站用电率</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>元/kWh</t>
-        </is>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>swap_business.valley_power_price_rmb_kwh</t>
+          <t>swap_business.auxiliary_power_rate</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>谷电价</t>
+          <t>站用电率（厂用电率）2% ← v3.2 §1.3.2 成本端口径：用户换走的电量不计入充电成本， / 只有循环效率损失（1−RTE）与设备自用电两部分按谷电价计成本</t>
         </is>
       </c>
     </row>
     <row r="41" hidden="1" outlineLevel="7">
       <c r="A41" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　场地租金</t>
+        <v>9</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　年换电交易电量</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13.032</v>
+        <v>1252.578</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>22.197</v>
+        <v>2372.1132</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>34.083</v>
+        <v>3951.502</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>亿kWh</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 站数 ) × 单站年场租</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
     </row>
     <row r="42" hidden="1" outlineLevel="7">
       <c r="A42" s="2" t="n">
@@ -1762,96 +1762,96 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　站数合计</t>
+          <t xml:space="preserve">　　　　　　　　　谷段电价</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>8688</v>
+        <v>0.3</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14798</v>
+        <v>0.3</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>22722</v>
+        <v>0.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>座</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>四个站型的兑现年站数之和</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
+          <t>元/kWh</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.valley_power_price_rmb_kwh</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>谷电价</t>
+        </is>
+      </c>
     </row>
     <row r="43" hidden="1" outlineLevel="7">
       <c r="A43" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　单站年场租</t>
+        <v>8</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　场地租金</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>15</v>
+        <v>13.032</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>15</v>
+        <v>22.197</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>15</v>
+        <v>34.083</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>万元/年</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.site_rent_wan_year</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>场租 15 万/站/年（统一不分站型）：200–300㎡×50 元/㎡/月×12 = 12–18 万取中。 / 巧克力核心区贵/重卡干线便宜，两者相抵；较蔚能二代站 10 万偏保守。不做敏感性</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Σ_池( 站数 ) × 单站年场租</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
     </row>
     <row r="44" hidden="1" outlineLevel="7">
       <c r="A44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　人工</t>
+        <v>9</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　站数合计</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>11.0977</v>
+        <v>8688</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>21.1758</v>
+        <v>14798</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>35.5905</v>
+        <v>22722</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>座</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>重卡站数 × 重卡单站年人工 ＋ 巧克力站数 × 巧克力单站年人工</t>
+          <t>四个站型的兑现年站数之和</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
     </row>
     <row r="45" hidden="1" outlineLevel="7">
       <c r="A45" s="2" t="n">
@@ -1859,65 +1859,65 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　重卡站数（兑现年）</t>
+          <t xml:space="preserve">　　　　　　　　　单站年场租</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>3622</v>
+        <v>15</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>7109</v>
+        <v>15</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>12187</v>
+        <v>15</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>座</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>骐骥短途站 ＋ 骐骥干线站</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr"/>
+          <t>万元/年</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.site_rent_wan_year</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>场租 15 万/站/年（统一不分站型）：200–300㎡×50 元/㎡/月×12 = 12–18 万取中。 / 巧克力核心区贵/重卡干线便宜，两者相抵；较蔚能二代站 10 万偏保守。不做敏感性</t>
+        </is>
+      </c>
     </row>
     <row r="46" hidden="1" outlineLevel="7">
       <c r="A46" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　重卡单站年人工</t>
+        <v>8</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　人工</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>26.88</v>
+        <v>11.0977</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>26.88</v>
+        <v>21.1758</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>26.88</v>
+        <v>35.5905</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>万元/年</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.heavy_station_labor_wan_year</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>重卡站人工 26.88 万/站/年：2 人×16h 双班倒×1.12 万/月×12（老模型精算口径回归）。 / v4.2 按次计价（30 元/次）废弃——隐含 4 人编制、高估 2 倍</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>重卡站数 × 重卡单站年人工 ＋ 巧克力站数 × 巧克力单站年人工</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
     </row>
     <row r="47" hidden="1" outlineLevel="7">
       <c r="A47" s="2" t="n">
@@ -1925,17 +1925,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　巧克力站数（兑现年）</t>
+          <t xml:space="preserve">　　　　　　　　　重卡站数（兑现年）</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>5066</v>
+        <v>3622</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7689</v>
+        <v>7109</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>10535</v>
+        <v>12187</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>巧克力乘用站 ＋ 巧克力城配站</t>
+          <t>骐骥短途站 ＋ 骐骥干线站</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -1956,17 +1956,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　巧克力单站年人工</t>
+          <t xml:space="preserve">　　　　　　　　　重卡单站年人工</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>2.688</v>
+        <v>26.88</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.688</v>
+        <v>26.88</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>2.688</v>
+        <v>26.88</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -1976,41 +1976,41 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>swap_business.passenger_station_labor_wan_year</t>
+          <t>swap_business.heavy_station_labor_wan_year</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>巧克力站直接人工 0.2 人/站保守档（2026-08-29 拍板，v4.3 从 0 上调）：≈5 站共用 1 名巡检员 / （0.2 人×1.12 万/月×12 = 2.688 万/站/年）。覆盖逻辑：官方"3 公里服务半径"密度（厦门试点口径）下</t>
+          <t>重卡站人工 26.88 万/站/年：2 人×16h 双班倒×1.12 万/月×12（老模型精算口径回归）。 / v4.2 按次计价（30 元/次）废弃——隐含 4 人编制、高估 2 倍</t>
         </is>
       </c>
     </row>
     <row r="49" hidden="1" outlineLevel="7">
       <c r="A49" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　软件调度</t>
+          <t xml:space="preserve">　　　　　　　　　巧克力站数（兑现年）</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>2</v>
+        <v>5066</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2</v>
+        <v>7689</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2</v>
+        <v>10535</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>座</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>固定投入，按站数份额分池</t>
+          <t>巧克力乘用站 ＋ 巧克力城配站</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -2018,34 +2018,38 @@
     </row>
     <row r="50" hidden="1" outlineLevel="7">
       <c r="A50" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　保险</t>
+          <t xml:space="preserve">　　　　　　　　　巧克力单站年人工</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>4.2164</v>
+        <v>2.688</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>8.263199999999999</v>
+        <v>2.688</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>13.9493</v>
+        <v>2.688</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>电池资产 × 电池保险费率 ＋ 站体资产 × 设备保险费率</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="3" t="inlineStr"/>
+          <t>万元/年</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.passenger_station_labor_wan_year</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>巧克力站直接人工 0.2 人/站保守档（2026-08-29 拍板，v4.3 从 0 上调）：≈5 站共用 1 名巡检员 / （0.2 人×1.12 万/月×12 = 2.688 万/站/年）。覆盖逻辑：官方"3 公里服务半径"密度（厦门试点口径）下</t>
+        </is>
+      </c>
     </row>
     <row r="51" hidden="1" outlineLevel="7">
       <c r="A51" s="2" t="n">
@@ -2053,17 +2057,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　池化维护</t>
+          <t xml:space="preserve">　　　　　　　　软件调度</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>3.7927</v>
+        <v>2</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>7.4994</v>
+        <v>2</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>12.7192</v>
+        <v>2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2072,7 +2076,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>电池资产 × 池化维护费率</t>
+          <t>固定投入，按站数份额分池</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -2084,17 +2088,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　仓储物流</t>
+          <t xml:space="preserve">　　　　　　　　保险</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.9482</v>
+        <v>4.2164</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1.8748</v>
+        <v>8.263199999999999</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>3.1798</v>
+        <v>13.9493</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2103,64 +2107,60 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>电池资产 × 仓储物流费率</t>
+          <t>电池资产 × 电池保险费率 ＋ 站体资产 × 设备保险费率</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr"/>
     </row>
-    <row r="53" hidden="1" outlineLevel="6">
+    <row r="53" hidden="1" outlineLevel="7">
       <c r="A53" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　运营 EV/EBITDA 倍数</t>
+          <t xml:space="preserve">　　　　　　　　池化维护</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>18</v>
+        <v>3.7927</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>18</v>
+        <v>7.4994</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>18</v>
+        <v>12.7192</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>finance.swap_ev_ebitda</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" hidden="1" outlineLevel="5">
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>电池资产 × 池化维护费率</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" hidden="1" outlineLevel="7">
       <c r="A54" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　稳态debt（2030在役资产历史成本×债务比）</t>
+          <t xml:space="preserve">　　　　　　　　仓储物流</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>1268.5311</v>
+        <v>0.9482</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2482.6986</v>
+        <v>1.8748</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>4186.5611</v>
+        <v>3.1798</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2169,60 +2169,64 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>电池资产 × 仓储物流费率</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="3" t="inlineStr"/>
     </row>
-    <row r="55" hidden="1" outlineLevel="4">
+    <row r="55" hidden="1" outlineLevel="6">
       <c r="A55" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　CATL建站持股比例</t>
+          <t xml:space="preserve">　　　　　　运营 EV/EBITDA 倍数</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.4</v>
+        <v>18</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.4</v>
+        <v>18</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>finance.construction_ownership</t>
+          <t>finance.swap_ev_ebitda</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" hidden="1" outlineLevel="3">
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" hidden="1" outlineLevel="5">
       <c r="A56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　制造侧锁量锁价增量</t>
+        <v>5</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　稳态debt（2030在役资产历史成本×债务比）</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>-1023.5803</v>
+        <v>1267.1874</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1239.6109</v>
+        <v>2492.0074</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>4448.0243</v>
+        <v>4201.7882</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2231,60 +2235,60 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>制造净利差 × 制造 PE</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr"/>
     </row>
     <row r="57" hidden="1" outlineLevel="4">
       <c r="A57" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　制造净利差（有换电 − 纯制造）</t>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>-51.179</v>
+        <v>0.4</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>61.9805</v>
+        <v>0.4</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>222.4012</v>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>量差效应 ＋ 换电段利润率效应 ＋ 其他段利润率效应</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58" hidden="1" outlineLevel="5">
+        <v>0.4</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" hidden="1" outlineLevel="3">
       <c r="A58" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　量差效应</t>
+          <t xml:space="preserve">　　　制造侧锁量锁价增量</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-51.179</v>
+        <v>-1033.1632</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>24.4089</v>
+        <v>742.9807</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>108.5285</v>
+        <v>3503.4164</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2293,104 +2297,104 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>锁定订单效应 ＋ 充电段份额效应（虹吸，通常为负）</t>
+          <t>制造净利差 × 制造 PE</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
     </row>
-    <row r="59" hidden="1" outlineLevel="6">
+    <row r="59" hidden="1" outlineLevel="4">
       <c r="A59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　制造净利差（有换电 − 纯制造）</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>-51.6582</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>37.149</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>175.1708</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>量差效应 ＋ 换电段利润率效应 ＋ 其他段利润率效应</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" hidden="1" outlineLevel="5">
+      <c r="A60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　量差效应</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>-51.6582</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1.4168</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>69.1699</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>锁定订单效应 ＋ 充电段份额效应（虹吸，通常为负）</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" hidden="1" outlineLevel="6">
+      <c r="A61" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　锁定订单效应</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>45.6257</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>88.227</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>147.0211</v>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="C61" s="2" t="n">
+        <v>45.1465</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>65.2349</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>107.6624</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>换电锁定出货 × 单位售价 × 纯制造净利率</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" hidden="1" outlineLevel="6">
-      <c r="A60" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　充电段份额效应（虹吸）</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>-96.8047</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>-63.8181</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>-38.4925</v>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>量差效应 − 锁定订单效应（换电对充电段的挤出）</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61" hidden="1" outlineLevel="5">
-      <c r="A61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　换电段利润率效应（护价）</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>37.5716</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>113.8727</v>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>换电可覆盖收入 × 净利率差</t>
-        </is>
-      </c>
       <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
     </row>
     <row r="62" hidden="1" outlineLevel="6">
       <c r="A62" s="2" t="n">
@@ -2398,374 +2402,374 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　换电可覆盖收入</t>
+          <t xml:space="preserve">　　　　　　充电段份额效应（虹吸）</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>2991.3345</v>
+        <v>-96.8047</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3757.1609</v>
+        <v>-63.8181</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>4554.907</v>
+        <v>-38.4925</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>亿元</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>量差效应 − 锁定订单效应（换电对充电段的挤出）</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr"/>
     </row>
-    <row r="63" hidden="1" outlineLevel="6">
+    <row r="63" hidden="1" outlineLevel="5">
       <c r="A63" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　净利率差（有换电 − 无换电）</t>
+          <t xml:space="preserve">　　　　　换电段利润率效应（护价）</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.01</v>
+        <v>35.7322</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
+        <v>106.0009</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>有换电制造净利率 − 无换电制造净利率</t>
+          <t>换电可覆盖收入 × 净利率差</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
     </row>
-    <row r="64" hidden="1" outlineLevel="7">
+    <row r="64" hidden="1" outlineLevel="6">
       <c r="A64" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　有换电制造净利率</t>
+          <t xml:space="preserve">　　　　　　换电可覆盖收入</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>0.125</v>
+        <v>2987.5013</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.135</v>
+        <v>3573.2238</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
+        <v>4240.0377</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="3" t="inlineStr"/>
     </row>
-    <row r="65" hidden="1" outlineLevel="7">
+    <row r="65" hidden="1" outlineLevel="6">
       <c r="A65" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　净利率差（有换电 − 无换电）</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>有换电制造净利率 − 无换电制造净利率</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" hidden="1" outlineLevel="7">
+      <c r="A66" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　无换电制造净利率</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　有换电制造净利率</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
         <v>0.125</v>
       </c>
-      <c r="D65" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" hidden="1" outlineLevel="5">
-      <c r="A66" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　其他段利润率效应</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D66" s="2" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>换电不可覆盖收入 × 净利率差</t>
-        </is>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="3" t="inlineStr"/>
     </row>
-    <row r="67" hidden="1" outlineLevel="4">
+    <row r="67" hidden="1" outlineLevel="7">
       <c r="A67" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　无换电制造净利率</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" hidden="1" outlineLevel="5">
+      <c r="A68" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　其他段利润率效应</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>换电不可覆盖收入 × 净利率差</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" hidden="1" outlineLevel="4">
+      <c r="A69" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　制造 PE</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C69" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D69" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E69" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>finance.manufacturing_pe</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>制造 PE 20× ← v3.2 §6.6：延续当前估值水平，不做扩张假设。 / 校核：2026 动力净利拍 600 亿 × 20 = 12,000 亿；对照集团市值 18,250 亿、</t>
         </is>
       </c>
     </row>
-    <row r="68" outlineLevel="2">
-      <c r="A68" s="2" t="n">
+    <row r="70" outlineLevel="2">
+      <c r="A70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　　增量价值 ÷ 集团市值</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>0.1186</v>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>0.5698</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>1.3554</v>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="C70" s="2" t="n">
+        <v>0.0839</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>可归因换电增量价值 ÷ 集团市值基准</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" hidden="1" outlineLevel="3">
-      <c r="A69" s="2" t="n">
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" hidden="1" outlineLevel="3">
+      <c r="A71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　可归因换电增量价值</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>2106.0754</v>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>10118.5588</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>24067.9771</v>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="C71" s="2" t="n">
+        <v>1489.3794</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>7558.9506</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>17706.7884</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>同上（引用）</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" hidden="1" outlineLevel="3">
-      <c r="A70" s="2" t="n">
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" hidden="1" outlineLevel="3">
+      <c r="A72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　集团市值基准（A+H）</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="C72" s="2" t="n">
         <v>17757</v>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D72" s="2" t="n">
         <v>17757</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E72" s="2" t="n">
         <v>17757</v>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71" outlineLevel="1">
-      <c r="A71" s="2" t="n">
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　做透的代价</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>567.5324000000001</v>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>1087.0169</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>1836.2982</v>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="C73" s="2" t="n">
+        <v>547.9404</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>849.1349</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>1315.3686</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>见下</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72" outlineLevel="2">
-      <c r="A72" s="2" t="n">
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" outlineLevel="2">
+      <c r="A74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　　CATL 全周期权益承诺</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>567.5324000000001</v>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>1087.0169</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>1836.2982</v>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="n">
+        <v>547.9404</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>849.1349</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>1315.3686</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>全周期资本底座 × (1 − 债务比例) × CATL建站持股比例</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73" hidden="1" outlineLevel="3">
-      <c r="A73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　全周期资本底座</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>3547.0776</v>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>6793.8554</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>11476.864</v>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74" hidden="1" outlineLevel="3">
-      <c r="A74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　项目债务比例</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>finance.debt_ratio</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>债务比例 60%：经验假设（类固收项目可做到 1:1.5 杠杆）</t>
-        </is>
-      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
     </row>
     <row r="75" hidden="1" outlineLevel="3">
       <c r="A75" s="2" t="n">
@@ -2773,154 +2777,154 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　CATL建站持股比例</t>
+          <t xml:space="preserve">　　　全周期资本底座</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>0.4</v>
+        <v>3424.6274</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.4</v>
+        <v>5307.0932</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" outlineLevel="2">
+        <v>8221.053599999999</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" hidden="1" outlineLevel="3">
       <c r="A76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　全周期资本底座（现值）</t>
+        <v>3</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　项目债务比例</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>3547.0776</v>
+        <v>0.6</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>6793.8554</v>
+        <v>0.6</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>11476.864</v>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>初装 CAPEX ＋ 全周期电池更新净额（按届时价格、扣回收残值，折现）</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>finance.debt_ratio</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>债务比例 60%：经验假设（类固收项目可做到 1:1.5 杠杆）</t>
+        </is>
+      </c>
     </row>
     <row r="77" hidden="1" outlineLevel="3">
       <c r="A77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="2">
+      <c r="A78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　全周期资本底座（现值）</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>3424.6274</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>5307.0932</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>8221.053599999999</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>初装 CAPEX ＋ 全周期电池更新净额（按届时价格、扣回收残值，折现）</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" hidden="1" outlineLevel="3">
+      <c r="A79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　初装 CAPEX 合计</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C79" s="2" t="n">
         <v>2122.9569</v>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D79" s="2" t="n">
         <v>4153.3457</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E79" s="2" t="n">
         <v>7002.9803</v>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>期初存量站投入 ＋ Σ_年( 车端电池 ＋ 站内电池 ＋ 站体 )</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78" hidden="1" outlineLevel="4">
-      <c r="A78" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　期初存量站投入</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>47.7533</v>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>47.7533</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>47.7533</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>2026 年之前已建成站的站体与站内电池</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79" hidden="1" outlineLevel="4">
-      <c r="A79" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　车端电池初装</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>1725.5363</v>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>3428.7641</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>5826.3385</v>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Σ_年( 当年新增换电装车 GWh × 当年电池价格 )</t>
-        </is>
-      </c>
       <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="3" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
     </row>
     <row r="80" hidden="1" outlineLevel="4">
       <c r="A80" s="2" t="n">
@@ -2928,17 +2932,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　站内周转电池初装</t>
+          <t xml:space="preserve">　　　　期初存量站投入</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>102.8974</v>
+        <v>47.7533</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>203.2483</v>
+        <v>47.7533</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>344.4885</v>
+        <v>47.7533</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2951,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Σ_年( 当年新增站数 × 站内周转块数 × 单块电量 × 当年电池价格 )</t>
+          <t>2026 年之前已建成站的站体与站内电池</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -2959,17 +2963,17 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　站体初装</t>
+          <t xml:space="preserve">　　　　车端电池初装</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>246.77</v>
+        <v>1725.5363</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>473.58</v>
+        <v>3428.7641</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>784.4</v>
+        <v>5826.3385</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2978,29 +2982,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Σ_年Σ_池( 当年新增站数 × 该站型单站站体造价 )</t>
+          <t>Σ_年( 当年新增换电装车 GWh × 当年电池价格 )</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr"/>
     </row>
-    <row r="82" hidden="1" outlineLevel="3">
+    <row r="82" hidden="1" outlineLevel="4">
       <c r="A82" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　全周期更新净额（现值）</t>
+          <t xml:space="preserve">　　　　站内周转电池初装</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1424.1207</v>
+        <v>102.8974</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2640.5097</v>
+        <v>203.2483</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>4473.8838</v>
+        <v>344.4885</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3009,29 +3013,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
+          <t>Σ_年( 当年新增站数 × 站内周转块数 × 单块电量 × 当年电池价格 )</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="3" t="inlineStr"/>
     </row>
-    <row r="83" outlineLevel="2">
+    <row r="83" hidden="1" outlineLevel="4">
       <c r="A83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年资本要求</t>
+        <v>4</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　站体初装</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>401.8839</v>
+        <v>246.77</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>769.7438</v>
+        <v>473.58</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1300.3287</v>
+        <v>784.4</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3040,11 +3044,11 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>全周期资本底座 × 资本回收系数 CRF</t>
+          <t>Σ_年Σ_池( 当年新增站数 × 该站型单站站体造价 )</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
     </row>
     <row r="84" hidden="1" outlineLevel="3">
       <c r="A84" s="2" t="n">
@@ -3052,17 +3056,17 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　全周期资本底座</t>
+          <t xml:space="preserve">　　　全周期更新净额（现值）</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>3547.0776</v>
+        <v>1301.6705</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>6793.8554</v>
+        <v>1153.7475</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>11476.864</v>
+        <v>1218.0733</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3071,60 +3075,60 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="3" t="inlineStr"/>
     </row>
-    <row r="85" hidden="1" outlineLevel="3">
+    <row r="85" outlineLevel="2">
       <c r="A85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年资本要求</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>388.0103</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>601.2936999999999</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>931.4453999999999</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全周期资本底座 × 资本回收系数 CRF</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86" hidden="1" outlineLevel="3">
+      <c r="A86" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　资本回收系数 CRF</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>finance.capital_recovery_factor</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" outlineLevel="2">
-      <c r="A86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　项目债务</t>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　全周期资本底座</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2128.2465</v>
+        <v>3424.6274</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4076.3132</v>
+        <v>5307.0932</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6886.1184</v>
+        <v>8221.053599999999</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3133,60 +3137,60 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>全周期资本底座 × 债务比例</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
     </row>
     <row r="87" hidden="1" outlineLevel="3">
       <c r="A87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　全周期资本底座（现值）</t>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　资本回收系数 CRF</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>3547.0776</v>
+        <v>0.1133</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>6793.8554</v>
+        <v>0.1133</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>11476.864</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>初装 CAPEX ＋ 全周期电池更新净额（按届时价格、扣回收残值，折现）</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88" hidden="1" outlineLevel="4">
+        <v>0.1133</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>finance.capital_recovery_factor</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" outlineLevel="2">
       <c r="A88" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　初装 CAPEX 合计</t>
+          <t xml:space="preserve">　　项目债务</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>2122.9569</v>
+        <v>2054.7764</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>4153.3457</v>
+        <v>3184.2559</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>7002.9803</v>
+        <v>4932.6321</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3195,29 +3199,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>期初存量站投入 ＋ Σ_年( 车端电池 ＋ 站内电池 ＋ 站体 )</t>
+          <t>全周期资本底座 × 债务比例</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" hidden="1" outlineLevel="5">
+    <row r="89" hidden="1" outlineLevel="3">
       <c r="A89" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　期初存量站投入</t>
+        <v>3</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　全周期资本底座（现值）</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>47.7533</v>
+        <v>3424.6274</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>47.7533</v>
+        <v>5307.0932</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>47.7533</v>
+        <v>8221.053599999999</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3226,29 +3230,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2026 年之前已建成站的站体与站内电池</t>
+          <t>初装 CAPEX ＋ 全周期电池更新净额（按届时价格、扣回收残值，折现）</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="3" t="inlineStr"/>
-    </row>
-    <row r="90" hidden="1" outlineLevel="5">
+      <c r="I89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" hidden="1" outlineLevel="4">
       <c r="A90" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　车端电池初装</t>
+        <v>4</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　初装 CAPEX 合计</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>1725.5363</v>
+        <v>2122.9569</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>3428.7641</v>
+        <v>4153.3457</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5826.3385</v>
+        <v>7002.9803</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3257,11 +3261,11 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Σ_年( 当年新增换电装车 GWh × 当年电池价格 )</t>
+          <t>期初存量站投入 ＋ Σ_年( 车端电池 ＋ 站内电池 ＋ 站体 )</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="3" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
     </row>
     <row r="91" hidden="1" outlineLevel="5">
       <c r="A91" s="2" t="n">
@@ -3269,17 +3273,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　站内周转电池初装</t>
+          <t xml:space="preserve">　　　　　期初存量站投入</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>102.8974</v>
+        <v>47.7533</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>203.2483</v>
+        <v>47.7533</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>344.4885</v>
+        <v>47.7533</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3292,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Σ_年( 当年新增站数 × 站内周转块数 × 单块电量 × 当年电池价格 )</t>
+          <t>2026 年之前已建成站的站体与站内电池</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -3300,17 +3304,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　站体初装</t>
+          <t xml:space="preserve">　　　　　车端电池初装</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>246.77</v>
+        <v>1725.5363</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>473.58</v>
+        <v>3428.7641</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>784.4</v>
+        <v>5826.3385</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3319,29 +3323,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Σ_年Σ_池( 当年新增站数 × 该站型单站站体造价 )</t>
+          <t>Σ_年( 当年新增换电装车 GWh × 当年电池价格 )</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="3" t="inlineStr"/>
     </row>
-    <row r="93" hidden="1" outlineLevel="4">
+    <row r="93" hidden="1" outlineLevel="5">
       <c r="A93" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　全周期更新净额（现值）</t>
+          <t xml:space="preserve">　　　　　站内周转电池初装</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>1424.1207</v>
+        <v>102.8974</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>2640.5097</v>
+        <v>203.2483</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>4473.8838</v>
+        <v>344.4885</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3350,193 +3354,193 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
+          <t>Σ_年( 当年新增站数 × 站内周转块数 × 单块电量 × 当年电池价格 )</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="3" t="inlineStr"/>
     </row>
-    <row r="94" hidden="1" outlineLevel="3">
+    <row r="94" hidden="1" outlineLevel="5">
       <c r="A94" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　站体初装</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>246.77</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>473.58</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>784.4</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Σ_年Σ_池( 当年新增站数 × 该站型单站站体造价 )</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95" hidden="1" outlineLevel="4">
+      <c r="A95" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　全周期更新净额（现值）</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1301.6705</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>1153.7475</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>1218.0733</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96" hidden="1" outlineLevel="3">
+      <c r="A96" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　项目债务比例</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
+      <c r="C96" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D96" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E96" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>finance.debt_ratio</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>债务比例 60%：经验假设（类固收项目可做到 1:1.5 杠杆）</t>
         </is>
       </c>
     </row>
-    <row r="95" outlineLevel="1">
-      <c r="A95" s="2" t="n">
+    <row r="97" outlineLevel="1">
+      <c r="A97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　体检：过不过线</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>1.1566</v>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>1.6347</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>2.0854</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="C97" s="2" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>1.5757</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>2.0363</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>见下</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96" outlineLevel="2">
-      <c r="A96" s="2" t="n">
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98" outlineLevel="2">
+      <c r="A98" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　　EBITDA 覆盖倍数</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>1.1566</v>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>1.6347</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>2.0854</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="C98" s="2" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1.5757</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>2.0363</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>可交付 EBITDA ÷ 资本回报要求 EBITDA</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97" hidden="1" outlineLevel="3">
-      <c r="A97" s="2" t="n">
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" hidden="1" outlineLevel="3">
+      <c r="A99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　可交付 EBITDA</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>505.1484</v>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>1371.1149</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>2957.5802</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="C99" s="2" t="n">
+        <v>420.7524</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1085.1073</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>2206.1232</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>同上（引用）</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="3" t="inlineStr"/>
-    </row>
-    <row r="98" hidden="1" outlineLevel="3">
-      <c r="A98" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　资本回报要求 EBITDA</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v>436.7401</v>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>838.7457000000001</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>1418.2539</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>由年资本要求反推的门槛 EBITDA</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="3" t="inlineStr"/>
-    </row>
-    <row r="99" outlineLevel="2">
-      <c r="A99" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　EBIT（账面）</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>207.8332</v>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>808.3769</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>2011.0271</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>EBITDA − 年折旧</t>
-        </is>
-      </c>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
     </row>
     <row r="100" hidden="1" outlineLevel="3">
       <c r="A100" s="2" t="n">
@@ -3544,17 +3548,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　EBITDA</t>
+          <t xml:space="preserve">　　　资本回报要求 EBITDA</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>505.1484</v>
+        <v>426.1024</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1371.1149</v>
+        <v>688.6297</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>2957.5802</v>
+        <v>1083.3997</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3563,29 +3567,29 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>由年资本要求反推的门槛 EBITDA</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="3" t="inlineStr"/>
     </row>
-    <row r="101" hidden="1" outlineLevel="3">
+    <row r="101" outlineLevel="2">
       <c r="A101" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　年折旧（成熟期）</t>
+          <t xml:space="preserve">　　EBIT（账面）</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>297.3152</v>
+        <v>147.0186</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>562.7380000000001</v>
+        <v>745.8217</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>946.553</v>
+        <v>1730.5409</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3594,29 +3598,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>电池折旧（按各池电池寿命） ＋ 站体折旧（站体总初装 ÷ 分析期）</t>
+          <t>EBITDA − 年折旧</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
     </row>
-    <row r="102" hidden="1" outlineLevel="4">
+    <row r="102" hidden="1" outlineLevel="3">
       <c r="A102" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　电池折旧</t>
+          <t xml:space="preserve">　　　EBITDA</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>278.4872</v>
+        <v>420.7524</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>528.7894</v>
+        <v>1085.1073</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>891.883</v>
+        <v>2206.1232</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3625,29 +3629,29 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>模型内按池 cohort 逐批计提：Σ_池( 池电池资本底座 ÷ 池电池寿命 )；此处由成熟期折旧扣站体折旧反解</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="3" t="inlineStr"/>
     </row>
-    <row r="103" hidden="1" outlineLevel="4">
+    <row r="103" hidden="1" outlineLevel="3">
       <c r="A103" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　站体总初装（含期初存量站）</t>
+          <t xml:space="preserve">　　　年折旧（成熟期）</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>282.42</v>
+        <v>273.7338</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>509.23</v>
+        <v>339.2856</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>820.05</v>
+        <v>475.5823</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3656,29 +3660,29 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Σ_年站体初装 ＋ 期初存量站数 × 该站型单站站体造价</t>
+          <t>电池折旧（按各池电池寿命） ＋ 站体折旧（站体总初装 ÷ 分析期）</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
     </row>
-    <row r="104" hidden="1" outlineLevel="5">
+    <row r="104" hidden="1" outlineLevel="4">
       <c r="A104" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　建设期站体初装</t>
+          <t xml:space="preserve">　　　　电池折旧</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>246.77</v>
+        <v>254.9058</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>473.58</v>
+        <v>305.337</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>784.4</v>
+        <v>420.9123</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3687,263 +3691,263 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Σ_年Σ_池( 当年新增站数 × 单站站体造价 )</t>
+          <t>模型内按池 cohort 逐批计提：Σ_池( 池电池资本底座 ÷ 池电池寿命 )；此处由成熟期折旧扣站体折旧反解</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="3" t="inlineStr"/>
     </row>
-    <row r="105" hidden="1" outlineLevel="5">
+    <row r="105" hidden="1" outlineLevel="4">
       <c r="A105" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　站体总初装（含期初存量站）</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>282.42</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>509.23</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>820.05</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Σ_年站体初装 ＋ 期初存量站数 × 该站型单站站体造价</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" hidden="1" outlineLevel="5">
+      <c r="A106" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　建设期站体初装</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>246.77</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>473.58</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>784.4</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Σ_年Σ_池( 当年新增站数 × 单站站体造价 )</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107" hidden="1" outlineLevel="5">
+      <c r="A107" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　期初存量站站体</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
+      <c r="C107" s="2" t="n">
         <v>35.65</v>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D107" s="2" t="n">
         <v>35.65</v>
       </c>
-      <c r="E105" s="2" t="n">
+      <c r="E107" s="2" t="n">
         <v>35.65</v>
       </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Σ_池( 期初存量站数 × 单站站体造价 )</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106" hidden="1" outlineLevel="4">
-      <c r="A106" s="2" t="n">
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108" hidden="1" outlineLevel="4">
+      <c r="A108" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　模型分析期</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
+      <c r="C108" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D106" s="2" t="n">
+      <c r="D108" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E106" s="2" t="n">
+      <c r="E108" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>finance.model_horizon_years</t>
         </is>
       </c>
-      <c r="I106" s="3" t="inlineStr">
+      <c r="I108" s="3" t="inlineStr">
         <is>
           <t>分析期 15 年（2026–2040）：与世联评估预测收益期 2025.12–2040.12 对齐（非 REITs 12 年存续期）</t>
         </is>
       </c>
     </row>
-    <row r="107" outlineLevel="2">
-      <c r="A107" s="2" t="n">
+    <row r="109" outlineLevel="2">
+      <c r="A109" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　　现金流支持的倍数（对照 拍的倍数）</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>7.9183</v>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>7.5252</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>7.3258</v>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="C109" s="2" t="n">
+        <v>8.055099999999999</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>7.3095</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>7.0953</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>DCF企业价值（与门槛同源口径）÷ EBITDA　——回答「你用 EBITDA 的倍数估值，那现金流本身支持几倍」</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108" hidden="1" outlineLevel="3">
-      <c r="A108" s="2" t="n">
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110" hidden="1" outlineLevel="3">
+      <c r="A110" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　DCF企业价值·与门槛同源</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>3999.9123</v>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>10317.9231</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>21666.5788</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="C110" s="2" t="n">
+        <v>3389.2125</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>7931.6144</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>15653.0274</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>成熟期 FCFF ÷ CRF（CRF 即设门槛 EBITDA 用的期望收益率年金因子，两者同源）</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109" hidden="1" outlineLevel="4">
-      <c r="A109" s="2" t="n">
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111" hidden="1" outlineLevel="4">
+      <c r="A111" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　成熟期 FCFF</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>453.1901</v>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>1169.0207</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>2454.8234</v>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="C111" s="2" t="n">
+        <v>383.9978</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>898.6519</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>1773.488</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>EBITDA ×(1−税率) ＋ 折旧 × 税率（重置已由 CRF 年金化内含）</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110" hidden="1" outlineLevel="4">
-      <c r="A110" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　资本回收系数 CRF</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>finance.capital_recovery_factor</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" hidden="1" outlineLevel="3">
-      <c r="A111" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　EBITDA</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v>505.1484</v>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>1371.1149</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>2957.5802</v>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="3" t="inlineStr"/>
     </row>
-    <row r="112" outlineLevel="2">
+    <row r="112" hidden="1" outlineLevel="4">
       <c r="A112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　战略溢价倍数（押注的大小）</t>
+        <v>4</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　资本回收系数 CRF</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2.2732</v>
+        <v>0.1133</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>2.392</v>
+        <v>0.1133</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>2.4571</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>倍</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>拍的 EV/EBITDA 倍数 ÷ 现金流支持的倍数　——这个数是判断不是计算，必须在报告正文里正面论证</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
+        <v>0.1133</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>finance.capital_recovery_factor</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
+        </is>
+      </c>
     </row>
     <row r="113" hidden="1" outlineLevel="3">
       <c r="A113" s="2" t="n">
@@ -3951,207 +3955,207 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　　EBITDA</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>420.7524</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>1085.1073</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>2206.1232</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114" outlineLevel="2">
+      <c r="A114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　战略溢价倍数（押注的大小）</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>2.2346</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>2.5369</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>倍</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>拍的 EV/EBITDA 倍数 ÷ 现金流支持的倍数　——这个数是判断不是计算，必须在报告正文里正面论证</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115" hidden="1" outlineLevel="3">
+      <c r="A115" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　　运营 EV/EBITDA 倍数</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
+      <c r="C115" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D113" s="2" t="n">
+      <c r="D115" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E115" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>finance.swap_ev_ebitda</t>
         </is>
       </c>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
         </is>
       </c>
     </row>
-    <row r="114" hidden="1" outlineLevel="3">
-      <c r="A114" s="2" t="n">
+    <row r="116" hidden="1" outlineLevel="3">
+      <c r="A116" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　现金流支持的倍数</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>7.9183</v>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>7.5252</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>7.3258</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="C116" s="2" t="n">
+        <v>8.055099999999999</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>7.3095</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>7.0953</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>同上（引用）</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115" outlineLevel="1">
-      <c r="A115" s="2" t="n">
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117" outlineLevel="1">
+      <c r="A117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　估值：这门生意最终值多少钱</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>3129.6557</v>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>8878.947899999999</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>19619.9527</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="C117" s="2" t="n">
+        <v>2522.5426</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>6815.9699</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>14203.372</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>见下——倍数法与DCF两套独立口径（DCF区分CRF捷径对照版 npv/catl_dcf、有限期账/基础账 npv_true/catl_dcf_true、永续账/开放上限npv_perpetual/catl_dcf_perpetual——两本账都不建模2030后规模增长（capex诊断.md§8.4已论证的既定假设），差异只在'停在2030规模不动'延续多久：15年还是永续，见第四轮§4.7），「押注」是倍数法与DCF基础账的结构性差值；debt_basis_drift、framework_ul_gap 只诊断、不参与本节点校验</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116" outlineLevel="2">
-      <c r="A116" s="2" t="n">
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118" outlineLevel="2">
+      <c r="A118" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　　项目NPV（DCF，CRF捷径EV，仅作对照）</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>94.66849999999999</v>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>2859.9913</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>9080.811100000001</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="C118" s="2" t="n">
+        <v>-372.6172</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>2189.8414</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>6793.7491</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>DCF企业价值(CRF年金捷径) ＋ 期末残值现值(target_year) − 估值资本PV(target_year)</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117" hidden="1" outlineLevel="3">
-      <c r="A117" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)·与门槛同源</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>3999.9123</v>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>10317.9231</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>21666.5788</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118" hidden="1" outlineLevel="3">
-      <c r="A118" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v>191.8274</v>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>373.9957</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>637.98</v>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
     </row>
-    <row r="119" hidden="1" outlineLevel="4">
+    <row r="119" hidden="1" outlineLevel="3">
       <c r="A119" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)·与门槛同源</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>143.6405</v>
+        <v>3389.2125</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>280.0482</v>
+        <v>7931.6144</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>477.7198</v>
+        <v>15653.0274</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4160,56 +4164,60 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="3" t="inlineStr"/>
     </row>
-    <row r="120" hidden="1" outlineLevel="4">
+    <row r="120" hidden="1" outlineLevel="3">
       <c r="A120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>194.3557</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>376.0029</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>611.6832000000001</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" hidden="1" outlineLevel="4">
+      <c r="A121" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121" hidden="1" outlineLevel="3">
-      <c r="A121" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>4097.0712</v>
+        <v>145.5337</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>7831.9275</v>
+        <v>281.5512</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>13223.7477</v>
+        <v>458.0287</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4218,11 +4226,11 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr"/>
     </row>
     <row r="122" hidden="1" outlineLevel="4">
       <c r="A122" s="2" t="n">
@@ -4230,137 +4238,133 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>3067.8891</v>
+        <v>1.3355</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>5864.5514</v>
+        <v>1.3355</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>9901.9493</v>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+        <v>1.3355</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="3" t="inlineStr"/>
     </row>
-    <row r="123" hidden="1" outlineLevel="4">
+    <row r="123" hidden="1" outlineLevel="3">
       <c r="A123" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>3956.1855</v>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>6117.7759</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>9470.961600000001</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124" hidden="1" outlineLevel="4">
+      <c r="A124" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>2962.3938</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>4580.9939</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>7091.861</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125" hidden="1" outlineLevel="4">
+      <c r="A125" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　移到target_year的复利因子</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
+      <c r="C125" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D125" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E125" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>(1+WACC)^(target_year−base_year)</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="3" t="inlineStr"/>
-    </row>
-    <row r="124" outlineLevel="2">
-      <c r="A124" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　CATL归属价值（DCF口径，CRF捷径EV，仅作对照）</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v>1169.2835</v>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>3283.6881</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>7247.1991</v>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>max(0, DCF企业价值(CRF捷径) ＋ 期末残值现值(target_year) − 稳态debt) × 持股比例</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125" hidden="1" outlineLevel="3">
-      <c r="A125" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v>3999.9123</v>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>10317.9231</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>21666.5788</v>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="3" t="inlineStr"/>
     </row>
-    <row r="126" hidden="1" outlineLevel="3">
+    <row r="126" outlineLevel="2">
       <c r="A126" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，CRF捷径EV，仅作对照）</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>191.8274</v>
+        <v>926.5524</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>373.9957</v>
+        <v>2326.244</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>637.98</v>
+        <v>4825.169</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4369,29 +4373,29 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>max(0, DCF企业价值(CRF捷径) ＋ 期末残值现值(target_year) − 稳态debt) × 持股比例</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
     </row>
-    <row r="127" hidden="1" outlineLevel="4">
+    <row r="127" hidden="1" outlineLevel="3">
       <c r="A127" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>143.6405</v>
+        <v>3389.2125</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>280.0482</v>
+        <v>7931.6144</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>477.7198</v>
+        <v>15653.0274</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4400,56 +4404,60 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="3" t="inlineStr"/>
     </row>
-    <row r="128" hidden="1" outlineLevel="4">
+    <row r="128" hidden="1" outlineLevel="3">
       <c r="A128" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>194.3557</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>376.0029</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>611.6832000000001</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129" hidden="1" outlineLevel="4">
+      <c r="A129" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="3" t="inlineStr"/>
-    </row>
-    <row r="129" hidden="1" outlineLevel="3">
-      <c r="A129" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>1268.5311</v>
+        <v>145.5337</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2482.6986</v>
+        <v>281.5512</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>4186.5611</v>
+        <v>458.0287</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4458,60 +4466,56 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="3" t="inlineStr"/>
     </row>
-    <row r="130" hidden="1" outlineLevel="3">
+    <row r="130" hidden="1" outlineLevel="4">
       <c r="A130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131" hidden="1" outlineLevel="3">
+      <c r="A131" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　CATL建站持股比例</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" outlineLevel="2">
-      <c r="A131" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　项目NPV（DCF，有限期账/基础账）</t>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>95.11920000000001</v>
+        <v>1267.1874</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2861.1538</v>
+        <v>2492.0074</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>9083.252200000001</v>
+        <v>4201.7882</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4520,11 +4524,11 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 估值资本PV(target_year，含真实更新排期)。【2026-09-05d】站体设备不设期末残值——永续账已把它按'每15年到期全额换新、不扣回收'处理，隐含'到期视为耗尽'，有限期账不能再给同一台设备一份残值（两套相反假设），且没有设备二手市场数据支撑折价比例</t>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
+      <c r="I131" s="3" t="inlineStr"/>
     </row>
     <row r="132" hidden="1" outlineLevel="3">
       <c r="A132" s="2" t="n">
@@ -4532,48 +4536,48 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>4000.363</v>
+        <v>0.4</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>10319.0855</v>
+        <v>0.4</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>21669.0199</v>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133" hidden="1" outlineLevel="3">
+        <v>0.4</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" outlineLevel="2">
       <c r="A133" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+          <t xml:space="preserve">　　项目NPV（DCF，有限期账/基础账）</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>191.8274</v>
+        <v>-372.2354</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>373.9957</v>
+        <v>2190.735</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>637.98</v>
+        <v>6795.5126</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4582,29 +4586,29 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 估值资本PV(target_year，含真实更新排期)。【2026-09-05d】站体设备不设期末残值——永续账已把它按'每15年到期全额换新、不扣回收'处理，隐含'到期视为耗尽'，有限期账不能再给同一台设备一份残值（两套相反假设），且没有设备二手市场数据支撑折价比例</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
     </row>
-    <row r="134" hidden="1" outlineLevel="4">
+    <row r="134" hidden="1" outlineLevel="3">
       <c r="A134" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>143.6405</v>
+        <v>3389.5944</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>280.0482</v>
+        <v>7932.5081</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>477.7198</v>
+        <v>15654.791</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4613,56 +4617,60 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" s="3" t="inlineStr"/>
     </row>
-    <row r="135" hidden="1" outlineLevel="4">
+    <row r="135" hidden="1" outlineLevel="3">
       <c r="A135" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>194.3557</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>376.0029</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>611.6832000000001</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136" hidden="1" outlineLevel="4">
+      <c r="A136" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="3" t="inlineStr"/>
-    </row>
-    <row r="136" hidden="1" outlineLevel="3">
-      <c r="A136" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>4097.0712</v>
+        <v>145.5337</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>7831.9275</v>
+        <v>281.5512</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>13223.7477</v>
+        <v>458.0287</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4671,11 +4679,11 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr"/>
     </row>
     <row r="137" hidden="1" outlineLevel="4">
       <c r="A137" s="2" t="n">
@@ -4683,137 +4691,133 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>3067.8891</v>
+        <v>1.3355</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>5864.5514</v>
+        <v>1.3355</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>9901.9493</v>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+        <v>1.3355</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="3" t="inlineStr"/>
     </row>
-    <row r="138" hidden="1" outlineLevel="4">
+    <row r="138" hidden="1" outlineLevel="3">
       <c r="A138" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>3956.1855</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>6117.7759</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>9470.961600000001</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139" hidden="1" outlineLevel="4">
+      <c r="A139" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>2962.3938</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>4580.9939</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>7091.861</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140" hidden="1" outlineLevel="4">
+      <c r="A140" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　移到target_year的复利因子</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n">
+      <c r="C140" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="D138" s="2" t="n">
+      <c r="D140" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="E138" s="2" t="n">
+      <c r="E140" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>(1+WACC)^(target_year−base_year)</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="3" t="inlineStr"/>
-    </row>
-    <row r="139" outlineLevel="2">
-      <c r="A139" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n">
-        <v>1169.4637</v>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>3284.1531</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>7248.1755</v>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140" hidden="1" outlineLevel="3">
-      <c r="A140" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>4000.363</v>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>10319.0855</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>21669.0199</v>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="3" t="inlineStr"/>
     </row>
-    <row r="141" hidden="1" outlineLevel="3">
+    <row r="141" outlineLevel="2">
       <c r="A141" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>191.8274</v>
+        <v>926.7051</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>373.9957</v>
+        <v>2326.6014</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>637.98</v>
+        <v>4825.8744</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4822,29 +4826,29 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
     </row>
-    <row r="142" hidden="1" outlineLevel="4">
+    <row r="142" hidden="1" outlineLevel="3">
       <c r="A142" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>143.6405</v>
+        <v>3389.5944</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>280.0482</v>
+        <v>7932.5081</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>477.7198</v>
+        <v>15654.791</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4853,56 +4857,60 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="3" t="inlineStr"/>
     </row>
-    <row r="143" hidden="1" outlineLevel="4">
+    <row r="143" hidden="1" outlineLevel="3">
       <c r="A143" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>194.3557</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>376.0029</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>611.6832000000001</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144" hidden="1" outlineLevel="4">
+      <c r="A144" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="3" t="inlineStr"/>
-    </row>
-    <row r="144" hidden="1" outlineLevel="3">
-      <c r="A144" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>1268.5311</v>
+        <v>145.5337</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2482.6986</v>
+        <v>281.5512</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>4186.5611</v>
+        <v>458.0287</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4911,60 +4919,56 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="3" t="inlineStr"/>
     </row>
-    <row r="145" hidden="1" outlineLevel="3">
+    <row r="145" hidden="1" outlineLevel="4">
       <c r="A145" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146" hidden="1" outlineLevel="3">
+      <c r="A146" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　CATL建站持股比例</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" outlineLevel="2">
-      <c r="A146" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　项目NPV（DCF，永续账/开放上限）</t>
+          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1100.6386</v>
+        <v>1267.1874</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>6108.3223</v>
+        <v>2492.0074</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>16777.4396</v>
+        <v>4201.7882</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -4973,60 +4977,60 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>DCF企业价值(永续) − 纯初装现值(target_year，剔除更换支出后的一次性投资，永续假设下不含期末残值——不会真的清算)</t>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="3" t="inlineStr"/>
     </row>
-    <row r="147" outlineLevel="2">
+    <row r="147" hidden="1" outlineLevel="3">
       <c r="A147" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　CATL归属价值（DCF口径，永续账/开放上限）</t>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>916.2222</v>
+        <v>0.4</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>3367.4412</v>
+        <v>0.4</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>8266.5362</v>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>max(0, DCF企业价值(永续) − 稳态debt) × 持股比例——与有限期账（基础账）共用同一个debt快照，差异只在EV怎么算（第一轮§1已论证debt该是资产负债表快照，跟期限假设无关）</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
     </row>
     <row r="148" outlineLevel="2">
       <c r="A148" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　CATL归属价值（倍数法口径）</t>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　项目NPV（DCF，永续账/开放上限）</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>3129.6557</v>
+        <v>390.736</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>8878.947899999999</v>
+        <v>4536.4382</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>19619.9527</v>
+        <v>11950.7145</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5035,29 +5039,29 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
+          <t>DCF企业价值(永续) − 纯初装现值(target_year，剔除更换支出后的一次性投资，永续假设下不含期末残值——不会真的清算)</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149" hidden="1" outlineLevel="3">
+      <c r="I148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149" outlineLevel="2">
       <c r="A149" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　EBITDA</t>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，永续账/开放上限）</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>505.1484</v>
+        <v>632.7987000000001</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1371.1149</v>
+        <v>2734.964</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>2957.5802</v>
+        <v>6329.7553</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5066,46 +5070,42 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>max(0, DCF企业价值(永续) − 稳态debt) × 持股比例——与有限期账（基础账）共用同一个debt快照，差异只在EV怎么算（第一轮§1已论证debt该是资产负债表快照，跟期限假设无关）</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="3" t="inlineStr"/>
     </row>
-    <row r="150" hidden="1" outlineLevel="3">
+    <row r="150" outlineLevel="2">
       <c r="A150" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　运营EV/EBITDA倍数</t>
+        <v>2</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　CATL归属价值（倍数法口径）</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>18</v>
+        <v>2522.5426</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>18</v>
+        <v>6815.9699</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>18</v>
+        <v>14203.372</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>finance.swap_ev_ebitda</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr"/>
     </row>
     <row r="151" hidden="1" outlineLevel="3">
       <c r="A151" s="2" t="n">
@@ -5113,17 +5113,17 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　稳态debt（同DCF线，2026-09-04起统一）</t>
+          <t xml:space="preserve">　　　EBITDA</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>1268.5311</v>
+        <v>420.7524</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2482.6986</v>
+        <v>1085.1073</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>4186.5611</v>
+        <v>2206.1232</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
@@ -5144,48 +5144,52 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　CATL建站持股比例</t>
+          <t xml:space="preserve">　　　运营EV/EBITDA倍数</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>0.4</v>
+        <v>18</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.4</v>
+        <v>18</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>finance.construction_ownership</t>
+          <t>finance.swap_ev_ebitda</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" outlineLevel="2">
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" hidden="1" outlineLevel="3">
       <c r="A153" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　押注部分（结构性差值）</t>
+        <v>3</v>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　稳态debt（同DCF线，2026-09-04起统一）</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1960.192</v>
+        <v>1267.1874</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>5594.7948</v>
+        <v>2492.0074</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>12371.7772</v>
+        <v>4201.7882</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5194,108 +5198,104 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>倍数法归属 − DCF归属(真实口径)　【2026-09-04：debt统一后，两条线现在真的在问同一个问题、用同一个debt，此前藏着的第三份「倍数法归属」（_dcf_cross_check内部现算、从未暴露的版本，见 DECISIONS「2026-09-03b」）已删除，三份合并为一份（T3已解决），此处直接用真正的倍数法headline数字相减】</t>
+          <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
-      <c r="I153" s="2" t="inlineStr"/>
+      <c r="I153" s="3" t="inlineStr"/>
     </row>
     <row r="154" hidden="1" outlineLevel="3">
       <c r="A154" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" outlineLevel="2">
+      <c r="A155" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　押注部分（结构性差值）</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>1595.8375</v>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>4489.3685</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>9377.497600000001</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>倍数法归属 − DCF归属(真实口径)　【2026-09-04：debt统一后，两条线现在真的在问同一个问题、用同一个debt，此前藏着的第三份「倍数法归属」（_dcf_cross_check内部现算、从未暴露的版本，见 DECISIONS「2026-09-03b」）已删除，三份合并为一份（T3已解决），此处直接用真正的倍数法headline数字相减】</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156" hidden="1" outlineLevel="3">
+      <c r="A156" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　CATL归属价值（倍数法口径）</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>3129.6557</v>
-      </c>
-      <c r="D154" s="2" t="n">
-        <v>8878.947899999999</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>19619.9527</v>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="C156" s="2" t="n">
+        <v>2522.5426</v>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>6815.9699</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>14203.372</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr"/>
-      <c r="I154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155" hidden="1" outlineLevel="4">
-      <c r="A155" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　EBITDA</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>505.1484</v>
-      </c>
-      <c r="D155" s="2" t="n">
-        <v>1371.1149</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>2957.5802</v>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" s="3" t="inlineStr"/>
-    </row>
-    <row r="156" hidden="1" outlineLevel="4">
-      <c r="A156" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　运营EV/EBITDA倍数</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D156" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E156" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>finance.swap_ev_ebitda</t>
-        </is>
-      </c>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
-        </is>
-      </c>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr"/>
     </row>
     <row r="157" hidden="1" outlineLevel="4">
       <c r="A157" s="2" t="n">
@@ -5303,17 +5303,17 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　稳态debt（同DCF线，2026-09-04起统一）</t>
+          <t xml:space="preserve">　　　　EBITDA</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>1268.5311</v>
+        <v>420.7524</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2482.6986</v>
+        <v>1085.1073</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>4186.5611</v>
+        <v>2206.1232</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
@@ -5334,48 +5334,52 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　CATL建站持股比例</t>
+          <t xml:space="preserve">　　　　运营EV/EBITDA倍数</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>0.4</v>
+        <v>18</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>0.4</v>
+        <v>18</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>finance.construction_ownership</t>
+          <t>finance.swap_ev_ebitda</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" hidden="1" outlineLevel="3">
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" hidden="1" outlineLevel="4">
       <c r="A159" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
+        <v>4</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　稳态debt（同DCF线，2026-09-04起统一）</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1169.4637</v>
+        <v>1267.1874</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>3284.1531</v>
+        <v>2492.0074</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>7248.1755</v>
+        <v>4201.7882</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5384,11 +5388,11 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
+          <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
+      <c r="I159" s="3" t="inlineStr"/>
     </row>
     <row r="160" hidden="1" outlineLevel="4">
       <c r="A160" s="2" t="n">
@@ -5396,48 +5400,48 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
+          <t xml:space="preserve">　　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>4000.363</v>
+        <v>0.4</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>10319.0855</v>
+        <v>0.4</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>21669.0199</v>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="3" t="inlineStr"/>
-    </row>
-    <row r="161" hidden="1" outlineLevel="4">
+        <v>0.4</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" hidden="1" outlineLevel="3">
       <c r="A161" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，移到target_year）</t>
+          <t xml:space="preserve">　　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>191.8274</v>
+        <v>926.7051</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>373.9957</v>
+        <v>2326.6014</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>637.98</v>
+        <v>4825.8744</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5446,29 +5450,29 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr"/>
     </row>
-    <row r="162" hidden="1" outlineLevel="5">
+    <row r="162" hidden="1" outlineLevel="4">
       <c r="A162" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>143.6405</v>
+        <v>3389.5944</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>280.0482</v>
+        <v>7932.5081</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>477.7198</v>
+        <v>15654.791</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5477,56 +5481,60 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="3" t="inlineStr"/>
     </row>
-    <row r="163" hidden="1" outlineLevel="5">
+    <row r="163" hidden="1" outlineLevel="4">
       <c r="A163" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>194.3557</v>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>376.0029</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>611.6832000000001</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164" hidden="1" outlineLevel="5">
+      <c r="A164" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　移到target_year的复利因子</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="D163" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="E163" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="3" t="inlineStr"/>
-    </row>
-    <row r="164" hidden="1" outlineLevel="4">
-      <c r="A164" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+          <t xml:space="preserve">　　　　　期末残值现值（税后，base_year）</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>1268.5311</v>
+        <v>145.5337</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2482.6986</v>
+        <v>281.5512</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>4186.5611</v>
+        <v>458.0287</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5535,100 +5543,158 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr"/>
       <c r="I164" s="3" t="inlineStr"/>
     </row>
-    <row r="165" hidden="1" outlineLevel="4">
+    <row r="165" hidden="1" outlineLevel="5">
       <c r="A165" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　移到target_year的复利因子</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166" hidden="1" outlineLevel="4">
+      <c r="A166" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　CATL建站持股比例</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D165" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E165" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" outlineLevel="2">
-      <c r="A166" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　稳态debt相对旧口径（门槛底座×债务比）改变了多少</t>
+          <t xml:space="preserve">　　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>-0.404</v>
+        <v>1267.1874</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-0.3909</v>
+        <v>2492.0074</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>-0.392</v>
-      </c>
-      <c r="F166" s="2" t="inlineStr"/>
+        <v>4201.7882</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>(新稳态debt − 旧门槛底座债务) ÷ 旧门槛底座债务——纯诊断：2026-09-04 起两条估值线已统一使用稳态debt，不再是「两条线口径分裂」（那个问题已解决），此节点只记录这次口径修正把debt改变了多少，见 DECISIONS「2026-09-03b」「2026-09-04」</t>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
       <c r="I166" s="3" t="inlineStr"/>
     </row>
-    <row r="167" outlineLevel="2">
+    <row r="167" hidden="1" outlineLevel="4">
       <c r="A167" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" outlineLevel="2">
+      <c r="A168" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B167" s="3" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　稳态debt相对旧口径（门槛底座×债务比）改变了多少</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>-0.3833</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>-0.2174</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>(新稳态debt − 旧门槛底座债务) ÷ 旧门槛底座债务——纯诊断：2026-09-04 起两条估值线已统一使用稳态debt，不再是「两条线口径分裂」（那个问题已解决），此节点只记录这次口径修正把debt改变了多少，见 DECISIONS「2026-09-03b」「2026-09-04」</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169" outlineLevel="2">
+      <c r="A169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　框架L(折现FCFE)相对框架U(EV−debt)的偏离</t>
         </is>
       </c>
-      <c r="C167" s="2" t="n">
-        <v>-0.7296</v>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>-0.6006</v>
-      </c>
-      <c r="E167" s="2" t="n">
-        <v>-0.5427</v>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="n">
+        <v>-0.7721</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>-0.4731</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>-0.4048</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>【T5，2026-09-04，纯诊断】(框架L股权价值 − 框架U股权价值) ÷ 框架U股权价值。框架L：Ke=[WACC−债务比×债务利率×(1−税率)]÷(1−债务比) 折现FCFE（FCFE=真实FCFF−税后利息，debt按steady_state_debt_yi固定不摊销、净新增借款=0，与forward_fcff/sustaining_capex同样的'稳态不变'假设）。两者不精确相等是预期内的：附录'情形C'证明U=L恒等式要求debt按'债务比×剩余项目价值'逐期摊销到0（value降、debt跟着降）；本模型debt是'target_year在役资产历史成本'快照，15年窗口内固定不变——这是两种不同的'稳定杠杆'定义，有限期+终值截断场景下不再代数等价。此gap量化这一口径差异的幅度，不参与上层校验、不代表程序错误</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" s="3" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1489.3794</v>
+        <v>1292.1725</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7558.9506</v>
+        <v>6230.5722</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17706.7884</v>
+        <v>11827.491</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1489.3794</v>
+        <v>1292.1725</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7558.9506</v>
+        <v>6230.5722</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17706.7884</v>
+        <v>11827.491</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2522.5426</v>
+        <v>2364.2034</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6815.9699</v>
+        <v>5485.408</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14203.372</v>
+        <v>8336.685600000001</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6306.3565</v>
+        <v>5910.5085</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17039.9247</v>
+        <v>13713.52</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35508.4301</v>
+        <v>20841.714</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7573.5439</v>
+        <v>7109.4783</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>19531.9321</v>
+        <v>16195.4727</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>39710.2183</v>
+        <v>24149.9753</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>420.7524</v>
+        <v>394.971</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1085.1073</v>
+        <v>899.7485</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2206.1232</v>
+        <v>1341.6653</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>496.6843</v>
+        <v>465.1016</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1225.4691</v>
+        <v>1039.8809</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2436.4983</v>
+        <v>1509.2723</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>108.9743</v>
+        <v>99.0311</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>246.6998</v>
+        <v>246.4259</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>486.0347</v>
+        <v>340.5234</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1252.578</v>
+        <v>1138.2885</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2372.1132</v>
+        <v>2369.4798</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3951.502</v>
+        <v>2768.4829</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2301600</v>
+        <v>2228800</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3960300</v>
+        <v>3956600</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6076400</v>
+        <v>5252100</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>194.3645</v>
+        <v>182.3993</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>213.919</v>
+        <v>213.8813</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>232.2511</v>
+        <v>188.2569</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>358.2212</v>
+        <v>338.8318</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>924.0543</v>
+        <v>738.8527</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1860.4708</v>
+        <v>1104.2501</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>(计费装机 − 乘用车池计费装机) × 重卡与城配月租 ＋ 乘用车池计费装机 × 乘用车月租</t>
+          <t>(计费装机 − 乘用车池计费装机) × 重卡与城配实付月租均价 ＋ 乘用车池计费装机 × 乘用车月租</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>313.6206</v>
+        <v>296.9631</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>620.9397</v>
+        <v>618.6168</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1053.7234</v>
+        <v>839.0767</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>301.9256</v>
+        <v>286.2014</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>599.0395</v>
+        <v>596.7635</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1017.4599</v>
+        <v>813.3866</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>11.695</v>
+        <v>10.7617</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>21.9002</v>
+        <v>21.8534</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36.2636</v>
+        <v>25.69</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>19.4916</v>
+        <v>17.9362</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>36.5003</v>
+        <v>36.4223</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>60.4393</v>
+        <v>42.8167</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1157,34 +1157,30 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　电池月租·重卡与城配</t>
+          <t xml:space="preserve">　　　　　　　　　电池月租·重卡与城配·实付均价</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>13.3</v>
+        <v>10.206</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>16</v>
+        <v>11.4039</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>元/kWh·月</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.battery_rent_rmb_kwh_month</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>电池租金 10 元/kWh·月（全市场可比综合口径：小车 8.8–9.7/大车 13–17 元加权， / rlut 重卡月租 4500–6000 元佐证"小车便宜大车贵"）</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>各池 max（保底 swap_business.battery_rent_rmb_kwh_month，超出价 swap_business.battery_rent_per_kwh_rmb × 每度容量月用电），按计费装机加权</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
     </row>
     <row r="24" hidden="1" outlineLevel="7">
       <c r="A24" s="2" t="n">
@@ -1262,13 +1258,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>25.1052</v>
+        <v>23.1018</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>47.0123</v>
+        <v>46.9119</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>77.8458</v>
+        <v>55.1479</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1293,13 +1289,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>19.4916</v>
+        <v>17.9362</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>36.5003</v>
+        <v>36.4223</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>60.4393</v>
+        <v>42.8167</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1425,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.3836</v>
+        <v>4.1368</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7.7027</v>
+        <v>7.6903</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12.1469</v>
+        <v>9.350899999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1456,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.3047</v>
+        <v>0.2788</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.5728</v>
+        <v>0.5715</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.6584</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1487,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2.0316</v>
+        <v>1.8588</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3.8184</v>
+        <v>3.8097</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6.3474</v>
+        <v>4.3893</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1518,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4.0789</v>
+        <v>3.858</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.1299</v>
+        <v>7.1189</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11.1948</v>
+        <v>8.692500000000001</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1549,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>75.9319</v>
+        <v>70.1306</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>140.3617</v>
+        <v>140.1324</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>230.3751</v>
+        <v>167.607</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1580,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>40.8449</v>
+        <v>37.1181</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>77.3515</v>
+        <v>77.26560000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>128.8533</v>
+        <v>90.2766</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1611,13 +1607,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1388.7278</v>
+        <v>1262.0155</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2629.9516</v>
+        <v>2627.032</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>4381.013</v>
+        <v>3069.405</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1642,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1252.578</v>
+        <v>1138.2885</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2372.1132</v>
+        <v>2369.4798</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3951.502</v>
+        <v>2768.4829</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1735,13 +1731,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1252.578</v>
+        <v>1138.2885</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2372.1132</v>
+        <v>2369.4798</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>3951.502</v>
+        <v>2768.4829</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1801,13 +1797,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13.032</v>
+        <v>12.4635</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>22.197</v>
+        <v>22.1685</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>34.083</v>
+        <v>27.642</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1832,13 +1828,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8688</v>
+        <v>8309</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14798</v>
+        <v>14779</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>22722</v>
+        <v>18428</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1898,13 +1894,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>11.0977</v>
+        <v>10.0789</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>21.1758</v>
+        <v>21.1247</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>35.5905</v>
+        <v>24.0482</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1929,13 +1925,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3622</v>
+        <v>3243</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7109</v>
+        <v>7090</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>12187</v>
+        <v>7893</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2092,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>4.2164</v>
+        <v>3.984</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.263199999999999</v>
+        <v>8.234</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>13.9493</v>
+        <v>11.0112</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2123,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.7927</v>
+        <v>3.5888</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.4994</v>
+        <v>7.4716</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>12.7192</v>
+        <v>10.1032</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2154,13 +2150,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.9482</v>
+        <v>0.8972</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.8748</v>
+        <v>1.8679</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3.1798</v>
+        <v>2.5258</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1267.1874</v>
+        <v>1198.9697</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2492.0074</v>
+        <v>2481.9527</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>4201.7882</v>
+        <v>3308.2613</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2282,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1033.1632</v>
+        <v>-1072.0309</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>742.9807</v>
+        <v>745.1641</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3503.4164</v>
+        <v>3490.8054</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2313,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-51.6582</v>
+        <v>-53.6015</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>37.149</v>
+        <v>37.2582</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>175.1708</v>
+        <v>174.5403</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2344,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-51.6582</v>
+        <v>-53.6015</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.4168</v>
+        <v>1.5179</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>69.1699</v>
+        <v>68.6444</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2375,13 +2371,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>45.1465</v>
+        <v>42.3086</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>65.2349</v>
+        <v>64.96210000000001</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>107.6624</v>
+        <v>86.93859999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2406,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-96.8047</v>
+        <v>-95.9101</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-63.8181</v>
+        <v>-63.4443</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-38.4925</v>
+        <v>-18.2942</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2440,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7322</v>
+        <v>35.7403</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>106.0009</v>
+        <v>105.8959</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2468,13 +2464,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2987.5013</v>
+        <v>2971.9543</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3573.2238</v>
+        <v>3574.0325</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4240.0377</v>
+        <v>4235.834</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2634,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.0839</v>
+        <v>0.0728</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.4257</v>
+        <v>0.3509</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.9972</v>
+        <v>0.6661</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2661,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1489.3794</v>
+        <v>1292.1725</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>7558.9506</v>
+        <v>6230.5722</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>17706.7884</v>
+        <v>11827.491</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2719,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>547.9404</v>
+        <v>524.481</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>849.1349</v>
+        <v>870.4582</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1315.3686</v>
+        <v>1047.6609</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2750,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>547.9404</v>
+        <v>524.481</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>849.1349</v>
+        <v>870.4582</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1315.3686</v>
+        <v>1047.6609</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2781,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3424.6274</v>
+        <v>3278.0065</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5307.0932</v>
+        <v>5440.364</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>8221.053599999999</v>
+        <v>6547.8805</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2874,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>3424.6274</v>
+        <v>3278.0065</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5307.0932</v>
+        <v>5440.364</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>8221.053599999999</v>
+        <v>6547.8805</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2905,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2122.9569</v>
+        <v>2005.9211</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4153.3457</v>
+        <v>4136.5878</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>7002.9803</v>
+        <v>5513.7689</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2967,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1725.5363</v>
+        <v>1636.6274</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3428.7641</v>
+        <v>3413.4164</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>5826.3385</v>
+        <v>4655.8003</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2998,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>102.8974</v>
+        <v>93.7204</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>203.2483</v>
+        <v>202.7882</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>344.4885</v>
+        <v>240.5153</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3029,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>246.77</v>
+        <v>227.82</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>473.58</v>
+        <v>472.63</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>784.4</v>
+        <v>569.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3060,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>1301.6705</v>
+        <v>1272.0855</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1153.7475</v>
+        <v>1303.7762</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1218.0733</v>
+        <v>1034.1116</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3091,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>388.0103</v>
+        <v>371.3981</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>601.2936999999999</v>
+        <v>616.3932</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>931.4453999999999</v>
+        <v>741.8749</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3122,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>3424.6274</v>
+        <v>3278.0065</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>5307.0932</v>
+        <v>5440.364</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>8221.053599999999</v>
+        <v>6547.8805</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3184,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>2054.7764</v>
+        <v>1966.8039</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3184.2559</v>
+        <v>3264.2184</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4932.6321</v>
+        <v>3928.7283</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3215,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>3424.6274</v>
+        <v>3278.0065</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5307.0932</v>
+        <v>5440.364</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>8221.053599999999</v>
+        <v>6547.8805</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3246,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2122.9569</v>
+        <v>2005.9211</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4153.3457</v>
+        <v>4136.5878</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>7002.9803</v>
+        <v>5513.7689</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1725.5363</v>
+        <v>1636.6274</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3428.7641</v>
+        <v>3413.4164</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>5826.3385</v>
+        <v>4655.8003</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>102.8974</v>
+        <v>93.7204</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>203.2483</v>
+        <v>202.7882</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>344.4885</v>
+        <v>240.5153</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3370,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>246.77</v>
+        <v>227.82</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>473.58</v>
+        <v>472.63</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>784.4</v>
+        <v>569.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3401,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1301.6705</v>
+        <v>1272.0855</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1153.7475</v>
+        <v>1303.7762</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1218.0733</v>
+        <v>1034.1116</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3463,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.5757</v>
+        <v>1.2925</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>2.0363</v>
+        <v>1.5654</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3490,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.5757</v>
+        <v>1.2925</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>2.0363</v>
+        <v>1.5654</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3521,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>420.7524</v>
+        <v>394.971</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1085.1073</v>
+        <v>899.7485</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>2206.1232</v>
+        <v>1341.6653</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3552,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>426.1024</v>
+        <v>405.0992</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>688.6297</v>
+        <v>696.1181</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1083.3997</v>
+        <v>857.0952</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3583,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>147.0186</v>
+        <v>124.676</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>745.8217</v>
+        <v>522.5297</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1730.5409</v>
+        <v>945.4514</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3614,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>420.7524</v>
+        <v>394.971</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1085.1073</v>
+        <v>899.7485</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>2206.1232</v>
+        <v>1341.6653</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3645,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>273.7338</v>
+        <v>270.295</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>339.2856</v>
+        <v>377.2187</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>475.5823</v>
+        <v>396.2139</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3676,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>254.9058</v>
+        <v>252.7303</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>305.337</v>
+        <v>343.3334</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>420.9123</v>
+        <v>355.8572</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3707,13 +3703,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>282.42</v>
+        <v>263.47</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>509.23</v>
+        <v>508.28</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>820.05</v>
+        <v>605.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3738,13 +3734,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>246.77</v>
+        <v>227.82</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>473.58</v>
+        <v>472.63</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>784.4</v>
+        <v>569.7</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3835,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>8.055099999999999</v>
+        <v>8.1296</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3095</v>
+        <v>7.5447</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.0953</v>
+        <v>7.2712</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3866,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>3389.2125</v>
+        <v>3210.9622</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>7931.6144</v>
+        <v>6788.3146</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>15653.0274</v>
+        <v>9755.5378</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3897,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>383.9978</v>
+        <v>363.802</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>898.6519</v>
+        <v>769.116</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1773.488</v>
+        <v>1105.3024</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3959,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>420.7524</v>
+        <v>394.971</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1085.1073</v>
+        <v>899.7485</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>2206.1232</v>
+        <v>1341.6653</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.2346</v>
+        <v>2.2141</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4625</v>
+        <v>2.3858</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.5369</v>
+        <v>2.4755</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4056,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>8.055099999999999</v>
+        <v>8.1296</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3095</v>
+        <v>7.5447</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.0953</v>
+        <v>7.2712</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4087,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2522.5426</v>
+        <v>2364.2034</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>6815.9699</v>
+        <v>5485.408</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14203.372</v>
+        <v>8336.685600000001</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4118,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>-372.6172</v>
+        <v>-394.1614</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>2189.8414</v>
+        <v>879.2382</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>6793.7491</v>
+        <v>2694.1149</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4149,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>3389.2125</v>
+        <v>3210.9622</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>7931.6144</v>
+        <v>6788.3146</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>15653.0274</v>
+        <v>9755.5378</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4180,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>194.3557</v>
+        <v>180.9963</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>376.0029</v>
+        <v>362.9393</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>611.6832000000001</v>
+        <v>478.2888</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4211,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>145.5337</v>
+        <v>135.5301</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>281.5512</v>
+        <v>271.7691</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>458.0287</v>
+        <v>358.1429</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4269,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>3956.1855</v>
+        <v>3786.1199</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>6117.7759</v>
+        <v>6272.0158</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>9470.961600000001</v>
+        <v>7539.7117</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4300,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2962.3938</v>
+        <v>2835.0486</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4580.9939</v>
+        <v>4696.4887</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>7091.861</v>
+        <v>5645.7401</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4358,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>926.5524</v>
+        <v>877.1955</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2326.244</v>
+        <v>1867.7205</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>4825.169</v>
+        <v>2770.2261</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4389,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>3389.2125</v>
+        <v>3210.9622</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>7931.6144</v>
+        <v>6788.3146</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>15653.0274</v>
+        <v>9755.5378</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4420,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>194.3557</v>
+        <v>180.9963</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>376.0029</v>
+        <v>362.9393</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>611.6832000000001</v>
+        <v>478.2888</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4451,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>145.5337</v>
+        <v>135.5301</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>281.5512</v>
+        <v>271.7691</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>458.0287</v>
+        <v>358.1429</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4509,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1267.1874</v>
+        <v>1198.9697</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2492.0074</v>
+        <v>2481.9527</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>4201.7882</v>
+        <v>3308.2613</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4571,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>-372.2354</v>
+        <v>-393.7996</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2190.735</v>
+        <v>880.003</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>6795.5126</v>
+        <v>2695.2141</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4602,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>3389.5944</v>
+        <v>3211.324</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>7932.5081</v>
+        <v>6789.0795</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>15654.791</v>
+        <v>9756.637000000001</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>194.3557</v>
+        <v>180.9963</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>376.0029</v>
+        <v>362.9393</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>611.6832000000001</v>
+        <v>478.2888</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4664,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>145.5337</v>
+        <v>135.5301</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>281.5512</v>
+        <v>271.7691</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>458.0287</v>
+        <v>358.1429</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4722,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>3956.1855</v>
+        <v>3786.1199</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>6117.7759</v>
+        <v>6272.0158</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>9470.961600000001</v>
+        <v>7539.7117</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4753,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2962.3938</v>
+        <v>2835.0486</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4580.9939</v>
+        <v>4696.4887</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>7091.861</v>
+        <v>5645.7401</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4811,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>926.7051</v>
+        <v>877.3402</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2326.6014</v>
+        <v>1868.0264</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>4825.8744</v>
+        <v>2770.6658</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4842,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>3389.5944</v>
+        <v>3211.324</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>7932.5081</v>
+        <v>6789.0795</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>15654.791</v>
+        <v>9756.637000000001</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4873,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>194.3557</v>
+        <v>180.9963</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>376.0029</v>
+        <v>362.9393</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>611.6832000000001</v>
+        <v>478.2888</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4904,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>145.5337</v>
+        <v>135.5301</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>281.5512</v>
+        <v>271.7691</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>458.0287</v>
+        <v>358.1429</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4962,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1267.1874</v>
+        <v>1198.9697</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2492.0074</v>
+        <v>2481.9527</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>4201.7882</v>
+        <v>3308.2613</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5024,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>390.736</v>
+        <v>277.6981</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>4536.4382</v>
+        <v>2487.458</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>11950.7145</v>
+        <v>5340.3409</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5055,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>632.7987000000001</v>
+        <v>560.6713</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2734.964</v>
+        <v>1911.7001</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>6329.7553</v>
+        <v>3354.7364</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5086,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2522.5426</v>
+        <v>2364.2034</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>6815.9699</v>
+        <v>5485.408</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>14203.372</v>
+        <v>8336.685600000001</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5117,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>420.7524</v>
+        <v>394.971</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1085.1073</v>
+        <v>899.7485</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>2206.1232</v>
+        <v>1341.6653</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5183,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1267.1874</v>
+        <v>1198.9697</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2492.0074</v>
+        <v>2481.9527</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>4201.7882</v>
+        <v>3308.2613</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5245,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1595.8375</v>
+        <v>1486.8632</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>4489.3685</v>
+        <v>3617.3816</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>9377.497600000001</v>
+        <v>5566.0198</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5276,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2522.5426</v>
+        <v>2364.2034</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>6815.9699</v>
+        <v>5485.408</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>14203.372</v>
+        <v>8336.685600000001</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5307,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>420.7524</v>
+        <v>394.971</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1085.1073</v>
+        <v>899.7485</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>2206.1232</v>
+        <v>1341.6653</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5373,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1267.1874</v>
+        <v>1198.9697</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2492.0074</v>
+        <v>2481.9527</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>4201.7882</v>
+        <v>3308.2613</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5435,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>926.7051</v>
+        <v>877.3402</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2326.6014</v>
+        <v>1868.0264</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>4825.8744</v>
+        <v>2770.6658</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5466,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>3389.5944</v>
+        <v>3211.324</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>7932.5081</v>
+        <v>6789.0795</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>15654.791</v>
+        <v>9756.637000000001</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5497,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>194.3557</v>
+        <v>180.9963</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>376.0029</v>
+        <v>362.9393</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>611.6832000000001</v>
+        <v>478.2888</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5528,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>145.5337</v>
+        <v>135.5301</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>281.5512</v>
+        <v>271.7691</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>458.0287</v>
+        <v>358.1429</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5586,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1267.1874</v>
+        <v>1198.9697</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2492.0074</v>
+        <v>2481.9527</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>4201.7882</v>
+        <v>3308.2613</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5648,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.3833</v>
+        <v>-0.3904</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.2174</v>
+        <v>-0.2396</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1482</v>
+        <v>-0.1579</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5675,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.7721</v>
+        <v>-0.8026</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4731</v>
+        <v>-0.5516</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4048</v>
+        <v>-0.4389</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1292.1725</v>
+        <v>1431.5173</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6230.5722</v>
+        <v>6331.0499</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11827.491</v>
+        <v>11959.9295</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1292.1725</v>
+        <v>1431.5173</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6230.5722</v>
+        <v>6331.0499</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11827.491</v>
+        <v>11959.9295</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2364.2034</v>
+        <v>2461.2714</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5485.408</v>
+        <v>5588.0691</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8336.685600000001</v>
+        <v>8473.843000000001</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5910.5085</v>
+        <v>6153.1785</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13713.52</v>
+        <v>13970.1728</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20841.714</v>
+        <v>21184.6076</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7109.4783</v>
+        <v>7402.6259</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>16195.4727</v>
+        <v>16497.5801</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>24149.9753</v>
+        <v>24534.739</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>394.971</v>
+        <v>411.257</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>899.7485</v>
+        <v>916.5322</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1341.6653</v>
+        <v>1363.0411</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>465.1016</v>
+        <v>488.2773</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1039.8809</v>
+        <v>1065.1348</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1509.2723</v>
+        <v>1543.3458</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>99.0311</v>
+        <v>109.4117</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>246.4259</v>
+        <v>261.8973</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>340.5234</v>
+        <v>367.7552</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1138.2885</v>
+        <v>1257.6054</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2369.4798</v>
+        <v>2518.243</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2768.4829</v>
+        <v>2989.88</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2228800</v>
+        <v>2353400</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3956600</v>
+        <v>4112900</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5252100</v>
+        <v>5497700</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>182.3993</v>
+        <v>190.8493</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>213.8813</v>
+        <v>218.6711</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>188.2569</v>
+        <v>194.2293</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>338.8318</v>
+        <v>347.7738</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>738.8527</v>
+        <v>743.8025</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1104.2501</v>
+        <v>1103.4923</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>296.9631</v>
+        <v>304.6452</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>618.6168</v>
+        <v>622.8973</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>839.0767</v>
+        <v>837.7906</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>286.2014</v>
+        <v>292.2853</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>596.7635</v>
+        <v>599.0395</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>813.3866</v>
+        <v>808.9487</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>10.7617</v>
+        <v>12.3598</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>21.8534</v>
+        <v>23.8578</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>25.69</v>
+        <v>28.8419</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>17.9362</v>
+        <v>20.5997</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>36.4223</v>
+        <v>39.7629</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>42.8167</v>
+        <v>48.0698</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10.206</v>
+        <v>10.2011</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.4039</v>
+        <v>11.4173</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>23.1018</v>
+        <v>26.5324</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>46.9119</v>
+        <v>51.2147</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>55.1479</v>
+        <v>61.9139</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>17.9362</v>
+        <v>20.5997</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>36.4223</v>
+        <v>39.7629</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>42.8167</v>
+        <v>48.0698</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.1368</v>
+        <v>4.5594</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7.6903</v>
+        <v>8.2204</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9.350899999999999</v>
+        <v>10.1844</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.2788</v>
+        <v>0.3232</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.5715</v>
+        <v>0.6271</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.6584</v>
+        <v>0.746</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1.8588</v>
+        <v>2.1547</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3.8097</v>
+        <v>4.1809</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>4.3893</v>
+        <v>4.973</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3.858</v>
+        <v>4.2362</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.1189</v>
+        <v>7.5932</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>8.692500000000001</v>
+        <v>9.4384</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>70.1306</v>
+        <v>77.02030000000001</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>140.1324</v>
+        <v>148.6026</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>167.607</v>
+        <v>180.3048</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>37.1181</v>
+        <v>41.0089</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>77.26560000000001</v>
+        <v>82.11660000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>90.2766</v>
+        <v>97.4961</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1262.0155</v>
+        <v>1394.3017</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2627.032</v>
+        <v>2791.9651</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3069.405</v>
+        <v>3314.867</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1138.2885</v>
+        <v>1257.6054</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2369.4798</v>
+        <v>2518.243</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2768.4829</v>
+        <v>2989.88</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1138.2885</v>
+        <v>1257.6054</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2369.4798</v>
+        <v>2518.243</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2768.4829</v>
+        <v>2989.88</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>12.4635</v>
+        <v>13.437</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>22.1685</v>
+        <v>23.3895</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>27.642</v>
+        <v>29.562</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8309</v>
+        <v>8958</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14779</v>
+        <v>15593</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>18428</v>
+        <v>19708</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>10.0789</v>
+        <v>11.8234</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>21.1247</v>
+        <v>23.3128</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24.0482</v>
+        <v>27.4888</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3243</v>
+        <v>3892</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7090</v>
+        <v>7904</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>7893</v>
+        <v>9173</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>3.984</v>
+        <v>4.1359</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.234</v>
+        <v>8.3613</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>11.0112</v>
+        <v>11.1168</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.5888</v>
+        <v>3.692</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.4716</v>
+        <v>7.5379</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10.1032</v>
+        <v>10.1128</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.8972</v>
+        <v>0.923</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.8679</v>
+        <v>1.8845</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2.5258</v>
+        <v>2.5282</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1198.9697</v>
+        <v>1249.4474</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2481.9527</v>
+        <v>2527.4073</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3308.2613</v>
+        <v>3350.1314</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1072.0309</v>
+        <v>-1029.7541</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>745.1641</v>
+        <v>742.9807</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3490.8054</v>
+        <v>3486.0865</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-53.6015</v>
+        <v>-51.4877</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>37.2582</v>
+        <v>37.149</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>174.5403</v>
+        <v>174.3043</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-53.6015</v>
+        <v>-51.4877</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.5179</v>
+        <v>1.4168</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.6444</v>
+        <v>68.4478</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>42.3086</v>
+        <v>45.2215</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>64.96210000000001</v>
+        <v>65.2349</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>86.93859999999999</v>
+        <v>86.4936</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-95.9101</v>
+        <v>-96.7093</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-63.4443</v>
+        <v>-63.8181</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-18.2942</v>
+        <v>-18.0458</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7403</v>
+        <v>35.7322</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>105.8959</v>
+        <v>105.8565</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2971.9543</v>
+        <v>2988.865</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3574.0325</v>
+        <v>3573.2238</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4235.834</v>
+        <v>4234.261</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.0728</v>
+        <v>0.0806</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3509</v>
+        <v>0.3565</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.6661</v>
+        <v>0.6735</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1292.1725</v>
+        <v>1431.5173</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>6230.5722</v>
+        <v>6331.0499</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11827.491</v>
+        <v>11959.9295</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>524.481</v>
+        <v>566.2012</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>870.4582</v>
+        <v>887.6063</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1047.6609</v>
+        <v>1058.6432</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>524.481</v>
+        <v>566.2012</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>870.4582</v>
+        <v>887.6063</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1047.6609</v>
+        <v>1058.6432</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3278.0065</v>
+        <v>3538.7573</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5440.364</v>
+        <v>5547.5391</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>6547.8805</v>
+        <v>6616.5203</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>3278.0065</v>
+        <v>3538.7573</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5440.364</v>
+        <v>5547.5391</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6547.8805</v>
+        <v>6616.5203</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2005.9211</v>
+        <v>2089.8544</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4136.5878</v>
+        <v>4212.3455</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5513.7689</v>
+        <v>5583.5524</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1636.6274</v>
+        <v>1672.3961</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3413.4164</v>
+        <v>3428.7641</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4655.8003</v>
+        <v>4630.5904</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>93.7204</v>
+        <v>109.435</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>202.7882</v>
+        <v>222.4981</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>240.5153</v>
+        <v>271.5087</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>227.82</v>
+        <v>260.27</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>472.63</v>
+        <v>513.33</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>569.7</v>
+        <v>633.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>1272.0855</v>
+        <v>1448.9028</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1303.7762</v>
+        <v>1335.1937</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1034.1116</v>
+        <v>1032.9679</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>371.3981</v>
+        <v>400.9412</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>616.3932</v>
+        <v>628.5362</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>741.8749</v>
+        <v>749.6518</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>3278.0065</v>
+        <v>3538.7573</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>5440.364</v>
+        <v>5547.5391</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6547.8805</v>
+        <v>6616.5203</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1966.8039</v>
+        <v>2123.2544</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3264.2184</v>
+        <v>3328.5235</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>3928.7283</v>
+        <v>3969.9122</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>3278.0065</v>
+        <v>3538.7573</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5440.364</v>
+        <v>5547.5391</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6547.8805</v>
+        <v>6616.5203</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2005.9211</v>
+        <v>2089.8544</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4136.5878</v>
+        <v>4212.3455</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5513.7689</v>
+        <v>5583.5524</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1636.6274</v>
+        <v>1672.3961</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3413.4164</v>
+        <v>3428.7641</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4655.8003</v>
+        <v>4630.5904</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>93.7204</v>
+        <v>109.435</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>202.7882</v>
+        <v>222.4981</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>240.5153</v>
+        <v>271.5087</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>227.82</v>
+        <v>260.27</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>472.63</v>
+        <v>513.33</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>569.7</v>
+        <v>633.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1272.0855</v>
+        <v>1448.9028</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1303.7762</v>
+        <v>1335.1937</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1034.1116</v>
+        <v>1032.9679</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>0.975</v>
+        <v>0.9448</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.2925</v>
+        <v>1.295</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.5654</v>
+        <v>1.5737</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>0.975</v>
+        <v>0.9448</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.2925</v>
+        <v>1.295</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.5654</v>
+        <v>1.5737</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>394.971</v>
+        <v>411.257</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>899.7485</v>
+        <v>916.5322</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1341.6653</v>
+        <v>1363.0411</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>405.0992</v>
+        <v>435.2934</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>696.1181</v>
+        <v>707.7643</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>857.0952</v>
+        <v>866.1547</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>124.676</v>
+        <v>113.3723</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>522.5297</v>
+        <v>525.6805000000001</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>945.4514</v>
+        <v>962.8982</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>394.971</v>
+        <v>411.257</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>899.7485</v>
+        <v>916.5322</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1341.6653</v>
+        <v>1363.0411</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>270.295</v>
+        <v>297.8847</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>377.2187</v>
+        <v>390.8517</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>396.2139</v>
+        <v>400.1428</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>252.7303</v>
+        <v>278.1567</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>343.3334</v>
+        <v>354.2531</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>355.8572</v>
+        <v>355.5195</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>263.47</v>
+        <v>295.92</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>508.28</v>
+        <v>548.98</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>605.35</v>
+        <v>669.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>227.82</v>
+        <v>260.27</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>472.63</v>
+        <v>513.33</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>569.7</v>
+        <v>633.7</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>8.1296</v>
+        <v>8.2178</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.5447</v>
+        <v>7.5606</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2712</v>
+        <v>7.2674</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>3210.9622</v>
+        <v>3379.6462</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6788.3146</v>
+        <v>6929.4978</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>9755.5378</v>
+        <v>9905.706099999999</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>363.802</v>
+        <v>382.9139</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>769.116</v>
+        <v>785.1121000000001</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1105.3024</v>
+        <v>1122.3165</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>394.971</v>
+        <v>411.257</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>899.7485</v>
+        <v>916.5322</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1341.6653</v>
+        <v>1363.0411</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.2141</v>
+        <v>2.1904</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.3858</v>
+        <v>2.3808</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4755</v>
+        <v>2.4768</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>8.1296</v>
+        <v>8.2178</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.5447</v>
+        <v>7.5606</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2712</v>
+        <v>7.2674</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2364.2034</v>
+        <v>2461.2714</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5485.408</v>
+        <v>5588.0691</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>8336.685600000001</v>
+        <v>8473.843000000001</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>-394.1614</v>
+        <v>-519.7944</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>879.2382</v>
+        <v>895.1365</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>2694.1149</v>
+        <v>2761.1862</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>3210.9622</v>
+        <v>3379.6462</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6788.3146</v>
+        <v>6929.4978</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>9755.5378</v>
+        <v>9905.706099999999</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>180.9963</v>
+        <v>189.4929</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>362.9393</v>
+        <v>364.0312</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>478.2888</v>
+        <v>479.2067</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>135.5301</v>
+        <v>141.8924</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>271.7691</v>
+        <v>272.5868</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>358.1429</v>
+        <v>358.8302</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>3786.1199</v>
+        <v>4088.9335</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>6272.0158</v>
+        <v>6398.3925</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>7539.7117</v>
+        <v>7623.7267</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2835.0486</v>
+        <v>3061.7956</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4696.4887</v>
+        <v>4791.1197</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5645.7401</v>
+        <v>5708.6506</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>877.1955</v>
+        <v>927.8767</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1867.7205</v>
+        <v>1906.4487</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>2770.2261</v>
+        <v>2813.9126</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>3210.9622</v>
+        <v>3379.6462</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>6788.3146</v>
+        <v>6929.4978</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9755.5378</v>
+        <v>9905.706099999999</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>180.9963</v>
+        <v>189.4929</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>362.9393</v>
+        <v>364.0312</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>478.2888</v>
+        <v>479.2067</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>135.5301</v>
+        <v>141.8924</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>271.7691</v>
+        <v>272.5868</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>358.1429</v>
+        <v>358.8302</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1198.9697</v>
+        <v>1249.4474</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2481.9527</v>
+        <v>2527.4073</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3308.2613</v>
+        <v>3350.1314</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>-393.7996</v>
+        <v>-519.4136</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>880.003</v>
+        <v>895.9173</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>2695.2141</v>
+        <v>2762.3022</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>3211.324</v>
+        <v>3380.0269</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>6789.0795</v>
+        <v>6930.2786</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>9756.637000000001</v>
+        <v>9906.822200000001</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>180.9963</v>
+        <v>189.4929</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>362.9393</v>
+        <v>364.0312</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>478.2888</v>
+        <v>479.2067</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>135.5301</v>
+        <v>141.8924</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>271.7691</v>
+        <v>272.5868</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>358.1429</v>
+        <v>358.8302</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>3786.1199</v>
+        <v>4088.9335</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>6272.0158</v>
+        <v>6398.3925</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>7539.7117</v>
+        <v>7623.7267</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2835.0486</v>
+        <v>3061.7956</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4696.4887</v>
+        <v>4791.1197</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>5645.7401</v>
+        <v>5708.6506</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>877.3402</v>
+        <v>928.029</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1868.0264</v>
+        <v>1906.761</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>2770.6658</v>
+        <v>2814.359</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>3211.324</v>
+        <v>3380.0269</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>6789.0795</v>
+        <v>6930.2786</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>9756.637000000001</v>
+        <v>9906.822200000001</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>180.9963</v>
+        <v>189.4929</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>362.9393</v>
+        <v>364.0312</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>478.2888</v>
+        <v>479.2067</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>135.5301</v>
+        <v>141.8924</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>271.7691</v>
+        <v>272.5868</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>358.1429</v>
+        <v>358.8302</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1198.9697</v>
+        <v>1249.4474</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2481.9527</v>
+        <v>2527.4073</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>3308.2613</v>
+        <v>3350.1314</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>277.6981</v>
+        <v>193.7845</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2487.458</v>
+        <v>2497.2738</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>5340.3409</v>
+        <v>5453.44</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>560.6713</v>
+        <v>546.3601</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1911.7001</v>
+        <v>1933.4324</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>3354.7364</v>
+        <v>3417.2454</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2364.2034</v>
+        <v>2461.2714</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5485.408</v>
+        <v>5588.0691</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>8336.685600000001</v>
+        <v>8473.843000000001</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>394.971</v>
+        <v>411.257</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>899.7485</v>
+        <v>916.5322</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1341.6653</v>
+        <v>1363.0411</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1198.9697</v>
+        <v>1249.4474</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2481.9527</v>
+        <v>2527.4073</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>3308.2613</v>
+        <v>3350.1314</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1486.8632</v>
+        <v>1533.2424</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3617.3816</v>
+        <v>3681.3081</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>5566.0198</v>
+        <v>5659.4841</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2364.2034</v>
+        <v>2461.2714</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>5485.408</v>
+        <v>5588.0691</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>8336.685600000001</v>
+        <v>8473.843000000001</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>394.971</v>
+        <v>411.257</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>899.7485</v>
+        <v>916.5322</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1341.6653</v>
+        <v>1363.0411</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1198.9697</v>
+        <v>1249.4474</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2481.9527</v>
+        <v>2527.4073</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3308.2613</v>
+        <v>3350.1314</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>877.3402</v>
+        <v>928.029</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1868.0264</v>
+        <v>1906.761</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>2770.6658</v>
+        <v>2814.359</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>3211.324</v>
+        <v>3380.0269</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>6789.0795</v>
+        <v>6930.2786</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>9756.637000000001</v>
+        <v>9906.822200000001</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>180.9963</v>
+        <v>189.4929</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>362.9393</v>
+        <v>364.0312</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>478.2888</v>
+        <v>479.2067</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>135.5301</v>
+        <v>141.8924</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>271.7691</v>
+        <v>272.5868</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>358.1429</v>
+        <v>358.8302</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1198.9697</v>
+        <v>1249.4474</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2481.9527</v>
+        <v>2527.4073</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>3308.2613</v>
+        <v>3350.1314</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.3904</v>
+        <v>-0.4115</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.2396</v>
+        <v>-0.2407</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1579</v>
+        <v>-0.1561</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.8026</v>
+        <v>-0.8383</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.5516</v>
+        <v>-0.5595</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4389</v>
+        <v>-0.4377</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -539,7 +539,7 @@
         <v>6331.0499</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11959.9295</v>
+        <v>12316.3231</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         <v>6331.0499</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11959.9295</v>
+        <v>12316.3231</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         <v>5588.0691</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8473.843000000001</v>
+        <v>8829.6626</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         <v>13970.1728</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>21184.6076</v>
+        <v>22074.1564</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>16497.5801</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>24534.739</v>
+        <v>25531.7467</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         <v>916.5322</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1363.0411</v>
+        <v>1418.4304</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>1065.1348</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1543.3458</v>
+        <v>1605.6404</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>261.8973</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>367.7552</v>
+        <v>383.5149</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>2518.243</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2989.88</v>
+        <v>3118.0069</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>4112900</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5497700</v>
+        <v>5588300</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>218.6711</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>194.2293</v>
+        <v>199.2688</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>743.8025</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1103.4923</v>
+        <v>1147.2309</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>622.8973</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>837.7906</v>
+        <v>864.1105</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>599.0395</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>808.9487</v>
+        <v>834.1088</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>23.8578</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>28.8419</v>
+        <v>30.0017</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>39.7629</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>48.0698</v>
+        <v>50.0028</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>10.2011</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.4173</v>
+        <v>11.5159</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>51.2147</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>61.9139</v>
+        <v>64.4036</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>39.7629</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>48.0698</v>
+        <v>50.0028</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>8.2204</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>10.1844</v>
+        <v>10.4911</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>0.6271</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.746</v>
+        <v>0.7782</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>4.1809</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>4.973</v>
+        <v>5.1878</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>7.5932</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.4384</v>
+        <v>9.712899999999999</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>148.6026</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>180.3048</v>
+        <v>187.21</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>82.11660000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>97.4961</v>
+        <v>101.6741</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>2791.9651</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3314.867</v>
+        <v>3456.9207</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>2518.243</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2989.88</v>
+        <v>3118.0069</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>2518.243</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2989.88</v>
+        <v>3118.0069</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>23.3895</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>29.562</v>
+        <v>30.2685</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>15593</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>19708</v>
+        <v>20179</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>23.3128</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>27.4888</v>
+        <v>28.7549</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>7904</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9173</v>
+        <v>9644</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>8.3613</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>11.1168</v>
+        <v>11.4719</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>7.5379</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10.1128</v>
+        <v>10.4325</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>1.8845</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2.5282</v>
+        <v>2.6081</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>2527.4073</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3350.1314</v>
+        <v>3457.5903</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>742.9807</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3486.0865</v>
+        <v>3486.6605</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>37.149</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>174.3043</v>
+        <v>174.333</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>1.4168</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.4478</v>
+        <v>68.4717</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>65.2349</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>86.4936</v>
+        <v>89.0453</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>-63.8181</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-18.0458</v>
+        <v>-20.5735</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>35.7322</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>105.8565</v>
+        <v>105.8613</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>3573.2238</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4234.261</v>
+        <v>4234.4524</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>0.3565</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.6735</v>
+        <v>0.6936</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
         <v>6331.0499</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11959.9295</v>
+        <v>12316.3231</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>887.6063</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1058.6432</v>
+        <v>1093.4632</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>887.6063</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1058.6432</v>
+        <v>1093.4632</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>5547.5391</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>6616.5203</v>
+        <v>6834.1453</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>5547.5391</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6616.5203</v>
+        <v>6834.1453</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>4212.3455</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5583.5524</v>
+        <v>5762.6504</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>3428.7641</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4630.5904</v>
+        <v>4774.7338</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>222.4981</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>271.5087</v>
+        <v>282.9134</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>513.33</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>633.7</v>
+        <v>657.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>1335.1937</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1032.9679</v>
+        <v>1071.4949</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>628.5362</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>749.6518</v>
+        <v>774.3087</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>5547.5391</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6616.5203</v>
+        <v>6834.1453</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>3328.5235</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>3969.9122</v>
+        <v>4100.4872</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>5547.5391</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6616.5203</v>
+        <v>6834.1453</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>4212.3455</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5583.5524</v>
+        <v>5762.6504</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>3428.7641</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4630.5904</v>
+        <v>4774.7338</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>222.4981</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>271.5087</v>
+        <v>282.9134</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>513.33</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>633.7</v>
+        <v>657.25</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>1335.1937</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1032.9679</v>
+        <v>1071.4949</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>1.295</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.5737</v>
+        <v>1.5864</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
         <v>1.295</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.5737</v>
+        <v>1.5864</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>916.5322</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1363.0411</v>
+        <v>1418.4304</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>707.7643</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>866.1547</v>
+        <v>894.0924</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>525.6805000000001</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>962.8982</v>
+        <v>1003.4729</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>916.5322</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1363.0411</v>
+        <v>1418.4304</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>390.8517</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>400.1428</v>
+        <v>414.9574</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>354.2531</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>355.5195</v>
+        <v>368.7641</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>548.98</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>669.35</v>
+        <v>692.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>513.33</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>633.7</v>
+        <v>657.25</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>7.5606</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2674</v>
+        <v>7.2651</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>6929.4978</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>9905.706099999999</v>
+        <v>10305.0498</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>785.1121000000001</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1122.3165</v>
+        <v>1167.5621</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>916.5322</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1363.0411</v>
+        <v>1418.4304</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>2.3808</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4768</v>
+        <v>2.4776</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>7.5606</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2674</v>
+        <v>7.2651</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>5588.0691</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>8473.843000000001</v>
+        <v>8829.6626</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>895.1365</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>2761.1862</v>
+        <v>2924.0654</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>6929.4978</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>9905.706099999999</v>
+        <v>10305.0498</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>364.0312</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>479.2067</v>
+        <v>493.8349</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>272.5868</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>358.8302</v>
+        <v>369.7838</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>6398.3925</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>7623.7267</v>
+        <v>7874.8193</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>4791.1197</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5708.6506</v>
+        <v>5896.6689</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>1906.4487</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>2813.9126</v>
+        <v>2936.5178</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>6929.4978</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9905.706099999999</v>
+        <v>10305.0498</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>364.0312</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>479.2067</v>
+        <v>493.8349</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>272.5868</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>358.8302</v>
+        <v>369.7838</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>2527.4073</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3350.1314</v>
+        <v>3457.5903</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>895.9173</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>2762.3022</v>
+        <v>2925.2264</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>6930.2786</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>9906.822200000001</v>
+        <v>10306.2108</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>364.0312</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>479.2067</v>
+        <v>493.8349</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>272.5868</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>358.8302</v>
+        <v>369.7838</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>6398.3925</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>7623.7267</v>
+        <v>7874.8193</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>4791.1197</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>5708.6506</v>
+        <v>5896.6689</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>1906.761</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>2814.359</v>
+        <v>2936.9822</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>6930.2786</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>9906.822200000001</v>
+        <v>10306.2108</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>364.0312</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>479.2067</v>
+        <v>493.8349</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>272.5868</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>358.8302</v>
+        <v>369.7838</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>2527.4073</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>3350.1314</v>
+        <v>3457.5903</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>2497.2738</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>5453.44</v>
+        <v>5734.2122</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>1933.4324</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>3417.2454</v>
+        <v>3569.2737</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>5588.0691</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>8473.843000000001</v>
+        <v>8829.6626</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>916.5322</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1363.0411</v>
+        <v>1418.4304</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>2527.4073</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>3350.1314</v>
+        <v>3457.5903</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>3681.3081</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>5659.4841</v>
+        <v>5892.6804</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>5588.0691</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>8473.843000000001</v>
+        <v>8829.6626</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>916.5322</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1363.0411</v>
+        <v>1418.4304</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>2527.4073</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3350.1314</v>
+        <v>3457.5903</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>1906.761</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>2814.359</v>
+        <v>2936.9822</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>6930.2786</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>9906.822200000001</v>
+        <v>10306.2108</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>364.0312</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>479.2067</v>
+        <v>493.8349</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>272.5868</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>358.8302</v>
+        <v>369.7838</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>2527.4073</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>3350.1314</v>
+        <v>3457.5903</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>-0.2407</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1561</v>
+        <v>-0.1568</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5677,7 +5677,7 @@
         <v>-0.5595</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4377</v>
+        <v>-0.4384</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1431.5173</v>
+        <v>1169.7093</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>6331.0499</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12316.3231</v>
+        <v>12544.9718</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1431.5173</v>
+        <v>1169.7093</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>6331.0499</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12316.3231</v>
+        <v>12544.9718</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2461.2714</v>
+        <v>2445.3719</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>5588.0691</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8829.6626</v>
+        <v>9060.348900000001</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6153.1785</v>
+        <v>6113.4297</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>13970.1728</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22074.1564</v>
+        <v>22650.8723</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7402.6259</v>
+        <v>7360.4888</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>16497.5801</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>25531.7467</v>
+        <v>25985.0091</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>411.257</v>
+        <v>408.916</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>916.5322</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1418.4304</v>
+        <v>1443.6116</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>488.2773</v>
+        <v>485.497</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>1065.1348</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1605.6404</v>
+        <v>1622.9173</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>109.4117</v>
+        <v>108.6994</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>261.8973</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>383.5149</v>
+        <v>454.5067</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1257.6054</v>
+        <v>1249.418</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2518.243</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3118.0069</v>
+        <v>2970.6323</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2353400</v>
+        <v>2347700</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>4112900</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5588300</v>
+        <v>5485700</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>190.8493</v>
+        <v>190.0672</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>218.6711</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>199.2688</v>
+        <v>193.401</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>347.7738</v>
+        <v>345.884</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>743.8025</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1147.2309</v>
+        <v>1096.6862</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>304.6452</v>
+        <v>303.0216</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>622.8973</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>864.1105</v>
+        <v>834.0170000000001</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>292.2853</v>
+        <v>290.7357</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>599.0395</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>834.1088</v>
+        <v>805.3302</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>12.3598</v>
+        <v>12.286</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>23.8578</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>30.0017</v>
+        <v>28.6868</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>20.5997</v>
+        <v>20.4766</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>39.7629</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>50.0028</v>
+        <v>47.8113</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>10.2011</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.5159</v>
+        <v>11.3953</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>26.5324</v>
+        <v>26.3739</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>51.2147</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>64.4036</v>
+        <v>61.5809</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20.5997</v>
+        <v>20.4766</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>39.7629</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>50.0028</v>
+        <v>47.8113</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.5594</v>
+        <v>4.5399</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>8.2204</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>10.4911</v>
+        <v>10.1433</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.3232</v>
+        <v>0.3212</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.6271</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.7782</v>
+        <v>0.7416</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2.1547</v>
+        <v>2.141</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>4.1809</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>5.1878</v>
+        <v>4.9443</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4.2362</v>
+        <v>4.2187</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>7.5932</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.712899999999999</v>
+        <v>9.4017</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>77.02030000000001</v>
+        <v>76.581</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>148.6026</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>187.21</v>
+        <v>179.3056</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>41.0089</v>
+        <v>40.7419</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>82.11660000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>101.6741</v>
+        <v>96.86839999999999</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1394.3017</v>
+        <v>1385.2243</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2791.9651</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3456.9207</v>
+        <v>3293.5271</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1257.6054</v>
+        <v>1249.418</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>2518.243</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3118.0069</v>
+        <v>2970.6323</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1257.6054</v>
+        <v>1249.418</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>2518.243</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>3118.0069</v>
+        <v>2970.6323</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13.437</v>
+        <v>13.392</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>23.3895</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>30.2685</v>
+        <v>29.4675</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8958</v>
+        <v>8928</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>15593</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>20179</v>
+        <v>19645</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>11.8234</v>
+        <v>11.7428</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>23.3128</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>28.7549</v>
+        <v>27.3195</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3892</v>
+        <v>3862</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>7904</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9644</v>
+        <v>9110</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>4.1359</v>
+        <v>4.1139</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>8.3613</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>11.4719</v>
+        <v>11.0664</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.692</v>
+        <v>3.6723</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>7.5379</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10.4325</v>
+        <v>10.0671</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.923</v>
+        <v>0.9181</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>1.8845</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2.6081</v>
+        <v>2.5168</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1249.4474</v>
+        <v>1247.0591</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>2527.4073</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3457.5903</v>
+        <v>3334.1368</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1029.7541</v>
+        <v>-1275.6625</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>742.9807</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3486.6605</v>
+        <v>3484.6229</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-51.4877</v>
+        <v>-63.7831</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>37.149</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>174.333</v>
+        <v>174.2311</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-51.4877</v>
+        <v>-63.7831</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>1.4168</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.4717</v>
+        <v>68.38679999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>45.2215</v>
+        <v>32.7902</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>65.2349</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>89.0453</v>
+        <v>86.1048</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-96.7093</v>
+        <v>-96.5733</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>-63.8181</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-20.5735</v>
+        <v>-17.718</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>35.7322</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>105.8613</v>
+        <v>105.8443</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2988.865</v>
+        <v>2890.5016</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>3573.2238</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4234.4524</v>
+        <v>4233.7732</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.0806</v>
+        <v>0.0659</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.3565</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.6936</v>
+        <v>0.7065</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1431.5173</v>
+        <v>1169.7093</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>6331.0499</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>12316.3231</v>
+        <v>12544.9718</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>566.2012</v>
+        <v>431.9389</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>887.6063</v>
+        <v>803.3567</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1093.4632</v>
+        <v>1043.2696</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>566.2012</v>
+        <v>431.9389</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>887.6063</v>
+        <v>803.3567</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1093.4632</v>
+        <v>1043.2696</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3538.7573</v>
+        <v>2699.6182</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5547.5391</v>
+        <v>5020.9791</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>6834.1453</v>
+        <v>6520.4348</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>3538.7573</v>
+        <v>2699.6182</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5547.5391</v>
+        <v>5020.9791</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6834.1453</v>
+        <v>6520.4348</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2089.8544</v>
+        <v>2078.4318</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>4212.3455</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5762.6504</v>
+        <v>5556.8947</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1672.3961</v>
+        <v>1663.1999</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>3428.7641</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4774.7338</v>
+        <v>4608.6081</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>109.435</v>
+        <v>108.7086</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>222.4981</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>282.9134</v>
+        <v>269.9833</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>260.27</v>
+        <v>258.77</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>513.33</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>657.25</v>
+        <v>630.55</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>1448.9028</v>
+        <v>621.1864</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1335.1937</v>
+        <v>808.6337</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1071.4949</v>
+        <v>963.5401000000001</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>400.9412</v>
+        <v>305.8667</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>628.5362</v>
+        <v>568.8769</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>774.3087</v>
+        <v>738.7653</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>3538.7573</v>
+        <v>2699.6182</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>5547.5391</v>
+        <v>5020.9791</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6834.1453</v>
+        <v>6520.4348</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>2123.2544</v>
+        <v>1619.7709</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3328.5235</v>
+        <v>3012.5875</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4100.4872</v>
+        <v>3912.2609</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>3538.7573</v>
+        <v>2699.6182</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5547.5391</v>
+        <v>5020.9791</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6834.1453</v>
+        <v>6520.4348</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2089.8544</v>
+        <v>2078.4318</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>4212.3455</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5762.6504</v>
+        <v>5556.8947</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1672.3961</v>
+        <v>1663.1999</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>3428.7641</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4774.7338</v>
+        <v>4608.6081</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>109.435</v>
+        <v>108.7086</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>222.4981</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>282.9134</v>
+        <v>269.9833</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>260.27</v>
+        <v>258.77</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>513.33</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>657.25</v>
+        <v>630.55</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1448.9028</v>
+        <v>621.1864</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1335.1937</v>
+        <v>808.6337</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1071.4949</v>
+        <v>963.5401000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>0.9448</v>
+        <v>1.1852</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.295</v>
+        <v>1.4026</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.5864</v>
+        <v>1.6801</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>0.9448</v>
+        <v>1.1852</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.295</v>
+        <v>1.4026</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.5864</v>
+        <v>1.6801</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>411.257</v>
+        <v>408.916</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>916.5322</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1418.4304</v>
+        <v>1443.6116</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>435.2934</v>
+        <v>345.0248</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>707.7643</v>
+        <v>653.4588</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>894.0924</v>
+        <v>859.2378</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>113.3723</v>
+        <v>220.5233</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>525.6805000000001</v>
+        <v>601.4007</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1003.4729</v>
+        <v>1066.2641</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>411.257</v>
+        <v>408.916</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>916.5322</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1418.4304</v>
+        <v>1443.6116</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>297.8847</v>
+        <v>188.3927</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>390.8517</v>
+        <v>315.1315</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>414.9574</v>
+        <v>377.3475</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>278.1567</v>
+        <v>168.7647</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>354.2531</v>
+        <v>278.5328</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>368.7641</v>
+        <v>332.9342</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>295.92</v>
+        <v>294.42</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>548.98</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>692.9</v>
+        <v>666.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>260.27</v>
+        <v>258.77</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>513.33</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>657.25</v>
+        <v>630.55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>8.2178</v>
+        <v>7.6362</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.5606</v>
+        <v>7.3783</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2651</v>
+        <v>7.1964</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>3379.6462</v>
+        <v>3122.5526</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6929.4978</v>
+        <v>6762.4187</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>10305.0498</v>
+        <v>10388.7519</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>382.9139</v>
+        <v>353.7852</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>785.1121000000001</v>
+        <v>766.182</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1167.5621</v>
+        <v>1177.0456</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>411.257</v>
+        <v>408.916</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>916.5322</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1418.4304</v>
+        <v>1443.6116</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.1904</v>
+        <v>2.3572</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.3808</v>
+        <v>2.4396</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4776</v>
+        <v>2.5013</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>8.2178</v>
+        <v>7.6362</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.5606</v>
+        <v>7.3783</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2651</v>
+        <v>7.1964</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2461.2714</v>
+        <v>2445.3719</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>5588.0691</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>8829.6626</v>
+        <v>9060.348900000001</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>-519.7944</v>
+        <v>176.0332</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>895.1365</v>
+        <v>1325.6399</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>2924.0654</v>
+        <v>3359.9798</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>3379.6462</v>
+        <v>3122.5526</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6929.4978</v>
+        <v>6762.4187</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>10305.0498</v>
+        <v>10388.7519</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>189.4929</v>
+        <v>176.4696</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>364.0312</v>
+        <v>353.4383</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>493.8349</v>
+        <v>483.6233</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>141.8924</v>
+        <v>132.1406</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>272.5868</v>
+        <v>264.6548</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>369.7838</v>
+        <v>362.1374</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>4088.9335</v>
+        <v>3122.9891</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>6398.3925</v>
+        <v>5790.2172</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>7874.8193</v>
+        <v>7512.3954</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>3061.7956</v>
+        <v>2338.4959</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4791.1197</v>
+        <v>4335.7177</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5896.6689</v>
+        <v>5625.2857</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>927.8767</v>
+        <v>820.7853</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1906.4487</v>
+        <v>1835.3799</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>2936.5178</v>
+        <v>3015.2954</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>3379.6462</v>
+        <v>3122.5526</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>6929.4978</v>
+        <v>6762.4187</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>10305.0498</v>
+        <v>10388.7519</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>189.4929</v>
+        <v>176.4696</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>364.0312</v>
+        <v>353.4383</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>493.8349</v>
+        <v>483.6233</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>141.8924</v>
+        <v>132.1406</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>272.5868</v>
+        <v>264.6548</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>369.7838</v>
+        <v>362.1374</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1249.4474</v>
+        <v>1247.0591</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>2527.4073</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3457.5903</v>
+        <v>3334.1368</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>-519.4136</v>
+        <v>176.385</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>895.9173</v>
+        <v>1326.4018</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>2925.2264</v>
+        <v>3361.1502</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>3380.0269</v>
+        <v>3122.9044</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>6930.2786</v>
+        <v>6763.1806</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>10306.2108</v>
+        <v>10389.9223</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>189.4929</v>
+        <v>176.4696</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>364.0312</v>
+        <v>353.4383</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>493.8349</v>
+        <v>483.6233</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>141.8924</v>
+        <v>132.1406</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>272.5868</v>
+        <v>264.6548</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>369.7838</v>
+        <v>362.1374</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>4088.9335</v>
+        <v>3122.9891</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>6398.3925</v>
+        <v>5790.2172</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>7874.8193</v>
+        <v>7512.3954</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>3061.7956</v>
+        <v>2338.4959</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4791.1197</v>
+        <v>4335.7177</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>5896.6689</v>
+        <v>5625.2857</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>928.029</v>
+        <v>820.926</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1906.761</v>
+        <v>1835.6847</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>2936.9822</v>
+        <v>3015.7635</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>3380.0269</v>
+        <v>3122.9044</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>6930.2786</v>
+        <v>6763.1806</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>10306.2108</v>
+        <v>10389.9223</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>189.4929</v>
+        <v>176.4696</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>364.0312</v>
+        <v>353.4383</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>493.8349</v>
+        <v>483.6233</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>141.8924</v>
+        <v>132.1406</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>272.5868</v>
+        <v>264.6548</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>369.7838</v>
+        <v>362.1374</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1249.4474</v>
+        <v>1247.0591</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>2527.4073</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>3457.5903</v>
+        <v>3334.1368</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>193.7845</v>
+        <v>814.2439000000001</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2497.2738</v>
+        <v>2918.1381</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>5734.2122</v>
+        <v>6411.6191</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>546.3601</v>
+        <v>790.2237</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1933.4324</v>
+        <v>2101.7781</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>3569.2737</v>
+        <v>3794.614</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2461.2714</v>
+        <v>2445.3719</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>5588.0691</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>8829.6626</v>
+        <v>9060.348900000001</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>411.257</v>
+        <v>408.916</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>916.5322</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1418.4304</v>
+        <v>1443.6116</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1249.4474</v>
+        <v>1247.0591</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>2527.4073</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>3457.5903</v>
+        <v>3334.1368</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1533.2424</v>
+        <v>1624.4459</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3681.3081</v>
+        <v>3752.3845</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>5892.6804</v>
+        <v>6044.5854</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2461.2714</v>
+        <v>2445.3719</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>5588.0691</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>8829.6626</v>
+        <v>9060.348900000001</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>411.257</v>
+        <v>408.916</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>916.5322</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1418.4304</v>
+        <v>1443.6116</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1249.4474</v>
+        <v>1247.0591</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>2527.4073</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3457.5903</v>
+        <v>3334.1368</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>928.029</v>
+        <v>820.926</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1906.761</v>
+        <v>1835.6847</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>2936.9822</v>
+        <v>3015.7635</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>3380.0269</v>
+        <v>3122.9044</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>6930.2786</v>
+        <v>6763.1806</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>10306.2108</v>
+        <v>10389.9223</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>189.4929</v>
+        <v>176.4696</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>364.0312</v>
+        <v>353.4383</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>493.8349</v>
+        <v>483.6233</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>141.8924</v>
+        <v>132.1406</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>272.5868</v>
+        <v>264.6548</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>369.7838</v>
+        <v>362.1374</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1249.4474</v>
+        <v>1247.0591</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>2527.4073</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>3457.5903</v>
+        <v>3334.1368</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.4115</v>
+        <v>-0.2301</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.2407</v>
+        <v>-0.1611</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1568</v>
+        <v>-0.1478</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.8383</v>
+        <v>-0.5767</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.5595</v>
+        <v>-0.4671</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4384</v>
+        <v>-0.4158</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -536,10 +536,10 @@
         <v>1169.7093</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6331.0499</v>
+        <v>6098.5133</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12544.9718</v>
+        <v>12538.5832</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -567,10 +567,10 @@
         <v>1169.7093</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6331.0499</v>
+        <v>6098.5133</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12544.9718</v>
+        <v>12538.5832</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -598,10 +598,10 @@
         <v>2445.3719</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5588.0691</v>
+        <v>5359.9666</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9060.348900000001</v>
+        <v>9050.855799999999</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
         <v>6113.4297</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13970.1728</v>
+        <v>13399.9164</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22650.8723</v>
+        <v>22627.1396</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
         <v>7360.4888</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>16497.5801</v>
+        <v>15826.8403</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>25985.0091</v>
+        <v>26148.7149</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -691,10 +691,10 @@
         <v>408.916</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>916.5322</v>
+        <v>879.2689</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1443.6116</v>
+        <v>1452.7064</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         <v>485.497</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1065.1348</v>
+        <v>1021.307</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1622.9173</v>
+        <v>1643.8845</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -753,10 +753,10 @@
         <v>108.6994</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>261.8973</v>
+        <v>249.1248</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>454.5067</v>
+        <v>392.5725</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         <v>1249.418</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2518.243</v>
+        <v>2395.4308</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2970.6323</v>
+        <v>3191.6464</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         <v>2347700</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4112900</v>
+        <v>4027400</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5485700</v>
+        <v>5639100</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -846,10 +846,10 @@
         <v>190.0672</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>218.6711</v>
+        <v>212.4227</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>193.401</v>
+        <v>202.1375</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
         <v>345.884</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>743.8025</v>
+        <v>715.3892</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1096.6862</v>
+        <v>1174.844</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         <v>303.0216</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>622.8973</v>
+        <v>598.6683</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>834.0170000000001</v>
+        <v>880.1385</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         <v>290.7357</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>599.0395</v>
+        <v>575.9063</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>805.3302</v>
+        <v>849.4843</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
         <v>12.286</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>23.8578</v>
+        <v>22.762</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>28.6868</v>
+        <v>30.6542</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
         <v>20.4766</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>39.7629</v>
+        <v>37.9367</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>47.8113</v>
+        <v>51.0904</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10.2011</v>
+        <v>10.2232</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.3953</v>
+        <v>11.5844</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         <v>26.3739</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>51.2147</v>
+        <v>48.8624</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>61.5809</v>
+        <v>65.8044</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         <v>20.4766</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>39.7629</v>
+        <v>37.9367</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>47.8113</v>
+        <v>51.0904</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         <v>4.5399</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8.2204</v>
+        <v>7.9306</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>10.1433</v>
+        <v>10.6636</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         <v>0.3212</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.6271</v>
+        <v>0.5967</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.7416</v>
+        <v>0.7963</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         <v>2.141</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4.1809</v>
+        <v>3.978</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>4.9443</v>
+        <v>5.3086</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
         <v>4.2187</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.5932</v>
+        <v>7.3339</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.4017</v>
+        <v>9.8673</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         <v>76.581</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>148.6026</v>
+        <v>142.0381</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>179.3056</v>
+        <v>191.1781</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         <v>40.7419</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>82.11660000000001</v>
+        <v>78.11190000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>96.86839999999999</v>
+        <v>104.0754</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1610,10 +1610,10 @@
         <v>1385.2243</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2791.9651</v>
+        <v>2655.8037</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3293.5271</v>
+        <v>3538.5644</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         <v>1249.418</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2518.243</v>
+        <v>2395.4308</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2970.6323</v>
+        <v>3191.6464</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
         <v>1249.418</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2518.243</v>
+        <v>2395.4308</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2970.6323</v>
+        <v>3191.6464</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         <v>13.392</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>23.3895</v>
+        <v>22.722</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>29.4675</v>
+        <v>30.666</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         <v>8928</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15593</v>
+        <v>15148</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>19645</v>
+        <v>20444</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         <v>11.7428</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>23.3128</v>
+        <v>22.1166</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>27.3195</v>
+        <v>29.4672</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         <v>3862</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7904</v>
+        <v>7459</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9110</v>
+        <v>9909</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         <v>4.1139</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.3613</v>
+        <v>8.0334</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>11.0664</v>
+        <v>11.686</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>3.6723</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.5379</v>
+        <v>7.2433</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10.0671</v>
+        <v>10.6268</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>0.9181</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.8845</v>
+        <v>1.8108</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2.5168</v>
+        <v>2.6567</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         <v>1247.0591</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2426.9238</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3334.1368</v>
+        <v>3521.5753</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         <v>-1275.6625</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>742.9807</v>
+        <v>738.5467</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3484.6229</v>
+        <v>3487.7273</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         <v>-63.7831</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>37.149</v>
+        <v>36.9273</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>174.2311</v>
+        <v>174.3864</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         <v>-63.7831</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.4168</v>
+        <v>1.2115</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.38679999999999</v>
+        <v>68.5162</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
         <v>32.7902</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>65.2349</v>
+        <v>62.8551</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>86.1048</v>
+        <v>90.5848</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
         <v>-96.5733</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-63.8181</v>
+        <v>-61.6435</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-17.718</v>
+        <v>-22.0687</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7322</v>
+        <v>35.7158</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>105.8443</v>
+        <v>105.8702</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
         <v>2890.5016</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3573.2238</v>
+        <v>3571.5816</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4233.7732</v>
+        <v>4234.808</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
         <v>0.0659</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3565</v>
+        <v>0.3434</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.7065</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2660,10 +2660,10 @@
         <v>1169.7093</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>6331.0499</v>
+        <v>6098.5133</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>12544.9718</v>
+        <v>12538.5832</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2718,10 +2718,10 @@
         <v>431.9389</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>803.3567</v>
+        <v>771.5255</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1043.2696</v>
+        <v>1101.8385</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         <v>431.9389</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>803.3567</v>
+        <v>771.5255</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1043.2696</v>
+        <v>1101.8385</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2780,10 +2780,10 @@
         <v>2699.6182</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5020.9791</v>
+        <v>4822.0346</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>6520.4348</v>
+        <v>6886.4909</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         <v>2699.6182</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5020.9791</v>
+        <v>4822.0346</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6520.4348</v>
+        <v>6886.4909</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2904,10 +2904,10 @@
         <v>2078.4318</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4212.3455</v>
+        <v>4044.8731</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5556.8947</v>
+        <v>5869.2922</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         <v>1663.1999</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3428.7641</v>
+        <v>3294.3167</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4608.6081</v>
+        <v>4861.709</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2997,10 +2997,10 @@
         <v>108.7086</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>222.4981</v>
+        <v>211.723</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>269.9833</v>
+        <v>289.33</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3028,10 +3028,10 @@
         <v>258.77</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>513.33</v>
+        <v>491.08</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>630.55</v>
+        <v>670.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         <v>621.1864</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>808.6337</v>
+        <v>777.1616</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>963.5401000000001</v>
+        <v>1017.1987</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>305.8667</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>568.8769</v>
+        <v>546.3365</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>738.7653</v>
+        <v>780.2394</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3121,10 +3121,10 @@
         <v>2699.6182</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>5020.9791</v>
+        <v>4822.0346</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6520.4348</v>
+        <v>6886.4909</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         <v>1619.7709</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3012.5875</v>
+        <v>2893.2208</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>3912.2609</v>
+        <v>4131.8945</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
         <v>2699.6182</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5020.9791</v>
+        <v>4822.0346</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6520.4348</v>
+        <v>6886.4909</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3245,10 +3245,10 @@
         <v>2078.4318</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4212.3455</v>
+        <v>4044.8731</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5556.8947</v>
+        <v>5869.2922</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
         <v>1663.1999</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3428.7641</v>
+        <v>3294.3167</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4608.6081</v>
+        <v>4861.709</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
         <v>108.7086</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>222.4981</v>
+        <v>211.723</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>269.9833</v>
+        <v>289.33</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         <v>258.77</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>513.33</v>
+        <v>491.08</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>630.55</v>
+        <v>670.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         <v>621.1864</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>808.6337</v>
+        <v>777.1616</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>963.5401000000001</v>
+        <v>1017.1987</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         <v>1.1852</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.4026</v>
+        <v>1.4013</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.6801</v>
+        <v>1.6008</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3489,10 +3489,10 @@
         <v>1.1852</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.4026</v>
+        <v>1.4013</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.6801</v>
+        <v>1.6008</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>408.916</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>916.5322</v>
+        <v>879.2689</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1443.6116</v>
+        <v>1452.7064</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         <v>345.0248</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>653.4588</v>
+        <v>627.468</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>859.2378</v>
+        <v>907.4657</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         <v>220.5233</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>601.4007</v>
+        <v>576.3269</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1066.2641</v>
+        <v>1054.1458</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         <v>408.916</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>916.5322</v>
+        <v>879.2689</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1443.6116</v>
+        <v>1452.7064</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         <v>188.3927</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>315.1315</v>
+        <v>302.942</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>377.3475</v>
+        <v>398.5606</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         <v>168.7647</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>278.5328</v>
+        <v>267.8267</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>332.9342</v>
+        <v>351.4839</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         <v>294.42</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>548.98</v>
+        <v>526.73</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>666.2</v>
+        <v>706.15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         <v>258.77</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>513.33</v>
+        <v>491.08</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>630.55</v>
+        <v>670.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3834,10 +3834,10 @@
         <v>7.6362</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3783</v>
+        <v>7.3798</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.1964</v>
+        <v>7.225</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3865,10 +3865,10 @@
         <v>3122.5526</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6762.4187</v>
+        <v>6488.8541</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>10388.7519</v>
+        <v>10495.7628</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
         <v>353.7852</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>766.182</v>
+        <v>735.1872</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1177.0456</v>
+        <v>1189.1699</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3958,10 +3958,10 @@
         <v>408.916</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>916.5322</v>
+        <v>879.2689</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1443.6116</v>
+        <v>1452.7064</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         <v>2.3572</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4396</v>
+        <v>2.4391</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.5013</v>
+        <v>2.4914</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
         <v>7.6362</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3783</v>
+        <v>7.3798</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.1964</v>
+        <v>7.225</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4086,10 +4086,10 @@
         <v>2445.3719</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5588.0691</v>
+        <v>5359.9666</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>9060.348900000001</v>
+        <v>9050.855799999999</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4117,10 +4117,10 @@
         <v>176.0332</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1325.6399</v>
+        <v>1267.5183</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>3359.9798</v>
+        <v>3071.8144</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4148,10 +4148,10 @@
         <v>3122.5526</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6762.4187</v>
+        <v>6488.8541</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>10388.7519</v>
+        <v>10495.7628</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4179,10 +4179,10 @@
         <v>176.4696</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>353.4383</v>
+        <v>339.3591</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>483.6233</v>
+        <v>510.6378</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4210,10 +4210,10 @@
         <v>132.1406</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>264.6548</v>
+        <v>254.1123</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>362.1374</v>
+        <v>382.3658</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4268,10 +4268,10 @@
         <v>3122.9891</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5790.2172</v>
+        <v>5560.6949</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>7512.3954</v>
+        <v>7934.5862</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         <v>2338.4959</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4335.7177</v>
+        <v>4163.8513</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5625.2857</v>
+        <v>5941.4223</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         <v>820.7853</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1835.3799</v>
+        <v>1760.5158</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>3015.2954</v>
+        <v>2993.9301</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4388,10 +4388,10 @@
         <v>3122.5526</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>6762.4187</v>
+        <v>6488.8541</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>10388.7519</v>
+        <v>10495.7628</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
         <v>176.4696</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>353.4383</v>
+        <v>339.3591</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>483.6233</v>
+        <v>510.6378</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4450,10 +4450,10 @@
         <v>132.1406</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>264.6548</v>
+        <v>254.1123</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>362.1374</v>
+        <v>382.3658</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4508,10 +4508,10 @@
         <v>1247.0591</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2426.9238</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3334.1368</v>
+        <v>3521.5753</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
         <v>176.385</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1326.4018</v>
+        <v>1268.2494</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>3361.1502</v>
+        <v>3072.997</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4601,10 +4601,10 @@
         <v>3122.9044</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>6763.1806</v>
+        <v>6489.5852</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>10389.9223</v>
+        <v>10496.9454</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         <v>176.4696</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>353.4383</v>
+        <v>339.3591</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>483.6233</v>
+        <v>510.6378</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4663,10 +4663,10 @@
         <v>132.1406</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>264.6548</v>
+        <v>254.1123</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>362.1374</v>
+        <v>382.3658</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4721,10 +4721,10 @@
         <v>3122.9891</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5790.2172</v>
+        <v>5560.6949</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>7512.3954</v>
+        <v>7934.5862</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>2338.4959</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4335.7177</v>
+        <v>4163.8513</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>5625.2857</v>
+        <v>5941.4223</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4810,10 +4810,10 @@
         <v>820.926</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1835.6847</v>
+        <v>1760.8082</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3015.7635</v>
+        <v>2994.4031</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4841,10 +4841,10 @@
         <v>3122.9044</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>6763.1806</v>
+        <v>6489.5852</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>10389.9223</v>
+        <v>10496.9454</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4872,10 +4872,10 @@
         <v>176.4696</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>353.4383</v>
+        <v>339.3591</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>483.6233</v>
+        <v>510.6378</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4903,10 +4903,10 @@
         <v>132.1406</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>264.6548</v>
+        <v>254.1123</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>362.1374</v>
+        <v>382.3658</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
         <v>1247.0591</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2426.9238</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>3334.1368</v>
+        <v>3521.5753</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
         <v>814.2439000000001</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2918.1381</v>
+        <v>2791.822</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>6411.6191</v>
+        <v>6051.4302</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         <v>790.2237</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2101.7781</v>
+        <v>2014.1019</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>3794.614</v>
+        <v>3719.787</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5085,10 +5085,10 @@
         <v>2445.3719</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5588.0691</v>
+        <v>5359.9666</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>9060.348900000001</v>
+        <v>9050.855799999999</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
         <v>408.916</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>916.5322</v>
+        <v>879.2689</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1443.6116</v>
+        <v>1452.7064</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5182,10 +5182,10 @@
         <v>1247.0591</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2426.9238</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>3334.1368</v>
+        <v>3521.5753</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
         <v>1624.4459</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3752.3845</v>
+        <v>3599.1584</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>6044.5854</v>
+        <v>6056.4527</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5275,10 +5275,10 @@
         <v>2445.3719</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>5588.0691</v>
+        <v>5359.9666</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>9060.348900000001</v>
+        <v>9050.855799999999</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         <v>408.916</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>916.5322</v>
+        <v>879.2689</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1443.6116</v>
+        <v>1452.7064</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5372,10 +5372,10 @@
         <v>1247.0591</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2426.9238</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3334.1368</v>
+        <v>3521.5753</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         <v>820.926</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1835.6847</v>
+        <v>1760.8082</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>3015.7635</v>
+        <v>2994.4031</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5465,10 +5465,10 @@
         <v>3122.9044</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>6763.1806</v>
+        <v>6489.5852</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>10389.9223</v>
+        <v>10496.9454</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5496,10 +5496,10 @@
         <v>176.4696</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>353.4383</v>
+        <v>339.3591</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>483.6233</v>
+        <v>510.6378</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5527,10 +5527,10 @@
         <v>132.1406</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>264.6548</v>
+        <v>254.1123</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>362.1374</v>
+        <v>382.3658</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5585,10 +5585,10 @@
         <v>1247.0591</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2426.9238</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>3334.1368</v>
+        <v>3521.5753</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5647,10 +5647,10 @@
         <v>-0.2301</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.1611</v>
+        <v>-0.1612</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1478</v>
+        <v>-0.1477</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5674,10 +5674,10 @@
         <v>-0.5767</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4671</v>
+        <v>-0.4677</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4158</v>
+        <v>-0.4191</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1169.7093</v>
+        <v>740.5584</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6098.5133</v>
+        <v>6166.8729</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12538.5832</v>
+        <v>13782.7161</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1169.7093</v>
+        <v>740.5584</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6098.5133</v>
+        <v>6166.8729</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12538.5832</v>
+        <v>13782.7161</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2445.3719</v>
+        <v>2031.6225</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5359.9666</v>
+        <v>5427.028</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9050.855799999999</v>
+        <v>10289.4749</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6113.4297</v>
+        <v>5079.0561</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13399.9164</v>
+        <v>13567.5699</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22627.1396</v>
+        <v>25723.6872</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7360.4888</v>
+        <v>6130.6592</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15826.8403</v>
+        <v>16023.8117</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26148.7149</v>
+        <v>29599.953</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>408.916</v>
+        <v>340.5922</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>879.2689</v>
+        <v>890.2118</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1452.7064</v>
+        <v>1644.4418</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>485.497</v>
+        <v>405.1741</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1021.307</v>
+        <v>1034.1441</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1643.8845</v>
+        <v>1863.2099</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>108.6994</v>
+        <v>89.367</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>249.1248</v>
+        <v>252.8146</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>392.5725</v>
+        <v>457.3424</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1249.418</v>
+        <v>1027.2069</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2395.4308</v>
+        <v>2430.9099</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3191.6464</v>
+        <v>3718.2306</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2347700</v>
+        <v>2193000</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4027400</v>
+        <v>4052100</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5639100</v>
+        <v>6005700</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>190.0672</v>
+        <v>167.2866</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>212.4227</v>
+        <v>214.2549</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>202.1375</v>
+        <v>221.1132</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>345.884</v>
+        <v>289.6786</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>715.3892</v>
+        <v>723.7764</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1174.844</v>
+        <v>1318.0656</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>303.0216</v>
+        <v>254.7353</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>598.6683</v>
+        <v>605.675</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>880.1385</v>
+        <v>962.9052</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>290.7357</v>
+        <v>244.434</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>575.9063</v>
+        <v>582.5979</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>849.4843</v>
+        <v>927.5503</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>12.286</v>
+        <v>10.3013</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>22.762</v>
+        <v>23.0772</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>30.6542</v>
+        <v>35.3549</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>20.4766</v>
+        <v>17.1688</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>37.9367</v>
+        <v>38.462</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>51.0904</v>
+        <v>58.9249</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10.2232</v>
+        <v>10.2196</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.5844</v>
+        <v>11.8983</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>26.3739</v>
+        <v>22.1134</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>48.8624</v>
+        <v>49.539</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>65.8044</v>
+        <v>75.89530000000001</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20.4766</v>
+        <v>17.1688</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>37.9367</v>
+        <v>38.462</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>51.0904</v>
+        <v>58.9249</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.5399</v>
+        <v>4.015</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7.9306</v>
+        <v>8.013999999999999</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>10.6636</v>
+        <v>11.9067</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.3212</v>
+        <v>0.266</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.5967</v>
+        <v>0.6055</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.7963</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2.141</v>
+        <v>1.7735</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3.978</v>
+        <v>4.0363</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>5.3086</v>
+        <v>6.1791</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4.2187</v>
+        <v>3.749</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.3339</v>
+        <v>7.4085</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.8673</v>
+        <v>10.9798</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>76.581</v>
+        <v>64.5819</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>142.0381</v>
+        <v>143.9323</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>191.1781</v>
+        <v>218.7681</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>40.7419</v>
+        <v>33.4959</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>78.11190000000001</v>
+        <v>79.2688</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>104.0754</v>
+        <v>121.2466</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1385.2243</v>
+        <v>1138.8598</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2655.8037</v>
+        <v>2695.1392</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3538.5644</v>
+        <v>4122.3861</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1249.418</v>
+        <v>1027.2069</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2395.4308</v>
+        <v>2430.9099</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3191.6464</v>
+        <v>3718.2306</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1249.418</v>
+        <v>1027.2069</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2395.4308</v>
+        <v>2430.9099</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>3191.6464</v>
+        <v>3718.2306</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13.392</v>
+        <v>12.183</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>22.722</v>
+        <v>22.914</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>30.666</v>
+        <v>33.5295</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8928</v>
+        <v>8122</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15148</v>
+        <v>15276</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>20444</v>
+        <v>22353</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>11.7428</v>
+        <v>9.5763</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>22.1166</v>
+        <v>22.4607</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>29.4672</v>
+        <v>34.5986</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3862</v>
+        <v>3056</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7459</v>
+        <v>7587</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9909</v>
+        <v>11818</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>4.1139</v>
+        <v>3.4681</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.0334</v>
+        <v>8.1282</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>11.686</v>
+        <v>12.8428</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.6723</v>
+        <v>3.0869</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.2433</v>
+        <v>7.3285</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10.6268</v>
+        <v>11.6404</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.9181</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.8108</v>
+        <v>1.8321</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2.6567</v>
+        <v>2.9101</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1247.0591</v>
+        <v>1051.6031</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2426.9238</v>
+        <v>2456.2417</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3521.5753</v>
+        <v>3876.2658</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1275.6625</v>
+        <v>-1291.064</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>738.5467</v>
+        <v>739.8449000000001</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3487.7273</v>
+        <v>3493.2412</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-63.7831</v>
+        <v>-64.5532</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>36.9273</v>
+        <v>36.9922</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>174.3864</v>
+        <v>174.6621</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-63.7831</v>
+        <v>-64.5532</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.2115</v>
+        <v>1.2716</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.5162</v>
+        <v>68.74590000000001</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>32.7902</v>
+        <v>28.0916</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>62.8551</v>
+        <v>63.5518</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>90.5848</v>
+        <v>98.542</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-96.5733</v>
+        <v>-92.6448</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-61.6435</v>
+        <v>-62.2802</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-22.0687</v>
+        <v>-29.7961</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7158</v>
+        <v>35.7206</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>105.8702</v>
+        <v>105.9161</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2890.5016</v>
+        <v>2884.341</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3571.5816</v>
+        <v>3572.0624</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4234.808</v>
+        <v>4236.6459</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.0659</v>
+        <v>0.0417</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3434</v>
+        <v>0.3473</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.7762</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1169.7093</v>
+        <v>740.5584</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>6098.5133</v>
+        <v>6166.8729</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>12538.5832</v>
+        <v>13782.7161</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>431.9389</v>
+        <v>359.2235</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>771.5255</v>
+        <v>780.8685</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1101.8385</v>
+        <v>1212.2253</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>431.9389</v>
+        <v>359.2235</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>771.5255</v>
+        <v>780.8685</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1101.8385</v>
+        <v>1212.2253</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2699.6182</v>
+        <v>2245.1466</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4822.0346</v>
+        <v>4880.428</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>6886.4909</v>
+        <v>7576.4082</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2699.6182</v>
+        <v>2245.1466</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4822.0346</v>
+        <v>4880.428</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6886.4909</v>
+        <v>7576.4082</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2078.4318</v>
+        <v>1752.6718</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4044.8731</v>
+        <v>4093.7362</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5869.2922</v>
+        <v>6460.4431</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1663.1999</v>
+        <v>1397.2561</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3294.3167</v>
+        <v>3333.6805</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4861.709</v>
+        <v>5311.1861</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>108.7086</v>
+        <v>89.1925</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>211.723</v>
+        <v>214.8224</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>289.33</v>
+        <v>335.5537</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>258.77</v>
+        <v>218.47</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>491.08</v>
+        <v>497.48</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>670.5</v>
+        <v>765.95</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>621.1864</v>
+        <v>492.4748</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>777.1616</v>
+        <v>786.6917999999999</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1017.1987</v>
+        <v>1115.9652</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>305.8667</v>
+        <v>254.3751</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>546.3365</v>
+        <v>552.9525</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>780.2394</v>
+        <v>858.4071</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2699.6182</v>
+        <v>2245.1466</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4822.0346</v>
+        <v>4880.428</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6886.4909</v>
+        <v>7576.4082</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1619.7709</v>
+        <v>1347.088</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2893.2208</v>
+        <v>2928.2568</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4131.8945</v>
+        <v>4545.8449</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2699.6182</v>
+        <v>2245.1466</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4822.0346</v>
+        <v>4880.428</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6886.4909</v>
+        <v>7576.4082</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2078.4318</v>
+        <v>1752.6718</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4044.8731</v>
+        <v>4093.7362</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5869.2922</v>
+        <v>6460.4431</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1663.1999</v>
+        <v>1397.2561</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3294.3167</v>
+        <v>3333.6805</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4861.709</v>
+        <v>5311.1861</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>108.7086</v>
+        <v>89.1925</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>211.723</v>
+        <v>214.8224</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>289.33</v>
+        <v>335.5537</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>258.77</v>
+        <v>218.47</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>491.08</v>
+        <v>497.48</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>670.5</v>
+        <v>765.95</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>621.1864</v>
+        <v>492.4748</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>777.1616</v>
+        <v>786.6917999999999</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1017.1987</v>
+        <v>1115.9652</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.1852</v>
+        <v>1.1856</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.4013</v>
+        <v>1.4018</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.6008</v>
+        <v>1.6474</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.1852</v>
+        <v>1.1856</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.4013</v>
+        <v>1.4018</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.6008</v>
+        <v>1.6474</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>408.916</v>
+        <v>340.5922</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>879.2689</v>
+        <v>890.2118</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1452.7064</v>
+        <v>1644.4418</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>345.0248</v>
+        <v>287.274</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>627.468</v>
+        <v>635.0625</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>907.4657</v>
+        <v>998.2012</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>220.5233</v>
+        <v>184.9137</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>576.3269</v>
+        <v>583.5894</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1054.1458</v>
+        <v>1205.4174</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>408.916</v>
+        <v>340.5922</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>879.2689</v>
+        <v>890.2118</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1452.7064</v>
+        <v>1644.4418</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>188.3927</v>
+        <v>155.6785</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>302.942</v>
+        <v>306.6224</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>398.5606</v>
+        <v>439.0245</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>168.7647</v>
+        <v>138.7371</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>267.8267</v>
+        <v>271.0804</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>351.4839</v>
+        <v>385.5845</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>294.42</v>
+        <v>254.12</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>526.73</v>
+        <v>533.13</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>706.15</v>
+        <v>801.6</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>258.77</v>
+        <v>218.47</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>491.08</v>
+        <v>497.48</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>670.5</v>
+        <v>765.95</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.6362</v>
+        <v>7.6282</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3798</v>
+        <v>7.3796</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.225</v>
+        <v>7.2087</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>3122.5526</v>
+        <v>2598.0913</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6488.8541</v>
+        <v>6569.4123</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>10495.7628</v>
+        <v>11854.2586</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>353.7852</v>
+        <v>294.3637</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>735.1872</v>
+        <v>744.3144</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1189.1699</v>
+        <v>1343.0875</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>408.916</v>
+        <v>340.5922</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>879.2689</v>
+        <v>890.2118</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1452.7064</v>
+        <v>1644.4418</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.3572</v>
+        <v>2.3597</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4391</v>
+        <v>2.4392</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4914</v>
+        <v>2.497</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.6362</v>
+        <v>7.6282</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3798</v>
+        <v>7.3796</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.225</v>
+        <v>7.2087</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2445.3719</v>
+        <v>2031.6225</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5359.9666</v>
+        <v>5427.028</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>9050.855799999999</v>
+        <v>10289.4749</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>176.0332</v>
+        <v>146.0052</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1267.5183</v>
+        <v>1284.8419</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>3071.8144</v>
+        <v>3681.8686</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>3122.5526</v>
+        <v>2598.0913</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6488.8541</v>
+        <v>6569.4123</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>10495.7628</v>
+        <v>11854.2586</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>176.4696</v>
+        <v>146.7836</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>339.3591</v>
+        <v>343.4457</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>510.6378</v>
+        <v>559.6994999999999</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>132.1406</v>
+        <v>109.9116</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>254.1123</v>
+        <v>257.1723</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>382.3658</v>
+        <v>419.1033</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>3122.9891</v>
+        <v>2598.8697</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5560.6949</v>
+        <v>5628.0161</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>7934.5862</v>
+        <v>8732.0895</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2338.4959</v>
+        <v>1946.035</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4163.8513</v>
+        <v>4214.2615</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5941.4223</v>
+        <v>6538.5932</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>820.7853</v>
+        <v>677.3087</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1760.5158</v>
+        <v>1782.6465</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>2993.9301</v>
+        <v>3415.0769</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>3122.5526</v>
+        <v>2598.0913</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>6488.8541</v>
+        <v>6569.4123</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>10495.7628</v>
+        <v>11854.2586</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>176.4696</v>
+        <v>146.7836</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>339.3591</v>
+        <v>343.4457</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>510.6378</v>
+        <v>559.6994999999999</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>132.1406</v>
+        <v>109.9116</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>254.1123</v>
+        <v>257.1723</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>382.3658</v>
+        <v>419.1033</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1247.0591</v>
+        <v>1051.6031</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2426.9238</v>
+        <v>2456.2417</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3521.5753</v>
+        <v>3876.2658</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>176.385</v>
+        <v>146.2979</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1268.2494</v>
+        <v>1285.5821</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>3072.997</v>
+        <v>3683.2042</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>3122.9044</v>
+        <v>2598.3841</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>6489.5852</v>
+        <v>6570.1525</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>10496.9454</v>
+        <v>11855.5942</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>176.4696</v>
+        <v>146.7836</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>339.3591</v>
+        <v>343.4457</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>510.6378</v>
+        <v>559.6994999999999</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>132.1406</v>
+        <v>109.9116</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>254.1123</v>
+        <v>257.1723</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>382.3658</v>
+        <v>419.1033</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>3122.9891</v>
+        <v>2598.8697</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5560.6949</v>
+        <v>5628.0161</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>7934.5862</v>
+        <v>8732.0895</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2338.4959</v>
+        <v>1946.035</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4163.8513</v>
+        <v>4214.2615</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>5941.4223</v>
+        <v>6538.5932</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>820.926</v>
+        <v>677.4258</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1760.8082</v>
+        <v>1782.9426</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>2994.4031</v>
+        <v>3415.6111</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>3122.9044</v>
+        <v>2598.3841</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>6489.5852</v>
+        <v>6570.1525</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>10496.9454</v>
+        <v>11855.5942</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>176.4696</v>
+        <v>146.7836</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>339.3591</v>
+        <v>343.4457</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>510.6378</v>
+        <v>559.6994999999999</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>132.1406</v>
+        <v>109.9116</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>254.1123</v>
+        <v>257.1723</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>382.3658</v>
+        <v>419.1033</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1247.0591</v>
+        <v>1051.6031</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2426.9238</v>
+        <v>2456.2417</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>3521.5753</v>
+        <v>3876.2658</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>814.2439000000001</v>
+        <v>659.6325000000001</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2791.822</v>
+        <v>2828.7063</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>6051.4302</v>
+        <v>7111.8413</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>790.2237</v>
+        <v>656.179</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2014.1019</v>
+        <v>2039.6941</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>3719.787</v>
+        <v>4275.6266</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2445.3719</v>
+        <v>2031.6225</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5359.9666</v>
+        <v>5427.028</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>9050.855799999999</v>
+        <v>10289.4749</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>408.916</v>
+        <v>340.5922</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>879.2689</v>
+        <v>890.2118</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1452.7064</v>
+        <v>1644.4418</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1247.0591</v>
+        <v>1051.6031</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2426.9238</v>
+        <v>2456.2417</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>3521.5753</v>
+        <v>3876.2658</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1624.4459</v>
+        <v>1354.1966</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3599.1584</v>
+        <v>3644.0854</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>6056.4527</v>
+        <v>6873.8637</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2445.3719</v>
+        <v>2031.6225</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>5359.9666</v>
+        <v>5427.028</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>9050.855799999999</v>
+        <v>10289.4749</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>408.916</v>
+        <v>340.5922</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>879.2689</v>
+        <v>890.2118</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1452.7064</v>
+        <v>1644.4418</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1247.0591</v>
+        <v>1051.6031</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2426.9238</v>
+        <v>2456.2417</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3521.5753</v>
+        <v>3876.2658</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>820.926</v>
+        <v>677.4258</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1760.8082</v>
+        <v>1782.9426</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>2994.4031</v>
+        <v>3415.6111</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>3122.9044</v>
+        <v>2598.3841</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>6489.5852</v>
+        <v>6570.1525</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>10496.9454</v>
+        <v>11855.5942</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>176.4696</v>
+        <v>146.7836</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>339.3591</v>
+        <v>343.4457</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>510.6378</v>
+        <v>559.6994999999999</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>132.1406</v>
+        <v>109.9116</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>254.1123</v>
+        <v>257.1723</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>382.3658</v>
+        <v>419.1033</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1247.0591</v>
+        <v>1051.6031</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2426.9238</v>
+        <v>2456.2417</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>3521.5753</v>
+        <v>3876.2658</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.2301</v>
+        <v>-0.2194</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>-0.1612</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1477</v>
+        <v>-0.1473</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.5767</v>
+        <v>-0.5699</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>-0.4677</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4191</v>
+        <v>-0.4174</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>359.2235</v>
+        <v>347.6655</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>780.8685</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>359.2235</v>
+        <v>347.6655</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>780.8685</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2245.1466</v>
+        <v>2172.9091</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>4880.428</v>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2245.1466</v>
+        <v>2172.9091</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>4880.428</v>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>492.4748</v>
+        <v>420.2373</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>786.6917999999999</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>254.3751</v>
+        <v>246.1906</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>552.9525</v>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2245.1466</v>
+        <v>2172.9091</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>4880.428</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1347.088</v>
+        <v>1303.7455</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>2928.2568</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2245.1466</v>
+        <v>2172.9091</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>4880.428</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>492.4748</v>
+        <v>420.2373</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>786.6917999999999</v>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.1856</v>
+        <v>1.2032</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>1.4018</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.1856</v>
+        <v>1.2032</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>1.4018</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>287.274</v>
+        <v>283.0776</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>635.0625</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>184.9137</v>
+        <v>205.0626</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>583.5894</v>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>155.6785</v>
+        <v>135.5296</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>306.6224</v>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>138.7371</v>
+        <v>118.5883</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>271.0804</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.6282</v>
+        <v>7.4976</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>7.3796</v>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2598.0913</v>
+        <v>2553.6322</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>6569.4123</v>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>294.3637</v>
+        <v>289.3265</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>744.3144</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.3597</v>
+        <v>2.4008</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>2.4392</v>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.6282</v>
+        <v>7.4976</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>7.3796</v>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>146.0052</v>
+        <v>191.1454</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>1284.8419</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>2598.0913</v>
+        <v>2553.6322</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>6569.4123</v>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>146.7836</v>
+        <v>152.5841</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>343.4457</v>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>109.9116</v>
+        <v>114.255</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>257.1723</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2598.8697</v>
+        <v>2515.071</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>5628.0161</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>1946.035</v>
+        <v>1883.2865</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>4214.2615</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>677.3087</v>
+        <v>661.8453</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>1782.6465</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2598.0913</v>
+        <v>2553.6322</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>6569.4123</v>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>146.7836</v>
+        <v>152.5841</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>343.4457</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>109.9116</v>
+        <v>114.255</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>257.1723</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>146.2979</v>
+        <v>191.4331</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>1285.5821</v>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2598.3841</v>
+        <v>2553.9199</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>6570.1525</v>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>146.7836</v>
+        <v>152.5841</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>343.4457</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>109.9116</v>
+        <v>114.255</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>257.1723</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2598.8697</v>
+        <v>2515.071</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>5628.0161</v>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>1946.035</v>
+        <v>1883.2865</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>4214.2615</v>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>677.4258</v>
+        <v>661.9604</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>1782.9426</v>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>2598.3841</v>
+        <v>2553.9199</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>6570.1525</v>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>146.7836</v>
+        <v>152.5841</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>343.4457</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>109.9116</v>
+        <v>114.255</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>257.1723</v>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>659.6325000000001</v>
+        <v>772.1475</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>2828.7063</v>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>656.179</v>
+        <v>701.1849999999999</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>2039.6941</v>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1354.1966</v>
+        <v>1369.6621</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>3644.0854</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>677.4258</v>
+        <v>661.9604</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>1782.9426</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>2598.3841</v>
+        <v>2553.9199</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>6570.1525</v>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>146.7836</v>
+        <v>152.5841</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>343.4457</v>
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>109.9116</v>
+        <v>114.255</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>257.1723</v>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.2194</v>
+        <v>-0.1934</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>-0.1612</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.5699</v>
+        <v>-0.5009</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>-0.4677</v>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>740.5584</v>
+        <v>770.2462</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6166.8729</v>
+        <v>5661.0027</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>13782.7161</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>740.5584</v>
+        <v>770.2462</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6166.8729</v>
+        <v>5661.0027</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>13782.7161</v>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2031.6225</v>
+        <v>2060.3074</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5427.028</v>
+        <v>4930.0167</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>10289.4749</v>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5079.0561</v>
+        <v>5150.7684</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13567.5699</v>
+        <v>12325.0416</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>25723.6872</v>
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6130.6592</v>
+        <v>6215.5742</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>16023.8117</v>
+        <v>14580.0187</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>29599.953</v>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>340.5922</v>
+        <v>345.3097</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>890.2118</v>
+        <v>810.001</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1644.4418</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>405.1741</v>
+        <v>410.8108</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1034.1441</v>
+        <v>940.6592000000001</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1863.2099</v>
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>89.367</v>
+        <v>90.86660000000001</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>252.8146</v>
+        <v>226.9859</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>457.3424</v>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1027.2069</v>
+        <v>1044.4437</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2430.9099</v>
+        <v>2182.5563</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>3718.2306</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2193000</v>
+        <v>2205000</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4052100</v>
+        <v>3879200</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>6005700</v>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>167.2866</v>
+        <v>169.1681</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>214.2549</v>
+        <v>200.9395</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>221.1132</v>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>289.6786</v>
+        <v>293.4417</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>723.7764</v>
+        <v>661.4638</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1318.0656</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>254.7353</v>
+        <v>257.9681</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>605.675</v>
+        <v>556.7215</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>962.9052</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>244.434</v>
+        <v>247.5118</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>582.5979</v>
+        <v>535.8605</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>927.5503</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>10.3013</v>
+        <v>10.4564</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>23.0772</v>
+        <v>20.861</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>35.3549</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>17.1688</v>
+        <v>17.4273</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>38.462</v>
+        <v>34.7684</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>58.9249</v>
@@ -1164,7 +1164,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10.2196</v>
+        <v>10.1751</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>11.8983</v>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>22.1134</v>
+        <v>22.4464</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>49.539</v>
+        <v>44.7817</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>75.89530000000001</v>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>17.1688</v>
+        <v>17.4273</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>38.462</v>
+        <v>34.7684</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>58.9249</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.015</v>
+        <v>4.0561</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8.013999999999999</v>
+        <v>7.4279</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>11.9067</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.266</v>
+        <v>0.2703</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.6055</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>0.9268999999999999</v>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1.7735</v>
+        <v>1.8022</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4.0363</v>
+        <v>3.6259</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>6.1791</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3.749</v>
+        <v>3.7857</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.4085</v>
+        <v>6.884</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>10.9798</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>64.5819</v>
+        <v>65.50109999999999</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>143.9323</v>
+        <v>130.6582</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>218.7681</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>33.4959</v>
+        <v>34.0579</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>79.2688</v>
+        <v>71.1703</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>121.2466</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1138.8598</v>
+        <v>1157.9702</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2695.1392</v>
+        <v>2419.7907</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>4122.3861</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1027.2069</v>
+        <v>1044.4437</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2430.9099</v>
+        <v>2182.5563</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>3718.2306</v>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1027.2069</v>
+        <v>1044.4437</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2430.9099</v>
+        <v>2182.5563</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>3718.2306</v>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>12.183</v>
+        <v>12.2775</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>22.914</v>
+        <v>21.564</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>33.5295</v>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8122</v>
+        <v>8185</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15276</v>
+        <v>14376</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>22353</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>9.5763</v>
+        <v>9.7456</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>22.4607</v>
+        <v>20.0415</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>34.5986</v>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3056</v>
+        <v>3119</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7587</v>
+        <v>6687</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>11818</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>3.4681</v>
+        <v>3.5122</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.1282</v>
+        <v>7.4656</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>12.8428</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.0869</v>
+        <v>3.1263</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.3285</v>
+        <v>6.7334</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>11.6404</v>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7816</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.8321</v>
+        <v>1.6834</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>2.9101</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1051.6031</v>
+        <v>1064.8058</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2456.2417</v>
+        <v>2254.9771</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>3876.2658</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1291.064</v>
+        <v>-1290.0611</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>739.8449000000001</v>
+        <v>730.986</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>3493.2412</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-64.5532</v>
+        <v>-64.5031</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>36.9922</v>
+        <v>36.5493</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>174.6621</v>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-64.5532</v>
+        <v>-64.5031</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.2716</v>
+        <v>0.8615</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>68.74590000000001</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>28.0916</v>
+        <v>28.3976</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>63.5518</v>
+        <v>58.7971</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>98.542</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-92.6448</v>
+        <v>-92.9007</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-62.2802</v>
+        <v>-57.9356</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>-29.7961</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7206</v>
+        <v>35.6878</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>105.9161</v>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2884.341</v>
+        <v>2884.7422</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3572.0624</v>
+        <v>3568.7813</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>4236.6459</v>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0434</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3473</v>
+        <v>0.3188</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>0.7762</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>740.5584</v>
+        <v>770.2462</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>6166.8729</v>
+        <v>5661.0027</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>13782.7161</v>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>347.6655</v>
+        <v>336.5382</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>780.8685</v>
+        <v>715.7413</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1212.2253</v>
+        <v>1228.8443</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>347.6655</v>
+        <v>336.5382</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>780.8685</v>
+        <v>715.7413</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1212.2253</v>
+        <v>1228.8443</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2172.9091</v>
+        <v>2103.3635</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4880.428</v>
+        <v>4473.3831</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>7576.4082</v>
+        <v>7680.2766</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2172.9091</v>
+        <v>2103.3635</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4880.428</v>
+        <v>4473.3831</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>7576.4082</v>
+        <v>7680.2766</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1752.6718</v>
+        <v>1774.6763</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4093.7362</v>
+        <v>3758.2951</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>6460.4431</v>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1397.2561</v>
+        <v>1414.5851</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3333.6805</v>
+        <v>3065.0317</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>5311.1861</v>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>89.1925</v>
+        <v>90.7179</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>214.8224</v>
+        <v>193.0301</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>335.5537</v>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>218.47</v>
+        <v>221.62</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>497.48</v>
+        <v>452.48</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>765.95</v>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>420.2373</v>
+        <v>328.6872</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>786.6917999999999</v>
+        <v>715.088</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1115.9652</v>
+        <v>1219.8336</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>246.1906</v>
+        <v>238.3111</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>552.9525</v>
+        <v>506.8343</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>858.4071</v>
+        <v>870.1753</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2172.9091</v>
+        <v>2103.3635</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4880.428</v>
+        <v>4473.3831</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>7576.4082</v>
+        <v>7680.2766</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1303.7455</v>
+        <v>1262.0181</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2928.2568</v>
+        <v>2684.0299</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4545.8449</v>
+        <v>4608.166</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2172.9091</v>
+        <v>2103.3635</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4880.428</v>
+        <v>4473.3831</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>7576.4082</v>
+        <v>7680.2766</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>1752.6718</v>
+        <v>1774.6763</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4093.7362</v>
+        <v>3758.2951</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>6460.4431</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1397.2561</v>
+        <v>1414.5851</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3333.6805</v>
+        <v>3065.0317</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>5311.1861</v>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>89.1925</v>
+        <v>90.7179</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>214.8224</v>
+        <v>193.0301</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>335.5537</v>
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>218.47</v>
+        <v>221.62</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>497.48</v>
+        <v>452.48</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>765.95</v>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>420.2373</v>
+        <v>328.6872</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>786.6917999999999</v>
+        <v>715.088</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1115.9652</v>
+        <v>1219.8336</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.2032</v>
+        <v>1.2591</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.4018</v>
+        <v>1.3898</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.6474</v>
+        <v>1.6404</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.2032</v>
+        <v>1.2591</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.4018</v>
+        <v>1.3898</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.6474</v>
+        <v>1.6404</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>340.5922</v>
+        <v>345.3097</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>890.2118</v>
+        <v>810.001</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>1644.4418</v>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>283.0776</v>
+        <v>274.2482</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>635.0625</v>
+        <v>582.8057</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>998.2012</v>
+        <v>1002.4677</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>205.0626</v>
+        <v>214.8098</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>583.5894</v>
+        <v>531.0809</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1205.4174</v>
+        <v>1171.1435</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>340.5922</v>
+        <v>345.3097</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>890.2118</v>
+        <v>810.001</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>1644.4418</v>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>135.5296</v>
+        <v>130.4998</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>306.6224</v>
+        <v>278.9201</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>439.0245</v>
+        <v>473.2984</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>118.5883</v>
+        <v>113.3485</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>271.0804</v>
+        <v>246.3781</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>385.5845</v>
+        <v>419.8584</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>254.12</v>
+        <v>257.27</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>533.13</v>
+        <v>488.13</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>801.6</v>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>218.47</v>
+        <v>221.62</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>497.48</v>
+        <v>452.48</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>765.95</v>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.4976</v>
+        <v>7.4535</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3796</v>
+        <v>7.3794</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2087</v>
+        <v>7.2547</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2553.6322</v>
+        <v>2573.7618</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6569.4123</v>
+        <v>5977.3239</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11854.2586</v>
+        <v>11929.885</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>289.3265</v>
+        <v>291.6072</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>744.3144</v>
+        <v>677.2308</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1343.0875</v>
+        <v>1351.656</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>340.5922</v>
+        <v>345.3097</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>890.2118</v>
+        <v>810.001</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>1644.4418</v>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.4008</v>
+        <v>2.415</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>2.4392</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.497</v>
+        <v>2.4812</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.4976</v>
+        <v>7.4535</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3796</v>
+        <v>7.3794</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2087</v>
+        <v>7.2547</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2031.6225</v>
+        <v>2060.3074</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5427.028</v>
+        <v>4930.0167</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>10289.4749</v>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>191.1454</v>
+        <v>286.417</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1284.8419</v>
+        <v>1134.9858</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>3681.8686</v>
+        <v>3626.5638</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>2553.6322</v>
+        <v>2573.7618</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6569.4123</v>
+        <v>5977.3239</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>11854.2586</v>
+        <v>11929.885</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>152.5841</v>
+        <v>147.068</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>343.4457</v>
+        <v>316.0802</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>559.6994999999999</v>
+        <v>549.0454</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>114.255</v>
+        <v>110.1246</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>257.1723</v>
+        <v>236.6811</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>419.1033</v>
+        <v>411.1255</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2515.071</v>
+        <v>2434.4129</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5628.0161</v>
+        <v>5158.4184</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>8732.0895</v>
+        <v>8852.366599999999</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>1883.2865</v>
+        <v>1822.8897</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4214.2615</v>
+        <v>3862.6264</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>6538.5932</v>
+        <v>6628.6568</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>661.8453</v>
+        <v>662.4096</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1782.6465</v>
+        <v>1615.3709</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>3415.0769</v>
+        <v>3441.0658</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2553.6322</v>
+        <v>2573.7618</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>6569.4123</v>
+        <v>5977.3239</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>11854.2586</v>
+        <v>11929.885</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>152.5841</v>
+        <v>147.068</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>343.4457</v>
+        <v>316.0802</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>559.6994999999999</v>
+        <v>549.0454</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>114.255</v>
+        <v>110.1246</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>257.1723</v>
+        <v>236.6811</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>419.1033</v>
+        <v>411.1255</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1051.6031</v>
+        <v>1064.8058</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2456.2417</v>
+        <v>2254.9771</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>3876.2658</v>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>191.4331</v>
+        <v>286.7069</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1285.5821</v>
+        <v>1135.6592</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>3683.2042</v>
+        <v>3627.9079</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2553.9199</v>
+        <v>2574.0518</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>6570.1525</v>
+        <v>5977.9974</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>11855.5942</v>
+        <v>11931.2291</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>152.5841</v>
+        <v>147.068</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>343.4457</v>
+        <v>316.0802</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>559.6994999999999</v>
+        <v>549.0454</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>114.255</v>
+        <v>110.1246</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>257.1723</v>
+        <v>236.6811</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>419.1033</v>
+        <v>411.1255</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2515.071</v>
+        <v>2434.4129</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5628.0161</v>
+        <v>5158.4184</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>8732.0895</v>
+        <v>8852.366599999999</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>1883.2865</v>
+        <v>1822.8897</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4214.2615</v>
+        <v>3862.6264</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>6538.5932</v>
+        <v>6628.6568</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>661.9604</v>
+        <v>662.5256000000001</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1782.9426</v>
+        <v>1615.6402</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3415.6111</v>
+        <v>3441.6035</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>2553.9199</v>
+        <v>2574.0518</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>6570.1525</v>
+        <v>5977.9974</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>11855.5942</v>
+        <v>11931.2291</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>152.5841</v>
+        <v>147.068</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>343.4457</v>
+        <v>316.0802</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>559.6994999999999</v>
+        <v>549.0454</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>114.255</v>
+        <v>110.1246</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>257.1723</v>
+        <v>236.6811</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>419.1033</v>
+        <v>411.1255</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1051.6031</v>
+        <v>1064.8058</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2456.2417</v>
+        <v>2254.9771</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>3876.2658</v>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>772.1475</v>
+        <v>823.4232</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2828.7063</v>
+        <v>2537.9873</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>7111.8413</v>
+        <v>6925.5286</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>701.1849999999999</v>
+        <v>726.5884</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2039.6941</v>
+        <v>1848.9828</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>4275.6266</v>
+        <v>4201.1015</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2031.6225</v>
+        <v>2060.3074</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5427.028</v>
+        <v>4930.0167</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>10289.4749</v>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>340.5922</v>
+        <v>345.3097</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>890.2118</v>
+        <v>810.001</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>1644.4418</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1051.6031</v>
+        <v>1064.8058</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2456.2417</v>
+        <v>2254.9771</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>3876.2658</v>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1369.6621</v>
+        <v>1397.7817</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3644.0854</v>
+        <v>3314.3764</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>6873.8637</v>
+        <v>6847.8714</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2031.6225</v>
+        <v>2060.3074</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>5427.028</v>
+        <v>4930.0167</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>10289.4749</v>
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>340.5922</v>
+        <v>345.3097</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>890.2118</v>
+        <v>810.001</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>1644.4418</v>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1051.6031</v>
+        <v>1064.8058</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2456.2417</v>
+        <v>2254.9771</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>3876.2658</v>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>661.9604</v>
+        <v>662.5256000000001</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1782.9426</v>
+        <v>1615.6402</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>3415.6111</v>
+        <v>3441.6035</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>2553.9199</v>
+        <v>2574.0518</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>6570.1525</v>
+        <v>5977.9974</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>11855.5942</v>
+        <v>11931.2291</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>152.5841</v>
+        <v>147.068</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>343.4457</v>
+        <v>316.0802</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>559.6994999999999</v>
+        <v>549.0454</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>114.255</v>
+        <v>110.1246</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>257.1723</v>
+        <v>236.6811</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>419.1033</v>
+        <v>411.1255</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1051.6031</v>
+        <v>1064.8058</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2456.2417</v>
+        <v>2254.9771</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>3876.2658</v>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.1934</v>
+        <v>-0.1563</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.1612</v>
+        <v>-0.1599</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1473</v>
+        <v>-0.1588</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.5009</v>
+        <v>-0.4771</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4677</v>
+        <v>-0.4653</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4174</v>
+        <v>-0.4407</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>770.2462</v>
+        <v>623.6992</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5661.0027</v>
+        <v>5581.0739</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13782.7161</v>
+        <v>13512.2165</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>770.2462</v>
+        <v>623.6992</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5661.0027</v>
+        <v>5581.0739</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13782.7161</v>
+        <v>13512.2165</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2060.3074</v>
+        <v>1900.7111</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4930.0167</v>
+        <v>4838.0932</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10289.4749</v>
+        <v>10015.883</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5150.7684</v>
+        <v>4751.7777</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12325.0416</v>
+        <v>12095.233</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25723.6872</v>
+        <v>25039.7075</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6215.5742</v>
+        <v>5981.3461</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14580.0187</v>
+        <v>14622.6403</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>29599.953</v>
+        <v>29105.1441</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>345.3097</v>
+        <v>332.297</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>810.001</v>
+        <v>812.3689000000001</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1644.4418</v>
+        <v>1616.9524</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>410.8108</v>
+        <v>407.7117</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>940.6592000000001</v>
+        <v>960.9715</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1863.2099</v>
+        <v>1848.2704</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>90.86660000000001</v>
+        <v>106.7999</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>226.9859</v>
+        <v>261.8973</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>457.3424</v>
+        <v>486.2114</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1044.4437</v>
+        <v>1227.5847</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2182.5563</v>
+        <v>2518.243</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3718.2306</v>
+        <v>3952.9384</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2205000</v>
+        <v>2332500</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3879200</v>
+        <v>4112900</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6005700</v>
+        <v>6169100</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>169.1681</v>
+        <v>187.9627</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>200.9395</v>
+        <v>218.6711</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>221.1132</v>
+        <v>228.8444</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>293.4417</v>
+        <v>270.4671</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>661.4638</v>
+        <v>639.6391</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1318.0656</v>
+        <v>1269.1987</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>257.9681</v>
+        <v>298.7212</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>556.7215</v>
+        <v>622.8973</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>962.9052</v>
+        <v>1009.1272</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>247.5118</v>
+        <v>286.6298</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>535.8605</v>
+        <v>599.0395</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>927.5503</v>
+        <v>971.6743</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>10.4564</v>
+        <v>12.0914</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>20.861</v>
+        <v>23.8578</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35.3549</v>
+        <v>37.4529</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>17.4273</v>
+        <v>20.1524</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>34.7684</v>
+        <v>39.7629</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>58.9249</v>
+        <v>62.4215</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2079</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10.1751</v>
+        <v>8.440799999999999</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.8983</v>
+        <v>10.6927</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>22.4464</v>
+        <v>25.9563</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>44.7817</v>
+        <v>51.2147</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>75.89530000000001</v>
+        <v>80.3989</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>17.4273</v>
+        <v>20.1524</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>34.7684</v>
+        <v>39.7629</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>58.9249</v>
+        <v>62.4215</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.0561</v>
+        <v>4.4884</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7.4279</v>
+        <v>8.2204</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11.9067</v>
+        <v>12.4614</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.2703</v>
+        <v>0.3157</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.6271</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9851</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1.8022</v>
+        <v>2.105</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3.6259</v>
+        <v>4.1809</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6.1791</v>
+        <v>6.5676</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3.7857</v>
+        <v>4.1727</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>6.884</v>
+        <v>7.5932</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>10.9798</v>
+        <v>11.4763</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>65.50109999999999</v>
+        <v>75.4147</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>130.6582</v>
+        <v>148.6026</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>218.7681</v>
+        <v>231.318</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>34.0579</v>
+        <v>40.0299</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>71.1703</v>
+        <v>82.11660000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>121.2466</v>
+        <v>128.9002</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1157.9702</v>
+        <v>1361.0178</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2419.7907</v>
+        <v>2791.9651</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>4122.3861</v>
+        <v>4382.6056</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1044.4437</v>
+        <v>1227.5847</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2182.5563</v>
+        <v>2518.243</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3718.2306</v>
+        <v>3952.9384</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1044.4437</v>
+        <v>1227.5847</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2182.5563</v>
+        <v>2518.243</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>3718.2306</v>
+        <v>3952.9384</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>12.2775</v>
+        <v>13.2735</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>21.564</v>
+        <v>23.3895</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>33.5295</v>
+        <v>34.8075</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8185</v>
+        <v>8849</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14376</v>
+        <v>15593</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>22353</v>
+        <v>23205</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>9.7456</v>
+        <v>11.5304</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>20.0415</v>
+        <v>23.3128</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>34.5986</v>
+        <v>36.8888</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3119</v>
+        <v>3783</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6687</v>
+        <v>7904</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11818</v>
+        <v>12670</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>3.5122</v>
+        <v>4.0557</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>7.4656</v>
+        <v>8.3613</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>12.8428</v>
+        <v>13.4686</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.1263</v>
+        <v>3.62</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>6.7334</v>
+        <v>7.5379</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>11.6404</v>
+        <v>12.2023</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.7816</v>
+        <v>0.905</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.6834</v>
+        <v>1.8845</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2.9101</v>
+        <v>3.0506</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1064.8058</v>
+        <v>1229.5684</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2254.9771</v>
+        <v>2527.4073</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3876.2658</v>
+        <v>4065.4366</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1290.0611</v>
+        <v>-1277.0119</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>730.986</v>
+        <v>742.9807</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3493.2412</v>
+        <v>3496.3335</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-64.5031</v>
+        <v>-63.8506</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>36.5493</v>
+        <v>37.149</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>174.6621</v>
+        <v>174.8167</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-64.5031</v>
+        <v>-63.8506</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.8615</v>
+        <v>1.4168</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.74590000000001</v>
+        <v>68.87479999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>28.3976</v>
+        <v>32.3785</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>58.7971</v>
+        <v>65.2349</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>98.542</v>
+        <v>103.0047</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-92.9007</v>
+        <v>-96.2291</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-57.9356</v>
+        <v>-63.8181</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-29.7961</v>
+        <v>-34.1299</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.6878</v>
+        <v>35.7322</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>105.9161</v>
+        <v>105.9419</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2884.7422</v>
+        <v>2889.9619</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3568.7813</v>
+        <v>3573.2238</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4236.6459</v>
+        <v>4237.6767</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.0434</v>
+        <v>0.0351</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3188</v>
+        <v>0.3143</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.7762</v>
+        <v>0.761</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>770.2462</v>
+        <v>623.6992</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>5661.0027</v>
+        <v>5581.0739</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13782.7161</v>
+        <v>13512.2165</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>336.5382</v>
+        <v>388.532</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>715.7413</v>
+        <v>803.3567</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1228.8443</v>
+        <v>1292.3007</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>336.5382</v>
+        <v>388.532</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>715.7413</v>
+        <v>803.3567</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1228.8443</v>
+        <v>1292.3007</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2103.3635</v>
+        <v>2428.3249</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4473.3831</v>
+        <v>5020.9791</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>7680.2766</v>
+        <v>8076.8791</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2103.3635</v>
+        <v>2428.3249</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4473.3831</v>
+        <v>5020.9791</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>7680.2766</v>
+        <v>8076.8791</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1774.6763</v>
+        <v>2049.2807</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>3758.2951</v>
+        <v>4212.3455</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>6460.4431</v>
+        <v>6775.7277</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1414.5851</v>
+        <v>1639.9117</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3065.0317</v>
+        <v>3428.7641</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>5311.1861</v>
+        <v>5563.2407</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>90.7179</v>
+        <v>106.7958</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>193.0301</v>
+        <v>222.4981</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>335.5537</v>
+        <v>356.1837</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>221.62</v>
+        <v>254.82</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>452.48</v>
+        <v>513.33</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>765.95</v>
+        <v>808.55</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>328.6872</v>
+        <v>379.0442</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>715.088</v>
+        <v>808.6337</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1219.8336</v>
+        <v>1301.1515</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>238.3111</v>
+        <v>275.1292</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>506.8343</v>
+        <v>568.8769</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>870.1753</v>
+        <v>915.1104</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2103.3635</v>
+        <v>2428.3249</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4473.3831</v>
+        <v>5020.9791</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>7680.2766</v>
+        <v>8076.8791</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1262.0181</v>
+        <v>1456.9949</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2684.0299</v>
+        <v>3012.5875</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4608.166</v>
+        <v>4846.1275</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2103.3635</v>
+        <v>2428.3249</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4473.3831</v>
+        <v>5020.9791</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>7680.2766</v>
+        <v>8076.8791</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>1774.6763</v>
+        <v>2049.2807</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>3758.2951</v>
+        <v>4212.3455</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>6460.4431</v>
+        <v>6775.7277</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1414.5851</v>
+        <v>1639.9117</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3065.0317</v>
+        <v>3428.7641</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>5311.1861</v>
+        <v>5563.2407</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>90.7179</v>
+        <v>106.7958</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>193.0301</v>
+        <v>222.4981</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>335.5537</v>
+        <v>356.1837</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>221.62</v>
+        <v>254.82</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>452.48</v>
+        <v>513.33</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>765.95</v>
+        <v>808.55</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>328.6872</v>
+        <v>379.0442</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>715.088</v>
+        <v>808.6337</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1219.8336</v>
+        <v>1301.1515</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.2591</v>
+        <v>1.0485</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.3898</v>
+        <v>1.2432</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.6404</v>
+        <v>1.5371</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.2591</v>
+        <v>1.0485</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.3898</v>
+        <v>1.2432</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.6404</v>
+        <v>1.5371</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>345.3097</v>
+        <v>332.297</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>810.001</v>
+        <v>812.3689000000001</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1644.4418</v>
+        <v>1616.9524</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>274.2482</v>
+        <v>316.9167</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>582.8057</v>
+        <v>653.4588</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1002.4677</v>
+        <v>1051.9737</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>214.8098</v>
+        <v>182.5301</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>531.0809</v>
+        <v>497.2374</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1171.1435</v>
+        <v>1112.432</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>345.3097</v>
+        <v>332.297</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>810.001</v>
+        <v>812.3689000000001</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1644.4418</v>
+        <v>1616.9524</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>130.4998</v>
+        <v>149.7669</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>278.9201</v>
+        <v>315.1315</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>473.2984</v>
+        <v>504.5205</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>113.3485</v>
+        <v>130.4022</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>246.3781</v>
+        <v>278.5328</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>419.8584</v>
+        <v>448.2405</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>257.27</v>
+        <v>290.47</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>488.13</v>
+        <v>548.98</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>801.6</v>
+        <v>844.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>221.62</v>
+        <v>254.82</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>452.48</v>
+        <v>513.33</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>765.95</v>
+        <v>808.55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.4535</v>
+        <v>7.6141</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3794</v>
+        <v>7.4755</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2547</v>
+        <v>7.3081</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2573.7618</v>
+        <v>2530.1366</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>5977.3239</v>
+        <v>6072.8998</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11929.885</v>
+        <v>11816.8089</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>291.6072</v>
+        <v>286.6645</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>677.2308</v>
+        <v>688.0596</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1351.656</v>
+        <v>1338.8445</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>345.3097</v>
+        <v>332.297</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>810.001</v>
+        <v>812.3689000000001</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1644.4418</v>
+        <v>1616.9524</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.415</v>
+        <v>2.364</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4392</v>
+        <v>2.4079</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4812</v>
+        <v>2.463</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.4535</v>
+        <v>7.6141</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3794</v>
+        <v>7.4755</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2547</v>
+        <v>7.3081</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2060.3074</v>
+        <v>1900.7111</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>4930.0167</v>
+        <v>4838.0932</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>10289.4749</v>
+        <v>10015.883</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>286.417</v>
+        <v>-108.3259</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1134.9858</v>
+        <v>636.121</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>3626.5638</v>
+        <v>3080.8744</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>2573.7618</v>
+        <v>2530.1366</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>5977.3239</v>
+        <v>6072.8998</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>11929.885</v>
+        <v>11816.8089</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>147.068</v>
+        <v>170.655</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>316.0802</v>
+        <v>353.4383</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>549.0454</v>
+        <v>573.4176</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>110.1246</v>
+        <v>127.7866</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>236.6811</v>
+        <v>264.6548</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>411.1255</v>
+        <v>429.3754</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2434.4129</v>
+        <v>2809.1176</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5158.4184</v>
+        <v>5790.2172</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>8852.366599999999</v>
+        <v>9309.352199999999</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>1822.8897</v>
+        <v>2103.4687</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3862.6264</v>
+        <v>4335.7177</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>6628.6568</v>
+        <v>6970.8479</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>662.4096</v>
+        <v>588.4893</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1615.3709</v>
+        <v>1559.5723</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>3441.0658</v>
+        <v>3329.916</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2573.7618</v>
+        <v>2530.1366</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>5977.3239</v>
+        <v>6072.8998</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>11929.885</v>
+        <v>11816.8089</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>147.068</v>
+        <v>170.655</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>316.0802</v>
+        <v>353.4383</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>549.0454</v>
+        <v>573.4176</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>110.1246</v>
+        <v>127.7866</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>236.6811</v>
+        <v>264.6548</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>411.1255</v>
+        <v>429.3754</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1064.8058</v>
+        <v>1229.5684</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2254.9771</v>
+        <v>2527.4073</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3876.2658</v>
+        <v>4065.4366</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>286.7069</v>
+        <v>-108.0409</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1135.6592</v>
+        <v>636.8052</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>3627.9079</v>
+        <v>3082.2057</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2574.0518</v>
+        <v>2530.4217</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>5977.9974</v>
+        <v>6073.584</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>11931.2291</v>
+        <v>11818.1403</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>147.068</v>
+        <v>170.655</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>316.0802</v>
+        <v>353.4383</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>549.0454</v>
+        <v>573.4176</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>110.1246</v>
+        <v>127.7866</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>236.6811</v>
+        <v>264.6548</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>411.1255</v>
+        <v>429.3754</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2434.4129</v>
+        <v>2809.1176</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5158.4184</v>
+        <v>5790.2172</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>8852.366599999999</v>
+        <v>9309.352199999999</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>1822.8897</v>
+        <v>2103.4687</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3862.6264</v>
+        <v>4335.7177</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>6628.6568</v>
+        <v>6970.8479</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>662.5256000000001</v>
+        <v>588.6033</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1615.6402</v>
+        <v>1559.846</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3441.6035</v>
+        <v>3330.4485</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>2574.0518</v>
+        <v>2530.4217</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>5977.9974</v>
+        <v>6073.584</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>11931.2291</v>
+        <v>11818.1403</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>147.068</v>
+        <v>170.655</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>316.0802</v>
+        <v>353.4383</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>549.0454</v>
+        <v>573.4176</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>110.1246</v>
+        <v>127.7866</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>236.6811</v>
+        <v>264.6548</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>411.1255</v>
+        <v>429.3754</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1064.8058</v>
+        <v>1229.5684</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2254.9771</v>
+        <v>2527.4073</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>3876.2658</v>
+        <v>4065.4366</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>823.4232</v>
+        <v>293.5377</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2537.9873</v>
+        <v>1876.5049</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>6925.5286</v>
+        <v>6141.6358</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>726.5884</v>
+        <v>575.4687</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1848.9828</v>
+        <v>1685.1248</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>4201.1015</v>
+        <v>3957.499</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2060.3074</v>
+        <v>1900.7111</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>4930.0167</v>
+        <v>4838.0932</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>10289.4749</v>
+        <v>10015.883</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>345.3097</v>
+        <v>332.297</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>810.001</v>
+        <v>812.3689000000001</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1644.4418</v>
+        <v>1616.9524</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1064.8058</v>
+        <v>1229.5684</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2254.9771</v>
+        <v>2527.4073</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>3876.2658</v>
+        <v>4065.4366</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1397.7817</v>
+        <v>1312.1078</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3314.3764</v>
+        <v>3278.2472</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>6847.8714</v>
+        <v>6685.4344</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2060.3074</v>
+        <v>1900.7111</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>4930.0167</v>
+        <v>4838.0932</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>10289.4749</v>
+        <v>10015.883</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>345.3097</v>
+        <v>332.297</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>810.001</v>
+        <v>812.3689000000001</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1644.4418</v>
+        <v>1616.9524</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1064.8058</v>
+        <v>1229.5684</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2254.9771</v>
+        <v>2527.4073</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3876.2658</v>
+        <v>4065.4366</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>662.5256000000001</v>
+        <v>588.6033</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1615.6402</v>
+        <v>1559.846</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>3441.6035</v>
+        <v>3330.4485</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>2574.0518</v>
+        <v>2530.4217</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>5977.9974</v>
+        <v>6073.584</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>11931.2291</v>
+        <v>11818.1403</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>147.068</v>
+        <v>170.655</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>316.0802</v>
+        <v>353.4383</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>549.0454</v>
+        <v>573.4176</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>110.1246</v>
+        <v>127.7866</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>236.6811</v>
+        <v>264.6548</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>411.1255</v>
+        <v>429.3754</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1064.8058</v>
+        <v>1229.5684</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2254.9771</v>
+        <v>2527.4073</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>3876.2658</v>
+        <v>4065.4366</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.1563</v>
+        <v>-0.1561</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.1599</v>
+        <v>-0.1611</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1588</v>
+        <v>-0.1611</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.4771</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4653</v>
+        <v>-0.4867</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4407</v>
+        <v>-0.4532</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>623.6992</v>
+        <v>1038.9509</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5581.0739</v>
+        <v>6502.6605</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13512.2165</v>
+        <v>15491.7933</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>623.6992</v>
+        <v>1038.9509</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5581.0739</v>
+        <v>6502.6605</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13512.2165</v>
+        <v>15491.7933</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1900.7111</v>
+        <v>2314.4374</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4838.0932</v>
+        <v>5759.8221</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10015.883</v>
+        <v>11995.4597</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4751.7777</v>
+        <v>5786.0934</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12095.233</v>
+        <v>14399.5552</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25039.7075</v>
+        <v>29988.6494</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5981.3461</v>
+        <v>7035.4211</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14622.6403</v>
+        <v>16923.9284</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>29105.1441</v>
+        <v>34054.086</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>332.297</v>
+        <v>390.8567</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>812.3689000000001</v>
+        <v>940.2182</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1616.9524</v>
+        <v>1891.8937</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>407.7117</v>
+        <v>467.5841</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>960.9715</v>
+        <v>1088.6739</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1848.2704</v>
+        <v>2123.2116</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>106.7999</v>
+        <v>160.2748</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>261.8973</v>
+        <v>386.6345</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>486.2114</v>
+        <v>729.7124</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1227.5847</v>
+        <v>1252.1471</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2518.243</v>
+        <v>2515.5138</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>3952.9384</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2332500</v>
+        <v>2349600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4112900</v>
+        <v>4111000</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>6169100</v>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>187.9627</v>
+        <v>190.3283</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>218.6711</v>
+        <v>218.5351</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>228.8444</v>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.104</v>
+        <v>0.1537</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.123</v>
+        <v>0.1846</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>270.4671</v>
+        <v>276.3362</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>639.6391</v>
+        <v>642.6638</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1269.1987</v>
+        <v>1300.6389</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>298.7212</v>
+        <v>303.5622</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>622.8973</v>
+        <v>622.3388</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1009.1272</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>286.6298</v>
+        <v>291.2517</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>599.0395</v>
+        <v>598.5057</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>971.6743</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>12.0914</v>
+        <v>12.3106</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>23.8578</v>
+        <v>23.8331</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>37.4529</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>20.1524</v>
+        <v>20.5176</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>39.7629</v>
+        <v>39.7219</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>62.4215</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7.2079</v>
+        <v>7.2663</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8.440799999999999</v>
+        <v>8.5015</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10.6927</v>
+        <v>11.0227</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>25.9563</v>
+        <v>26.4267</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>51.2147</v>
+        <v>51.1618</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>80.3989</v>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20.1524</v>
+        <v>20.5176</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>39.7629</v>
+        <v>39.7219</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>62.4215</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.4884</v>
+        <v>4.5464</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8.2204</v>
+        <v>8.213900000000001</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>12.4614</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.3157</v>
+        <v>0.3218</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.6271</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>0.9851</v>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2.105</v>
+        <v>2.1456</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4.1809</v>
+        <v>4.1763</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>6.5676</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4.1727</v>
+        <v>4.2245</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.5932</v>
+        <v>7.5874</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>11.4763</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>75.4147</v>
+        <v>76.7274</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>148.6026</v>
+        <v>148.4557</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>231.318</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>40.0299</v>
+        <v>40.8309</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>82.11660000000001</v>
+        <v>82.02760000000001</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>128.9002</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1361.0178</v>
+        <v>1388.2501</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2791.9651</v>
+        <v>2788.9393</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>4382.6056</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1227.5847</v>
+        <v>1252.1471</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2518.243</v>
+        <v>2515.5138</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>3952.9384</v>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1227.5847</v>
+        <v>1252.1471</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2518.243</v>
+        <v>2515.5138</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>3952.9384</v>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13.2735</v>
+        <v>13.407</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>23.3895</v>
+        <v>23.3745</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>34.8075</v>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8849</v>
+        <v>8938</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15593</v>
+        <v>15583</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>23205</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>11.5304</v>
+        <v>11.7697</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>23.3128</v>
+        <v>23.2859</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>36.8888</v>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3783</v>
+        <v>3872</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7904</v>
+        <v>7894</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>12670</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>4.0557</v>
+        <v>4.1213</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.3613</v>
+        <v>8.3538</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>13.4686</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.62</v>
+        <v>3.6789</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.5379</v>
+        <v>7.5311</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>12.2023</v>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.905</v>
+        <v>0.9197</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.8845</v>
+        <v>1.8828</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>3.0506</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1229.5684</v>
+        <v>1249.3277</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2524.3733</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>4065.4366</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1277.0119</v>
+        <v>-1275.4865</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>742.9807</v>
+        <v>742.8384</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>3496.3335</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-63.8506</v>
+        <v>-63.7743</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>37.149</v>
+        <v>37.1419</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>174.8167</v>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-63.8506</v>
+        <v>-63.7743</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.4168</v>
+        <v>1.4102</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>68.87479999999999</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>32.3785</v>
+        <v>32.8439</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>65.2349</v>
+        <v>65.1585</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>103.0047</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-96.2291</v>
+        <v>-96.6182</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-63.8181</v>
+        <v>-63.7483</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>-34.1299</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7322</v>
+        <v>35.7317</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>105.9419</v>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2889.9619</v>
+        <v>2890.572</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3573.2238</v>
+        <v>3573.1711</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>4237.6767</v>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.0351</v>
+        <v>0.0585</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3143</v>
+        <v>0.3662</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.761</v>
+        <v>0.8724</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>623.6992</v>
+        <v>1038.9509</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>5581.0739</v>
+        <v>6502.6605</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13512.2165</v>
+        <v>15491.7933</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>388.532</v>
+        <v>398.8304</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>803.3567</v>
+        <v>809.7293</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1292.3007</v>
+        <v>1304.2598</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>388.532</v>
+        <v>398.8304</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>803.3567</v>
+        <v>809.7293</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1292.3007</v>
+        <v>1304.2598</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2428.3249</v>
+        <v>2492.6899</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5020.9791</v>
+        <v>5060.8084</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>8076.8791</v>
+        <v>8151.6237</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2428.3249</v>
+        <v>2492.6899</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5020.9791</v>
+        <v>5060.8084</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>8076.8791</v>
+        <v>8151.6237</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2049.2807</v>
+        <v>2082.2128</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4212.3455</v>
+        <v>4207.2888</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>6775.7277</v>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1639.9117</v>
+        <v>1666.2388</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3428.7641</v>
+        <v>3424.4496</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>5563.2407</v>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>106.7958</v>
+        <v>108.9508</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>222.4981</v>
+        <v>222.256</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>356.1837</v>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>254.82</v>
+        <v>259.27</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>513.33</v>
+        <v>512.83</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>808.55</v>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>379.0442</v>
+        <v>410.4771</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>808.6337</v>
+        <v>853.5196</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1301.1515</v>
+        <v>1375.8961</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>275.1292</v>
+        <v>282.4218</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>568.8769</v>
+        <v>573.3896</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>915.1104</v>
+        <v>923.579</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2428.3249</v>
+        <v>2492.6899</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>5020.9791</v>
+        <v>5060.8084</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>8076.8791</v>
+        <v>8151.6237</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1456.9949</v>
+        <v>1495.614</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3012.5875</v>
+        <v>3036.485</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4846.1275</v>
+        <v>4890.9742</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2428.3249</v>
+        <v>2492.6899</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5020.9791</v>
+        <v>5060.8084</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>8076.8791</v>
+        <v>8151.6237</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2049.2807</v>
+        <v>2082.2128</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4212.3455</v>
+        <v>4207.2888</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>6775.7277</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1639.9117</v>
+        <v>1666.2388</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3428.7641</v>
+        <v>3424.4496</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>5563.2407</v>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>106.7958</v>
+        <v>108.9508</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>222.4981</v>
+        <v>222.256</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>356.1837</v>
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>254.82</v>
+        <v>259.27</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>513.33</v>
+        <v>512.83</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>808.55</v>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>379.0442</v>
+        <v>410.4771</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>808.6337</v>
+        <v>853.5196</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1301.1515</v>
+        <v>1375.8961</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.0485</v>
+        <v>1.2068</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.2432</v>
+        <v>1.4326</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.5371</v>
+        <v>1.7883</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.0485</v>
+        <v>1.2068</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.2432</v>
+        <v>1.4326</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.5371</v>
+        <v>1.7883</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>332.297</v>
+        <v>390.8567</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>812.3689000000001</v>
+        <v>940.2182</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1616.9524</v>
+        <v>1891.8937</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>316.9167</v>
+        <v>323.8795</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>653.4588</v>
+        <v>656.3241</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1051.9737</v>
+        <v>1057.8993</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>182.5301</v>
+        <v>232.8083</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>497.2374</v>
+        <v>615.6323</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1112.432</v>
+        <v>1371.2757</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>332.297</v>
+        <v>390.8567</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>812.3689000000001</v>
+        <v>940.2182</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1616.9524</v>
+        <v>1891.8937</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>149.7669</v>
+        <v>158.0484</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>315.1315</v>
+        <v>324.586</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>504.5205</v>
+        <v>520.6180000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>130.4022</v>
+        <v>138.3871</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>278.5328</v>
+        <v>288.0206</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>448.2405</v>
+        <v>464.338</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>290.47</v>
+        <v>294.92</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>548.98</v>
+        <v>548.48</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>844.2</v>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>254.82</v>
+        <v>259.27</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>513.33</v>
+        <v>512.83</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>808.55</v>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.6141</v>
+        <v>7.5118</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.4755</v>
+        <v>7.3813</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.3081</v>
+        <v>7.2268</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2530.1366</v>
+        <v>2936.0516</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6072.8998</v>
+        <v>6940.0721</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11816.8089</v>
+        <v>13672.3278</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>286.6645</v>
+        <v>332.6547</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>688.0596</v>
+        <v>786.3102</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1338.8445</v>
+        <v>1549.0747</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>332.297</v>
+        <v>390.8567</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>812.3689000000001</v>
+        <v>940.2182</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1616.9524</v>
+        <v>1891.8937</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.364</v>
+        <v>2.3962</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4079</v>
+        <v>2.4386</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.463</v>
+        <v>2.4907</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.6141</v>
+        <v>7.5118</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.4755</v>
+        <v>7.3813</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.3081</v>
+        <v>7.2268</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>1900.7111</v>
+        <v>2314.4374</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>4838.0932</v>
+        <v>5759.8221</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>10015.883</v>
+        <v>11995.4597</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>-108.3259</v>
+        <v>226.0579</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>636.121</v>
+        <v>1457.2832</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>3080.8744</v>
+        <v>4850.6966</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>2530.1366</v>
+        <v>2936.0516</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6072.8998</v>
+        <v>6940.0721</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>11816.8089</v>
+        <v>13672.3278</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>170.655</v>
+        <v>173.1417</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>353.4383</v>
+        <v>353.042</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>573.4176</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>127.7866</v>
+        <v>129.6486</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>264.6548</v>
+        <v>264.358</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>429.3754</v>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2809.1176</v>
+        <v>2883.1354</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5790.2172</v>
+        <v>5835.8309</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>9309.352199999999</v>
+        <v>9395.0489</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2103.4687</v>
+        <v>2158.8933</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4335.7177</v>
+        <v>4369.8733</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>6970.8479</v>
+        <v>7035.0176</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>588.4893</v>
+        <v>743.9463</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1559.5723</v>
+        <v>1907.4963</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>3329.916</v>
+        <v>4072.1236</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2530.1366</v>
+        <v>2936.0516</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>6072.8998</v>
+        <v>6940.0721</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>11816.8089</v>
+        <v>13672.3278</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>170.655</v>
+        <v>173.1417</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>353.4383</v>
+        <v>353.042</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>573.4176</v>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>127.7866</v>
+        <v>129.6486</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>264.6548</v>
+        <v>264.358</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>429.3754</v>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1229.5684</v>
+        <v>1249.3277</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2524.3733</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>4065.4366</v>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>-108.0409</v>
+        <v>226.3887</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>636.8052</v>
+        <v>1458.0651</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>3082.2057</v>
+        <v>4852.237</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2530.4217</v>
+        <v>2936.3824</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>6073.584</v>
+        <v>6940.8541</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>11818.1403</v>
+        <v>13673.8682</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>170.655</v>
+        <v>173.1417</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>353.4383</v>
+        <v>353.042</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>573.4176</v>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>127.7866</v>
+        <v>129.6486</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>264.6548</v>
+        <v>264.358</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>429.3754</v>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2809.1176</v>
+        <v>2883.1354</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5790.2172</v>
+        <v>5835.8309</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>9309.352199999999</v>
+        <v>9395.0489</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2103.4687</v>
+        <v>2158.8933</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4335.7177</v>
+        <v>4369.8733</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>6970.8479</v>
+        <v>7035.0176</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>588.6033</v>
+        <v>744.0786000000001</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1559.846</v>
+        <v>1907.8091</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3330.4485</v>
+        <v>4072.7397</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>2530.4217</v>
+        <v>2936.3824</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>6073.584</v>
+        <v>6940.8541</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>11818.1403</v>
+        <v>13673.8682</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>170.655</v>
+        <v>173.1417</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>353.4383</v>
+        <v>353.042</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>573.4176</v>
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>127.7866</v>
+        <v>129.6486</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>264.6548</v>
+        <v>264.358</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>429.3754</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1229.5684</v>
+        <v>1249.3277</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2524.3733</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>4065.4366</v>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>293.5377</v>
+        <v>781.3342</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1876.5049</v>
+        <v>3073.3489</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>6141.6358</v>
+        <v>8745.8827</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>575.4687</v>
+        <v>777.8987</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1685.1248</v>
+        <v>2162.7439</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>3957.499</v>
+        <v>4999.1978</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>1900.7111</v>
+        <v>2314.4374</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>4838.0932</v>
+        <v>5759.8221</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>10015.883</v>
+        <v>11995.4597</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>332.297</v>
+        <v>390.8567</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>812.3689000000001</v>
+        <v>940.2182</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1616.9524</v>
+        <v>1891.8937</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1229.5684</v>
+        <v>1249.3277</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2524.3733</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>4065.4366</v>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1312.1078</v>
+        <v>1570.3588</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3278.2472</v>
+        <v>3852.013</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>6685.4344</v>
+        <v>7922.72</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>1900.7111</v>
+        <v>2314.4374</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>4838.0932</v>
+        <v>5759.8221</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>10015.883</v>
+        <v>11995.4597</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>332.297</v>
+        <v>390.8567</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>812.3689000000001</v>
+        <v>940.2182</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1616.9524</v>
+        <v>1891.8937</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1229.5684</v>
+        <v>1249.3277</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2524.3733</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>4065.4366</v>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>588.6033</v>
+        <v>744.0786000000001</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1559.846</v>
+        <v>1907.8091</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>3330.4485</v>
+        <v>4072.7397</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>2530.4217</v>
+        <v>2936.3824</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>6073.584</v>
+        <v>6940.8541</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>11818.1403</v>
+        <v>13673.8682</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>170.655</v>
+        <v>173.1417</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>353.4383</v>
+        <v>353.042</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>573.4176</v>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>127.7866</v>
+        <v>129.6486</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>264.6548</v>
+        <v>264.358</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>429.3754</v>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1229.5684</v>
+        <v>1249.3277</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2527.4073</v>
+        <v>2524.3733</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>4065.4366</v>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.1561</v>
+        <v>-0.1647</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.1611</v>
+        <v>-0.1687</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1611</v>
+        <v>-0.1688</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.4989</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4867</v>
+        <v>-0.4753</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4532</v>
+        <v>-0.4458</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1038.9509</v>
+        <v>1011.7819</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6502.6605</v>
+        <v>5390.9981</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15491.7933</v>
+        <v>12734.1808</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1038.9509</v>
+        <v>1011.7819</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6502.6605</v>
+        <v>5390.9981</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15491.7933</v>
+        <v>12734.1808</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2314.4374</v>
+        <v>2288.7913</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5759.8221</v>
+        <v>4648.4065</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11995.4597</v>
+        <v>9203.813099999999</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5786.0934</v>
+        <v>5721.9782</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14399.5552</v>
+        <v>11621.0162</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29988.6494</v>
+        <v>23009.5327</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7035.4211</v>
+        <v>6951.5724</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>16923.9284</v>
+        <v>13660.8407</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34054.086</v>
+        <v>26214.5923</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>390.8567</v>
+        <v>386.1985</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>940.2182</v>
+        <v>758.9356</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1891.8937</v>
+        <v>1456.3662</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>467.5841</v>
+        <v>461.6131</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1088.6739</v>
+        <v>876.2616</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2123.2116</v>
+        <v>1632.5279</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>160.2748</v>
+        <v>157.1308</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>386.6345</v>
+        <v>299.399</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>729.7124</v>
+        <v>544.5869</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1252.1471</v>
+        <v>1227.5847</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2515.5138</v>
+        <v>1947.9443</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3952.9384</v>
+        <v>2950.0918</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2349600</v>
+        <v>2332500</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4111000</v>
+        <v>3687400</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6169100</v>
+        <v>5415400</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>190.3283</v>
+        <v>187.9627</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>218.5351</v>
+        <v>188.668</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>228.8444</v>
+        <v>194.557</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>276.3362</v>
+        <v>274.0376</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>642.6638</v>
+        <v>530.5842</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1300.6389</v>
+        <v>1018.3897</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>303.5622</v>
+        <v>298.7221</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>622.3388</v>
+        <v>504.7638</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1009.1272</v>
+        <v>800.1961</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>291.2517</v>
+        <v>286.6307</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>598.5057</v>
+        <v>486.3627</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>971.6743</v>
+        <v>772.4106</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>12.3106</v>
+        <v>12.0914</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>23.8331</v>
+        <v>18.4011</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.4529</v>
+        <v>27.7855</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>20.5176</v>
+        <v>20.1524</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>39.7219</v>
+        <v>30.6685</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>62.4215</v>
+        <v>46.3092</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7.2663</v>
+        <v>7.3343</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8.5015</v>
+        <v>8.676399999999999</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.0227</v>
+        <v>10.9387</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>26.4267</v>
+        <v>25.9563</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>51.1618</v>
+        <v>39.501</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>80.3989</v>
+        <v>59.6463</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20.5176</v>
+        <v>20.1524</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>39.7219</v>
+        <v>30.6685</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>62.4215</v>
+        <v>46.3092</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.5464</v>
+        <v>4.4884</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8.213900000000001</v>
+        <v>6.7774</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12.4614</v>
+        <v>9.904999999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.3218</v>
+        <v>0.3157</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.4756</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.9851</v>
+        <v>0.7166</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2.1456</v>
+        <v>2.105</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4.1763</v>
+        <v>3.1704</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6.5676</v>
+        <v>4.7774</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4.2245</v>
+        <v>4.1727</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.5874</v>
+        <v>6.3019</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11.4763</v>
+        <v>9.1884</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>76.7274</v>
+        <v>75.4147</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>148.4557</v>
+        <v>117.326</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>231.318</v>
+        <v>176.1617</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>40.8309</v>
+        <v>40.0299</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>82.02760000000001</v>
+        <v>63.5199</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>128.9002</v>
+        <v>96.1986</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1388.2501</v>
+        <v>1361.0178</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2788.9393</v>
+        <v>2159.6774</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>4382.6056</v>
+        <v>3270.7539</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1252.1471</v>
+        <v>1227.5847</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2515.5138</v>
+        <v>1947.9443</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3952.9384</v>
+        <v>2950.0918</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1252.1471</v>
+        <v>1227.5847</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2515.5138</v>
+        <v>1947.9443</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>3952.9384</v>
+        <v>2950.0918</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13.407</v>
+        <v>13.2735</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>23.3745</v>
+        <v>20.0655</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>34.8075</v>
+        <v>28.9185</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8938</v>
+        <v>8849</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15583</v>
+        <v>13377</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>23205</v>
+        <v>19279</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>11.7697</v>
+        <v>11.5304</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>23.2859</v>
+        <v>17.3561</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>36.8888</v>
+        <v>26.3357</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3872</v>
+        <v>3783</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7894</v>
+        <v>5688</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>12670</v>
+        <v>8744</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>4.1213</v>
+        <v>4.0557</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.3538</v>
+        <v>6.7582</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>13.4686</v>
+        <v>10.6327</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.6789</v>
+        <v>3.62</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.5311</v>
+        <v>6.101</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>12.2023</v>
+        <v>9.6609</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.9197</v>
+        <v>0.905</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.8828</v>
+        <v>1.5252</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3.0506</v>
+        <v>2.4152</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1249.3277</v>
+        <v>1229.5942</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2524.3733</v>
+        <v>2039.8245</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>4065.4366</v>
+        <v>3205.0596</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1275.4865</v>
+        <v>-1277.0094</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>742.8384</v>
+        <v>742.5916</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3496.3335</v>
+        <v>3530.3677</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-63.7743</v>
+        <v>-63.8505</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>37.1419</v>
+        <v>37.1296</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>174.8167</v>
+        <v>176.5184</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-63.7743</v>
+        <v>-63.8505</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.4102</v>
+        <v>1.3988</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.87479999999999</v>
+        <v>70.2929</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>32.8439</v>
+        <v>32.3793</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>65.1585</v>
+        <v>53.7528</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.0047</v>
+        <v>82.76439999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-96.6182</v>
+        <v>-96.2298</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-63.7483</v>
+        <v>-52.3541</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-34.1299</v>
+        <v>-12.4715</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7317</v>
+        <v>35.7308</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>105.9419</v>
+        <v>106.2255</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2890.572</v>
+        <v>2889.9629</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3573.1711</v>
+        <v>3573.0797</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4237.6767</v>
+        <v>4249.0215</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.0585</v>
+        <v>0.057</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3662</v>
+        <v>0.3036</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.8724</v>
+        <v>0.7171</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1038.9509</v>
+        <v>1011.7819</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>6502.6605</v>
+        <v>5390.9981</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>15491.7933</v>
+        <v>12734.1808</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>398.8304</v>
+        <v>392.0252</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>809.7293</v>
+        <v>653.25</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1304.2598</v>
+        <v>1026.6302</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>398.8304</v>
+        <v>392.0252</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>809.7293</v>
+        <v>653.25</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1304.2598</v>
+        <v>1026.6302</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2492.6899</v>
+        <v>2450.1577</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5060.8084</v>
+        <v>4082.8123</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>8151.6237</v>
+        <v>6416.439</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2492.6899</v>
+        <v>2450.1577</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5060.8084</v>
+        <v>4082.8123</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>8151.6237</v>
+        <v>6416.439</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2082.2128</v>
+        <v>2049.3237</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4207.2888</v>
+        <v>3399.7075</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>6775.7277</v>
+        <v>5341.766</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1666.2388</v>
+        <v>1639.9547</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3424.4496</v>
+        <v>2780.5835</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>5563.2407</v>
+        <v>4420.6416</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>108.9508</v>
+        <v>106.7958</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>222.256</v>
+        <v>168.8408</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>356.1837</v>
+        <v>261.1211</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>259.27</v>
+        <v>254.82</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>512.83</v>
+        <v>402.53</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>808.55</v>
+        <v>612.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>410.4771</v>
+        <v>400.834</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>853.5196</v>
+        <v>683.1048</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1375.8961</v>
+        <v>1074.6731</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>282.4218</v>
+        <v>277.6029</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>573.3896</v>
+        <v>462.5826</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>923.579</v>
+        <v>726.9825</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2492.6899</v>
+        <v>2450.1577</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>5060.8084</v>
+        <v>4082.8123</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>8151.6237</v>
+        <v>6416.439</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1495.614</v>
+        <v>1470.0946</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3036.485</v>
+        <v>2449.6874</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4890.9742</v>
+        <v>3849.8634</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2492.6899</v>
+        <v>2450.1577</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5060.8084</v>
+        <v>4082.8123</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>8151.6237</v>
+        <v>6416.439</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2082.2128</v>
+        <v>2049.3237</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4207.2888</v>
+        <v>3399.7075</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>6775.7277</v>
+        <v>5341.766</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1666.2388</v>
+        <v>1639.9547</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3424.4496</v>
+        <v>2780.5835</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>5563.2407</v>
+        <v>4420.6416</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>108.9508</v>
+        <v>106.7958</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>222.256</v>
+        <v>168.8408</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>356.1837</v>
+        <v>261.1211</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>259.27</v>
+        <v>254.82</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>512.83</v>
+        <v>402.53</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>808.55</v>
+        <v>612.25</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>410.4771</v>
+        <v>400.834</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>853.5196</v>
+        <v>683.1048</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1375.8961</v>
+        <v>1074.6731</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.2068</v>
+        <v>1.2119</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.4326</v>
+        <v>1.4314</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.7883</v>
+        <v>1.7462</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.2068</v>
+        <v>1.2119</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.4326</v>
+        <v>1.4314</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.7883</v>
+        <v>1.7462</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>390.8567</v>
+        <v>386.1985</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>940.2182</v>
+        <v>758.9356</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1891.8937</v>
+        <v>1456.3662</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>323.8795</v>
+        <v>318.6629</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>656.3241</v>
+        <v>530.2021</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1057.8993</v>
+        <v>834.0142</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>232.8083</v>
+        <v>231.7756</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>615.6323</v>
+        <v>499.2114</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1371.2757</v>
+        <v>1050.4788</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>390.8567</v>
+        <v>386.1985</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>940.2182</v>
+        <v>758.9356</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1891.8937</v>
+        <v>1456.3662</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>158.0484</v>
+        <v>154.4229</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>324.586</v>
+        <v>259.7242</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>520.6180000000001</v>
+        <v>405.8874</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>138.3871</v>
+        <v>135.0582</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>288.0206</v>
+        <v>230.5122</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>464.338</v>
+        <v>362.6941</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>294.92</v>
+        <v>290.47</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>548.48</v>
+        <v>438.18</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>844.2</v>
+        <v>647.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>259.27</v>
+        <v>254.82</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>512.83</v>
+        <v>402.53</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>808.55</v>
+        <v>612.25</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.5118</v>
+        <v>7.5019</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3813</v>
+        <v>7.3747</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2268</v>
+        <v>7.2346</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2936.0516</v>
+        <v>2897.216</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6940.0721</v>
+        <v>5596.9351</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>13672.3278</v>
+        <v>10536.1566</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>332.6547</v>
+        <v>328.2546</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>786.3102</v>
+        <v>634.1327</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1549.0747</v>
+        <v>1193.7465</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>390.8567</v>
+        <v>386.1985</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>940.2182</v>
+        <v>758.9356</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1891.8937</v>
+        <v>1456.3662</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.3962</v>
+        <v>2.3994</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4386</v>
+        <v>2.4408</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4907</v>
+        <v>2.4881</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.5118</v>
+        <v>7.5019</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3813</v>
+        <v>7.3747</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2268</v>
+        <v>7.2346</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2314.4374</v>
+        <v>2288.7913</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5759.8221</v>
+        <v>4648.4065</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>11995.4597</v>
+        <v>9203.813099999999</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>226.0579</v>
+        <v>233.7352</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1457.2832</v>
+        <v>1175.7594</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>4850.6966</v>
+        <v>3597.9634</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>2936.0516</v>
+        <v>2897.216</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6940.0721</v>
+        <v>5596.9351</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>13672.3278</v>
+        <v>10536.1566</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>173.1417</v>
+        <v>170.6586</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>353.042</v>
+        <v>286.3118</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>573.4176</v>
+        <v>454.8536</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>129.6486</v>
+        <v>127.7893</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>264.358</v>
+        <v>214.3904</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>429.3754</v>
+        <v>340.5946</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2883.1354</v>
+        <v>2834.1395</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5835.8309</v>
+        <v>4707.4874</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>9395.0489</v>
+        <v>7393.0468</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2158.8933</v>
+        <v>2122.2051</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4369.8733</v>
+        <v>3524.9691</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>7035.0176</v>
+        <v>5535.9174</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>743.9463</v>
+        <v>735.3122</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1907.4963</v>
+        <v>1537.3689</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>4072.1236</v>
+        <v>3114.3803</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2936.0516</v>
+        <v>2897.216</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>6940.0721</v>
+        <v>5596.9351</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>13672.3278</v>
+        <v>10536.1566</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>173.1417</v>
+        <v>170.6586</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>353.042</v>
+        <v>286.3118</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>573.4176</v>
+        <v>454.8536</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>129.6486</v>
+        <v>127.7893</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>264.358</v>
+        <v>214.3904</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>429.3754</v>
+        <v>340.5946</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1249.3277</v>
+        <v>1229.5942</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2524.3733</v>
+        <v>2039.8245</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>4065.4366</v>
+        <v>3205.0596</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>226.3887</v>
+        <v>234.0616</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1458.0651</v>
+        <v>1176.39</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>4852.237</v>
+        <v>3599.1505</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2936.3824</v>
+        <v>2897.5425</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>6940.8541</v>
+        <v>5597.5657</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>13673.8682</v>
+        <v>10537.3437</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>173.1417</v>
+        <v>170.6586</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>353.042</v>
+        <v>286.3118</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>573.4176</v>
+        <v>454.8536</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>129.6486</v>
+        <v>127.7893</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>264.358</v>
+        <v>214.3904</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>429.3754</v>
+        <v>340.5946</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2883.1354</v>
+        <v>2834.1395</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5835.8309</v>
+        <v>4707.4874</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>9395.0489</v>
+        <v>7393.0468</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2158.8933</v>
+        <v>2122.2051</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4369.8733</v>
+        <v>3524.9691</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>7035.0176</v>
+        <v>5535.9174</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>744.0786000000001</v>
+        <v>735.4428</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1907.8091</v>
+        <v>1537.6212</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>4072.7397</v>
+        <v>3114.8551</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>2936.3824</v>
+        <v>2897.5425</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>6940.8541</v>
+        <v>5597.5657</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>13673.8682</v>
+        <v>10537.3437</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>173.1417</v>
+        <v>170.6586</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>353.042</v>
+        <v>286.3118</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>573.4176</v>
+        <v>454.8536</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>129.6486</v>
+        <v>127.7893</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>264.358</v>
+        <v>214.3904</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>429.3754</v>
+        <v>340.5946</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1249.3277</v>
+        <v>1229.5942</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2524.3733</v>
+        <v>2039.8245</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>4065.4366</v>
+        <v>3205.0596</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>781.3342</v>
+        <v>790.208</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>3073.3489</v>
+        <v>2488.6124</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>8745.8827</v>
+        <v>6568.8554</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>777.8987</v>
+        <v>774.1462</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2162.7439</v>
+        <v>1749.6544</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>4999.1978</v>
+        <v>3810.1868</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2314.4374</v>
+        <v>2288.7913</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5759.8221</v>
+        <v>4648.4065</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>11995.4597</v>
+        <v>9203.813099999999</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>390.8567</v>
+        <v>386.1985</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>940.2182</v>
+        <v>758.9356</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1891.8937</v>
+        <v>1456.3662</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1249.3277</v>
+        <v>1229.5942</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2524.3733</v>
+        <v>2039.8245</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>4065.4366</v>
+        <v>3205.0596</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1570.3588</v>
+        <v>1553.3485</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3852.013</v>
+        <v>3110.7853</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>7922.72</v>
+        <v>6088.958</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2314.4374</v>
+        <v>2288.7913</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>5759.8221</v>
+        <v>4648.4065</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>11995.4597</v>
+        <v>9203.813099999999</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>390.8567</v>
+        <v>386.1985</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>940.2182</v>
+        <v>758.9356</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1891.8937</v>
+        <v>1456.3662</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1249.3277</v>
+        <v>1229.5942</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2524.3733</v>
+        <v>2039.8245</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>4065.4366</v>
+        <v>3205.0596</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>744.0786000000001</v>
+        <v>735.4428</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1907.8091</v>
+        <v>1537.6212</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>4072.7397</v>
+        <v>3114.8551</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>2936.3824</v>
+        <v>2897.5425</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>6940.8541</v>
+        <v>5597.5657</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>13673.8682</v>
+        <v>10537.3437</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>173.1417</v>
+        <v>170.6586</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>353.042</v>
+        <v>286.3118</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>573.4176</v>
+        <v>454.8536</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>129.6486</v>
+        <v>127.7893</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>264.358</v>
+        <v>214.3904</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>429.3754</v>
+        <v>340.5946</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1249.3277</v>
+        <v>1229.5942</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2524.3733</v>
+        <v>2039.8245</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>4065.4366</v>
+        <v>3205.0596</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.1647</v>
+        <v>-0.1636</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.1687</v>
+        <v>-0.1673</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1688</v>
+        <v>-0.1675</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.4989</v>
+        <v>-0.4945</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4753</v>
+        <v>-0.4716</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4458</v>
+        <v>-0.445</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1011.7819</v>
+        <v>1064.5785</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5390.9981</v>
+        <v>6607.7638</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12734.1808</v>
+        <v>15696.4132</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1011.7819</v>
+        <v>1064.5785</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5390.9981</v>
+        <v>6607.7638</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12734.1808</v>
+        <v>15696.4132</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2288.7913</v>
+        <v>2341.8068</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4648.4065</v>
+        <v>5865.8201</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9203.813099999999</v>
+        <v>12200.0797</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5721.9782</v>
+        <v>5854.5169</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11621.0162</v>
+        <v>14664.5503</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>23009.5327</v>
+        <v>30500.1991</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6951.5724</v>
+        <v>7080.9546</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>13660.8407</v>
+        <v>17168.6821</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26214.5923</v>
+        <v>34565.6357</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>386.1985</v>
+        <v>393.3864</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>758.9356</v>
+        <v>953.8157</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1456.3662</v>
+        <v>1920.3131</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>461.6131</v>
+        <v>468.5215</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>876.2616</v>
+        <v>1100.9583</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1632.5279</v>
+        <v>2151.6311</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>157.1308</v>
+        <v>156.4322</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>299.399</v>
+        <v>382.8592</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>544.5869</v>
+        <v>729.7124</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1227.5847</v>
+        <v>1222.1264</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1947.9443</v>
+        <v>2490.9514</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2950.0918</v>
+        <v>3952.9384</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2332500</v>
+        <v>2328700</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3687400</v>
+        <v>4093900</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5415400</v>
+        <v>6169100</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>187.9627</v>
+        <v>187.4323</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>188.668</v>
+        <v>217.3051</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>194.557</v>
+        <v>228.8444</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>274.0376</v>
+        <v>281.7634</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>530.5842</v>
+        <v>659.2519</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1018.3897</v>
+        <v>1329.0583</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>298.7221</v>
+        <v>298.1405</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>504.7638</v>
+        <v>617.4896</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>800.1961</v>
+        <v>1009.1272</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>286.6307</v>
+        <v>286.0983</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>486.3627</v>
+        <v>593.8756</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>772.4106</v>
+        <v>971.6743</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>12.0914</v>
+        <v>12.0422</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>18.4011</v>
+        <v>23.614</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>27.7855</v>
+        <v>37.4529</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>20.1524</v>
+        <v>20.0703</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>30.6685</v>
+        <v>39.3566</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46.3092</v>
+        <v>62.4215</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7.3343</v>
+        <v>7.6266</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8.676399999999999</v>
+        <v>8.8695</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10.9387</v>
+        <v>11.321</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>25.9563</v>
+        <v>25.8505</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>39.501</v>
+        <v>50.6914</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>59.6463</v>
+        <v>80.3989</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20.1524</v>
+        <v>20.0703</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>30.6685</v>
+        <v>39.3566</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46.3092</v>
+        <v>62.4215</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.4884</v>
+        <v>4.4754</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6.7774</v>
+        <v>8.155900000000001</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9.904999999999999</v>
+        <v>12.4614</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.3157</v>
+        <v>0.3144</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.4756</v>
+        <v>0.6204</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.7166</v>
+        <v>0.9851</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2.105</v>
+        <v>2.0959</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3.1704</v>
+        <v>4.1358</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>4.7774</v>
+        <v>6.5676</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4.1727</v>
+        <v>4.161</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>6.3019</v>
+        <v>7.5355</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.1884</v>
+        <v>11.4763</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>75.4147</v>
+        <v>75.13509999999999</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>117.326</v>
+        <v>147.1427</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>176.1617</v>
+        <v>231.318</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>40.0299</v>
+        <v>39.8519</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>63.5199</v>
+        <v>81.22669999999999</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>96.1986</v>
+        <v>128.9002</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1361.0178</v>
+        <v>1354.9662</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2159.6774</v>
+        <v>2761.707</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3270.7539</v>
+        <v>4382.6056</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1227.5847</v>
+        <v>1222.1264</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1947.9443</v>
+        <v>2490.9514</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2950.0918</v>
+        <v>3952.9384</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1227.5847</v>
+        <v>1222.1264</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1947.9443</v>
+        <v>2490.9514</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2950.0918</v>
+        <v>3952.9384</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13.2735</v>
+        <v>13.2435</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>20.0655</v>
+        <v>23.241</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>28.9185</v>
+        <v>34.8075</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8849</v>
+        <v>8829</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>13377</v>
+        <v>15494</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>19279</v>
+        <v>23205</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>11.5304</v>
+        <v>11.4767</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>17.3561</v>
+        <v>23.0466</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>26.3357</v>
+        <v>36.8888</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3783</v>
+        <v>3763</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>5688</v>
+        <v>7805</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>8744</v>
+        <v>12670</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>4.0557</v>
+        <v>4.047</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>6.7582</v>
+        <v>8.2882</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>10.6327</v>
+        <v>13.4686</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.62</v>
+        <v>3.6128</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>6.101</v>
+        <v>7.4721</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>9.6609</v>
+        <v>12.2023</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.905</v>
+        <v>0.9032</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.5252</v>
+        <v>1.868</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2.4152</v>
+        <v>3.0506</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1229.5942</v>
+        <v>1226.4377</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2039.8245</v>
+        <v>2504.1317</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3205.0596</v>
+        <v>4065.4366</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1277.0094</v>
+        <v>-1277.2282</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>742.5916</v>
+        <v>741.9437</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3530.3677</v>
+        <v>3496.3335</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-63.8505</v>
+        <v>-63.8614</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>37.1296</v>
+        <v>37.0972</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>176.5184</v>
+        <v>174.8167</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-63.8505</v>
+        <v>-63.8614</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.3988</v>
+        <v>1.3688</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>70.2929</v>
+        <v>68.87479999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>32.3793</v>
+        <v>32.3125</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>53.7528</v>
+        <v>64.67829999999999</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>82.76439999999999</v>
+        <v>103.0047</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-96.2298</v>
+        <v>-96.17400000000001</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-52.3541</v>
+        <v>-63.3095</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-12.4715</v>
+        <v>-34.1299</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7308</v>
+        <v>35.7284</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>106.2255</v>
+        <v>105.9419</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2889.9629</v>
+        <v>2889.8753</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3573.0797</v>
+        <v>3572.8397</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4249.0215</v>
+        <v>4237.6767</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.057</v>
+        <v>0.06</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3036</v>
+        <v>0.3721</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.7171</v>
+        <v>0.884</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1011.7819</v>
+        <v>1064.5785</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>5390.9981</v>
+        <v>6607.7638</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>12734.1808</v>
+        <v>15696.4132</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>392.0252</v>
+        <v>391.3597</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>653.25</v>
+        <v>803.0578</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1026.6302</v>
+        <v>1304.2598</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>392.0252</v>
+        <v>391.3597</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>653.25</v>
+        <v>803.0578</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1026.6302</v>
+        <v>1304.2598</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2450.1577</v>
+        <v>2445.9982</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4082.8123</v>
+        <v>5019.1115</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>6416.439</v>
+        <v>8151.6237</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2450.1577</v>
+        <v>2445.9982</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4082.8123</v>
+        <v>5019.1115</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6416.439</v>
+        <v>8151.6237</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2049.3237</v>
+        <v>2044.0628</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>3399.7075</v>
+        <v>4173.5529</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5341.766</v>
+        <v>6775.7277</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1639.9547</v>
+        <v>1636.1781</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2780.5835</v>
+        <v>3397.3187</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4420.6416</v>
+        <v>5563.2407</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>106.7958</v>
+        <v>106.3115</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>168.8408</v>
+        <v>220.101</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>261.1211</v>
+        <v>356.1837</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>254.82</v>
+        <v>253.82</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>402.53</v>
+        <v>508.38</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>612.25</v>
+        <v>808.55</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>400.834</v>
+        <v>401.9353</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>683.1048</v>
+        <v>845.5586</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1074.6731</v>
+        <v>1375.8961</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>277.6029</v>
+        <v>277.1316</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>462.5826</v>
+        <v>568.6653</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>726.9825</v>
+        <v>923.579</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2450.1577</v>
+        <v>2445.9982</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4082.8123</v>
+        <v>5019.1115</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6416.439</v>
+        <v>8151.6237</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1470.0946</v>
+        <v>1467.5989</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2449.6874</v>
+        <v>3011.4669</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>3849.8634</v>
+        <v>4890.9742</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2450.1577</v>
+        <v>2445.9982</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4082.8123</v>
+        <v>5019.1115</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6416.439</v>
+        <v>8151.6237</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2049.3237</v>
+        <v>2044.0628</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>3399.7075</v>
+        <v>4173.5529</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5341.766</v>
+        <v>6775.7277</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1639.9547</v>
+        <v>1636.1781</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>2780.5835</v>
+        <v>3397.3187</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4420.6416</v>
+        <v>5563.2407</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>106.7958</v>
+        <v>106.3115</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>168.8408</v>
+        <v>220.101</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>261.1211</v>
+        <v>356.1837</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>254.82</v>
+        <v>253.82</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>402.53</v>
+        <v>508.38</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>612.25</v>
+        <v>808.55</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>400.834</v>
+        <v>401.9353</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>683.1048</v>
+        <v>845.5586</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1074.6731</v>
+        <v>1375.8961</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.2119</v>
+        <v>1.2374</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.4314</v>
+        <v>1.4651</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.7462</v>
+        <v>1.8152</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.2119</v>
+        <v>1.2374</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.4314</v>
+        <v>1.4651</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.7462</v>
+        <v>1.8152</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>386.1985</v>
+        <v>393.3864</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>758.9356</v>
+        <v>953.8157</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1456.3662</v>
+        <v>1920.3131</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>318.6629</v>
+        <v>317.9105</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>530.2021</v>
+        <v>651.0261</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>834.0142</v>
+        <v>1057.8993</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>231.7756</v>
+        <v>238.5914</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>499.2114</v>
+        <v>632.2327</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1050.4788</v>
+        <v>1399.6951</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>386.1985</v>
+        <v>393.3864</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>758.9356</v>
+        <v>953.8157</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1456.3662</v>
+        <v>1920.3131</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>154.4229</v>
+        <v>154.795</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>259.7242</v>
+        <v>321.583</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>405.8874</v>
+        <v>520.6180000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>135.0582</v>
+        <v>135.497</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>230.5122</v>
+        <v>285.3143</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>362.6941</v>
+        <v>464.338</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>290.47</v>
+        <v>289.47</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>438.18</v>
+        <v>544.03</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>647.9</v>
+        <v>844.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>254.82</v>
+        <v>253.82</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>402.53</v>
+        <v>508.38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>612.25</v>
+        <v>808.55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.5019</v>
+        <v>7.4878</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3747</v>
+        <v>7.3635</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2346</v>
+        <v>7.2178</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2897.216</v>
+        <v>2945.618</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>5596.9351</v>
+        <v>7023.4555</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>10536.1566</v>
+        <v>13860.4529</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>328.2546</v>
+        <v>333.7385</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>634.1327</v>
+        <v>795.7575000000001</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1193.7465</v>
+        <v>1570.3893</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>386.1985</v>
+        <v>393.3864</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>758.9356</v>
+        <v>953.8157</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1456.3662</v>
+        <v>1920.3131</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.3994</v>
+        <v>2.4039</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4408</v>
+        <v>2.4445</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4881</v>
+        <v>2.4938</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.5019</v>
+        <v>7.4878</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3747</v>
+        <v>7.3635</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2346</v>
+        <v>7.2178</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2288.7913</v>
+        <v>2341.8068</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>4648.4065</v>
+        <v>5865.8201</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>9203.813099999999</v>
+        <v>12200.0797</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>233.7352</v>
+        <v>286.4381</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1175.7594</v>
+        <v>1585.9947</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>3597.9634</v>
+        <v>5038.8217</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>2897.216</v>
+        <v>2945.618</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>5596.9351</v>
+        <v>7023.4555</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>10536.1566</v>
+        <v>13860.4529</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>170.6586</v>
+        <v>170.0613</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>286.3118</v>
+        <v>350.3118</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>454.8536</v>
+        <v>573.4176</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>127.7893</v>
+        <v>127.342</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>214.3904</v>
+        <v>262.3136</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>340.5946</v>
+        <v>429.3754</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2834.1395</v>
+        <v>2829.2412</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>4707.4874</v>
+        <v>5787.7725</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>7393.0468</v>
+        <v>9395.0489</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2122.2051</v>
+        <v>2118.5373</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3524.9691</v>
+        <v>4333.8872</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5535.9174</v>
+        <v>7035.0176</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>735.3122</v>
+        <v>755.6967</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1537.3689</v>
+        <v>1947.8542</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>3114.3803</v>
+        <v>4147.3736</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2897.216</v>
+        <v>2945.618</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>5596.9351</v>
+        <v>7023.4555</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>10536.1566</v>
+        <v>13860.4529</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>170.6586</v>
+        <v>170.0613</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>286.3118</v>
+        <v>350.3118</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>454.8536</v>
+        <v>573.4176</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>127.7893</v>
+        <v>127.342</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>214.3904</v>
+        <v>262.3136</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>340.5946</v>
+        <v>429.3754</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1229.5942</v>
+        <v>1226.4377</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2039.8245</v>
+        <v>2504.1317</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3205.0596</v>
+        <v>4065.4366</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>234.0616</v>
+        <v>286.77</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1176.39</v>
+        <v>1586.786</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>3599.1505</v>
+        <v>5040.3833</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2897.5425</v>
+        <v>2945.9499</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>5597.5657</v>
+        <v>7024.2468</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>10537.3437</v>
+        <v>13862.0145</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>170.6586</v>
+        <v>170.0613</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>286.3118</v>
+        <v>350.3118</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>454.8536</v>
+        <v>573.4176</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>127.7893</v>
+        <v>127.342</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>214.3904</v>
+        <v>262.3136</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>340.5946</v>
+        <v>429.3754</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2834.1395</v>
+        <v>2829.2412</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>4707.4874</v>
+        <v>5787.7725</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>7393.0468</v>
+        <v>9395.0489</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2122.2051</v>
+        <v>2118.5373</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3524.9691</v>
+        <v>4333.8872</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>5535.9174</v>
+        <v>7035.0176</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>735.4428</v>
+        <v>755.8294</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1537.6212</v>
+        <v>1948.1707</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3114.8551</v>
+        <v>4147.9982</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>2897.5425</v>
+        <v>2945.9499</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>5597.5657</v>
+        <v>7024.2468</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>10537.3437</v>
+        <v>13862.0145</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>170.6586</v>
+        <v>170.0613</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>286.3118</v>
+        <v>350.3118</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>454.8536</v>
+        <v>573.4176</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>127.7893</v>
+        <v>127.342</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>214.3904</v>
+        <v>262.3136</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>340.5946</v>
+        <v>429.3754</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1229.5942</v>
+        <v>1226.4377</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2039.8245</v>
+        <v>2504.1317</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>3205.0596</v>
+        <v>4065.4366</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>790.208</v>
+        <v>865.7138</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2488.6124</v>
+        <v>3262.2268</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>6568.8554</v>
+        <v>9030.076999999999</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>774.1462</v>
+        <v>803.1738</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1749.6544</v>
+        <v>2230.8167</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>3810.1868</v>
+        <v>5112.8755</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2288.7913</v>
+        <v>2341.8068</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>4648.4065</v>
+        <v>5865.8201</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>9203.813099999999</v>
+        <v>12200.0797</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>386.1985</v>
+        <v>393.3864</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>758.9356</v>
+        <v>953.8157</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1456.3662</v>
+        <v>1920.3131</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1229.5942</v>
+        <v>1226.4377</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2039.8245</v>
+        <v>2504.1317</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>3205.0596</v>
+        <v>4065.4366</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1553.3485</v>
+        <v>1585.9774</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3110.7853</v>
+        <v>3917.6494</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>6088.958</v>
+        <v>8052.0814</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2288.7913</v>
+        <v>2341.8068</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>4648.4065</v>
+        <v>5865.8201</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>9203.813099999999</v>
+        <v>12200.0797</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>386.1985</v>
+        <v>393.3864</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>758.9356</v>
+        <v>953.8157</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1456.3662</v>
+        <v>1920.3131</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1229.5942</v>
+        <v>1226.4377</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2039.8245</v>
+        <v>2504.1317</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3205.0596</v>
+        <v>4065.4366</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>735.4428</v>
+        <v>755.8294</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1537.6212</v>
+        <v>1948.1707</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>3114.8551</v>
+        <v>4147.9982</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>2897.5425</v>
+        <v>2945.9499</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>5597.5657</v>
+        <v>7024.2468</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>10537.3437</v>
+        <v>13862.0145</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>170.6586</v>
+        <v>170.0613</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>286.3118</v>
+        <v>350.3118</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>454.8536</v>
+        <v>573.4176</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>127.7893</v>
+        <v>127.342</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>214.3904</v>
+        <v>262.3136</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>340.5946</v>
+        <v>429.3754</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1229.5942</v>
+        <v>1226.4377</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2039.8245</v>
+        <v>2504.1317</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>3205.0596</v>
+        <v>4065.4366</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.1636</v>
+        <v>-0.1643</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.1673</v>
+        <v>-0.1685</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1675</v>
+        <v>-0.1688</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.4945</v>
+        <v>-0.4929</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4716</v>
+        <v>-0.4715</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.445</v>
+        <v>-0.4443</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1064.5785</v>
+        <v>2298.5616</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6607.7638</v>
+        <v>8042.9096</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15696.4132</v>
+        <v>18300.285</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1064.5785</v>
+        <v>2298.5616</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6607.7638</v>
+        <v>8042.9096</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15696.4132</v>
+        <v>18300.285</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2341.8068</v>
+        <v>3518.7054</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5865.8201</v>
+        <v>7271.4996</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12200.0797</v>
+        <v>14768.2263</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5854.5169</v>
+        <v>8796.7636</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14664.5503</v>
+        <v>18178.7491</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>30500.1991</v>
+        <v>36920.5659</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7080.9546</v>
+        <v>10746.2346</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>17168.6821</v>
+        <v>21471.191</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34565.6357</v>
+        <v>42054.4838</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>393.3864</v>
+        <v>597.013</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>953.8157</v>
+        <v>1192.8439</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1920.3131</v>
+        <v>2336.3602</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>468.5215</v>
+        <v>722.7392</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1100.9583</v>
+        <v>1395.9028</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2151.6311</v>
+        <v>2645.0063</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>156.4322</v>
+        <v>261.1339</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>382.8592</v>
+        <v>510.1726</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>729.7124</v>
+        <v>937.2616</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1222.1264</v>
+        <v>2040.1083</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2490.9514</v>
+        <v>3319.2754</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3952.9384</v>
+        <v>5077.2565</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2328700</v>
+        <v>2886500</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4093900</v>
+        <v>4670100</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6169100</v>
+        <v>6927100</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>187.4323</v>
+        <v>252.4199</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>217.3051</v>
+        <v>253.8394</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>228.8444</v>
+        <v>261.7698</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>281.7634</v>
+        <v>404.2597</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>659.2519</v>
+        <v>793.2374</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1329.0583</v>
+        <v>1567.1086</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>298.1405</v>
+        <v>460.7957</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>617.4896</v>
+        <v>786.9899</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1009.1272</v>
+        <v>1235.5121</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>286.0983</v>
+        <v>437.5472</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>593.8756</v>
+        <v>749.4215</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>971.6743</v>
+        <v>1178.2443</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>12.0422</v>
+        <v>23.2486</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>23.614</v>
+        <v>37.5684</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.4529</v>
+        <v>57.2678</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>20.0703</v>
+        <v>38.7476</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>39.3566</v>
+        <v>62.614</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>62.4215</v>
+        <v>95.4464</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7.6266</v>
+        <v>7.0739</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8.8695</v>
+        <v>8.280900000000001</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.321</v>
+        <v>10.7534</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>25.8505</v>
+        <v>49.9069</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>50.6914</v>
+        <v>80.6469</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>80.3989</v>
+        <v>122.935</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20.0703</v>
+        <v>38.7476</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>39.3566</v>
+        <v>62.614</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>62.4215</v>
+        <v>95.4464</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.4754</v>
+        <v>7.4388</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8.155900000000001</v>
+        <v>11.846</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12.4614</v>
+        <v>17.7012</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.3144</v>
+        <v>0.6257</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.6204</v>
+        <v>1.008</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.9851</v>
+        <v>1.5356</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2.0959</v>
+        <v>4.1711</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4.1358</v>
+        <v>6.7199</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6.5676</v>
+        <v>10.2371</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4.161</v>
+        <v>6.8131</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7.5355</v>
+        <v>10.838</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11.4763</v>
+        <v>16.1657</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>75.13509999999999</v>
+        <v>125.7262</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>147.1427</v>
+        <v>203.0589</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>231.318</v>
+        <v>308.6461</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>39.8519</v>
+        <v>66.5253</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>81.22669999999999</v>
+        <v>108.2372</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>128.9002</v>
+        <v>165.5627</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1354.9662</v>
+        <v>2261.8592</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2761.707</v>
+        <v>3680.0662</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>4382.6056</v>
+        <v>5629.1322</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1222.1264</v>
+        <v>2040.1083</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2490.9514</v>
+        <v>3319.2754</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3952.9384</v>
+        <v>5077.2565</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1222.1264</v>
+        <v>2040.1083</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2490.9514</v>
+        <v>3319.2754</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>3952.9384</v>
+        <v>5077.2565</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13.2435</v>
+        <v>20.07</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>23.241</v>
+        <v>31.7415</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>34.8075</v>
+        <v>46.878</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8829</v>
+        <v>13380</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15494</v>
+        <v>21161</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>23205</v>
+        <v>31252</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>11.4767</v>
+        <v>23.7098</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>23.0466</v>
+        <v>38.2795</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>36.8888</v>
+        <v>58.5191</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3763</v>
+        <v>8314</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7805</v>
+        <v>13472</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>12670</v>
+        <v>20717</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>4.047</v>
+        <v>6.3958</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.2882</v>
+        <v>10.8231</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>13.4686</v>
+        <v>16.8994</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3.6128</v>
+        <v>5.6203</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.4721</v>
+        <v>9.582000000000001</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>12.2023</v>
+        <v>15.0296</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.9032</v>
+        <v>1.4051</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.868</v>
+        <v>2.3955</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3.0506</v>
+        <v>3.7574</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1226.4377</v>
+        <v>1949.471</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2504.1317</v>
+        <v>3292.4419</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>4065.4366</v>
+        <v>5133.9179</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1277.2282</v>
+        <v>-1220.1438</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>741.9437</v>
+        <v>771.41</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3496.3335</v>
+        <v>3532.0586</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-63.8614</v>
+        <v>-61.0072</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>37.0972</v>
+        <v>38.5705</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>174.8167</v>
+        <v>176.6029</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-63.8614</v>
+        <v>-61.0072</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.3688</v>
+        <v>2.733</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.87479999999999</v>
+        <v>70.3633</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>32.3125</v>
+        <v>47.6529</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>64.67829999999999</v>
+        <v>80.4935</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.0047</v>
+        <v>123.9601</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-96.17400000000001</v>
+        <v>-108.6601</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-63.3095</v>
+        <v>-77.7606</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-34.1299</v>
+        <v>-53.5968</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.7284</v>
+        <v>35.8375</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>105.9419</v>
+        <v>106.2396</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2889.8753</v>
+        <v>2912.7091</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3572.8397</v>
+        <v>3583.7531</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4237.6767</v>
+        <v>4249.5851</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1294</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.3721</v>
+        <v>0.4529</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.884</v>
+        <v>1.0306</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1064.5785</v>
+        <v>2298.5616</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>6607.7638</v>
+        <v>8042.9096</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>15696.4132</v>
+        <v>18300.285</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>391.3597</v>
+        <v>621.4655</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>803.0578</v>
+        <v>1050.3628</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1304.2598</v>
+        <v>1638.6857</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>391.3597</v>
+        <v>621.4655</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>803.0578</v>
+        <v>1050.3628</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1304.2598</v>
+        <v>1638.6857</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>2445.9982</v>
+        <v>3884.1593</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5019.1115</v>
+        <v>6564.7674</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>8151.6237</v>
+        <v>10241.7855</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2445.9982</v>
+        <v>3884.1593</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5019.1115</v>
+        <v>6564.7674</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>8151.6237</v>
+        <v>10241.7855</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>2044.0628</v>
+        <v>3249.1183</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4173.5529</v>
+        <v>5487.4031</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>6775.7277</v>
+        <v>8556.5298</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1636.1781</v>
+        <v>2503.4874</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3397.3187</v>
+        <v>4290.6004</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>5563.2407</v>
+        <v>6746.846</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>106.3115</v>
+        <v>216.5076</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>220.101</v>
+        <v>357.3194</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>356.1837</v>
+        <v>551.0305</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>253.82</v>
+        <v>481.37</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>508.38</v>
+        <v>791.73</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>808.55</v>
+        <v>1210.9</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>401.9353</v>
+        <v>635.0410000000001</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>845.5586</v>
+        <v>1077.3643</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1375.8961</v>
+        <v>1685.2557</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>277.1316</v>
+        <v>440.0752</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>568.6653</v>
+        <v>743.7881</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>923.579</v>
+        <v>1160.3943</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2445.9982</v>
+        <v>3884.1593</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>5019.1115</v>
+        <v>6564.7674</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>8151.6237</v>
+        <v>10241.7855</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1467.5989</v>
+        <v>2330.4956</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3011.4669</v>
+        <v>3938.8604</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>4890.9742</v>
+        <v>6145.0713</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2445.9982</v>
+        <v>3884.1593</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5019.1115</v>
+        <v>6564.7674</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>8151.6237</v>
+        <v>10241.7855</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2044.0628</v>
+        <v>3249.1183</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4173.5529</v>
+        <v>5487.4031</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>6775.7277</v>
+        <v>8556.5298</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1636.1781</v>
+        <v>2503.4874</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3397.3187</v>
+        <v>4290.6004</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>5563.2407</v>
+        <v>6746.846</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>106.3115</v>
+        <v>216.5076</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>220.101</v>
+        <v>357.3194</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>356.1837</v>
+        <v>551.0305</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>253.82</v>
+        <v>481.37</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>508.38</v>
+        <v>791.73</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>808.55</v>
+        <v>1210.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>401.9353</v>
+        <v>635.0410000000001</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>845.5586</v>
+        <v>1077.3643</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1375.8961</v>
+        <v>1685.2557</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.2374</v>
+        <v>1.1845</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.4651</v>
+        <v>1.3994</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.8152</v>
+        <v>1.7563</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.2374</v>
+        <v>1.1845</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.4651</v>
+        <v>1.3994</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.8152</v>
+        <v>1.7563</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>393.3864</v>
+        <v>597.013</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>953.8157</v>
+        <v>1192.8439</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1920.3131</v>
+        <v>2336.3602</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>317.9105</v>
+        <v>504.0387</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>651.0261</v>
+        <v>852.4032</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1057.8993</v>
+        <v>1330.2952</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>238.5914</v>
+        <v>348.8281</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>632.2327</v>
+        <v>774.901</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1399.6951</v>
+        <v>1685.6686</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>393.3864</v>
+        <v>597.013</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>953.8157</v>
+        <v>1192.8439</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1920.3131</v>
+        <v>2336.3602</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>154.795</v>
+        <v>248.1849</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>321.583</v>
+        <v>417.9429</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>520.6180000000001</v>
+        <v>650.6916</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>135.497</v>
+        <v>213.7169</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>285.3143</v>
+        <v>362.7843</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>464.338</v>
+        <v>567.5883</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>289.47</v>
+        <v>517.02</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>544.03</v>
+        <v>827.38</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>844.2</v>
+        <v>1246.55</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>253.82</v>
+        <v>481.37</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>508.38</v>
+        <v>791.73</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>808.55</v>
+        <v>1210.9</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.4878</v>
+        <v>7.5369</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3635</v>
+        <v>7.3927</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2178</v>
+        <v>7.2341</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2945.618</v>
+        <v>4499.6117</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>7023.4555</v>
+        <v>8818.346799999999</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>13860.4529</v>
+        <v>16901.5275</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>333.7385</v>
+        <v>509.806</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>795.7575000000001</v>
+        <v>999.1187</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1570.3893</v>
+        <v>1914.9431</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>393.3864</v>
+        <v>597.013</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>953.8157</v>
+        <v>1192.8439</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>1920.3131</v>
+        <v>2336.3602</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.4039</v>
+        <v>2.3883</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4445</v>
+        <v>2.4348</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4938</v>
+        <v>2.4882</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.4878</v>
+        <v>7.5369</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3635</v>
+        <v>7.3927</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2178</v>
+        <v>7.2341</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2341.8068</v>
+        <v>3518.7054</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5865.8201</v>
+        <v>7271.4996</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>12200.0797</v>
+        <v>14768.2263</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>286.4381</v>
+        <v>268.8053</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1585.9947</v>
+        <v>1687.7415</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>5038.8217</v>
+        <v>5787.0795</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>2945.618</v>
+        <v>4499.6117</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>7023.4555</v>
+        <v>8818.346799999999</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>13860.4529</v>
+        <v>16901.5275</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>170.0613</v>
+        <v>264.2046</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>350.3118</v>
+        <v>450.8699</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>573.4176</v>
+        <v>708.0028</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>127.342</v>
+        <v>197.8365</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>262.3136</v>
+        <v>337.6116</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>429.3754</v>
+        <v>530.1529</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2829.2412</v>
+        <v>4495.0109</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5787.7725</v>
+        <v>7581.4752</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>9395.0489</v>
+        <v>11822.4508</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2118.5373</v>
+        <v>3365.8666</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4333.8872</v>
+        <v>5677.0127</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>7035.0176</v>
+        <v>8852.6574</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>755.6967</v>
+        <v>1125.7381</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1947.8542</v>
+        <v>2390.7099</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>4147.3736</v>
+        <v>4990.245</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2945.618</v>
+        <v>4499.6117</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>7023.4555</v>
+        <v>8818.346799999999</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>13860.4529</v>
+        <v>16901.5275</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>170.0613</v>
+        <v>264.2046</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>350.3118</v>
+        <v>450.8699</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>573.4176</v>
+        <v>708.0028</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>127.342</v>
+        <v>197.8365</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>262.3136</v>
+        <v>337.6116</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>429.3754</v>
+        <v>530.1529</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1226.4377</v>
+        <v>1949.471</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2504.1317</v>
+        <v>3292.4419</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>4065.4366</v>
+        <v>5133.9179</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>286.77</v>
+        <v>269.3123</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1586.786</v>
+        <v>1688.7351</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>5040.3833</v>
+        <v>5788.9838</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2945.9499</v>
+        <v>4500.1186</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>7024.2468</v>
+        <v>8819.340399999999</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>13862.0145</v>
+        <v>16903.4318</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>170.0613</v>
+        <v>264.2046</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>350.3118</v>
+        <v>450.8699</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>573.4176</v>
+        <v>708.0028</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>127.342</v>
+        <v>197.8365</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>262.3136</v>
+        <v>337.6116</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>429.3754</v>
+        <v>530.1529</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4718,13 +4718,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2829.2412</v>
+        <v>4495.0109</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5787.7725</v>
+        <v>7581.4752</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>9395.0489</v>
+        <v>11822.4508</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2118.5373</v>
+        <v>3365.8666</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4333.8872</v>
+        <v>5677.0127</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>7035.0176</v>
+        <v>8852.6574</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>755.8294</v>
+        <v>1125.9409</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1948.1707</v>
+        <v>2391.1074</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>4147.9982</v>
+        <v>4991.0067</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>2945.9499</v>
+        <v>4500.1186</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>7024.2468</v>
+        <v>8819.340399999999</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>13862.0145</v>
+        <v>16903.4318</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>170.0613</v>
+        <v>264.2046</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>350.3118</v>
+        <v>450.8699</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>573.4176</v>
+        <v>708.0028</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>127.342</v>
+        <v>197.8365</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>262.3136</v>
+        <v>337.6116</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>429.3754</v>
+        <v>530.1529</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1226.4377</v>
+        <v>1949.471</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2504.1317</v>
+        <v>3292.4419</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>4065.4366</v>
+        <v>5133.9179</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>865.7138</v>
+        <v>1083.7318</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>3262.2268</v>
+        <v>3698</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>9030.076999999999</v>
+        <v>10543.1038</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>803.1738</v>
+        <v>1159.9497</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2230.8167</v>
+        <v>2700.1196</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>5112.8755</v>
+        <v>6118.5295</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2341.8068</v>
+        <v>3518.7054</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5865.8201</v>
+        <v>7271.4996</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>12200.0797</v>
+        <v>14768.2263</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>393.3864</v>
+        <v>597.013</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>953.8157</v>
+        <v>1192.8439</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>1920.3131</v>
+        <v>2336.3602</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1226.4377</v>
+        <v>1949.471</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2504.1317</v>
+        <v>3292.4419</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>4065.4366</v>
+        <v>5133.9179</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1585.9774</v>
+        <v>2392.7645</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3917.6494</v>
+        <v>4880.3923</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>8052.0814</v>
+        <v>9777.2197</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>2341.8068</v>
+        <v>3518.7054</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>5865.8201</v>
+        <v>7271.4996</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>12200.0797</v>
+        <v>14768.2263</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>393.3864</v>
+        <v>597.013</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>953.8157</v>
+        <v>1192.8439</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1920.3131</v>
+        <v>2336.3602</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1226.4377</v>
+        <v>1949.471</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2504.1317</v>
+        <v>3292.4419</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>4065.4366</v>
+        <v>5133.9179</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>755.8294</v>
+        <v>1125.9409</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1948.1707</v>
+        <v>2391.1074</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>4147.9982</v>
+        <v>4991.0067</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>2945.9499</v>
+        <v>4500.1186</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>7024.2468</v>
+        <v>8819.340399999999</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>13862.0145</v>
+        <v>16903.4318</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>170.0613</v>
+        <v>264.2046</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>350.3118</v>
+        <v>450.8699</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>573.4176</v>
+        <v>708.0028</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>127.342</v>
+        <v>197.8365</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>262.3136</v>
+        <v>337.6116</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>429.3754</v>
+        <v>530.1529</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1226.4377</v>
+        <v>1949.471</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2504.1317</v>
+        <v>3292.4419</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>4065.4366</v>
+        <v>5133.9179</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>-0.1643</v>
+        <v>-0.1635</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-0.1685</v>
+        <v>-0.1641</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-0.1688</v>
+        <v>-0.1645</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.4929</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4715</v>
+        <v>-0.4745</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4443</v>
+        <v>-0.4451</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2298.5616</v>
+        <v>2156.1074</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8042.9096</v>
+        <v>7775.0504</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18300.285</v>
+        <v>17768.1476</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2298.5616</v>
+        <v>2156.1074</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8042.9096</v>
+        <v>7775.0504</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18300.285</v>
+        <v>17768.1476</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3518.7054</v>
+        <v>3376.2512</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7271.4996</v>
+        <v>7003.6404</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14768.2263</v>
+        <v>14236.0889</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8796.7636</v>
+        <v>8440.628000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18178.7491</v>
+        <v>17509.101</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>36920.5659</v>
+        <v>35590.2223</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10746.2346</v>
+        <v>10390.0989</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>21471.191</v>
+        <v>20801.5429</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>42054.4838</v>
+        <v>40724.1402</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>597.013</v>
+        <v>577.2277</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1192.8439</v>
+        <v>1155.6413</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2336.3602</v>
+        <v>2262.4522</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>722.7392</v>
+        <v>702.9539</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1395.9028</v>
+        <v>1358.7002</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2645.0063</v>
+        <v>2571.0984</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>404.2597</v>
+        <v>384.4744</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>793.2374</v>
+        <v>756.0347</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1567.1086</v>
+        <v>1493.2006</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>460.7957</v>
+        <v>437.5472</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>786.9899</v>
+        <v>749.4215</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1235.5121</v>
+        <v>1178.2443</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>23.2486</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.5684</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>57.2678</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7.0739</v>
+        <v>7.0797</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8.280900000000001</v>
+        <v>8.284800000000001</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10.7534</v>
+        <v>10.751</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>63.2705</v>
+        <v>61.768</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>129.7781</v>
+        <v>127.904</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>215.1827</v>
+        <v>213.136</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.1294</v>
+        <v>0.1214</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.4529</v>
+        <v>0.4379</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1.0306</v>
+        <v>1.0006</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>2298.5616</v>
+        <v>2156.1074</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>8042.9096</v>
+        <v>7775.0504</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>18300.285</v>
+        <v>17768.1476</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.1845</v>
+        <v>1.1452</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.3994</v>
+        <v>1.3557</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.7563</v>
+        <v>1.7007</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.1845</v>
+        <v>1.1452</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.3994</v>
+        <v>1.3557</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.7563</v>
+        <v>1.7007</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>597.013</v>
+        <v>577.2277</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1192.8439</v>
+        <v>1155.6413</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>2336.3602</v>
+        <v>2262.4522</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>348.8281</v>
+        <v>329.0428</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>774.901</v>
+        <v>737.6983</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1685.6686</v>
+        <v>1611.7606</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>597.013</v>
+        <v>577.2277</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1192.8439</v>
+        <v>1155.6413</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>2336.3602</v>
+        <v>2262.4522</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.5369</v>
+        <v>7.5683</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.3927</v>
+        <v>7.4176</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2341</v>
+        <v>7.2542</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>4499.6117</v>
+        <v>4368.6409</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>8818.346799999999</v>
+        <v>8572.0802</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>16901.5275</v>
+        <v>16412.2867</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>509.806</v>
+        <v>494.967</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>999.1187</v>
+        <v>971.2166999999999</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1914.9431</v>
+        <v>1859.5121</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>597.013</v>
+        <v>577.2277</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1192.8439</v>
+        <v>1155.6413</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>2336.3602</v>
+        <v>2262.4522</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.3883</v>
+        <v>2.3783</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4348</v>
+        <v>2.4267</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4882</v>
+        <v>2.4813</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.5369</v>
+        <v>7.5683</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.3927</v>
+        <v>7.4176</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2341</v>
+        <v>7.2542</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>3518.7054</v>
+        <v>3376.2512</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>7271.4996</v>
+        <v>7003.6404</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14768.2263</v>
+        <v>14236.0889</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>268.8053</v>
+        <v>137.8346</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1687.7415</v>
+        <v>1441.4749</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>5787.0795</v>
+        <v>5297.8388</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>4499.6117</v>
+        <v>4368.6409</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>8818.346799999999</v>
+        <v>8572.0802</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>16901.5275</v>
+        <v>16412.2867</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>1125.7381</v>
+        <v>1073.3498</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2390.7099</v>
+        <v>2292.2033</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>4990.245</v>
+        <v>4794.5487</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>4499.6117</v>
+        <v>4368.6409</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>8818.346799999999</v>
+        <v>8572.0802</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>16901.5275</v>
+        <v>16412.2867</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>269.3123</v>
+        <v>138.3268</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1688.7351</v>
+        <v>1442.4407</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>5788.9838</v>
+        <v>5299.6879</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>4500.1186</v>
+        <v>4369.1331</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>8819.340399999999</v>
+        <v>8573.046</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>16903.4318</v>
+        <v>16414.1359</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>1125.9409</v>
+        <v>1073.5467</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2391.1074</v>
+        <v>2292.5896</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>4991.0067</v>
+        <v>4795.2883</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>4500.1186</v>
+        <v>4369.1331</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>8819.340399999999</v>
+        <v>8573.046</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>16903.4318</v>
+        <v>16414.1359</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>1083.7318</v>
+        <v>885.8787</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>3698</v>
+        <v>3325.9733</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>10543.1038</v>
+        <v>9804.023999999999</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>1159.9497</v>
+        <v>1080.8084</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2700.1196</v>
+        <v>2551.3089</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>6118.5295</v>
+        <v>5822.8976</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>3518.7054</v>
+        <v>3376.2512</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>7271.4996</v>
+        <v>7003.6404</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>14768.2263</v>
+        <v>14236.0889</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>597.013</v>
+        <v>577.2277</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1192.8439</v>
+        <v>1155.6413</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>2336.3602</v>
+        <v>2262.4522</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>2392.7645</v>
+        <v>2302.7045</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>4880.3923</v>
+        <v>4711.0508</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>9777.2197</v>
+        <v>9440.8006</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>3518.7054</v>
+        <v>3376.2512</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>7271.4996</v>
+        <v>7003.6404</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>14768.2263</v>
+        <v>14236.0889</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>597.013</v>
+        <v>577.2277</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1192.8439</v>
+        <v>1155.6413</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>2336.3602</v>
+        <v>2262.4522</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>1125.9409</v>
+        <v>1073.5467</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2391.1074</v>
+        <v>2292.5896</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>4991.0067</v>
+        <v>4795.2883</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>4500.1186</v>
+        <v>4369.1331</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>8819.340399999999</v>
+        <v>8573.046</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>16903.4318</v>
+        <v>16414.1359</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.5142</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-0.4745</v>
+        <v>-0.4795</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0.4451</v>
+        <v>-0.4485</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>车端装机 ＋ 站内周转装机中归外部权益的部分</t>
+          <t>车端装机（站内周转电池的租金是换电站与电池银行之间的内部结算，不进系统收入；见 src/entities.py）</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1060,52 +1060,52 @@
     </row>
     <row r="20" hidden="1" outlineLevel="7">
       <c r="A20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　站内周转装机·外部权益部分</t>
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　电池月租·重卡与城配·实付均价</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>7.0797</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>8.284800000000001</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>10.751</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>GWh</t>
+          <t>元/kWh·月</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>站内周转装机 × (1 − CATL建站持股比例)</t>
+          <t>各池 max（保底 swap_business.battery_rent_rmb_kwh_month，超出价 swap_business.battery_rent_per_kwh_rmb × 每度容量月用电），按计费装机加权</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21" hidden="1" outlineLevel="7">
       <c r="A21" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　　　站内周转装机</t>
+          <t xml:space="preserve">　　　　　　　　　乘用车池计费装机</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>38.7476</v>
+        <v>61.768</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>62.614</v>
+        <v>127.904</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>95.4464</v>
+        <v>213.136</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 站数 × 站内周转电池块数 × 单块电量 )</t>
+          <t>乘用车池车端装机 ＋ 站内周转装机中归外部权益的部分</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1122,65 +1122,69 @@
     </row>
     <row r="22" hidden="1" outlineLevel="7">
       <c r="A22" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　　　CATL建站持股比例</t>
+          <t xml:space="preserve">　　　　　　　　　电池月租·乘用车</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.4</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>元/kWh·月</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>finance.construction_ownership</t>
+          <t>swap_business.battery_rent_passenger_rmb_kwh_month</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+          <t>乘用车月租 9.0（三档 8.8／9.0／9.7）：巧克力 369 元/42 度＝8.8、499 元/56 度＝8.9；蔚来 728 元/75 度＝9.7（台账批次 5 推导链）</t>
         </is>
       </c>
     </row>
     <row r="23" hidden="1" outlineLevel="7">
       <c r="A23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　电池月租·重卡与城配·实付均价</t>
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　峰谷套利收入</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7.0797</v>
+        <v>49.9069</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8.284800000000001</v>
+        <v>80.6469</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10.751</v>
+        <v>122.935</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>元/kWh·月</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>各池 max（保底 swap_business.battery_rent_rmb_kwh_month，超出价 swap_business.battery_rent_per_kwh_rmb × 每度容量月用电），按计费装机加权</t>
+          <t>站内周转装机 × 运营天数 × 峰谷价差 × 站效率</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24" hidden="1" outlineLevel="7">
       <c r="A24" s="2" t="n">
@@ -1188,17 +1192,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　乘用车池计费装机</t>
+          <t xml:space="preserve">　　　　　　　　　站内周转装机</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>61.768</v>
+        <v>38.7476</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>127.904</v>
+        <v>62.614</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>213.136</v>
+        <v>95.4464</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1207,7 +1211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>乘用车池车端装机 ＋ 站内周转装机中归外部权益的部分</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1219,65 +1223,69 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　电池月租·乘用车</t>
+          <t xml:space="preserve">　　　　　　　　　年运营天数</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>350</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9</v>
+        <v>350</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>350</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>元/kWh·月</t>
+          <t>天</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>swap_business.battery_rent_passenger_rmb_kwh_month</t>
+          <t>swap_business.operating_days</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>乘用车月租 9.0（三档 8.8／9.0／9.7）：巧克力 369 元/42 度＝8.8、499 元/56 度＝8.9；蔚来 728 元/75 度＝9.7（台账批次 5 推导链）</t>
+          <t>年运营天数 350 天 ← v3.2 §1.3.1：营运车全年营运，留 15 天检修与极端天气停运</t>
         </is>
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="7">
       <c r="A26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　峰谷套利收入</t>
+        <v>9</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　峰谷价差</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>49.9069</v>
+        <v>0.4</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>80.6469</v>
+        <v>0.4</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>122.935</v>
+        <v>0.4</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>站内周转装机 × 运营天数 × 峰谷价差 × 站效率</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>元/kWh</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.grid_spread_rmb_kwh</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>峰谷套利价差</t>
+        </is>
+      </c>
     </row>
     <row r="27" hidden="1" outlineLevel="7">
       <c r="A27" s="2" t="n">
@@ -1285,65 +1293,61 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　站内周转装机</t>
+          <t xml:space="preserve">　　　　　　　　　站内充放效率 RTE</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>38.7476</v>
+        <v>0.92</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>62.614</v>
+        <v>0.92</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>95.4464</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>GWh</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
+        <v>0.92</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.rte</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>往返效率 RTE 0.92 ← v3.2 §2.3／MANIFEST §5：LFP 系统充放往返效率 88–94% 区间中值（工程常识， / 信源审计台账已核为「保留」）。三处用到它，口径同一：① 充电电量 = 换电电量 ÷ RTE ×(1＋站用电率)；</t>
+        </is>
+      </c>
     </row>
     <row r="28" hidden="1" outlineLevel="7">
       <c r="A28" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　年运营天数</t>
+        <v>8</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　电网辅助服务收入</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>350</v>
+        <v>7.4388</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>350</v>
+        <v>11.846</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>350</v>
+        <v>17.7012</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>天</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.operating_days</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>年运营天数 350 天 ← v3.2 §1.3.1：营运车全年营运，留 15 天检修与极端天气停运</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>容量补偿 ＋ 孰高( 需求响应, 调频 )　——容量补偿是站建成即可申报的「存在型」收益；后两项须实际提供服务才有收益，且争夺同一份可调容量，同一时段只能干一件事，故孰高取一、不可相加</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
     </row>
     <row r="29" hidden="1" outlineLevel="7">
       <c r="A29" s="2" t="n">
@@ -1351,34 +1355,30 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　峰谷价差</t>
+          <t xml:space="preserve">　　　　　　　　　容量补偿</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6257</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.4</v>
+        <v>1.008</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.4</v>
+        <v>1.5356</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>元/kWh</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.grid_spread_rmb_kwh</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>峰谷套利价差</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Σ_池( 站数 × 单站申报容量 × 容量补偿价 )——站在即可申报，无条件计入</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
     </row>
     <row r="30" hidden="1" outlineLevel="7">
       <c r="A30" s="2" t="n">
@@ -1386,48 +1386,48 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　站内充放效率 RTE</t>
+          <t xml:space="preserve">　　　　　　　　　需求响应（候选·须实际提供服务）</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.92</v>
+        <v>4.1711</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.92</v>
+        <v>6.7199</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.rte</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>往返效率 RTE 0.92 ← v3.2 §2.3／MANIFEST §5：LFP 系统充放往返效率 88–94% 区间中值（工程常识， / 信源审计台账已核为「保留」）。三处用到它，口径同一：① 充电电量 = 换电电量 ÷ RTE ×(1＋站用电率)；</t>
-        </is>
-      </c>
+        <v>10.2371</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Σ_池( 站数 × 单站申报容量 × 年响应小时 × 响应价 )</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
     </row>
     <row r="31" hidden="1" outlineLevel="7">
       <c r="A31" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　电网辅助服务收入</t>
+        <v>9</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　调频（候选·须实际提供服务）</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7.4388</v>
+        <v>6.8131</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>11.846</v>
+        <v>10.838</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>17.7012</v>
+        <v>16.1657</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1436,29 +1436,29 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>容量补偿 ＋ 孰高( 需求响应, 调频 )　——容量补偿是站建成即可申报的「存在型」收益；后两项须实际提供服务才有收益，且争夺同一份可调容量，同一时段只能干一件事，故孰高取一、不可相加</t>
+          <t>Σ_池( 站数 × 单站调频容量 × 年调频小时 × 调频价 )</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
     </row>
     <row r="32" hidden="1" outlineLevel="7">
       <c r="A32" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　容量补偿</t>
+        <v>7</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　运营 OPEX</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.6257</v>
+        <v>125.7262</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.008</v>
+        <v>203.0589</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.5356</v>
+        <v>308.6461</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1467,29 +1467,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 站数 × 单站申报容量 × 容量补偿价 )——站在即可申报，无条件计入</t>
+          <t>电费 ＋ 场租 ＋ 人工 ＋ 软件调度 ＋ 保险 ＋ 池化维护 ＋ 仓储物流</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
     </row>
     <row r="33" hidden="1" outlineLevel="7">
       <c r="A33" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　需求响应（候选·须实际提供服务）</t>
+        <v>8</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　电费</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>4.1711</v>
+        <v>66.5253</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>6.7199</v>
+        <v>108.2372</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10.2371</v>
+        <v>165.5627</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1498,143 +1498,143 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 站数 × 单站申报容量 × 年响应小时 × 响应价 )</t>
+          <t>( 充电电量 − 换电电量 ) × 谷电价</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34" hidden="1" outlineLevel="7">
       <c r="A34" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　调频（候选·须实际提供服务）</t>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　年充电电量</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6.8131</v>
+        <v>2261.8592</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>10.838</v>
+        <v>3680.0662</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>16.1657</v>
+        <v>5629.1322</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>亿kWh</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 站数 × 单站调频容量 × 年调频小时 × 调频价 )</t>
+          <t>换电电量 ÷ RTE × ( 1 ＋ 站用电率 )</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35" hidden="1" outlineLevel="7">
       <c r="A35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　运营 OPEX</t>
+        <v>10</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　年换电交易电量</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>125.7262</v>
+        <v>2040.1083</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>203.0589</v>
+        <v>3319.2754</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>308.6461</v>
+        <v>5077.2565</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>亿kWh</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>电费 ＋ 场租 ＋ 人工 ＋ 软件调度 ＋ 保险 ＋ 池化维护 ＋ 仓储物流</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
     </row>
     <row r="36" hidden="1" outlineLevel="7">
       <c r="A36" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　电费</t>
+        <v>10</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　站内充放效率 RTE</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>66.5253</v>
+        <v>0.92</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>108.2372</v>
+        <v>0.92</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>165.5627</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>( 充电电量 − 换电电量 ) × 谷电价</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+        <v>0.92</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.rte</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>往返效率 RTE 0.92 ← v3.2 §2.3／MANIFEST §5：LFP 系统充放往返效率 88–94% 区间中值（工程常识， / 信源审计台账已核为「保留」）。三处用到它，口径同一：① 充电电量 = 换电电量 ÷ RTE ×(1＋站用电率)；</t>
+        </is>
+      </c>
     </row>
     <row r="37" hidden="1" outlineLevel="7">
       <c r="A37" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　年充电电量</t>
+        <v>10</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　站用电率</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2261.8592</v>
+        <v>0.02</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>3680.0662</v>
+        <v>0.02</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>5629.1322</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>亿kWh</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>换电电量 ÷ RTE × ( 1 ＋ 站用电率 )</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.auxiliary_power_rate</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>站用电率（厂用电率）2% ← v3.2 §1.3.2 成本端口径：用户换走的电量不计入充电成本， / 只有循环效率损失（1−RTE）与设备自用电两部分按谷电价计成本</t>
+        </is>
+      </c>
     </row>
     <row r="38" hidden="1" outlineLevel="7">
       <c r="A38" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　　年换电交易电量</t>
+          <t xml:space="preserve">　　　　　　　　　年换电交易电量</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1661,65 +1661,69 @@
     </row>
     <row r="39" hidden="1" outlineLevel="7">
       <c r="A39" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　　站内充放效率 RTE</t>
+          <t xml:space="preserve">　　　　　　　　　谷段电价</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.92</v>
+        <v>0.3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.92</v>
+        <v>0.3</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>元/kWh</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>swap_business.rte</t>
+          <t>swap_business.valley_power_price_rmb_kwh</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>往返效率 RTE 0.92 ← v3.2 §2.3／MANIFEST §5：LFP 系统充放往返效率 88–94% 区间中值（工程常识， / 信源审计台账已核为「保留」）。三处用到它，口径同一：① 充电电量 = 换电电量 ÷ RTE ×(1＋站用电率)；</t>
+          <t>谷电价</t>
         </is>
       </c>
     </row>
     <row r="40" hidden="1" outlineLevel="7">
       <c r="A40" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　站用电率</t>
+        <v>8</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　场地租金</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.02</v>
+        <v>20.07</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.02</v>
+        <v>31.7415</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.auxiliary_power_rate</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>站用电率（厂用电率）2% ← v3.2 §1.3.2 成本端口径：用户换走的电量不计入充电成本， / 只有循环效率损失（1−RTE）与设备自用电两部分按谷电价计成本</t>
-        </is>
-      </c>
+        <v>46.878</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Σ_池( 站数 ) × 单站年场租</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
     </row>
     <row r="41" hidden="1" outlineLevel="7">
       <c r="A41" s="2" t="n">
@@ -1727,26 +1731,26 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　年换电交易电量</t>
+          <t xml:space="preserve">　　　　　　　　　站数合计</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>2040.1083</v>
+        <v>13380</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>3319.2754</v>
+        <v>21161</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>5077.2565</v>
+        <v>31252</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>亿kWh</t>
+          <t>座</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>四个站型的兑现年站数之和</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -1758,32 +1762,32 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　谷段电价</t>
+          <t xml:space="preserve">　　　　　　　　　单站年场租</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.3</v>
+        <v>15</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.3</v>
+        <v>15</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.3</v>
+        <v>15</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>元/kWh</t>
+          <t>万元/年</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>swap_business.valley_power_price_rmb_kwh</t>
+          <t>swap_business.site_rent_wan_year</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>谷电价</t>
+          <t>场租 15 万/站/年（统一不分站型）：200–300㎡×50 元/㎡/月×12 = 12–18 万取中。 / 巧克力核心区贵/重卡干线便宜，两者相抵；较蔚能二代站 10 万偏保守。不做敏感性</t>
         </is>
       </c>
     </row>
@@ -1793,17 +1797,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　场地租金</t>
+          <t xml:space="preserve">　　　　　　　　人工</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>20.07</v>
+        <v>23.7098</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>31.7415</v>
+        <v>38.2795</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>46.878</v>
+        <v>58.5191</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1816,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 站数 ) × 单站年场租</t>
+          <t>重卡站数 × 重卡单站年人工 ＋ 巧克力站数 × 巧克力单站年人工</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -1824,17 +1828,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　站数合计</t>
+          <t xml:space="preserve">　　　　　　　　　重卡站数（兑现年）</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>13380</v>
+        <v>8314</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>21161</v>
+        <v>13472</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>31252</v>
+        <v>20717</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>四个站型的兑现年站数之和</t>
+          <t>骐骥短途站 ＋ 骐骥干线站</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -1855,17 +1859,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　单站年场租</t>
+          <t xml:space="preserve">　　　　　　　　　重卡单站年人工</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>15</v>
+        <v>26.88</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>15</v>
+        <v>26.88</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>15</v>
+        <v>26.88</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -1875,45 +1879,45 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>swap_business.site_rent_wan_year</t>
+          <t>swap_business.heavy_station_labor_wan_year</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>场租 15 万/站/年（统一不分站型）：200–300㎡×50 元/㎡/月×12 = 12–18 万取中。 / 巧克力核心区贵/重卡干线便宜，两者相抵；较蔚能二代站 10 万偏保守。不做敏感性</t>
+          <t>重卡站人工 26.88 万/站/年：2 人×16h 双班倒×1.12 万/月×12（老模型精算口径回归）。 / v4.2 按次计价（30 元/次）废弃——隐含 4 人编制、高估 2 倍</t>
         </is>
       </c>
     </row>
     <row r="46" hidden="1" outlineLevel="7">
       <c r="A46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　人工</t>
+        <v>9</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　巧克力站数（兑现年）</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>23.7098</v>
+        <v>5066</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>38.2795</v>
+        <v>7689</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>58.5191</v>
+        <v>10535</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>座</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>重卡站数 × 重卡单站年人工 ＋ 巧克力站数 × 巧克力单站年人工</t>
+          <t>巧克力乘用站 ＋ 巧克力城配站</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
     </row>
     <row r="47" hidden="1" outlineLevel="7">
       <c r="A47" s="2" t="n">
@@ -1921,92 +1925,92 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　重卡站数（兑现年）</t>
+          <t xml:space="preserve">　　　　　　　　　巧克力单站年人工</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>8314</v>
+        <v>2.688</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>13472</v>
+        <v>2.688</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>20717</v>
+        <v>2.688</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>座</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>骐骥短途站 ＋ 骐骥干线站</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="3" t="inlineStr"/>
+          <t>万元/年</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>swap_business.passenger_station_labor_wan_year</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>巧克力站直接人工 0.2 人/站保守档（2026-08-29 拍板，v4.3 从 0 上调）：≈5 站共用 1 名巡检员 / （0.2 人×1.12 万/月×12 = 2.688 万/站/年）。覆盖逻辑：官方"3 公里服务半径"密度（厦门试点口径）下</t>
+        </is>
+      </c>
     </row>
     <row r="48" hidden="1" outlineLevel="7">
       <c r="A48" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　重卡单站年人工</t>
+          <t xml:space="preserve">　　　　　　　　软件调度</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>26.88</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>26.88</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>26.88</v>
+        <v>2</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>万元/年</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.heavy_station_labor_wan_year</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>重卡站人工 26.88 万/站/年：2 人×16h 双班倒×1.12 万/月×12（老模型精算口径回归）。 / v4.2 按次计价（30 元/次）废弃——隐含 4 人编制、高估 2 倍</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>固定投入，按站数份额分池</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
     </row>
     <row r="49" hidden="1" outlineLevel="7">
       <c r="A49" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　巧克力站数（兑现年）</t>
+          <t xml:space="preserve">　　　　　　　　保险</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>5066</v>
+        <v>6.3958</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>7689</v>
+        <v>10.8231</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10535</v>
+        <v>16.8994</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>座</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>巧克力乘用站 ＋ 巧克力城配站</t>
+          <t>电池资产 × 电池保险费率 ＋ 站体资产 × 设备保险费率</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -2014,38 +2018,34 @@
     </row>
     <row r="50" hidden="1" outlineLevel="7">
       <c r="A50" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　　巧克力单站年人工</t>
+          <t xml:space="preserve">　　　　　　　　池化维护</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>2.688</v>
+        <v>5.6203</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2.688</v>
+        <v>9.582000000000001</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2.688</v>
+        <v>15.0296</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>万元/年</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>swap_business.passenger_station_labor_wan_year</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>巧克力站直接人工 0.2 人/站保守档（2026-08-29 拍板，v4.3 从 0 上调）：≈5 站共用 1 名巡检员 / （0.2 人×1.12 万/月×12 = 2.688 万/站/年）。覆盖逻辑：官方"3 公里服务半径"密度（厦门试点口径）下</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>电池资产 × 池化维护费率</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr"/>
     </row>
     <row r="51" hidden="1" outlineLevel="7">
       <c r="A51" s="2" t="n">
@@ -2053,17 +2053,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　软件调度</t>
+          <t xml:space="preserve">　　　　　　　　仓储物流</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>2</v>
+        <v>1.4051</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2</v>
+        <v>2.3955</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2</v>
+        <v>3.7574</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2072,60 +2072,64 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>固定投入，按站数份额分池</t>
+          <t>电池资产 × 仓储物流费率</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr"/>
     </row>
-    <row r="52" hidden="1" outlineLevel="7">
+    <row r="52" hidden="1" outlineLevel="6">
       <c r="A52" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　保险</t>
+          <t xml:space="preserve">　　　　　　运营 EV/EBITDA 倍数</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>6.3958</v>
+        <v>18</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10.8231</v>
+        <v>18</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>16.8994</v>
+        <v>18</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>电池资产 × 电池保险费率 ＋ 站体资产 × 设备保险费率</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53" hidden="1" outlineLevel="7">
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>finance.swap_ev_ebitda</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" hidden="1" outlineLevel="5">
       <c r="A53" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　池化维护</t>
+          <t xml:space="preserve">　　　　　稳态debt（2030在役资产历史成本×债务比）</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>5.6203</v>
+        <v>1949.471</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>9.582000000000001</v>
+        <v>3292.4419</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>15.0296</v>
+        <v>5133.9179</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2134,157 +2138,153 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>电池资产 × 池化维护费率</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr"/>
     </row>
-    <row r="54" hidden="1" outlineLevel="7">
+    <row r="54" hidden="1" outlineLevel="4">
       <c r="A54" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　仓储物流</t>
+          <t xml:space="preserve">　　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>1.4051</v>
+        <v>0.4</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2.3955</v>
+        <v>0.4</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3.7574</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>电池资产 × 仓储物流费率</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55" hidden="1" outlineLevel="6">
+        <v>0.4</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" hidden="1" outlineLevel="3">
       <c r="A55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　制造侧锁量锁价增量</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>-1220.1438</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>771.41</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>3532.0586</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>制造净利差 × 制造 PE</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" hidden="1" outlineLevel="4">
+      <c r="A56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　制造净利差（有换电 − 纯制造）</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>-61.0072</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>38.5705</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>176.6029</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>量差效应 ＋ 换电段利润率效应 ＋ 其他段利润率效应</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" hidden="1" outlineLevel="5">
+      <c r="A57" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　量差效应</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>-61.0072</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2.733</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>70.3633</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>锁定订单效应 ＋ 充电段份额效应（虹吸，通常为负）</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" hidden="1" outlineLevel="6">
+      <c r="A58" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　运营 EV/EBITDA 倍数</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>finance.swap_ev_ebitda</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" hidden="1" outlineLevel="5">
-      <c r="A56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　稳态debt（2030在役资产历史成本×债务比）</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>1949.471</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>3292.4419</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>5133.9179</v>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57" hidden="1" outlineLevel="4">
-      <c r="A57" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　CATL建站持股比例</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" hidden="1" outlineLevel="3">
-      <c r="A58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　制造侧锁量锁价增量</t>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　锁定订单效应</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>-1220.1438</v>
+        <v>47.6529</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>771.41</v>
+        <v>80.4935</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3532.0586</v>
+        <v>123.9601</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2293,29 +2293,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>制造净利差 × 制造 PE</t>
+          <t>换电锁定出货 × 单位售价 × 纯制造净利率</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" hidden="1" outlineLevel="4">
+      <c r="I58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" hidden="1" outlineLevel="6">
       <c r="A59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　制造净利差（有换电 − 纯制造）</t>
+        <v>6</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　充电段份额效应（虹吸）</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-61.0072</v>
+        <v>-108.6601</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>38.5705</v>
+        <v>-77.7606</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>176.6029</v>
+        <v>-53.5968</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2324,11 +2324,11 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>量差效应 ＋ 换电段利润率效应 ＋ 其他段利润率效应</t>
+          <t>量差效应 − 锁定订单效应（换电对充电段的挤出）</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
     </row>
     <row r="60" hidden="1" outlineLevel="5">
       <c r="A60" s="2" t="n">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　量差效应</t>
+          <t xml:space="preserve">　　　　　换电段利润率效应（护价）</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>-61.0072</v>
+        <v>0</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2.733</v>
+        <v>35.8375</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>70.3633</v>
+        <v>106.2396</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>锁定订单效应 ＋ 充电段份额效应（虹吸，通常为负）</t>
+          <t>换电可覆盖收入 × 净利率差</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -2367,28 +2367,24 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　锁定订单效应</t>
+          <t xml:space="preserve">　　　　　　换电可覆盖收入</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>47.6529</v>
+        <v>2912.7091</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>80.4935</v>
+        <v>3583.7531</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>123.9601</v>
+        <v>4249.5851</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>亿元</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>换电锁定出货 × 单位售价 × 纯制造净利率</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr"/>
     </row>
@@ -2396,181 +2392,185 @@
       <c r="A62" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　充电段份额效应（虹吸）</t>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　净利率差（有换电 − 无换电）</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>-108.6601</v>
+        <v>0</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>-77.7606</v>
+        <v>0.01</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-53.5968</v>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>量差效应 − 锁定订单效应（换电对充电段的挤出）</t>
+          <t>有换电制造净利率 − 无换电制造净利率</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63" hidden="1" outlineLevel="5">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" hidden="1" outlineLevel="7">
       <c r="A63" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　换电段利润率效应（护价）</t>
+        <v>7</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　有换电制造净利率</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>35.8375</v>
+        <v>0.135</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>106.2396</v>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>换电可覆盖收入 × 净利率差</t>
-        </is>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64" hidden="1" outlineLevel="6">
+      <c r="I63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" hidden="1" outlineLevel="7">
       <c r="A64" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　换电可覆盖收入</t>
+          <t xml:space="preserve">　　　　　　　无换电制造净利率</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>2912.7091</v>
+        <v>0.125</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3583.7531</v>
+        <v>0.125</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4249.5851</v>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+        <v>0.125</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="3" t="inlineStr"/>
     </row>
-    <row r="65" hidden="1" outlineLevel="6">
+    <row r="65" hidden="1" outlineLevel="5">
       <c r="A65" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　净利率差（有换电 − 无换电）</t>
+        <v>5</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　其他段利润率效应</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>有换电制造净利率 − 无换电制造净利率</t>
+          <t>换电不可覆盖收入 × 净利率差</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66" hidden="1" outlineLevel="7">
+      <c r="I65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" hidden="1" outlineLevel="4">
       <c r="A66" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　有换电制造净利率</t>
+          <t xml:space="preserve">　　　　制造 PE</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>0.125</v>
+        <v>20</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.135</v>
+        <v>20</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67" hidden="1" outlineLevel="7">
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>finance.manufacturing_pe</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>制造 PE 20× ← v3.2 §6.6：延续当前估值水平，不做扩张假设。 / 校核：2026 动力净利拍 600 亿 × 20 = 12,000 亿；对照集团市值 18,250 亿、</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" outlineLevel="2">
       <c r="A67" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　无换电制造净利率</t>
+        <v>2</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　增量价值 ÷ 集团市值</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>0.125</v>
+        <v>0.1214</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.125</v>
+        <v>0.4379</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.125</v>
+        <v>1.0006</v>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>可归因换电增量价值 ÷ 集团市值基准</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" hidden="1" outlineLevel="5">
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" hidden="1" outlineLevel="3">
       <c r="A68" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　其他段利润率效应</t>
+          <t xml:space="preserve">　　　可归因换电增量价值</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0</v>
+        <v>2156.1074</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0</v>
+        <v>7775.0504</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0</v>
+        <v>17768.1476</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -2579,91 +2579,87 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>换电不可覆盖收入 × 净利率差</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr"/>
     </row>
-    <row r="69" hidden="1" outlineLevel="4">
+    <row r="69" hidden="1" outlineLevel="3">
       <c r="A69" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　制造 PE</t>
+          <t xml:space="preserve">　　　集团市值基准（A+H）</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>20</v>
+        <v>17757</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>20</v>
+        <v>17757</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>20</v>
+        <v>17757</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>finance.manufacturing_pe</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>制造 PE 20× ← v3.2 §6.6：延续当前估值水平，不做扩张假设。 / 校核：2026 动力净利拍 600 亿 × 20 = 12,000 亿；对照集团市值 18,250 亿、</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" outlineLevel="2">
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" outlineLevel="1">
       <c r="A70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　增量价值 ÷ 集团市值</t>
+          <t xml:space="preserve">　做透的代价</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.1214</v>
+        <v>621.4655</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.4379</v>
+        <v>1050.3628</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1.0006</v>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
+        <v>1638.6857</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>可归因换电增量价值 ÷ 集团市值基准</t>
+          <t>见下</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
     </row>
-    <row r="71" hidden="1" outlineLevel="3">
+    <row r="71" outlineLevel="2">
       <c r="A71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　可归因换电增量价值</t>
+        <v>2</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　CATL 全周期权益承诺</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>2156.1074</v>
+        <v>621.4655</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>7775.0504</v>
+        <v>1050.3628</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>17768.1476</v>
+        <v>1638.6857</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2672,11 +2668,11 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>全周期资本底座 × (1 − 债务比例) × CATL建站持股比例</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
     </row>
     <row r="72" hidden="1" outlineLevel="3">
       <c r="A72" s="2" t="n">
@@ -2684,96 +2680,100 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　集团市值基准（A+H）</t>
+          <t xml:space="preserve">　　　全周期资本底座</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>17757</v>
+        <v>3884.1593</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>17757</v>
+        <v>6564.7674</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>17757</v>
+        <v>10241.7855</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>亿元</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="3" t="inlineStr"/>
     </row>
-    <row r="73" outlineLevel="1">
+    <row r="73" hidden="1" outlineLevel="3">
       <c r="A73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　做透的代价</t>
+        <v>3</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　项目债务比例</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>621.4655</v>
+        <v>0.6</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1050.3628</v>
+        <v>0.6</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1638.6857</v>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>见下</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74" outlineLevel="2">
+        <v>0.6</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>finance.debt_ratio</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>债务比例 60%：经验假设（类固收项目可做到 1:1.5 杠杆）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" hidden="1" outlineLevel="3">
       <c r="A74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" outlineLevel="2">
+      <c r="A75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　CATL 全周期权益承诺</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>621.4655</v>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>1050.3628</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>1638.6857</v>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>全周期资本底座 × (1 − 债务比例) × CATL建站持股比例</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75" hidden="1" outlineLevel="3">
-      <c r="A75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　全周期资本底座</t>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　全周期资本底座（现值）</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -2792,91 +2792,91 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>初装 CAPEX ＋ 全周期电池更新净额（按届时价格、扣回收残值，折现）</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
     </row>
     <row r="76" hidden="1" outlineLevel="3">
       <c r="A76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　项目债务比例</t>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　初装 CAPEX 合计</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>0.6</v>
+        <v>3249.1183</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.6</v>
+        <v>5487.4031</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>finance.debt_ratio</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>债务比例 60%：经验假设（类固收项目可做到 1:1.5 杠杆）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" hidden="1" outlineLevel="3">
+        <v>8556.5298</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>期初存量站投入 ＋ Σ_年( 车端电池 ＋ 站内电池 ＋ 站体 )</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" hidden="1" outlineLevel="4">
       <c r="A77" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　CATL建站持股比例</t>
+          <t xml:space="preserve">　　　　期初存量站投入</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>0.4</v>
+        <v>47.7533</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.4</v>
+        <v>47.7533</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" outlineLevel="2">
+        <v>47.7533</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>2026 年之前已建成站的站体与站内电池</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" hidden="1" outlineLevel="4">
       <c r="A78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　全周期资本底座（现值）</t>
+        <v>4</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　车端电池初装</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>3884.1593</v>
+        <v>2503.4874</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>6564.7674</v>
+        <v>4290.6004</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>10241.7855</v>
+        <v>6746.846</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2885,29 +2885,29 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>初装 CAPEX ＋ 全周期电池更新净额（按届时价格、扣回收残值，折现）</t>
+          <t>Σ_年( 当年新增换电装车 GWh × 当年电池价格 )</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79" hidden="1" outlineLevel="3">
+      <c r="I78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79" hidden="1" outlineLevel="4">
       <c r="A79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　初装 CAPEX 合计</t>
+        <v>4</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　站内周转电池初装</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>3249.1183</v>
+        <v>216.5076</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>5487.4031</v>
+        <v>357.3194</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>8556.5298</v>
+        <v>551.0305</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2916,11 +2916,11 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>期初存量站投入 ＋ Σ_年( 车端电池 ＋ 站内电池 ＋ 站体 )</t>
+          <t>Σ_年( 当年新增站数 × 站内周转块数 × 单块电量 × 当年电池价格 )</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
     </row>
     <row r="80" hidden="1" outlineLevel="4">
       <c r="A80" s="2" t="n">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期初存量站投入</t>
+          <t xml:space="preserve">　　　　站体初装</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>47.7533</v>
+        <v>481.37</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>47.7533</v>
+        <v>791.73</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>47.7533</v>
+        <v>1210.9</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -2947,29 +2947,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2026 年之前已建成站的站体与站内电池</t>
+          <t>Σ_年Σ_池( 当年新增站数 × 该站型单站站体造价 )</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="3" t="inlineStr"/>
     </row>
-    <row r="81" hidden="1" outlineLevel="4">
+    <row r="81" hidden="1" outlineLevel="3">
       <c r="A81" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　车端电池初装</t>
+          <t xml:space="preserve">　　　全周期更新净额（现值）</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>2503.4874</v>
+        <v>635.0410000000001</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>4290.6004</v>
+        <v>1077.3643</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>6746.846</v>
+        <v>1685.2557</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2978,29 +2978,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Σ_年( 当年新增换电装车 GWh × 当年电池价格 )</t>
+          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr"/>
     </row>
-    <row r="82" hidden="1" outlineLevel="4">
+    <row r="82" outlineLevel="2">
       <c r="A82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　站内周转电池初装</t>
+        <v>2</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年资本要求</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>216.5076</v>
+        <v>440.0752</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>357.3194</v>
+        <v>743.7881</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>551.0305</v>
+        <v>1160.3943</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3009,29 +3009,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Σ_年( 当年新增站数 × 站内周转块数 × 单块电量 × 当年电池价格 )</t>
+          <t>全周期资本底座 × 资本回收系数 CRF</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83" hidden="1" outlineLevel="4">
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" hidden="1" outlineLevel="3">
       <c r="A83" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　站体初装</t>
+          <t xml:space="preserve">　　　全周期资本底座</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>481.37</v>
+        <v>3884.1593</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>791.73</v>
+        <v>6564.7674</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1210.9</v>
+        <v>10241.7855</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Σ_年Σ_池( 当年新增站数 × 该站型单站站体造价 )</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -3052,30 +3052,30 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　全周期更新净额（现值）</t>
+          <t xml:space="preserve">　　　资本回收系数 CRF</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>635.0410000000001</v>
+        <v>0.1133</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1077.3643</v>
+        <v>0.1133</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1685.2557</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="3" t="inlineStr"/>
+        <v>0.1133</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>finance.capital_recovery_factor</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
+        </is>
+      </c>
     </row>
     <row r="85" outlineLevel="2">
       <c r="A85" s="2" t="n">
@@ -3083,17 +3083,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　年资本要求</t>
+          <t xml:space="preserve">　　项目债务</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>440.0752</v>
+        <v>2330.4956</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>743.7881</v>
+        <v>3938.8604</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1160.3943</v>
+        <v>6145.0713</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>全周期资本底座 × 资本回收系数 CRF</t>
+          <t>全周期资本底座 × 债务比例</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -3112,9 +3112,9 @@
       <c r="A86" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　全周期资本底座</t>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　全周期资本底座（现值）</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -3133,60 +3133,60 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>初装 CAPEX ＋ 全周期电池更新净额（按届时价格、扣回收残值，折现）</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="3" t="inlineStr"/>
-    </row>
-    <row r="87" hidden="1" outlineLevel="3">
+      <c r="I86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" hidden="1" outlineLevel="4">
       <c r="A87" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　资本回收系数 CRF</t>
+        <v>4</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　初装 CAPEX 合计</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>0.1133</v>
+        <v>3249.1183</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.1133</v>
+        <v>5487.4031</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>finance.capital_recovery_factor</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" outlineLevel="2">
+        <v>8556.5298</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>期初存量站投入 ＋ Σ_年( 车端电池 ＋ 站内电池 ＋ 站体 )</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" hidden="1" outlineLevel="5">
       <c r="A88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　项目债务</t>
+        <v>5</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　期初存量站投入</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>2330.4956</v>
+        <v>47.7533</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3938.8604</v>
+        <v>47.7533</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>6145.0713</v>
+        <v>47.7533</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3195,29 +3195,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>全周期资本底座 × 债务比例</t>
+          <t>2026 年之前已建成站的站体与站内电池</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89" hidden="1" outlineLevel="3">
+      <c r="I88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89" hidden="1" outlineLevel="5">
       <c r="A89" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　全周期资本底座（现值）</t>
+        <v>5</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　车端电池初装</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>3884.1593</v>
+        <v>2503.4874</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>6564.7674</v>
+        <v>4290.6004</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>10241.7855</v>
+        <v>6746.846</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3226,29 +3226,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>初装 CAPEX ＋ 全周期电池更新净额（按届时价格、扣回收残值，折现）</t>
+          <t>Σ_年( 当年新增换电装车 GWh × 当年电池价格 )</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90" hidden="1" outlineLevel="4">
+      <c r="I89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90" hidden="1" outlineLevel="5">
       <c r="A90" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　初装 CAPEX 合计</t>
+        <v>5</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　站内周转电池初装</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>3249.1183</v>
+        <v>216.5076</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>5487.4031</v>
+        <v>357.3194</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>8556.5298</v>
+        <v>551.0305</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>期初存量站投入 ＋ Σ_年( 车端电池 ＋ 站内电池 ＋ 站体 )</t>
+          <t>Σ_年( 当年新增站数 × 站内周转块数 × 单块电量 × 当年电池价格 )</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr"/>
     </row>
     <row r="91" hidden="1" outlineLevel="5">
       <c r="A91" s="2" t="n">
@@ -3269,17 +3269,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　期初存量站投入</t>
+          <t xml:space="preserve">　　　　　站体初装</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>47.7533</v>
+        <v>481.37</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>47.7533</v>
+        <v>791.73</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>47.7533</v>
+        <v>1210.9</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3288,29 +3288,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2026 年之前已建成站的站体与站内电池</t>
+          <t>Σ_年Σ_池( 当年新增站数 × 该站型单站站体造价 )</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr"/>
     </row>
-    <row r="92" hidden="1" outlineLevel="5">
+    <row r="92" hidden="1" outlineLevel="4">
       <c r="A92" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　车端电池初装</t>
+          <t xml:space="preserve">　　　　全周期更新净额（现值）</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>2503.4874</v>
+        <v>635.0410000000001</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>4290.6004</v>
+        <v>1077.3643</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>6746.846</v>
+        <v>1685.2557</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3319,104 +3319,100 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Σ_年( 当年新增换电装车 GWh × 当年电池价格 )</t>
+          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="3" t="inlineStr"/>
     </row>
-    <row r="93" hidden="1" outlineLevel="5">
+    <row r="93" hidden="1" outlineLevel="3">
       <c r="A93" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　站内周转电池初装</t>
+          <t xml:space="preserve">　　　项目债务比例</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>216.5076</v>
+        <v>0.6</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>357.3194</v>
+        <v>0.6</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>551.0305</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Σ_年( 当年新增站数 × 站内周转块数 × 单块电量 × 当年电池价格 )</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="3" t="inlineStr"/>
-    </row>
-    <row r="94" hidden="1" outlineLevel="5">
+        <v>0.6</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>finance.debt_ratio</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>债务比例 60%：经验假设（类固收项目可做到 1:1.5 杠杆）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" outlineLevel="1">
       <c r="A94" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　站体初装</t>
+        <v>1</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　体检：过不过线</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>481.37</v>
+        <v>1.1452</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>791.73</v>
+        <v>1.3557</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1210.9</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+        <v>1.7007</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Σ_年Σ_池( 当年新增站数 × 该站型单站站体造价 )</t>
+          <t>见下</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="3" t="inlineStr"/>
-    </row>
-    <row r="95" hidden="1" outlineLevel="4">
+      <c r="I94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" outlineLevel="2">
       <c r="A95" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　全周期更新净额（现值）</t>
+        <v>2</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　EBITDA 覆盖倍数</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>635.0410000000001</v>
+        <v>1.1452</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1077.3643</v>
+        <v>1.3557</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1685.2557</v>
+        <v>1.7007</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>全周期电池更新净额现值＝底座−初装（差额算式只住 capex.py 一处）</t>
+          <t>可交付 EBITDA ÷ 资本回报要求 EBITDA</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="3" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
     </row>
     <row r="96" hidden="1" outlineLevel="3">
       <c r="A96" s="2" t="n">
@@ -3424,57 +3420,61 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　项目债务比例</t>
+          <t xml:space="preserve">　　　可交付 EBITDA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.6</v>
+        <v>577.2277</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.6</v>
+        <v>1155.6413</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>finance.debt_ratio</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>债务比例 60%：经验假设（类固收项目可做到 1:1.5 杠杆）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" outlineLevel="1">
+        <v>2262.4522</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97" hidden="1" outlineLevel="3">
       <c r="A97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　体检：过不过线</t>
+        <v>3</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　资本回报要求 EBITDA</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1.1452</v>
+        <v>504.0387</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.3557</v>
+        <v>852.4032</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1.7007</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr"/>
+        <v>1330.2952</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>见下</t>
+          <t>由年资本要求反推的门槛 EBITDA</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
     </row>
     <row r="98" outlineLevel="2">
       <c r="A98" s="2" t="n">
@@ -3482,26 +3482,26 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　EBITDA 覆盖倍数</t>
+          <t xml:space="preserve">　　EBIT（账面）</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1.1452</v>
+        <v>329.0428</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.3557</v>
+        <v>737.6983</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1.7007</v>
+        <v>1611.7606</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>可交付 EBITDA ÷ 资本回报要求 EBITDA</t>
+          <t>EBITDA − 年折旧</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　可交付 EBITDA</t>
+          <t xml:space="preserve">　　　EBITDA</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -3542,19 +3542,19 @@
       <c r="A100" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　资本回报要求 EBITDA</t>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　年折旧（成熟期）</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>504.0387</v>
+        <v>248.1849</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>852.4032</v>
+        <v>417.9429</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1330.2952</v>
+        <v>650.6916</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3563,29 +3563,29 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>由年资本要求反推的门槛 EBITDA</t>
+          <t>电池折旧（按各池电池寿命） ＋ 站体折旧（站体总初装 ÷ 分析期）</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="3" t="inlineStr"/>
-    </row>
-    <row r="101" outlineLevel="2">
+      <c r="I100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" hidden="1" outlineLevel="4">
       <c r="A101" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　EBIT（账面）</t>
+        <v>4</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　电池折旧</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>329.0428</v>
+        <v>213.7169</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>737.6983</v>
+        <v>362.7843</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1611.7606</v>
+        <v>567.5883</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3594,29 +3594,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>EBITDA − 年折旧</t>
+          <t>模型内按池 cohort 逐批计提：Σ_池( 池电池资本底座 ÷ 池电池寿命 )；此处由成熟期折旧扣站体折旧反解</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102" hidden="1" outlineLevel="3">
+      <c r="I101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102" hidden="1" outlineLevel="4">
       <c r="A102" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　EBITDA</t>
+        <v>4</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　站体总初装（含期初存量站）</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>577.2277</v>
+        <v>517.02</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1155.6413</v>
+        <v>827.38</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>2262.4522</v>
+        <v>1246.55</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3625,29 +3625,29 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>Σ_年站体初装 ＋ 期初存量站数 × 该站型单站站体造价</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="3" t="inlineStr"/>
-    </row>
-    <row r="103" hidden="1" outlineLevel="3">
+      <c r="I102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103" hidden="1" outlineLevel="5">
       <c r="A103" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　年折旧（成熟期）</t>
+        <v>5</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　建设期站体初装</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>248.1849</v>
+        <v>481.37</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>417.9429</v>
+        <v>791.73</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>650.6916</v>
+        <v>1210.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3656,29 +3656,29 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>电池折旧（按各池电池寿命） ＋ 站体折旧（站体总初装 ÷ 分析期）</t>
+          <t>Σ_年Σ_池( 当年新增站数 × 单站站体造价 )</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104" hidden="1" outlineLevel="4">
+      <c r="I103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104" hidden="1" outlineLevel="5">
       <c r="A104" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　电池折旧</t>
+          <t xml:space="preserve">　　　　　期初存量站站体</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>213.7169</v>
+        <v>35.65</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>362.7843</v>
+        <v>35.65</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>567.5883</v>
+        <v>35.65</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>模型内按池 cohort 逐批计提：Σ_池( 池电池资本底座 ÷ 池电池寿命 )；此处由成熟期折旧扣站体折旧反解</t>
+          <t>Σ_池( 期初存量站数 × 单站站体造价 )</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -3697,81 +3697,85 @@
       <c r="A105" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　站体总初装（含期初存量站）</t>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　模型分析期</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>517.02</v>
+        <v>15</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>827.38</v>
+        <v>15</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>1246.55</v>
+        <v>15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Σ_年站体初装 ＋ 期初存量站数 × 该站型单站站体造价</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106" hidden="1" outlineLevel="5">
+          <t>年</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>finance.model_horizon_years</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>分析期 15 年（2026–2040）：与世联评估预测收益期 2025.12–2040.12 对齐（非 REITs 12 年存续期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" outlineLevel="2">
       <c r="A106" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　建设期站体初装</t>
+        <v>2</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　现金流支持的倍数（对照 拍的倍数）</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>481.37</v>
+        <v>7.5683</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>791.73</v>
+        <v>7.4176</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>1210.9</v>
+        <v>7.2542</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Σ_年Σ_池( 当年新增站数 × 单站站体造价 )</t>
+          <t>DCF企业价值（与门槛同源口径）÷ EBITDA　——回答「你用 EBITDA 的倍数估值，那现金流本身支持几倍」</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107" hidden="1" outlineLevel="5">
+      <c r="I106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107" hidden="1" outlineLevel="3">
       <c r="A107" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　期初存量站站体</t>
+        <v>3</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　DCF企业价值·与门槛同源</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>35.65</v>
+        <v>4368.6409</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>35.65</v>
+        <v>8572.0802</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>35.65</v>
+        <v>16412.2867</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3780,11 +3784,11 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Σ_池( 期初存量站数 × 单站站体造价 )</t>
+          <t>成熟期 FCFF ÷ CRF（CRF 即设门槛 EBITDA 用的期望收益率年金因子，两者同源）</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="3" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
     </row>
     <row r="108" hidden="1" outlineLevel="4">
       <c r="A108" s="2" t="n">
@@ -3792,83 +3796,79 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　模型分析期</t>
+          <t xml:space="preserve">　　　　成熟期 FCFF</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>15</v>
+        <v>494.967</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>15</v>
+        <v>971.2166999999999</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>15</v>
+        <v>1859.5121</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>finance.model_horizon_years</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>分析期 15 年（2026–2040）：与世联评估预测收益期 2025.12–2040.12 对齐（非 REITs 12 年存续期）</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" outlineLevel="2">
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA ×(1−税率) ＋ 折旧 × 税率（重置已由 CRF 年金化内含）</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109" hidden="1" outlineLevel="4">
       <c r="A109" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　现金流支持的倍数（对照 拍的倍数）</t>
+        <v>4</v>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　资本回收系数 CRF</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7.5683</v>
+        <v>0.1133</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.4176</v>
+        <v>0.1133</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7.2542</v>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>DCF企业价值（与门槛同源口径）÷ EBITDA　——回答「你用 EBITDA 的倍数估值，那现金流本身支持几倍」</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
+        <v>0.1133</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>finance.capital_recovery_factor</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
+        </is>
+      </c>
     </row>
     <row r="110" hidden="1" outlineLevel="3">
       <c r="A110" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　DCF企业价值·与门槛同源</t>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　EBITDA</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>4368.6409</v>
+        <v>577.2277</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>8572.0802</v>
+        <v>1155.6413</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>16412.2867</v>
+        <v>2262.4522</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3877,71 +3877,75 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>成熟期 FCFF ÷ CRF（CRF 即设门槛 EBITDA 用的期望收益率年金因子，两者同源）</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111" hidden="1" outlineLevel="4">
+      <c r="I110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111" outlineLevel="2">
       <c r="A111" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　成熟期 FCFF</t>
+        <v>2</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　战略溢价倍数（押注的大小）</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>494.967</v>
+        <v>2.3783</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>971.2166999999999</v>
+        <v>2.4267</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1859.5121</v>
+        <v>2.4813</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>倍</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>EBITDA ×(1−税率) ＋ 折旧 × 税率（重置已由 CRF 年金化内含）</t>
+          <t>拍的 EV/EBITDA 倍数 ÷ 现金流支持的倍数　——这个数是判断不是计算，必须在报告正文里正面论证</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112" hidden="1" outlineLevel="4">
+      <c r="I111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112" hidden="1" outlineLevel="3">
       <c r="A112" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　资本回收系数 CRF</t>
+          <t xml:space="preserve">　　　运营 EV/EBITDA 倍数</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>0.1133</v>
+        <v>18</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.1133</v>
+        <v>18</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>finance.capital_recovery_factor</t>
+          <t>finance.swap_ev_ebitda</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>CRF **不再是一个拍值，是 WACC 的推论**：CRF = wacc ÷ (1−(1+wacc)^−运营年限)。 / `config_loader.load_config()` 每次加载都硬断言这个恒等式，改 WACC 不改这里会当场中断。</t>
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
         </is>
       </c>
     </row>
@@ -3951,21 +3955,21 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　EBITDA</t>
+          <t xml:space="preserve">　　　现金流支持的倍数</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>577.2277</v>
+        <v>7.5683</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1155.6413</v>
+        <v>7.4176</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>2262.4522</v>
+        <v>7.2542</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -3976,71 +3980,67 @@
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="3" t="inlineStr"/>
     </row>
-    <row r="114" outlineLevel="2">
+    <row r="114" outlineLevel="1">
       <c r="A114" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　战略溢价倍数（押注的大小）</t>
+          <t xml:space="preserve">　估值：这门生意最终值多少钱</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2.3783</v>
+        <v>3376.2512</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.4267</v>
+        <v>7003.6404</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.4813</v>
+        <v>14236.0889</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>拍的 EV/EBITDA 倍数 ÷ 现金流支持的倍数　——这个数是判断不是计算，必须在报告正文里正面论证</t>
+          <t>见下——倍数法与DCF两套独立口径（DCF区分CRF捷径对照版 npv/catl_dcf、有限期账/基础账 npv_true/catl_dcf_true、永续账/开放上限npv_perpetual/catl_dcf_perpetual——两本账都不建模2030后规模增长（capex诊断.md§8.4已论证的既定假设），差异只在'停在2030规模不动'延续多久：15年还是永续，见第四轮§4.7），「押注」是倍数法与DCF基础账的结构性差值；debt_basis_drift、framework_ul_gap 只诊断、不参与本节点校验</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
     </row>
-    <row r="115" hidden="1" outlineLevel="3">
+    <row r="115" outlineLevel="2">
       <c r="A115" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　运营 EV/EBITDA 倍数</t>
+        <v>2</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　项目NPV（DCF，CRF捷径EV，仅作对照）</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>18</v>
+        <v>137.8346</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>18</v>
+        <v>1441.4749</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18</v>
+        <v>5297.8388</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>finance.swap_ev_ebitda</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr">
-        <is>
-          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>DCF企业价值(CRF年金捷径) ＋ 期末残值现值(target_year) − 估值资本PV(target_year)</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
     </row>
     <row r="116" hidden="1" outlineLevel="3">
       <c r="A116" s="2" t="n">
@@ -4048,21 +4048,21 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　现金流支持的倍数</t>
+          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)·与门槛同源</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>7.5683</v>
+        <v>4368.6409</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.4176</v>
+        <v>8572.0802</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>7.2542</v>
+        <v>16412.2867</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4073,23 +4073,23 @@
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="3" t="inlineStr"/>
     </row>
-    <row r="117" outlineLevel="1">
+    <row r="117" hidden="1" outlineLevel="3">
       <c r="A117" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　估值：这门生意最终值多少钱</t>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>3376.2512</v>
+        <v>264.2046</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>7003.6404</v>
+        <v>450.8699</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14236.0889</v>
+        <v>708.0028</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4098,29 +4098,29 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>见下——倍数法与DCF两套独立口径（DCF区分CRF捷径对照版 npv/catl_dcf、有限期账/基础账 npv_true/catl_dcf_true、永续账/开放上限npv_perpetual/catl_dcf_perpetual——两本账都不建模2030后规模增长（capex诊断.md§8.4已论证的既定假设），差异只在'停在2030规模不动'延续多久：15年还是永续，见第四轮§4.7），「押注」是倍数法与DCF基础账的结构性差值；debt_basis_drift、framework_ul_gap 只诊断、不参与本节点校验</t>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
     </row>
-    <row r="118" outlineLevel="2">
+    <row r="118" hidden="1" outlineLevel="4">
       <c r="A118" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　项目NPV（DCF，CRF捷径EV，仅作对照）</t>
+        <v>4</v>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>137.8346</v>
+        <v>197.8365</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1441.4749</v>
+        <v>337.6116</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>5297.8388</v>
+        <v>530.1529</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4129,35 +4129,31 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>DCF企业价值(CRF年金捷径) ＋ 期末残值现值(target_year) − 估值资本PV(target_year)</t>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119" hidden="1" outlineLevel="3">
+      <c r="I118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119" hidden="1" outlineLevel="4">
       <c r="A119" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)·与门槛同源</t>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>4368.6409</v>
+        <v>1.3355</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>8572.0802</v>
+        <v>1.3355</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>16412.2867</v>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+        <v>1.3355</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
           <t>同上（引用）</t>
@@ -4172,17 +4168,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>264.2046</v>
+        <v>4495.0109</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>450.8699</v>
+        <v>7581.4752</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>708.0028</v>
+        <v>11822.4508</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4191,7 +4187,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
@@ -4203,17 +4199,17 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>197.8365</v>
+        <v>3365.8666</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>337.6116</v>
+        <v>5677.0127</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>530.1529</v>
+        <v>8852.6574</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4222,7 +4218,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -4249,29 +4245,29 @@
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>(1+WACC)^(target_year−base_year)</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="3" t="inlineStr"/>
     </row>
-    <row r="123" hidden="1" outlineLevel="3">
+    <row r="123" outlineLevel="2">
       <c r="A123" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，CRF捷径EV，仅作对照）</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>4495.0109</v>
+        <v>1073.3498</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>7581.4752</v>
+        <v>2292.2033</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>11822.4508</v>
+        <v>4794.5487</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4280,29 +4276,29 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>max(0, DCF企业价值(CRF捷径) ＋ 期末残值现值(target_year) − 稳态debt) × 持股比例</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr"/>
     </row>
-    <row r="124" hidden="1" outlineLevel="4">
+    <row r="124" hidden="1" outlineLevel="3">
       <c r="A124" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
+          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>3365.8666</v>
+        <v>4368.6409</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>5677.0127</v>
+        <v>8572.0802</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>8852.6574</v>
+        <v>16412.2867</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4311,93 +4307,93 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="3" t="inlineStr"/>
     </row>
-    <row r="125" hidden="1" outlineLevel="4">
+    <row r="125" hidden="1" outlineLevel="3">
       <c r="A125" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>264.2046</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>450.8699</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>708.0028</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126" hidden="1" outlineLevel="4">
+      <c r="A126" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>197.8365</v>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>337.6116</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>530.1529</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127" hidden="1" outlineLevel="4">
+      <c r="A127" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　移到target_year的复利因子</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
+      <c r="C127" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="D125" s="2" t="n">
+      <c r="D127" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>(1+WACC)^(target_year−base_year)</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126" outlineLevel="2">
-      <c r="A126" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　CATL归属价值（DCF口径，CRF捷径EV，仅作对照）</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n">
-        <v>1073.3498</v>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>2292.2033</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>4794.5487</v>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>max(0, DCF企业价值(CRF捷径) ＋ 期末残值现值(target_year) − 稳态debt) × 持股比例</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127" hidden="1" outlineLevel="3">
-      <c r="A127" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　DCF企业价值(CRF捷径)</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v>4368.6409</v>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>8572.0802</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>16412.2867</v>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+      <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
           <t>同上（引用）</t>
@@ -4410,19 +4406,19 @@
       <c r="A128" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>264.2046</v>
+        <v>1949.471</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>450.8699</v>
+        <v>3292.4419</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>708.0028</v>
+        <v>5133.9179</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4431,69 +4427,73 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129" hidden="1" outlineLevel="4">
+      <c r="I128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129" hidden="1" outlineLevel="3">
       <c r="A129" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>197.8365</v>
+        <v>0.4</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>337.6116</v>
+        <v>0.4</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>530.1529</v>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130" hidden="1" outlineLevel="4">
+        <v>0.4</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" outlineLevel="2">
       <c r="A130" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+        <v>2</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　项目NPV（DCF，有限期账/基础账）</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>1.3355</v>
+        <v>138.3268</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1.3355</v>
+        <v>1442.4407</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="F130" s="2" t="inlineStr"/>
+        <v>5299.6879</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 估值资本PV(target_year，含真实更新排期)。【2026-09-05d】站体设备不设期末残值——永续账已把它按'每15年到期全额换新、不扣回收'处理，隐含'到期视为耗尽'，有限期账不能再给同一台设备一份残值（两套相反假设），且没有设备二手市场数据支撑折价比例</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="3" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
     </row>
     <row r="131" hidden="1" outlineLevel="3">
       <c r="A131" s="2" t="n">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1949.471</v>
+        <v>4369.1331</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>3292.4419</v>
+        <v>8573.046</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>5133.9179</v>
+        <v>16414.1359</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
@@ -4530,50 +4530,50 @@
       <c r="A132" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　CATL建站持股比例</t>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>0.4</v>
+        <v>264.2046</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.4</v>
+        <v>450.8699</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" outlineLevel="2">
+        <v>708.0028</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133" hidden="1" outlineLevel="4">
       <c r="A133" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　项目NPV（DCF，有限期账/基础账）</t>
+        <v>4</v>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>138.3268</v>
+        <v>197.8365</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1442.4407</v>
+        <v>337.6116</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>5299.6879</v>
+        <v>530.1529</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4582,38 +4582,34 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 估值资本PV(target_year，含真实更新排期)。【2026-09-05d】站体设备不设期末残值——永续账已把它按'每15年到期全额换新、不扣回收'处理，隐含'到期视为耗尽'，有限期账不能再给同一台设备一份残值（两套相反假设），且没有设备二手市场数据支撑折价比例</t>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134" hidden="1" outlineLevel="3">
+      <c r="I133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134" hidden="1" outlineLevel="4">
       <c r="A134" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
+          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>4369.1331</v>
+        <v>1.3355</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>8573.046</v>
+        <v>1.3355</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>16414.1359</v>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+        <v>1.3355</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -4625,17 +4621,17 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>264.2046</v>
+        <v>4495.0109</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>450.8699</v>
+        <v>7581.4752</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>708.0028</v>
+        <v>11822.4508</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4644,7 +4640,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
@@ -4656,17 +4652,17 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>197.8365</v>
+        <v>3365.8666</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>337.6116</v>
+        <v>5677.0127</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>530.1529</v>
+        <v>8852.6574</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4675,7 +4671,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -4702,29 +4698,29 @@
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>(1+WACC)^(target_year−base_year)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="3" t="inlineStr"/>
     </row>
-    <row r="138" hidden="1" outlineLevel="3">
+    <row r="138" outlineLevel="2">
       <c r="A138" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　估值资本PV（移到target_year，DCF专用）</t>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>4495.0109</v>
+        <v>1073.5467</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>7581.4752</v>
+        <v>2292.5896</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>11822.4508</v>
+        <v>4795.2883</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4733,29 +4729,29 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>估值资本PV(base_year) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
     </row>
-    <row r="139" hidden="1" outlineLevel="4">
+    <row r="139" hidden="1" outlineLevel="3">
       <c r="A139" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　估值资本PV（折到基年，DCF专用）</t>
+          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>3365.8666</v>
+        <v>4369.1331</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>5677.0127</v>
+        <v>8573.046</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>8852.6574</v>
+        <v>16414.1359</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4764,96 +4760,96 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>全部CAPEX统一折到base_year——与「做透的代价」分支的门槛口径 lifecycle_capital_base 不共用</t>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="3" t="inlineStr"/>
     </row>
-    <row r="140" hidden="1" outlineLevel="4">
+    <row r="140" hidden="1" outlineLevel="3">
       <c r="A140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>264.2046</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>450.8699</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>708.0028</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141" hidden="1" outlineLevel="4">
+      <c r="A141" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>197.8365</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>337.6116</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>530.1529</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142" hidden="1" outlineLevel="4">
+      <c r="A142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　移到target_year的复利因子</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
+      <c r="C142" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="D140" s="2" t="n">
+      <c r="D142" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="E140" s="2" t="n">
+      <c r="E142" s="2" t="n">
         <v>1.3355</v>
       </c>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>(1+WACC)^(target_year−base_year)</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="3" t="inlineStr"/>
-    </row>
-    <row r="141" outlineLevel="2">
-      <c r="A141" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>1073.5467</v>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>2292.5896</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>4795.2883</v>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142" hidden="1" outlineLevel="3">
-      <c r="A142" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>4369.1331</v>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>8573.046</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>16414.1359</v>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+      <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr"/>
@@ -4863,19 +4859,19 @@
       <c r="A143" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　期末残值现值（税后，移到target_year）</t>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>264.2046</v>
+        <v>1949.471</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>450.8699</v>
+        <v>3292.4419</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>708.0028</v>
+        <v>5133.9179</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4884,87 +4880,91 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144" hidden="1" outlineLevel="4">
+      <c r="I143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144" hidden="1" outlineLevel="3">
       <c r="A144" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>197.8365</v>
+        <v>0.4</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>337.6116</v>
+        <v>0.4</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>530.1529</v>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="3" t="inlineStr"/>
-    </row>
-    <row r="145" hidden="1" outlineLevel="4">
+        <v>0.4</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" outlineLevel="2">
       <c r="A145" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　移到target_year的复利因子</t>
+          <t xml:space="preserve">　　项目NPV（DCF，永续账/开放上限）</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>1.3355</v>
+        <v>885.8787</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.3355</v>
+        <v>3325.9733</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>1.3355</v>
-      </c>
-      <c r="F145" s="2" t="inlineStr"/>
+        <v>9804.023999999999</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>DCF企业价值(永续) − 纯初装现值(target_year，剔除更换支出后的一次性投资，永续假设下不含期末残值——不会真的清算)</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr"/>
     </row>
-    <row r="146" hidden="1" outlineLevel="3">
+    <row r="146" outlineLevel="2">
       <c r="A146" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+          <t xml:space="preserve">　　CATL归属价值（DCF口径，永续账/开放上限）</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1949.471</v>
+        <v>1080.8084</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>3292.4419</v>
+        <v>2551.3089</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>5133.9179</v>
+        <v>5822.8976</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -4973,60 +4973,60 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+          <t>max(0, DCF企业价值(永续) − 稳态debt) × 持股比例——与有限期账（基础账）共用同一个debt快照，差异只在EV怎么算（第一轮§1已论证debt该是资产负债表快照，跟期限假设无关）</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="3" t="inlineStr"/>
     </row>
-    <row r="147" hidden="1" outlineLevel="3">
+    <row r="147" outlineLevel="2">
       <c r="A147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　CATL归属价值（倍数法口径）</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>3376.2512</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>7003.6404</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>14236.0889</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148" hidden="1" outlineLevel="3">
+      <c r="A148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　CATL建站持股比例</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D147" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" outlineLevel="2">
-      <c r="A148" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　项目NPV（DCF，永续账/开放上限）</t>
+          <t xml:space="preserve">　　　EBITDA</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>885.8787</v>
+        <v>577.2277</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>3325.9733</v>
+        <v>1155.6413</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>9804.023999999999</v>
+        <v>2262.4522</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5035,60 +5035,64 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>DCF企业价值(永续) − 纯初装现值(target_year，剔除更换支出后的一次性投资，永续假设下不含期末残值——不会真的清算)</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="3" t="inlineStr"/>
     </row>
-    <row r="149" outlineLevel="2">
+    <row r="149" hidden="1" outlineLevel="3">
       <c r="A149" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　CATL归属价值（DCF口径，永续账/开放上限）</t>
+          <t xml:space="preserve">　　　运营EV/EBITDA倍数</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>1080.8084</v>
+        <v>18</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2551.3089</v>
+        <v>18</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>5822.8976</v>
+        <v>18</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>max(0, DCF企业价值(永续) − 稳态debt) × 持股比例——与有限期账（基础账）共用同一个debt快照，差异只在EV怎么算（第一轮§1已论证debt该是资产负债表快照，跟期限假设无关）</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr"/>
-      <c r="I149" s="3" t="inlineStr"/>
-    </row>
-    <row r="150" outlineLevel="2">
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>finance.swap_ev_ebitda</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" hidden="1" outlineLevel="3">
       <c r="A150" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　CATL归属价值（倍数法口径）</t>
+        <v>3</v>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　稳态debt（同DCF线，2026-09-04起统一）</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>3376.2512</v>
+        <v>1949.471</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>7003.6404</v>
+        <v>3292.4419</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>14236.0889</v>
+        <v>5133.9179</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5097,11 +5101,11 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
+          <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="2" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr"/>
     </row>
     <row r="151" hidden="1" outlineLevel="3">
       <c r="A151" s="2" t="n">
@@ -5109,189 +5113,189 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　EBITDA</t>
+          <t xml:space="preserve">　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>577.2277</v>
+        <v>0.4</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1155.6413</v>
+        <v>0.4</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>2262.4522</v>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" s="3" t="inlineStr"/>
-    </row>
-    <row r="152" hidden="1" outlineLevel="3">
+        <v>0.4</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" outlineLevel="2">
       <c r="A152" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　运营EV/EBITDA倍数</t>
+        <v>2</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　押注部分（结构性差值）</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>18</v>
+        <v>2302.7045</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>18</v>
+        <v>4711.0508</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>18</v>
+        <v>9440.8006</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>finance.swap_ev_ebitda</t>
-        </is>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>倍数法归属 − DCF归属(真实口径)　【2026-09-04：debt统一后，两条线现在真的在问同一个问题、用同一个debt，此前藏着的第三份「倍数法归属」（_dcf_cross_check内部现算、从未暴露的版本，见 DECISIONS「2026-09-03b」）已删除，三份合并为一份（T3已解决），此处直接用真正的倍数法headline数字相减】</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr"/>
     </row>
     <row r="153" hidden="1" outlineLevel="3">
       <c r="A153" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　稳态debt（同DCF线，2026-09-04起统一）</t>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL归属价值（倍数法口径）</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
+        <v>3376.2512</v>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>7003.6404</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>14236.0889</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154" hidden="1" outlineLevel="4">
+      <c r="A154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　EBITDA</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>577.2277</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>1155.6413</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>2262.4522</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>同上（引用）</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155" hidden="1" outlineLevel="4">
+      <c r="A155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　运营EV/EBITDA倍数</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>finance.swap_ev_ebitda</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" hidden="1" outlineLevel="4">
+      <c r="A156" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　稳态debt（同DCF线，2026-09-04起统一）</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
         <v>1949.471</v>
       </c>
-      <c r="D153" s="2" t="n">
+      <c r="D156" s="2" t="n">
         <v>3292.4419</v>
       </c>
-      <c r="E153" s="2" t="n">
+      <c r="E156" s="2" t="n">
         <v>5133.9179</v>
       </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr"/>
-      <c r="I153" s="3" t="inlineStr"/>
-    </row>
-    <row r="154" hidden="1" outlineLevel="3">
-      <c r="A154" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　CATL建站持股比例</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D154" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" outlineLevel="2">
-      <c r="A155" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　押注部分（结构性差值）</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>2302.7045</v>
-      </c>
-      <c r="D155" s="2" t="n">
-        <v>4711.0508</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>9440.8006</v>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>倍数法归属 − DCF归属(真实口径)　【2026-09-04：debt统一后，两条线现在真的在问同一个问题、用同一个debt，此前藏着的第三份「倍数法归属」（_dcf_cross_check内部现算、从未暴露的版本，见 DECISIONS「2026-09-03b」）已删除，三份合并为一份（T3已解决），此处直接用真正的倍数法headline数字相减】</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156" hidden="1" outlineLevel="3">
-      <c r="A156" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　CATL归属价值（倍数法口径）</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>3376.2512</v>
-      </c>
-      <c r="D156" s="2" t="n">
-        <v>7003.6404</v>
-      </c>
-      <c r="E156" s="2" t="n">
-        <v>14236.0889</v>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>max(0, EBITDA×拍定倍数 − 稳态debt) × 持股比例（分池计算，单池权益不为负；此处聚合层重算未做分池取0下限，与逐池加总可能有微小差异，属已知近似，见待办清单#12）</t>
-        </is>
-      </c>
       <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr"/>
+      <c r="I156" s="3" t="inlineStr"/>
     </row>
     <row r="157" hidden="1" outlineLevel="4">
       <c r="A157" s="2" t="n">
@@ -5299,65 +5303,61 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　EBITDA</t>
+          <t xml:space="preserve">　　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>577.2277</v>
+        <v>0.4</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1155.6413</v>
+        <v>0.4</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>2262.4522</v>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>同上（引用）</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="3" t="inlineStr"/>
-    </row>
-    <row r="158" hidden="1" outlineLevel="4">
+        <v>0.4</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" hidden="1" outlineLevel="3">
       <c r="A158" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　运营EV/EBITDA倍数</t>
+        <v>3</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>18</v>
+        <v>1073.5467</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>18</v>
+        <v>2292.5896</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>18</v>
+        <v>4795.2883</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>finance.swap_ev_ebitda</t>
-        </is>
-      </c>
-      <c r="I158" s="3" t="inlineStr">
-        <is>
-          <t>运营 EV/EBITDA 18× ← v3.2 §4.1「18× 是含战略溢价的基建运营倍数，不是 GP/科技资管倍数」。 / 三族对照（判断倍数看"谁扛资产、谁赚什么钱"，不能只看资产轻重）：</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr"/>
     </row>
     <row r="159" hidden="1" outlineLevel="4">
       <c r="A159" s="2" t="n">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　稳态debt（同DCF线，2026-09-04起统一）</t>
+          <t xml:space="preserve">　　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1949.471</v>
+        <v>4369.1331</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>3292.4419</v>
+        <v>8573.046</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>5133.9179</v>
+        <v>16414.1359</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2030年在役资产历史成本×债务比例——与DCF线共用同一个数（T3已解决）</t>
+          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr"/>
@@ -5394,50 +5394,50 @@
       <c r="A160" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　CATL建站持股比例</t>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　期末残值现值（税后，移到target_year）</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>0.4</v>
+        <v>264.2046</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0.4</v>
+        <v>450.8699</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" hidden="1" outlineLevel="3">
+        <v>708.0028</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161" hidden="1" outlineLevel="5">
       <c r="A161" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
+        <v>5</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　期末残值现值（税后，base_year）</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>1073.5467</v>
+        <v>197.8365</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2292.5896</v>
+        <v>337.6116</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>4795.2883</v>
+        <v>530.1529</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5446,38 +5446,34 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>max(0, DCF企业价值(毛现金流) ＋ 期末残值现值(电池,target_year) − 稳态debt) × 持股比例（站体设备不设期末残值，理由同val.npv_true）</t>
+          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162" hidden="1" outlineLevel="4">
+      <c r="I161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162" hidden="1" outlineLevel="5">
       <c r="A162" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　DCF企业价值（有限期账/基础账，毛现金流资本化）</t>
+          <t xml:space="preserve">　　　　　移到target_year的复利因子</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>4369.1331</v>
+        <v>1.3355</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>8573.046</v>
+        <v>1.3355</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>16414.1359</v>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
+        <v>1.3355</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>成熟期FCFF（毛现金流，不扣任何资本性支出代理）× 15年WACC年金因子——资本性支出已经在 valuation_capital_target 里用真实排期精确扣过，这里不再重复扣减（此前用折旧代理再扣一次是bug，见 DECISIONS「2026-09-04c」）</t>
+          <t>同上（引用）</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
@@ -5487,19 +5483,19 @@
       <c r="A163" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　期末残值现值（税后，移到target_year）</t>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>264.2046</v>
+        <v>1949.471</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>450.8699</v>
+        <v>3292.4419</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>708.0028</v>
+        <v>5133.9179</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5508,189 +5504,100 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>期末残值现值(base_year,税后) × (1+WACC)^(target_year−base_year)——精确操作，非近似</t>
+          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164" hidden="1" outlineLevel="5">
+      <c r="I163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164" hidden="1" outlineLevel="4">
       <c r="A164" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　期末残值现值（税后，base_year）</t>
+          <t xml:space="preserve">　　　　CATL建站持股比例</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>197.8365</v>
+        <v>0.4</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>337.6116</v>
+        <v>0.4</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>530.1529</v>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>亿元</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>各cohort期末残值按tax_rate计税、折回base_year后加总——见 DECISIONS「2026-09-03 · 末代残值不再降级储能」</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="3" t="inlineStr"/>
-    </row>
-    <row r="165" hidden="1" outlineLevel="5">
+        <v>0.4</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" outlineLevel="2">
       <c r="A165" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　移到target_year的复利因子</t>
+          <t xml:space="preserve">　　稳态debt相对旧口径（门槛底座×债务比）改变了多少</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>1.3355</v>
+        <v>-0.1635</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>1.3355</v>
+        <v>-0.1641</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>1.3355</v>
+        <v>-0.1645</v>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>同上（引用）</t>
+          <t>(新稳态debt − 旧门槛底座债务) ÷ 旧门槛底座债务——纯诊断：2026-09-04 起两条估值线已统一使用稳态debt，不再是「两条线口径分裂」（那个问题已解决），此节点只记录这次口径修正把debt改变了多少，见 DECISIONS「2026-09-03b」「2026-09-04」</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr"/>
       <c r="I165" s="3" t="inlineStr"/>
     </row>
-    <row r="166" hidden="1" outlineLevel="4">
+    <row r="166" outlineLevel="2">
       <c r="A166" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　稳态debt（2030在役资产历史成本×债务比，倍数法与DCF共用）</t>
+          <t xml:space="preserve">　　框架L(折现FCFE)相对框架U(EV−debt)的偏离</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>1949.471</v>
+        <v>-0.5142</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>3292.4419</v>
+        <v>-0.4795</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>5133.9179</v>
+        <v>-0.4485</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Σ_cohort( target_year在役那一代的历史成本，含站体 ) × 债务比例——倍数法（val.catl_multiple）与DCF法在此共用同一个数，T3已解决</t>
+          <t>【T5，2026-09-04，纯诊断】(框架L股权价值 − 框架U股权价值) ÷ 框架U股权价值。框架L：Ke=[WACC−债务比×债务利率×(1−税率)]÷(1−债务比) 折现FCFE（FCFE=真实FCFF−税后利息，debt按steady_state_debt_yi固定不摊销、净新增借款=0，与forward_fcff/sustaining_capex同样的'稳态不变'假设）。两者不精确相等是预期内的：附录'情形C'证明U=L恒等式要求debt按'债务比×剩余项目价值'逐期摊销到0（value降、debt跟着降）；本模型debt是'target_year在役资产历史成本'快照，15年窗口内固定不变——这是两种不同的'稳定杠杆'定义，有限期+终值截断场景下不再代数等价。此gap量化这一口径差异的幅度，不参与上层校验、不代表程序错误</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
       <c r="I166" s="3" t="inlineStr"/>
-    </row>
-    <row r="167" hidden="1" outlineLevel="4">
-      <c r="A167" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　CATL建站持股比例</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E167" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="I167" s="3" t="inlineStr">
-        <is>
-          <t>建站持股比例 40%：假设值（保守档）。锚=蔚能案例：蔚来经天地资本增资后 27.8% 实控。 / 敏感性：0.278（蔚能锚）/ 0.30 / 0.40（保守）。v4.3 单一真相源——外部销售口径在代码中以 1-0.40 派生（原 external_sales_share 已删除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" outlineLevel="2">
-      <c r="A168" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　稳态debt相对旧口径（门槛底座×债务比）改变了多少</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>-0.1635</v>
-      </c>
-      <c r="D168" s="2" t="n">
-        <v>-0.1641</v>
-      </c>
-      <c r="E168" s="2" t="n">
-        <v>-0.1645</v>
-      </c>
-      <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>(新稳态debt − 旧门槛底座债务) ÷ 旧门槛底座债务——纯诊断：2026-09-04 起两条估值线已统一使用稳态debt，不再是「两条线口径分裂」（那个问题已解决），此节点只记录这次口径修正把debt改变了多少，见 DECISIONS「2026-09-03b」「2026-09-04」</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr"/>
-      <c r="I168" s="3" t="inlineStr"/>
-    </row>
-    <row r="169" outlineLevel="2">
-      <c r="A169" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　框架L(折现FCFE)相对框架U(EV−debt)的偏离</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>-0.5142</v>
-      </c>
-      <c r="D169" s="2" t="n">
-        <v>-0.4795</v>
-      </c>
-      <c r="E169" s="2" t="n">
-        <v>-0.4485</v>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>【T5，2026-09-04，纯诊断】(框架L股权价值 − 框架U股权价值) ÷ 框架U股权价值。框架L：Ke=[WACC−债务比×债务利率×(1−税率)]÷(1−债务比) 折现FCFE（FCFE=真实FCFF−税后利息，debt按steady_state_debt_yi固定不摊销、净新增借款=0，与forward_fcff/sustaining_capex同样的'稳态不变'假设）。两者不精确相等是预期内的：附录'情形C'证明U=L恒等式要求debt按'债务比×剩余项目价值'逐期摊销到0（value降、debt跟着降）；本模型debt是'target_year在役资产历史成本'快照，15年窗口内固定不变——这是两种不同的'稳定杠杆'定义，有限期+终值截断场景下不再代数等价。此gap量化这一口径差异的幅度，不参与上层校验、不代表程序错误</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2156.1074</v>
+        <v>2148.8441</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7775.0504</v>
+        <v>7755.5209</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17768.1476</v>
+        <v>17760.7156</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2156.1074</v>
+        <v>2148.8441</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7775.0504</v>
+        <v>7755.5209</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17768.1476</v>
+        <v>17760.7156</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3376.2512</v>
+        <v>3369.06</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7003.6404</v>
+        <v>6984.4207</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14236.0889</v>
+        <v>14228.6569</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8440.628000000001</v>
+        <v>8422.65</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17509.101</v>
+        <v>17461.0517</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35590.2223</v>
+        <v>35571.6423</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10390.0989</v>
+        <v>10391.0128</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>20801.5429</v>
+        <v>20778.9843</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>40724.1402</v>
+        <v>40756.1442</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>577.2277</v>
+        <v>577.2785</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1155.6413</v>
+        <v>1154.388</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2262.4522</v>
+        <v>2264.2302</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>702.9539</v>
+        <v>704.8306</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1358.7002</v>
+        <v>1360.1949</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2571.0984</v>
+        <v>2577.8429</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>261.1339</v>
+        <v>260.7845</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>510.1726</v>
+        <v>508.9142</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>937.2616</v>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2040.1083</v>
+        <v>2037.3791</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3319.2754</v>
+        <v>3311.0879</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>5077.2565</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2886500</v>
+        <v>2884600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4670100</v>
+        <v>4664400</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>6927100</v>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>252.4199</v>
+        <v>252.2483</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>253.8394</v>
+        <v>253.5227</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>261.7698</v>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>384.4744</v>
+        <v>384.0821</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>756.0347</v>
+        <v>754.6378</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1493.2006</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>437.5472</v>
+        <v>437.0527</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>749.4215</v>
+        <v>747.8756</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1178.2443</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>437.5472</v>
+        <v>437.0527</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>749.4215</v>
+        <v>747.8756</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1178.2443</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7.0797</v>
+        <v>7.0803</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8.284800000000001</v>
+        <v>8.2867</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>10.751</v>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>49.9069</v>
+        <v>52.238</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>80.6469</v>
+        <v>84.3417</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>122.935</v>
+        <v>128.9398</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>38.7476</v>
+        <v>40.5575</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>62.614</v>
+        <v>65.48269999999999</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>95.4464</v>
+        <v>100.1086</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7.4388</v>
+        <v>7.726</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>11.846</v>
+        <v>12.3011</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>17.7012</v>
+        <v>18.4409</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.6257</v>
+        <v>0.6558</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.008</v>
+        <v>1.0558</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.5356</v>
+        <v>1.6133</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>4.1711</v>
+        <v>4.3722</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6.7199</v>
+        <v>7.0387</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>10.2371</v>
+        <v>10.7551</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6.8131</v>
+        <v>7.0701</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>10.838</v>
+        <v>11.2453</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>16.1657</v>
+        <v>16.8277</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>125.7262</v>
+        <v>127.5521</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>203.0589</v>
+        <v>205.8069</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>308.6461</v>
+        <v>313.6127</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>66.5253</v>
+        <v>66.4363</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>108.2372</v>
+        <v>107.9703</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>165.5627</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2261.8592</v>
+        <v>2258.8334</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3680.0662</v>
+        <v>3670.9888</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>5629.1322</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>2040.1083</v>
+        <v>2037.3791</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>3319.2754</v>
+        <v>3311.0879</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>5077.2565</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2040.1083</v>
+        <v>2037.3791</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>3319.2754</v>
+        <v>3311.0879</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>5077.2565</v>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>20.07</v>
+        <v>20.7315</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>31.7415</v>
+        <v>32.79</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>46.878</v>
+        <v>48.582</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13380</v>
+        <v>13821</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>21161</v>
+        <v>21860</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>31252</v>
+        <v>32388</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>23.7098</v>
+        <v>24.8952</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>38.2795</v>
+        <v>40.1585</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>58.5191</v>
+        <v>61.5727</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8314</v>
+        <v>8755</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>13472</v>
+        <v>14171</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>20717</v>
+        <v>21853</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>6.3958</v>
+        <v>6.4444</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10.8231</v>
+        <v>10.8911</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>16.8994</v>
+        <v>17.0396</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>5.6203</v>
+        <v>5.6358</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>9.582000000000001</v>
+        <v>9.5976</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>15.0296</v>
+        <v>15.0846</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1.4051</v>
+        <v>1.409</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.3955</v>
+        <v>2.3994</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>3.7574</v>
+        <v>3.7711</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1949.471</v>
+        <v>1968.3628</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>3292.4419</v>
+        <v>3317.9326</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>5133.9179</v>
+        <v>5184.5019</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>-1220.1438</v>
+        <v>-1220.2159</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>771.41</v>
+        <v>771.1002</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>3532.0586</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>-61.0072</v>
+        <v>-61.0108</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>38.5705</v>
+        <v>38.555</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>176.6029</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>-61.0072</v>
+        <v>-61.0108</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2.733</v>
+        <v>2.7186</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>70.3633</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>47.6529</v>
+        <v>47.6309</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>80.4935</v>
+        <v>80.3272</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>123.9601</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-108.6601</v>
+        <v>-108.6417</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>-77.7606</v>
+        <v>-77.6086</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>-53.5968</v>
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>35.8375</v>
+        <v>35.8364</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>106.2396</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>2912.7091</v>
+        <v>2912.6803</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>3583.7531</v>
+        <v>3583.6384</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>4249.5851</v>
@@ -2537,13 +2537,13 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>0.1214</v>
+        <v>0.121</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.4379</v>
+        <v>0.4368</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.0006</v>
+        <v>1.0002</v>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
@@ -2564,13 +2564,13 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>2156.1074</v>
+        <v>2148.8441</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>7775.0504</v>
+        <v>7755.5209</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17768.1476</v>
+        <v>17760.7156</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>621.4655</v>
+        <v>626.5672</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1050.3628</v>
+        <v>1056.98</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1638.6857</v>
+        <v>1652.4575</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>621.4655</v>
+        <v>626.5672</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1050.3628</v>
+        <v>1056.98</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1638.6857</v>
+        <v>1652.4575</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>3884.1593</v>
+        <v>3916.0449</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>6564.7674</v>
+        <v>6606.1248</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>10241.7855</v>
+        <v>10327.8594</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3884.1593</v>
+        <v>3916.0449</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>6564.7674</v>
+        <v>6606.1248</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>10241.7855</v>
+        <v>10327.8594</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>3249.1183</v>
+        <v>3280.6046</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>5487.4031</v>
+        <v>5529.8876</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>8556.5298</v>
+        <v>8640.836499999999</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2503.4874</v>
+        <v>2502.2456</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4290.6004</v>
+        <v>4281.2096</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>6746.846</v>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>216.5076</v>
+        <v>227.1858</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>357.3194</v>
+        <v>374.2447</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>551.0305</v>
+        <v>578.5372</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>481.37</v>
+        <v>503.42</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>791.73</v>
+        <v>826.6799999999999</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1210.9</v>
+        <v>1267.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>635.0410000000001</v>
+        <v>635.4403</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1077.3643</v>
+        <v>1076.2372</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1685.2557</v>
+        <v>1687.0229</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>440.0752</v>
+        <v>443.6879</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>743.7881</v>
+        <v>748.4739</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1160.3943</v>
+        <v>1170.1465</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>3884.1593</v>
+        <v>3916.0449</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>6564.7674</v>
+        <v>6606.1248</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>10241.7855</v>
+        <v>10327.8594</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>2330.4956</v>
+        <v>2349.6269</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3938.8604</v>
+        <v>3963.6749</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>6145.0713</v>
+        <v>6196.7156</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>3884.1593</v>
+        <v>3916.0449</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>6564.7674</v>
+        <v>6606.1248</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>10241.7855</v>
+        <v>10327.8594</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>3249.1183</v>
+        <v>3280.6046</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>5487.4031</v>
+        <v>5529.8876</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>8556.5298</v>
+        <v>8640.836499999999</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2503.4874</v>
+        <v>2502.2456</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4290.6004</v>
+        <v>4281.2096</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>6746.846</v>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>216.5076</v>
+        <v>227.1858</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>357.3194</v>
+        <v>374.2447</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>551.0305</v>
+        <v>578.5372</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>481.37</v>
+        <v>503.42</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>791.73</v>
+        <v>826.6799999999999</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1210.9</v>
+        <v>1267.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>635.0410000000001</v>
+        <v>635.4403</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1077.3643</v>
+        <v>1076.2372</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>1685.2557</v>
+        <v>1687.0229</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>1.1452</v>
+        <v>1.1356</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.3557</v>
+        <v>1.3454</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1.7007</v>
+        <v>1.6874</v>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
@@ -3393,13 +3393,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1.1452</v>
+        <v>1.1356</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.3557</v>
+        <v>1.3454</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.7007</v>
+        <v>1.6874</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>577.2277</v>
+        <v>577.2785</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1155.6413</v>
+        <v>1154.388</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>2262.4522</v>
+        <v>2264.2302</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>504.0387</v>
+        <v>508.3284</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>852.4032</v>
+        <v>858.0124</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1330.2952</v>
+        <v>1341.8572</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>329.0428</v>
+        <v>327.5122</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>737.6983</v>
+        <v>734.5295</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1611.7606</v>
+        <v>1609.2159</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>577.2277</v>
+        <v>577.2785</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1155.6413</v>
+        <v>1154.388</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>2262.4522</v>
+        <v>2264.2302</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>248.1849</v>
+        <v>249.7663</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>417.9429</v>
+        <v>419.8586</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>650.6916</v>
+        <v>655.0144</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>213.7169</v>
+        <v>213.8283</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>362.7843</v>
+        <v>362.3699</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>567.5883</v>
+        <v>568.1244</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>517.02</v>
+        <v>539.0700000000001</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>827.38</v>
+        <v>862.33</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1246.55</v>
+        <v>1303.35</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>481.37</v>
+        <v>503.42</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>791.73</v>
+        <v>826.6799999999999</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>1210.9</v>
+        <v>1267.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3738,13 +3738,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>7.5683</v>
+        <v>7.5743</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7.4176</v>
+        <v>7.4221</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>7.2542</v>
+        <v>7.2579</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>4368.6409</v>
+        <v>4372.4664</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>8572.0802</v>
+        <v>8568.011</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>16412.2867</v>
+        <v>16433.5946</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>494.967</v>
+        <v>495.4004</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>971.2166999999999</v>
+        <v>970.7557</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>1859.5121</v>
+        <v>1861.9263</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>577.2277</v>
+        <v>577.2785</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1155.6413</v>
+        <v>1154.388</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>2262.4522</v>
+        <v>2264.2302</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>2.3783</v>
+        <v>2.3765</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2.4267</v>
+        <v>2.4252</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>2.4813</v>
+        <v>2.4801</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3959,13 +3959,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>7.5683</v>
+        <v>7.5743</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>7.4176</v>
+        <v>7.4221</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>7.2542</v>
+        <v>7.2579</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>3376.2512</v>
+        <v>3369.06</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>7003.6404</v>
+        <v>6984.4207</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>14236.0889</v>
+        <v>14228.6569</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>137.8346</v>
+        <v>104.3645</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1441.4749</v>
+        <v>1388.0768</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>5297.8388</v>
+        <v>5218.8745</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>4368.6409</v>
+        <v>4372.4664</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>8572.0802</v>
+        <v>8568.011</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>16412.2867</v>
+        <v>16433.5946</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>264.2046</v>
+        <v>265.316</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>450.8699</v>
+        <v>451.9186</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>708.0028</v>
+        <v>711.1748</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>197.8365</v>
+        <v>198.6688</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>337.6116</v>
+        <v>338.3969</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>530.1529</v>
+        <v>532.5281</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>4495.0109</v>
+        <v>4533.418</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>7581.4752</v>
+        <v>7631.8528</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>11822.4508</v>
+        <v>11925.8948</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4203,13 +4203,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3365.8666</v>
+        <v>3394.6258</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>5677.0127</v>
+        <v>5714.7354</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>8852.6574</v>
+        <v>8930.116400000001</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>1073.3498</v>
+        <v>1067.7679</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2292.2033</v>
+        <v>2280.7988</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>4794.5487</v>
+        <v>4784.107</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>4368.6409</v>
+        <v>4372.4664</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>8572.0802</v>
+        <v>8568.011</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>16412.2867</v>
+        <v>16433.5946</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>264.2046</v>
+        <v>265.316</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>450.8699</v>
+        <v>451.9186</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>708.0028</v>
+        <v>711.1748</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>197.8365</v>
+        <v>198.6688</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>337.6116</v>
+        <v>338.3969</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>530.1529</v>
+        <v>532.5281</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>1949.471</v>
+        <v>1968.3628</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3292.4419</v>
+        <v>3317.9326</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>5133.9179</v>
+        <v>5184.5019</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>138.3268</v>
+        <v>104.8571</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1442.4407</v>
+        <v>1389.0421</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>5299.6879</v>
+        <v>5220.726</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>4369.1331</v>
+        <v>4372.9591</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>8573.046</v>
+        <v>8568.9764</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>16414.1359</v>
+        <v>16435.4461</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>264.2046</v>
+        <v>265.316</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>450.8699</v>
+        <v>451.9186</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>708.0028</v>
+        <v>711.1748</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>197.8365</v>
+        <v>198.6688</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>337.6116</v>
+        <v>338.3969</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>530.1529</v>
+        <v>532.5281</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>4495.0109</v>
+        <v>4533.418</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>7581.4752</v>
+        <v>7631.8528</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>11822.4508</v>
+        <v>11925.8948</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>3365.8666</v>
+        <v>3394.6258</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>5677.0127</v>
+        <v>5714.7354</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>8852.6574</v>
+        <v>8930.116400000001</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4714,13 +4714,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>1073.5467</v>
+        <v>1067.9649</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2292.5896</v>
+        <v>2281.1849</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>4795.2883</v>
+        <v>4784.8476</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>4369.1331</v>
+        <v>4372.9591</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>8573.046</v>
+        <v>8568.9764</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>16414.1359</v>
+        <v>16435.4461</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>264.2046</v>
+        <v>265.316</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>450.8699</v>
+        <v>451.9186</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>708.0028</v>
+        <v>711.1748</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>197.8365</v>
+        <v>198.6688</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>337.6116</v>
+        <v>338.3969</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>530.1529</v>
+        <v>532.5281</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1949.471</v>
+        <v>1968.3628</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3292.4419</v>
+        <v>3317.9326</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>5133.9179</v>
+        <v>5184.5019</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>885.8787</v>
+        <v>842.5229</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>3325.9733</v>
+        <v>3255.1034</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>9804.023999999999</v>
+        <v>9704.016299999999</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1080.8084</v>
+        <v>1071.0359</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2551.3089</v>
+        <v>2533.3464</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>5822.8976</v>
+        <v>5803.0905</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>3376.2512</v>
+        <v>3369.06</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>7003.6404</v>
+        <v>6984.4207</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>14236.0889</v>
+        <v>14228.6569</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>577.2277</v>
+        <v>577.2785</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1155.6413</v>
+        <v>1154.388</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>2262.4522</v>
+        <v>2264.2302</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5086,13 +5086,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>1949.471</v>
+        <v>1968.3628</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>3292.4419</v>
+        <v>3317.9326</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>5133.9179</v>
+        <v>5184.5019</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>2302.7045</v>
+        <v>2301.0951</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>4711.0508</v>
+        <v>4703.2357</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>9440.8006</v>
+        <v>9443.809300000001</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>3376.2512</v>
+        <v>3369.06</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>7003.6404</v>
+        <v>6984.4207</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>14236.0889</v>
+        <v>14228.6569</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>577.2277</v>
+        <v>577.2785</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1155.6413</v>
+        <v>1154.388</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>2262.4522</v>
+        <v>2264.2302</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -5276,13 +5276,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>1949.471</v>
+        <v>1968.3628</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>3292.4419</v>
+        <v>3317.9326</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>5133.9179</v>
+        <v>5184.5019</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5338,13 +5338,13 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>1073.5467</v>
+        <v>1067.9649</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2292.5896</v>
+        <v>2281.1849</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>4795.2883</v>
+        <v>4784.8476</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>4369.1331</v>
+        <v>4372.9591</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>8573.046</v>
+        <v>8568.9764</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>16414.1359</v>
+        <v>16435.4461</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>264.2046</v>
+        <v>265.316</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>450.8699</v>
+        <v>451.9186</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>708.0028</v>
+        <v>711.1748</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>197.8365</v>
+        <v>198.6688</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>337.6116</v>
+        <v>338.3969</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>530.1529</v>
+        <v>532.5281</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>1949.471</v>
+        <v>1968.3628</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>3292.4419</v>
+        <v>3317.9326</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>5133.9179</v>
+        <v>5184.5019</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>-0.1635</v>
+        <v>-0.1623</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-0.1641</v>
+        <v>-0.1629</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>-0.1645</v>
+        <v>-0.1633</v>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>-0.5142</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-0.4795</v>
+        <v>-0.4796</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>-0.4485</v>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2148.8441</v>
+        <v>1504.4299</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7755.5209</v>
+        <v>6794.5335</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17760.7156</v>
+        <v>16492.2252</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2148.8441</v>
+        <v>1504.4299</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7755.5209</v>
+        <v>6794.5335</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17760.7156</v>
+        <v>16492.2252</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3369.06</v>
+        <v>2726.034</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6984.4207</v>
+        <v>6023.9709</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14228.6569</v>
+        <v>12960.1665</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8422.65</v>
+        <v>6815.0849</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17461.0517</v>
+        <v>15059.9272</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35571.6423</v>
+        <v>32400.4163</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10391.0128</v>
+        <v>8664.808499999999</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>20778.9843</v>
+        <v>18259.1684</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>40756.1442</v>
+        <v>37509.621</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>577.2785</v>
+        <v>481.3783</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1154.388</v>
+        <v>1014.3982</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2264.2302</v>
+        <v>2083.8678</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>704.8306</v>
+        <v>581.9636</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1360.1949</v>
+        <v>1191.6157</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2577.8429</v>
+        <v>2376.6353</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>260.7845</v>
+        <v>195.5513</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>508.9142</v>
+        <v>424.8874</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>937.2616</v>
+        <v>861.1078</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2037.3791</v>
+        <v>1527.7444</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3311.0879</v>
+        <v>2764.3941</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5077.2565</v>
+        <v>4664.7224</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2884600</v>
+        <v>2529800</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4664400</v>
+        <v>4283800</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6927100</v>
+        <v>6639900</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>252.2483</v>
+        <v>215.6783</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>253.5227</v>
+        <v>230.4691</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>261.7698</v>
+        <v>250.9032</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>384.0821</v>
+        <v>340.353</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>754.6378</v>
+        <v>684.6077</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1493.2006</v>
+        <v>1378.1864</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>437.0527</v>
+        <v>432.9419</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>747.8756</v>
+        <v>745.292</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1178.2443</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>437.0527</v>
+        <v>432.9419</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>747.8756</v>
+        <v>745.292</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1178.2443</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7.0803</v>
+        <v>6.1769</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8.2867</v>
+        <v>7.3761</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10.751</v>
+        <v>9.757899999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>52.238</v>
+        <v>39.8583</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>84.3417</v>
+        <v>71.4123</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>128.9398</v>
+        <v>120.0013</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>40.5575</v>
+        <v>30.9459</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>65.48269999999999</v>
+        <v>55.4443</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>100.1086</v>
+        <v>93.1687</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7.726</v>
+        <v>6.201</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12.3011</v>
+        <v>10.7084</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>18.4409</v>
+        <v>17.3399</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.6558</v>
+        <v>0.4956</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.0558</v>
+        <v>0.8885</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.6133</v>
+        <v>1.4976</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>4.3722</v>
+        <v>3.3043</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7.0387</v>
+        <v>5.9233</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>10.7551</v>
+        <v>9.984</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7.0701</v>
+        <v>5.7053</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>11.2453</v>
+        <v>9.819900000000001</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>16.8277</v>
+        <v>15.8423</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>127.5521</v>
+        <v>100.5853</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>205.8069</v>
+        <v>177.2175</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>313.6127</v>
+        <v>292.7675</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>66.4363</v>
+        <v>49.8178</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>107.9703</v>
+        <v>90.1433</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>165.5627</v>
+        <v>152.1105</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2258.8334</v>
+        <v>1693.8036</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3670.9888</v>
+        <v>3064.8717</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>5629.1322</v>
+        <v>5171.7575</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>2037.3791</v>
+        <v>1527.7444</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>3311.0879</v>
+        <v>2764.3941</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>5077.2565</v>
+        <v>4664.7224</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2037.3791</v>
+        <v>1527.7444</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>3311.0879</v>
+        <v>2764.3941</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>5077.2565</v>
+        <v>4664.7224</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>20.7315</v>
+        <v>17.2185</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>32.79</v>
+        <v>29.121</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>48.582</v>
+        <v>46.0455</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13821</v>
+        <v>11479</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>21860</v>
+        <v>19414</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>32388</v>
+        <v>30697</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>24.8952</v>
+        <v>18.5999</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>40.1585</v>
+        <v>33.5836</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>61.5727</v>
+        <v>57.0273</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8755</v>
+        <v>6413</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14171</v>
+        <v>11725</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>21853</v>
+        <v>20162</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>6.4444</v>
+        <v>6.1068</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10.8911</v>
+        <v>10.5587</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>17.0396</v>
+        <v>16.8309</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>5.6358</v>
+        <v>5.4739</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>9.5976</v>
+        <v>9.448700000000001</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>15.0846</v>
+        <v>15.0027</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1.409</v>
+        <v>1.3685</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.3994</v>
+        <v>2.3622</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>3.7711</v>
+        <v>3.7507</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1968.3628</v>
+        <v>1849.7236</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>3317.9326</v>
+        <v>3199.2412</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>5184.5019</v>
+        <v>5109.2048</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>-1220.2159</v>
+        <v>-1221.6041</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>771.1002</v>
+        <v>770.5626999999999</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>3532.0586</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>-61.0108</v>
+        <v>-61.0802</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>38.555</v>
+        <v>38.5281</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>176.6029</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>-61.0108</v>
+        <v>-61.0802</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2.7186</v>
+        <v>2.6937</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>70.3633</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>47.6309</v>
+        <v>47.2074</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>80.3272</v>
+        <v>80.03870000000001</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>123.9601</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-108.6417</v>
+        <v>-108.2876</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>-77.6086</v>
+        <v>-77.345</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>-53.5968</v>
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>35.8364</v>
+        <v>35.8344</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>106.2396</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>2912.6803</v>
+        <v>2912.125</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>3583.6384</v>
+        <v>3583.4393</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>4249.5851</v>
@@ -2537,13 +2537,13 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>0.121</v>
+        <v>0.0847</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.4368</v>
+        <v>0.3826</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.0002</v>
+        <v>0.9288</v>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
@@ -2564,13 +2564,13 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>2148.8441</v>
+        <v>1504.4299</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>7755.5209</v>
+        <v>6794.5335</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17760.7156</v>
+        <v>16492.2252</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>626.5672</v>
+        <v>581.982</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1056.98</v>
+        <v>1006.191</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1652.4575</v>
+        <v>1622.8501</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>626.5672</v>
+        <v>581.982</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1056.98</v>
+        <v>1006.191</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1652.4575</v>
+        <v>1622.8501</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>3916.0449</v>
+        <v>3637.3873</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>6606.1248</v>
+        <v>6288.6938</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>10327.8594</v>
+        <v>10142.813</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3916.0449</v>
+        <v>3637.3873</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>6606.1248</v>
+        <v>6288.6938</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>10327.8594</v>
+        <v>10142.813</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>3280.6046</v>
+        <v>3082.8727</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>5529.8876</v>
+        <v>5332.0686</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>8640.836499999999</v>
+        <v>8515.3413</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2502.2456</v>
+        <v>2478.3219</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4281.2096</v>
+        <v>4264.9171</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>6746.846</v>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>227.1858</v>
+        <v>170.4775</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>374.2447</v>
+        <v>315.0183</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>578.5372</v>
+        <v>537.592</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>503.42</v>
+        <v>386.32</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>826.6799999999999</v>
+        <v>704.38</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1267.7</v>
+        <v>1183.15</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>635.4403</v>
+        <v>554.5146</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1076.2372</v>
+        <v>956.6251999999999</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1687.0229</v>
+        <v>1627.4718</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>443.6879</v>
+        <v>412.116</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>748.4739</v>
+        <v>712.509</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1170.1465</v>
+        <v>1149.1807</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>3916.0449</v>
+        <v>3637.3873</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>6606.1248</v>
+        <v>6288.6938</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>10327.8594</v>
+        <v>10142.813</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>2349.6269</v>
+        <v>2182.4324</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3963.6749</v>
+        <v>3773.2163</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>6196.7156</v>
+        <v>6085.6878</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>3916.0449</v>
+        <v>3637.3873</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>6606.1248</v>
+        <v>6288.6938</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>10327.8594</v>
+        <v>10142.813</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>3280.6046</v>
+        <v>3082.8727</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>5529.8876</v>
+        <v>5332.0686</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>8640.836499999999</v>
+        <v>8515.3413</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2502.2456</v>
+        <v>2478.3219</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4281.2096</v>
+        <v>4264.9171</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>6746.846</v>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>227.1858</v>
+        <v>170.4775</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>374.2447</v>
+        <v>315.0183</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>578.5372</v>
+        <v>537.592</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>503.42</v>
+        <v>386.32</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>826.6799999999999</v>
+        <v>704.38</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1267.7</v>
+        <v>1183.15</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>635.4403</v>
+        <v>554.5146</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1076.2372</v>
+        <v>956.6251999999999</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>1687.0229</v>
+        <v>1627.4718</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>1.1356</v>
+        <v>1.0078</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.3454</v>
+        <v>1.2284</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1.6874</v>
+        <v>1.5756</v>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
@@ -3393,13 +3393,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1.1356</v>
+        <v>1.0078</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.3454</v>
+        <v>1.2284</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.6874</v>
+        <v>1.5756</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>577.2785</v>
+        <v>481.3783</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1154.388</v>
+        <v>1014.3982</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>2264.2302</v>
+        <v>2083.8678</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>508.3284</v>
+        <v>477.6693</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>858.0124</v>
+        <v>825.7933</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1341.8572</v>
+        <v>1322.5847</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>327.5122</v>
+        <v>265.9222</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>734.5295</v>
+        <v>641.742</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1609.2159</v>
+        <v>1454.8992</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>577.2785</v>
+        <v>481.3783</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1154.388</v>
+        <v>1014.3982</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>2264.2302</v>
+        <v>2083.8678</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>249.7663</v>
+        <v>215.4561</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>419.8586</v>
+        <v>372.6563</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>655.0144</v>
+        <v>628.9687</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>213.8283</v>
+        <v>187.3248</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>362.3699</v>
+        <v>323.3209</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>568.1244</v>
+        <v>547.7153</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>539.0700000000001</v>
+        <v>421.97</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>862.33</v>
+        <v>740.03</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1303.35</v>
+        <v>1218.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>503.42</v>
+        <v>386.32</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>826.6799999999999</v>
+        <v>704.38</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>1267.7</v>
+        <v>1183.15</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3738,13 +3738,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>7.5743</v>
+        <v>7.6072</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7.4221</v>
+        <v>7.4302</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>7.2579</v>
+        <v>7.2856</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>4372.4664</v>
+        <v>3661.9392</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>8568.011</v>
+        <v>7537.1822</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>16433.5946</v>
+        <v>15182.1981</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>495.4004</v>
+        <v>414.8977</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>970.7557</v>
+        <v>853.9627</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>1861.9263</v>
+        <v>1720.143</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>577.2785</v>
+        <v>481.3783</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1154.388</v>
+        <v>1014.3982</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>2264.2302</v>
+        <v>2083.8678</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>2.3765</v>
+        <v>2.3662</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2.4252</v>
+        <v>2.4225</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>2.4801</v>
+        <v>2.4706</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3959,13 +3959,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>7.5743</v>
+        <v>7.6072</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>7.4221</v>
+        <v>7.4302</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>7.2579</v>
+        <v>7.2856</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>3369.06</v>
+        <v>2726.034</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>6984.4207</v>
+        <v>6023.9709</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>14228.6569</v>
+        <v>12960.1665</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>104.3645</v>
+        <v>-277.8231</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1388.0768</v>
+        <v>735.4112</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>5218.8745</v>
+        <v>4188.8078</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>4372.4664</v>
+        <v>3661.9392</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>8568.011</v>
+        <v>7537.1822</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>16433.5946</v>
+        <v>15182.1981</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>265.316</v>
+        <v>263.427</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>451.9186</v>
+        <v>454.4144</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>711.1748</v>
+        <v>711.7343</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>198.6688</v>
+        <v>197.2543</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>338.3969</v>
+        <v>340.2657</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>532.5281</v>
+        <v>532.9471</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>4533.418</v>
+        <v>4203.1893</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>7631.8528</v>
+        <v>7256.1854</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>11925.8948</v>
+        <v>11705.1246</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4203,13 +4203,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3394.6258</v>
+        <v>3147.3503</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>5714.7354</v>
+        <v>5433.4355</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>8930.116400000001</v>
+        <v>8764.8035</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>1067.7679</v>
+        <v>830.2569999999999</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2280.7988</v>
+        <v>1916.9422</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>4784.107</v>
+        <v>4313.8911</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>4372.4664</v>
+        <v>3661.9392</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>8568.011</v>
+        <v>7537.1822</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>16433.5946</v>
+        <v>15182.1981</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>265.316</v>
+        <v>263.427</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>451.9186</v>
+        <v>454.4144</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>711.1748</v>
+        <v>711.7343</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>198.6688</v>
+        <v>197.2543</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>338.3969</v>
+        <v>340.2657</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>532.5281</v>
+        <v>532.9471</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>1968.3628</v>
+        <v>1849.7236</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3317.9326</v>
+        <v>3199.2412</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>5184.5019</v>
+        <v>5109.2048</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>104.8571</v>
+        <v>-277.4105</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1389.0421</v>
+        <v>736.2604</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>5220.726</v>
+        <v>4190.5183</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>4372.9591</v>
+        <v>3662.3518</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>8568.9764</v>
+        <v>7538.0314</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>16435.4461</v>
+        <v>15183.9086</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>265.316</v>
+        <v>263.427</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>451.9186</v>
+        <v>454.4144</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>711.1748</v>
+        <v>711.7343</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>198.6688</v>
+        <v>197.2543</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>338.3969</v>
+        <v>340.2657</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>532.5281</v>
+        <v>532.9471</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>4533.418</v>
+        <v>4203.1893</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>7631.8528</v>
+        <v>7256.1854</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>11925.8948</v>
+        <v>11705.1246</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>3394.6258</v>
+        <v>3147.3503</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>5714.7354</v>
+        <v>5433.4355</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>8930.116400000001</v>
+        <v>8764.8035</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4714,13 +4714,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>1067.9649</v>
+        <v>830.4221</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2281.1849</v>
+        <v>1917.2819</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>4784.8476</v>
+        <v>4314.5753</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>4372.9591</v>
+        <v>3662.3518</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>8568.9764</v>
+        <v>7538.0314</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>16435.4461</v>
+        <v>15183.9086</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>265.316</v>
+        <v>263.427</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>451.9186</v>
+        <v>454.4144</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>711.1748</v>
+        <v>711.7343</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>198.6688</v>
+        <v>197.2543</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>338.3969</v>
+        <v>340.2657</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>532.5281</v>
+        <v>532.9471</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1968.3628</v>
+        <v>1849.7236</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3317.9326</v>
+        <v>3199.2412</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>5184.5019</v>
+        <v>5109.2048</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>842.5229</v>
+        <v>291.4519</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>3255.1034</v>
+        <v>2334.2355</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>9704.016299999999</v>
+        <v>8183.5555</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1071.0359</v>
+        <v>803.7637</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2533.3464</v>
+        <v>2117.9684</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>5803.0905</v>
+        <v>5164.8408</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>3369.06</v>
+        <v>2726.034</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>6984.4207</v>
+        <v>6023.9709</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>14228.6569</v>
+        <v>12960.1665</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>577.2785</v>
+        <v>481.3783</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1154.388</v>
+        <v>1014.3982</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>2264.2302</v>
+        <v>2083.8678</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5086,13 +5086,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>1968.3628</v>
+        <v>1849.7236</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>3317.9326</v>
+        <v>3199.2412</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>5184.5019</v>
+        <v>5109.2048</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>2301.0951</v>
+        <v>1895.6119</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>4703.2357</v>
+        <v>4106.689</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>9443.809300000001</v>
+        <v>8645.591200000001</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>3369.06</v>
+        <v>2726.034</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>6984.4207</v>
+        <v>6023.9709</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>14228.6569</v>
+        <v>12960.1665</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>577.2785</v>
+        <v>481.3783</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1154.388</v>
+        <v>1014.3982</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>2264.2302</v>
+        <v>2083.8678</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -5276,13 +5276,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>1968.3628</v>
+        <v>1849.7236</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>3317.9326</v>
+        <v>3199.2412</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>5184.5019</v>
+        <v>5109.2048</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5338,13 +5338,13 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>1067.9649</v>
+        <v>830.4221</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2281.1849</v>
+        <v>1917.2819</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>4784.8476</v>
+        <v>4314.5753</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>4372.9591</v>
+        <v>3662.3518</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>8568.9764</v>
+        <v>7538.0314</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>16435.4461</v>
+        <v>15183.9086</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>265.316</v>
+        <v>263.427</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>451.9186</v>
+        <v>454.4144</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>711.1748</v>
+        <v>711.7343</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>198.6688</v>
+        <v>197.2543</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>338.3969</v>
+        <v>340.2657</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>532.5281</v>
+        <v>532.9471</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>1968.3628</v>
+        <v>1849.7236</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>3317.9326</v>
+        <v>3199.2412</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>5184.5019</v>
+        <v>5109.2048</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>-0.1623</v>
+        <v>-0.1524</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-0.1629</v>
+        <v>-0.1521</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>-0.1633</v>
+        <v>-0.1605</v>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.4917</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-0.4796</v>
+        <v>-0.457</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>-0.4485</v>
+        <v>-0.4475</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>

--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电决策树_v4.3.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1504.4299</v>
+        <v>1494.1634</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6794.5335</v>
+        <v>6822.7632</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16492.2252</v>
+        <v>16496.6543</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1504.4299</v>
+        <v>1494.1634</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6794.5335</v>
+        <v>6822.7632</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>16492.2252</v>
+        <v>16496.6543</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2726.034</v>
+        <v>2716.494</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6023.9709</v>
+        <v>6051.5647</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12960.1665</v>
+        <v>12964.5956</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6815.0849</v>
+        <v>6791.235</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>15059.9272</v>
+        <v>15128.9118</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32400.4163</v>
+        <v>32411.489</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8664.808499999999</v>
+        <v>8622.359</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18259.1684</v>
+        <v>18325.3334</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37509.621</v>
+        <v>37490.5482</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>481.3783</v>
+        <v>479.0199</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1014.3982</v>
+        <v>1018.0741</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2083.8678</v>
+        <v>2082.8082</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>581.9636</v>
+        <v>578.2183</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1191.6157</v>
+        <v>1194.4535</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2376.6353</v>
+        <v>2372.6159</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>195.5513</v>
+        <v>194.5952</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>424.8874</v>
+        <v>427.2055</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>861.1078</v>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1527.7444</v>
+        <v>1520.2751</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2764.3941</v>
+        <v>2779.4763</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4664.7224</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2529800</v>
+        <v>2524600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4283800</v>
+        <v>4294300</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>6639900</v>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>215.6783</v>
+        <v>215.0659</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>230.4691</v>
+        <v>231.1599</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>250.9032</v>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>340.353</v>
+        <v>339.0422</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>684.6077</v>
+        <v>687.0449</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1378.1864</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>432.9419</v>
+        <v>430.8801</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>745.292</v>
+        <v>748.3892</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1178.2443</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>432.9419</v>
+        <v>430.8801</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>745.292</v>
+        <v>748.3892</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1178.2443</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6.1769</v>
+        <v>6.1818</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7.3761</v>
+        <v>7.372</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>9.757899999999999</v>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>39.8583</v>
+        <v>38.5421</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>71.4123</v>
+        <v>69.70489999999999</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>120.0013</v>
+        <v>116.4227</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>30.9459</v>
+        <v>29.924</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>55.4443</v>
+        <v>54.1187</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>93.1687</v>
+        <v>90.3903</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6.201</v>
+        <v>6.0388</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10.7084</v>
+        <v>10.4981</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>17.3399</v>
+        <v>16.899</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.4956</v>
+        <v>0.4786</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.8885</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.4976</v>
+        <v>1.4513</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3.3043</v>
+        <v>3.1907</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5.9233</v>
+        <v>5.776</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>9.984</v>
+        <v>9.6753</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5.7053</v>
+        <v>5.5602</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>9.819900000000001</v>
+        <v>9.6317</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>15.8423</v>
+        <v>15.4477</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>100.5853</v>
+        <v>99.19840000000001</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>177.2175</v>
+        <v>176.3794</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>292.7675</v>
+        <v>289.8077</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>49.8178</v>
+        <v>49.5742</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>90.1433</v>
+        <v>90.63509999999999</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>152.1105</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1693.8036</v>
+        <v>1685.5224</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3064.8717</v>
+        <v>3081.5933</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>5171.7575</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1527.7444</v>
+        <v>1520.2751</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2764.3941</v>
+        <v>2779.4763</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>4664.7224</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1527.7444</v>
+        <v>1520.2751</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2764.3941</v>
+        <v>2779.4763</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>4664.7224</v>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>17.2185</v>
+        <v>16.845</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>29.121</v>
+        <v>28.6365</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>46.0455</v>
+        <v>45.03</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>11479</v>
+        <v>11230</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>19414</v>
+        <v>19091</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>30697</v>
+        <v>30020</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>18.5999</v>
+        <v>17.9306</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>33.5836</v>
+        <v>32.7154</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>57.0273</v>
+        <v>55.2075</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>6413</v>
+        <v>6164</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>11725</v>
+        <v>11402</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>20162</v>
+        <v>19485</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>6.1068</v>
+        <v>6.0518</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10.5587</v>
+        <v>10.5554</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>16.8309</v>
+        <v>16.7473</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>5.4739</v>
+        <v>5.4375</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>9.448700000000001</v>
+        <v>9.4696</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>15.0027</v>
+        <v>14.9699</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1.3685</v>
+        <v>1.3594</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.3622</v>
+        <v>2.3674</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>3.7507</v>
+        <v>3.7425</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1849.7236</v>
+        <v>1831.124</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>3199.2412</v>
+        <v>3196.4217</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>5109.2048</v>
+        <v>5079.0592</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>-1221.6041</v>
+        <v>-1222.3306</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>770.5626999999999</v>
+        <v>771.1985</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>3532.0586</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>-61.0802</v>
+        <v>-61.1165</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>38.5281</v>
+        <v>38.5599</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>176.6029</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>-61.0802</v>
+        <v>-61.1165</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2.6937</v>
+        <v>2.7232</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>70.3633</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>47.2074</v>
+        <v>46.9858</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>80.03870000000001</v>
+        <v>80.38</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>123.9601</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>-108.2876</v>
+        <v>-108.1023</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>-77.345</v>
+        <v>-77.6568</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>-53.5968</v>
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>35.8344</v>
+        <v>35.8367</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>106.2396</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>2912.125</v>
+        <v>2911.8344</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>3583.4393</v>
+        <v>3583.6748</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>4249.5851</v>
@@ -2537,13 +2537,13 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>0.0847</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.3826</v>
+        <v>0.3842</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.9288</v>
+        <v>0.929</v>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
@@ -2564,13 +2564,13 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>1504.4299</v>
+        <v>1494.1634</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>6794.5335</v>
+        <v>6822.7632</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>16492.2252</v>
+        <v>16496.6543</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>581.982</v>
+        <v>576.4053</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1006.191</v>
+        <v>1005.8232</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1622.8501</v>
+        <v>1614.6634</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>581.982</v>
+        <v>576.4053</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1006.191</v>
+        <v>1005.8232</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1622.8501</v>
+        <v>1614.6634</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>3637.3873</v>
+        <v>3602.5333</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>6288.6938</v>
+        <v>6286.3947</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>10142.813</v>
+        <v>10091.646</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3637.3873</v>
+        <v>3602.5333</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>6288.6938</v>
+        <v>6286.3947</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>10142.813</v>
+        <v>10091.646</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>3082.8727</v>
+        <v>3051.8734</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>5332.0686</v>
+        <v>5327.3694</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>8515.3413</v>
+        <v>8465.098599999999</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2478.3219</v>
+        <v>2465.8018</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4264.9171</v>
+        <v>4284.1889</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>6746.846</v>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>170.4775</v>
+        <v>164.4483</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>315.0183</v>
+        <v>307.1973</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>537.592</v>
+        <v>521.1994</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>386.32</v>
+        <v>373.87</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>704.38</v>
+        <v>688.23</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1183.15</v>
+        <v>1149.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>554.5146</v>
+        <v>550.66</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>956.6251999999999</v>
+        <v>959.0253</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1627.4718</v>
+        <v>1626.5473</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>412.116</v>
+        <v>408.167</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>712.509</v>
+        <v>712.2485</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1149.1807</v>
+        <v>1143.3835</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>3637.3873</v>
+        <v>3602.5333</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>6288.6938</v>
+        <v>6286.3947</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>10142.813</v>
+        <v>10091.646</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>2182.4324</v>
+        <v>2161.52</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3773.2163</v>
+        <v>3771.8368</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>6085.6878</v>
+        <v>6054.9876</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>3637.3873</v>
+        <v>3602.5333</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>6288.6938</v>
+        <v>6286.3947</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>10142.813</v>
+        <v>10091.646</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>3082.8727</v>
+        <v>3051.8734</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>5332.0686</v>
+        <v>5327.3694</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>8515.3413</v>
+        <v>8465.098599999999</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2478.3219</v>
+        <v>2465.8018</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4264.9171</v>
+        <v>4284.1889</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>6746.846</v>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>170.4775</v>
+        <v>164.4483</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>315.0183</v>
+        <v>307.1973</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>537.592</v>
+        <v>521.1994</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>386.32</v>
+        <v>373.87</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>704.38</v>
+        <v>688.23</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1183.15</v>
+        <v>1149.3</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>554.5146</v>
+        <v>550.66</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>956.6251999999999</v>
+        <v>959.0253</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>1627.4718</v>
+        <v>1626.5473</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>1.0078</v>
+        <v>1.0125</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.2284</v>
+        <v>1.2332</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1.5756</v>
+        <v>1.583</v>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
@@ -3393,13 +3393,13 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1.0078</v>
+        <v>1.0125</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.2284</v>
+        <v>1.2332</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1.5756</v>
+        <v>1.583</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>481.3783</v>
+        <v>479.0199</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1014.3982</v>
+        <v>1018.0741</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>2083.8678</v>
+        <v>2082.8082</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>477.6693</v>
+        <v>473.1165</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>825.7933</v>
+        <v>825.5368</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1322.5847</v>
+        <v>1315.7175</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>265.9222</v>
+        <v>265.7013</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>641.742</v>
+        <v>645.6903</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1454.8992</v>
+        <v>1456.4269</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>481.3783</v>
+        <v>479.0199</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1014.3982</v>
+        <v>1018.0741</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>2083.8678</v>
+        <v>2082.8082</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>215.4561</v>
+        <v>213.3187</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>372.6563</v>
+        <v>372.3838</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>628.9687</v>
+        <v>626.3814</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>187.3248</v>
+        <v>186.0174</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>323.3209</v>
+        <v>324.1251</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>547.7153</v>
+        <v>547.3847</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>421.97</v>
+        <v>409.52</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>740.03</v>
+        <v>723.88</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1218.8</v>
+        <v>1184.95</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>386.32</v>
+        <v>373.87</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>704.38</v>
+        <v>688.23</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>1183.15</v>
+        <v>1149.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3738,13 +3738,13 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>7.6072</v>
+        <v>7.6022</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7.4302</v>
+        <v>7.4267</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>7.2856</v>
+        <v>7.2832</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>3661.9392</v>
+        <v>3641.6119</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>7537.1822</v>
+        <v>7560.9135</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>15182.1981</v>
+        <v>15169.475</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>414.8977</v>
+        <v>412.5946</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>853.9627</v>
+        <v>856.6515000000001</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>1720.143</v>
+        <v>1718.7015</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>481.3783</v>
+        <v>479.0199</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1014.3982</v>
+        <v>1018.0741</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>2083.8678</v>
+        <v>2082.8082</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>2.3662</v>
+        <v>2.3677</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2.4225</v>
+        <v>2.4237</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>2.4706</v>
+        <v>2.4714</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3959,13 +3959,13 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>7.6072</v>
+        <v>7.6022</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>7.4302</v>
+        <v>7.4267</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>7.2856</v>
+        <v>7.2832</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2726.034</v>
+        <v>2716.494</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>6023.9709</v>
+        <v>6051.5647</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>12960.1665</v>
+        <v>12964.5956</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>-277.8231</v>
+        <v>-259.0562</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>735.4112</v>
+        <v>764.2910000000001</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>4188.8078</v>
+        <v>4235.5089</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>3661.9392</v>
+        <v>3641.6119</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7537.1822</v>
+        <v>7560.9135</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>15182.1981</v>
+        <v>15169.475</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>263.427</v>
+        <v>261.5698</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>454.4144</v>
+        <v>455.5162</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>711.7343</v>
+        <v>709.8194999999999</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>197.2543</v>
+        <v>195.8636</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>340.2657</v>
+        <v>341.0908</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>532.9471</v>
+        <v>531.5132</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>4203.1893</v>
+        <v>4162.2379</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>7256.1854</v>
+        <v>7252.1388</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>11705.1246</v>
+        <v>11643.7856</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4203,13 +4203,13 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3147.3503</v>
+        <v>3116.6859</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>5433.4355</v>
+        <v>5430.4054</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>8764.8035</v>
+        <v>8718.8729</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>830.2569999999999</v>
+        <v>828.8231</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1916.9422</v>
+        <v>1928.0032</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>4313.8911</v>
+        <v>4320.0941</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>3661.9392</v>
+        <v>3641.6119</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>7537.1822</v>
+        <v>7560.9135</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>15182.1981</v>
+        <v>15169.475</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>263.427</v>
+        <v>261.5698</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>454.4144</v>
+        <v>455.5162</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>711.7343</v>
+        <v>709.8194999999999</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>197.2543</v>
+        <v>195.8636</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>340.2657</v>
+        <v>341.0908</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>532.9471</v>
+        <v>531.5132</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>1849.7236</v>
+        <v>1831.124</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3199.2412</v>
+        <v>3196.4217</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>5109.2048</v>
+        <v>5079.0592</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>-277.4105</v>
+        <v>-258.6459</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>736.2604</v>
+        <v>765.1428</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>4190.5183</v>
+        <v>4237.218</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>3662.3518</v>
+        <v>3642.0222</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>7538.0314</v>
+        <v>7561.7654</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>15183.9086</v>
+        <v>15171.1841</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>263.427</v>
+        <v>261.5698</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>454.4144</v>
+        <v>455.5162</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>711.7343</v>
+        <v>709.8194999999999</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>197.2543</v>
+        <v>195.8636</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>340.2657</v>
+        <v>341.0908</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>532.9471</v>
+        <v>531.5132</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>4203.1893</v>
+        <v>4162.2379</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>7256.1854</v>
+        <v>7252.1388</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>11705.1246</v>
+        <v>11643.7856</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>3147.3503</v>
+        <v>3116.6859</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>5433.4355</v>
+        <v>5430.4054</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>8764.8035</v>
+        <v>8718.8729</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4714,13 +4714,13 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>830.4221</v>
+        <v>828.9872</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1917.2819</v>
+        <v>1928.344</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>4314.5753</v>
+        <v>4320.7778</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>3662.3518</v>
+        <v>3642.0222</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>7538.0314</v>
+        <v>7561.7654</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>15183.9086</v>
+        <v>15171.1841</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>263.427</v>
+        <v>261.5698</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>454.4144</v>
+        <v>455.5162</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>711.7343</v>
+        <v>709.8194999999999</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>197.2543</v>
+        <v>195.8636</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>340.2657</v>
+        <v>341.0908</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>532.9471</v>
+        <v>531.5132</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1849.7236</v>
+        <v>1831.124</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3199.2412</v>
+        <v>3196.4217</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>5109.2048</v>
+        <v>5079.0592</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>291.4519</v>
+        <v>313.6405</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2334.2355</v>
+        <v>2378.6376</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>8183.5555</v>
+        <v>8243.2431</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>803.7637</v>
+        <v>805.4906</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2117.9684</v>
+        <v>2134.1752</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>5164.8408</v>
+        <v>5176.6798</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>2726.034</v>
+        <v>2716.494</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>6023.9709</v>
+        <v>6051.5647</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>12960.1665</v>
+        <v>12964.5956</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>481.3783</v>
+        <v>479.0199</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1014.3982</v>
+        <v>1018.0741</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>2083.8678</v>
+        <v>2082.8082</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5086,13 +5086,13 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>1849.7236</v>
+        <v>1831.124</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>3199.2412</v>
+        <v>3196.4217</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>5109.2048</v>
+        <v>5079.0592</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>1895.6119</v>
+        <v>1887.5068</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>4106.689</v>
+        <v>4123.2207</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>8645.591200000001</v>
+        <v>8643.8179</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>2726.034</v>
+        <v>2716.494</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>6023.9709</v>
+        <v>6051.5647</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>12960.1665</v>
+        <v>12964.5956</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>481.3783</v>
+        <v>479.0199</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1014.3982</v>
+        <v>1018.0741</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>2083.8678</v>
+        <v>2082.8082</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -5276,13 +5276,13 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>1849.7236</v>
+        <v>1831.124</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>3199.2412</v>
+        <v>3196.4217</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>5109.2048</v>
+        <v>5079.0592</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5338,13 +5338,13 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>830.4221</v>
+        <v>828.9872</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1917.2819</v>
+        <v>1928.344</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>4314.5753</v>
+        <v>4320.7778</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>3662.3518</v>
+        <v>3642.0222</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>7538.0314</v>
+        <v>7561.7654</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>15183.9086</v>
+        <v>15171.1841</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>263.427</v>
+        <v>261.5698</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>454.4144</v>
+        <v>455.5162</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>711.7343</v>
+        <v>709.8194999999999</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>197.2543</v>
+        <v>195.8636</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>340.2657</v>
+        <v>341.0908</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>532.9471</v>
+        <v>531.5132</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>1849.7236</v>
+        <v>1831.124</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>3199.2412</v>
+        <v>3196.4217</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>5109.2048</v>
+        <v>5079.0592</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>-0.1524</v>
+        <v>-0.1529</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-0.1521</v>
+        <v>-0.1526</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>-0.1605</v>
+        <v>-0.1612</v>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>-0.4917</v>
+        <v>-0.4907</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-0.457</v>
+        <v>-0.4564</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>-0.4475</v>
